--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="700">
   <si>
     <t>IDSocio</t>
   </si>
@@ -103,6 +103,9 @@
     <t>Rutina</t>
   </si>
   <si>
+    <t>260403</t>
+  </si>
+  <si>
     <t>320033</t>
   </si>
   <si>
@@ -112,34 +115,55 @@
     <t>290316</t>
   </si>
   <si>
+    <t>123833</t>
+  </si>
+  <si>
+    <t>238288</t>
+  </si>
+  <si>
     <t>158386</t>
   </si>
   <si>
-    <t>238288</t>
-  </si>
-  <si>
     <t>299954</t>
   </si>
   <si>
+    <t>340255</t>
+  </si>
+  <si>
+    <t>340713</t>
+  </si>
+  <si>
+    <t>340641</t>
+  </si>
+  <si>
+    <t>340697</t>
+  </si>
+  <si>
     <t>337242</t>
   </si>
   <si>
-    <t>340255</t>
-  </si>
-  <si>
-    <t>340641</t>
+    <t>340789</t>
+  </si>
+  <si>
+    <t>342294</t>
+  </si>
+  <si>
+    <t>342087</t>
   </si>
   <si>
     <t>340481</t>
   </si>
   <si>
-    <t>340713</t>
-  </si>
-  <si>
-    <t>340789</t>
-  </si>
-  <si>
-    <t>340697</t>
+    <t>341132</t>
+  </si>
+  <si>
+    <t>342457</t>
+  </si>
+  <si>
+    <t>342822</t>
+  </si>
+  <si>
+    <t>342482</t>
   </si>
   <si>
     <t>340791</t>
@@ -148,37 +172,52 @@
     <t>340808</t>
   </si>
   <si>
-    <t>341132</t>
+    <t>342478</t>
+  </si>
+  <si>
+    <t>342580</t>
   </si>
   <si>
     <t>341819</t>
   </si>
   <si>
+    <t>342583</t>
+  </si>
+  <si>
     <t>341834</t>
   </si>
   <si>
+    <t>343384</t>
+  </si>
+  <si>
     <t>342336</t>
   </si>
   <si>
+    <t>343139</t>
+  </si>
+  <si>
+    <t>342783</t>
+  </si>
+  <si>
+    <t>342997</t>
+  </si>
+  <si>
+    <t>342323</t>
+  </si>
+  <si>
     <t>342474</t>
   </si>
   <si>
-    <t>342478</t>
-  </si>
-  <si>
-    <t>342580</t>
-  </si>
-  <si>
-    <t>342294</t>
-  </si>
-  <si>
-    <t>342457</t>
-  </si>
-  <si>
-    <t>342583</t>
-  </si>
-  <si>
-    <t>342323</t>
+    <t>344132</t>
+  </si>
+  <si>
+    <t>344345</t>
+  </si>
+  <si>
+    <t>343135</t>
+  </si>
+  <si>
+    <t>343713</t>
   </si>
   <si>
     <t>342776</t>
@@ -187,37 +226,25 @@
     <t>343025</t>
   </si>
   <si>
-    <t>342783</t>
-  </si>
-  <si>
-    <t>342482</t>
+    <t>342794</t>
+  </si>
+  <si>
+    <t>343140</t>
   </si>
   <si>
     <t>343557</t>
   </si>
   <si>
-    <t>342822</t>
-  </si>
-  <si>
-    <t>343384</t>
-  </si>
-  <si>
-    <t>342997</t>
-  </si>
-  <si>
-    <t>343135</t>
-  </si>
-  <si>
-    <t>342794</t>
-  </si>
-  <si>
-    <t>343140</t>
-  </si>
-  <si>
-    <t>343713</t>
-  </si>
-  <si>
-    <t>343139</t>
+    <t>344134</t>
+  </si>
+  <si>
+    <t>344409</t>
+  </si>
+  <si>
+    <t>344391</t>
+  </si>
+  <si>
+    <t>344630</t>
   </si>
   <si>
     <t>343612</t>
@@ -226,6 +253,21 @@
     <t>343714</t>
   </si>
   <si>
+    <t>344451</t>
+  </si>
+  <si>
+    <t>344464</t>
+  </si>
+  <si>
+    <t>344453</t>
+  </si>
+  <si>
+    <t>344505</t>
+  </si>
+  <si>
+    <t>57907</t>
+  </si>
+  <si>
     <t>17530</t>
   </si>
   <si>
@@ -235,34 +277,55 @@
     <t>87814</t>
   </si>
   <si>
+    <t>21519</t>
+  </si>
+  <si>
+    <t>35793</t>
+  </si>
+  <si>
     <t>55922</t>
   </si>
   <si>
-    <t>35793</t>
-  </si>
-  <si>
     <t>97452</t>
   </si>
   <si>
+    <t>18073</t>
+  </si>
+  <si>
+    <t>18531</t>
+  </si>
+  <si>
+    <t>18459</t>
+  </si>
+  <si>
+    <t>18515</t>
+  </si>
+  <si>
     <t>22968</t>
   </si>
   <si>
-    <t>18073</t>
-  </si>
-  <si>
-    <t>18459</t>
+    <t>18607</t>
+  </si>
+  <si>
+    <t>20112</t>
+  </si>
+  <si>
+    <t>19905</t>
   </si>
   <si>
     <t>18299</t>
   </si>
   <si>
-    <t>18531</t>
-  </si>
-  <si>
-    <t>18607</t>
-  </si>
-  <si>
-    <t>18515</t>
+    <t>18950</t>
+  </si>
+  <si>
+    <t>20274</t>
+  </si>
+  <si>
+    <t>20639</t>
+  </si>
+  <si>
+    <t>20299</t>
   </si>
   <si>
     <t>18609</t>
@@ -271,37 +334,52 @@
     <t>18626</t>
   </si>
   <si>
-    <t>18950</t>
+    <t>20295</t>
+  </si>
+  <si>
+    <t>20397</t>
   </si>
   <si>
     <t>19637</t>
   </si>
   <si>
+    <t>20400</t>
+  </si>
+  <si>
     <t>19652</t>
   </si>
   <si>
+    <t>21201</t>
+  </si>
+  <si>
     <t>20154</t>
   </si>
   <si>
+    <t>20956</t>
+  </si>
+  <si>
+    <t>20600</t>
+  </si>
+  <si>
+    <t>20814</t>
+  </si>
+  <si>
+    <t>20141</t>
+  </si>
+  <si>
     <t>20291</t>
   </si>
   <si>
-    <t>20295</t>
-  </si>
-  <si>
-    <t>20397</t>
-  </si>
-  <si>
-    <t>20112</t>
-  </si>
-  <si>
-    <t>20274</t>
-  </si>
-  <si>
-    <t>20400</t>
-  </si>
-  <si>
-    <t>20141</t>
+    <t>21949</t>
+  </si>
+  <si>
+    <t>22162</t>
+  </si>
+  <si>
+    <t>20952</t>
+  </si>
+  <si>
+    <t>21530</t>
   </si>
   <si>
     <t>20593</t>
@@ -310,37 +388,25 @@
     <t>20842</t>
   </si>
   <si>
-    <t>20600</t>
-  </si>
-  <si>
-    <t>20299</t>
+    <t>20611</t>
+  </si>
+  <si>
+    <t>20957</t>
   </si>
   <si>
     <t>21374</t>
   </si>
   <si>
-    <t>20639</t>
-  </si>
-  <si>
-    <t>21201</t>
-  </si>
-  <si>
-    <t>20814</t>
-  </si>
-  <si>
-    <t>20952</t>
-  </si>
-  <si>
-    <t>20611</t>
-  </si>
-  <si>
-    <t>20957</t>
-  </si>
-  <si>
-    <t>21530</t>
-  </si>
-  <si>
-    <t>20956</t>
+    <t>21951</t>
+  </si>
+  <si>
+    <t>22226</t>
+  </si>
+  <si>
+    <t>22208</t>
+  </si>
+  <si>
+    <t>22447</t>
   </si>
   <si>
     <t>21429</t>
@@ -349,9 +415,24 @@
     <t>21531</t>
   </si>
   <si>
+    <t>22268</t>
+  </si>
+  <si>
+    <t>22281</t>
+  </si>
+  <si>
+    <t>22270</t>
+  </si>
+  <si>
+    <t>22322</t>
+  </si>
+  <si>
     <t>INDEPENDENCIA</t>
   </si>
   <si>
+    <t>SAMUEL ESTEBAN</t>
+  </si>
+  <si>
     <t>OMAR</t>
   </si>
   <si>
@@ -361,34 +442,55 @@
     <t>VANESSA</t>
   </si>
   <si>
+    <t>AKYEL</t>
+  </si>
+  <si>
+    <t>SILVIA PAOLA</t>
+  </si>
+  <si>
     <t xml:space="preserve">JESUS </t>
   </si>
   <si>
-    <t>SILVIA PAOLA</t>
-  </si>
-  <si>
     <t>EUNICE</t>
   </si>
   <si>
+    <t>STEPHANY</t>
+  </si>
+  <si>
+    <t>LESLIE</t>
+  </si>
+  <si>
+    <t>LUCIA YADIRA</t>
+  </si>
+  <si>
+    <t>CRISTIAN ISMAEL</t>
+  </si>
+  <si>
     <t xml:space="preserve">MARTHA ELENA </t>
   </si>
   <si>
-    <t>STEPHANY</t>
-  </si>
-  <si>
-    <t>LUCIA YADIRA</t>
+    <t xml:space="preserve">DANIELA </t>
+  </si>
+  <si>
+    <t>CARLOS ANTONIO</t>
+  </si>
+  <si>
+    <t>KARLA VERÓNICA</t>
   </si>
   <si>
     <t>HILDA</t>
   </si>
   <si>
-    <t>LESLIE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DANIELA </t>
-  </si>
-  <si>
-    <t>CRISTIAN ISMAEL</t>
+    <t xml:space="preserve">NAHOMI ESTEFANIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE </t>
+  </si>
+  <si>
+    <t>LEOPOLDO</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
   </si>
   <si>
     <t>HECTOR MANUEL</t>
@@ -397,34 +499,49 @@
     <t>RENE</t>
   </si>
   <si>
-    <t xml:space="preserve">NAHOMI ESTEFANIA </t>
+    <t>FERNANDO</t>
   </si>
   <si>
     <t>KARYME</t>
   </si>
   <si>
+    <t>SHESLY DENNIS</t>
+  </si>
+  <si>
     <t>DARIANA</t>
   </si>
   <si>
+    <t>BRISA</t>
+  </si>
+  <si>
     <t>MARCO ALEJANDRO</t>
   </si>
   <si>
+    <t>NICZA ARELI</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
     <t>MELISSA</t>
   </si>
   <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>CARLOS ANTONIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOSE </t>
-  </si>
-  <si>
-    <t>SHESLY DENNIS</t>
-  </si>
-  <si>
-    <t>MARCO</t>
+    <t xml:space="preserve">ANGELES </t>
+  </si>
+  <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>JESSICA ALEJANDRA</t>
   </si>
   <si>
     <t>JUAN MANUEL</t>
@@ -433,37 +550,25 @@
     <t>DYLAN</t>
   </si>
   <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VANESSA </t>
   </si>
   <si>
     <t>JUAN CARLOS</t>
   </si>
   <si>
-    <t>LEOPOLDO</t>
-  </si>
-  <si>
-    <t>BRISA</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VANESSA </t>
-  </si>
-  <si>
-    <t>JESSICA ALEJANDRA</t>
-  </si>
-  <si>
-    <t>NICZA ARELI</t>
+    <t>DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>JESUS LEONEL</t>
   </si>
   <si>
     <t>OSCAR</t>
@@ -472,6 +577,21 @@
     <t>OLVIA YISEL</t>
   </si>
   <si>
+    <t>TIFFANY JAZMIN</t>
+  </si>
+  <si>
+    <t>MICHELLE JAZLIM</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>KENIA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
     <t>AMEZQUITA</t>
   </si>
   <si>
@@ -481,34 +601,55 @@
     <t>HIGUERA</t>
   </si>
   <si>
+    <t>CASTANEDO</t>
+  </si>
+  <si>
+    <t>PAYAN</t>
+  </si>
+  <si>
     <t>VALENZUELA</t>
   </si>
   <si>
-    <t>PAYAN</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>BEJARANO</t>
+  </si>
+  <si>
+    <t>MERCADO</t>
+  </si>
+  <si>
+    <t>PONCE</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>MAEDA</t>
   </si>
   <si>
-    <t>BEJARANO</t>
-  </si>
-  <si>
-    <t>PONCE</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>OCHOA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
   </si>
   <si>
     <t>BENAVIDEZ</t>
   </si>
   <si>
-    <t>MERCADO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
+    <t xml:space="preserve">MEDINA </t>
+  </si>
+  <si>
+    <t>FRANCISCO</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
   </si>
   <si>
     <t>ALVARADO</t>
@@ -517,28 +658,34 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t xml:space="preserve">MEDINA </t>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>PIÑA</t>
   </si>
   <si>
     <t>MACIAS</t>
   </si>
   <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>IZAGUIRRE</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>OCHOA</t>
-  </si>
-  <si>
-    <t>FRANCISCO</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
+    <t>CARMONA</t>
+  </si>
+  <si>
+    <t>TOPETE</t>
+  </si>
+  <si>
+    <t>OLIVAS</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
@@ -547,111 +694,132 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>TAPIA</t>
+    <t>GALVAN</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>OLIVAS</t>
-  </si>
-  <si>
-    <t>GALVAN</t>
-  </si>
-  <si>
-    <t>IZAGUIRRE</t>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>BELTRAN</t>
+  </si>
+  <si>
+    <t>GALAVIZ</t>
   </si>
   <si>
     <t>HURTADO</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>MENDIETA</t>
   </si>
   <si>
     <t>ROSAS</t>
   </si>
   <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
     <t>ESPINOZA</t>
   </si>
   <si>
-    <t>GUEVARA</t>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>OSUNA</t>
+  </si>
+  <si>
+    <t>VELARDE</t>
+  </si>
+  <si>
+    <t>X</t>
   </si>
   <si>
     <t xml:space="preserve">GARCIA </t>
   </si>
   <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>VELARDE</t>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>PALAFOX</t>
   </si>
   <si>
     <t>PEÑA</t>
   </si>
   <si>
-    <t>OSUNA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>X</t>
+    <t>TALAMANTES</t>
+  </si>
+  <si>
+    <t>FIERRO</t>
+  </si>
+  <si>
+    <t>COBO</t>
+  </si>
+  <si>
+    <t>CACERES</t>
   </si>
   <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>TALAMANTES</t>
+    <t>OLIVEROS</t>
   </si>
   <si>
     <t>MEZA</t>
   </si>
   <si>
-    <t>OLIVEROS</t>
-  </si>
-  <si>
-    <t>FIERRO</t>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>AGUAYO</t>
   </si>
   <si>
     <t>ORDUÑO</t>
   </si>
   <si>
+    <t>SIQUEIROS</t>
+  </si>
+  <si>
     <t>MADRID</t>
   </si>
   <si>
-    <t>AGUAYO</t>
-  </si>
-  <si>
-    <t>CACERES</t>
-  </si>
-  <si>
-    <t>COBO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>LIAÑO</t>
+  </si>
+  <si>
+    <t>ARTEAGA</t>
   </si>
   <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>BELTRAN</t>
+    <t>HOPKINS</t>
+  </si>
+  <si>
+    <t>RICO</t>
   </si>
   <si>
     <t>52</t>
   </si>
   <si>
+    <t>6862393566</t>
+  </si>
+  <si>
     <t>6863074437</t>
   </si>
   <si>
@@ -661,34 +829,55 @@
     <t>6861744727</t>
   </si>
   <si>
+    <t>6531131589</t>
+  </si>
+  <si>
+    <t>6864629400</t>
+  </si>
+  <si>
     <t>6861480734</t>
   </si>
   <si>
-    <t>6864629400</t>
-  </si>
-  <si>
     <t>6865848338</t>
   </si>
   <si>
+    <t>6865923181</t>
+  </si>
+  <si>
+    <t>6865257334</t>
+  </si>
+  <si>
+    <t>6861822416</t>
+  </si>
+  <si>
+    <t>6863537341</t>
+  </si>
+  <si>
     <t>6861253578</t>
   </si>
   <si>
-    <t>6865923181</t>
-  </si>
-  <si>
-    <t>6861822416</t>
+    <t>6861739204</t>
+  </si>
+  <si>
+    <t>6863473949</t>
+  </si>
+  <si>
+    <t>6861244927</t>
   </si>
   <si>
     <t>6864150761</t>
   </si>
   <si>
-    <t>6865257334</t>
-  </si>
-  <si>
-    <t>6861739204</t>
-  </si>
-  <si>
-    <t>6863537341</t>
+    <t>6643120858</t>
+  </si>
+  <si>
+    <t>6861575086</t>
+  </si>
+  <si>
+    <t>6862120595</t>
+  </si>
+  <si>
+    <t>6867220400</t>
   </si>
   <si>
     <t>5628369350</t>
@@ -697,37 +886,52 @@
     <t>6863485358</t>
   </si>
   <si>
-    <t>6643120858</t>
+    <t>6861146223</t>
+  </si>
+  <si>
+    <t>6865895862</t>
   </si>
   <si>
     <t>6861351566</t>
   </si>
   <si>
+    <t>6861234727</t>
+  </si>
+  <si>
     <t>6862489316</t>
   </si>
   <si>
+    <t>6863912198</t>
+  </si>
+  <si>
     <t>6861632588</t>
   </si>
   <si>
+    <t>6864650098</t>
+  </si>
+  <si>
+    <t>6623654956</t>
+  </si>
+  <si>
+    <t>8130964314</t>
+  </si>
+  <si>
+    <t>6861601599</t>
+  </si>
+  <si>
     <t>6863242180</t>
   </si>
   <si>
-    <t>6861146223</t>
-  </si>
-  <si>
-    <t>6865895862</t>
-  </si>
-  <si>
-    <t>6863473949</t>
-  </si>
-  <si>
-    <t>6861575086</t>
-  </si>
-  <si>
-    <t>6861234727</t>
-  </si>
-  <si>
-    <t>6861601599</t>
+    <t>6863378715</t>
+  </si>
+  <si>
+    <t>6865890812</t>
+  </si>
+  <si>
+    <t>6862316574</t>
+  </si>
+  <si>
+    <t>6863648770</t>
   </si>
   <si>
     <t>6867292744</t>
@@ -736,37 +940,25 @@
     <t>6861698256</t>
   </si>
   <si>
-    <t>6623654956</t>
-  </si>
-  <si>
-    <t>6867220400</t>
+    <t>6861127057</t>
+  </si>
+  <si>
+    <t>6864164007</t>
   </si>
   <si>
     <t>6863903522</t>
   </si>
   <si>
-    <t>6862120595</t>
-  </si>
-  <si>
-    <t>6863912198</t>
-  </si>
-  <si>
-    <t>8130964314</t>
-  </si>
-  <si>
-    <t>6862316574</t>
-  </si>
-  <si>
-    <t>6861127057</t>
-  </si>
-  <si>
-    <t>6864164007</t>
-  </si>
-  <si>
-    <t>6863648770</t>
-  </si>
-  <si>
-    <t>6864650098</t>
+    <t>6531662052</t>
+  </si>
+  <si>
+    <t>6863940285</t>
+  </si>
+  <si>
+    <t>6311261612</t>
+  </si>
+  <si>
+    <t>6865866356</t>
   </si>
   <si>
     <t>6865906261</t>
@@ -775,52 +967,76 @@
     <t>6863667098</t>
   </si>
   <si>
+    <t>6866190407</t>
+  </si>
+  <si>
+    <t>6865111469</t>
+  </si>
+  <si>
+    <t>6861762359</t>
+  </si>
+  <si>
+    <t>6869460269</t>
+  </si>
+  <si>
     <t>INDEPENDENCIA 1</t>
   </si>
   <si>
+    <t>DEL CARRIZO 3015</t>
+  </si>
+  <si>
     <t>IND123</t>
   </si>
   <si>
     <t>INDEPENDENCIA 38</t>
   </si>
   <si>
+    <t>INDEPENDENCIA1</t>
+  </si>
+  <si>
     <t>CULTURA OLMECA 3608</t>
   </si>
   <si>
+    <t>INDEPENDENCIA3</t>
+  </si>
+  <si>
+    <t>MAYA CAMPESTRE</t>
+  </si>
+  <si>
+    <t>IND111111</t>
+  </si>
+  <si>
     <t>LINEZO1</t>
   </si>
   <si>
-    <t>INDEPENDENCIA1</t>
-  </si>
-  <si>
-    <t>MAYA CAMPESTRE</t>
-  </si>
-  <si>
-    <t>INDEPENDENCIA3</t>
+    <t>SANTA FE</t>
+  </si>
+  <si>
+    <t>INDEPENDENCIA02</t>
   </si>
   <si>
     <t>INDEPENDENCIA 23</t>
   </si>
   <si>
-    <t>SANTA FE</t>
+    <t>INDEPENDENCIA01</t>
+  </si>
+  <si>
+    <t>PRESA DE LA ANGOSURA 1491</t>
   </si>
   <si>
     <t>SAN CARLO1</t>
   </si>
   <si>
-    <t>INDEPENDENCIA01</t>
-  </si>
-  <si>
-    <t>INDEPENDENCIA02</t>
-  </si>
-  <si>
-    <t>PRESA DE LA ANGOSURA 1491</t>
+    <t xml:space="preserve">TORRE LAS ARCAS </t>
+  </si>
+  <si>
+    <t>CERRO DEL POTOSI 1119</t>
   </si>
   <si>
     <t>INDEPENDENCIA0</t>
   </si>
   <si>
-    <t>CERRO DEL POTOSI 1119</t>
+    <t>JOSE MARIA AGUAYO 506</t>
   </si>
   <si>
     <t>INDEPENDENCI1</t>
@@ -829,21 +1045,24 @@
     <t>AV TORRE LAS ARCAS 2045</t>
   </si>
   <si>
-    <t>JOSE MARIA AGUAYO 506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORRE LAS ARCAS </t>
+    <t>EEEE12</t>
   </si>
   <si>
     <t>AV LAGO BAHIJASH 634</t>
   </si>
   <si>
+    <t>IND22222</t>
+  </si>
+  <si>
     <t>Masculino</t>
   </si>
   <si>
     <t>Femenino</t>
   </si>
   <si>
+    <t>28-05-2001</t>
+  </si>
+  <si>
     <t>21-10-1966</t>
   </si>
   <si>
@@ -853,34 +1072,55 @@
     <t>22-07-1992</t>
   </si>
   <si>
+    <t>01-10-2003</t>
+  </si>
+  <si>
+    <t>18-02-2009</t>
+  </si>
+  <si>
     <t>14-03-1988</t>
   </si>
   <si>
-    <t>18-02-2009</t>
-  </si>
-  <si>
     <t>11-06-2001</t>
   </si>
   <si>
+    <t>18-01-1995</t>
+  </si>
+  <si>
+    <t>10-06-1994</t>
+  </si>
+  <si>
+    <t>13-12-1990</t>
+  </si>
+  <si>
+    <t>22-06-1995</t>
+  </si>
+  <si>
     <t>06-10-1952</t>
   </si>
   <si>
-    <t>18-01-1995</t>
-  </si>
-  <si>
-    <t>13-12-1990</t>
+    <t>06-09-1989</t>
+  </si>
+  <si>
+    <t>25-10-2003</t>
+  </si>
+  <si>
+    <t>26-05-1986</t>
   </si>
   <si>
     <t>21-07-1961</t>
   </si>
   <si>
-    <t>10-06-1994</t>
-  </si>
-  <si>
-    <t>06-09-1989</t>
-  </si>
-  <si>
-    <t>22-06-1995</t>
+    <t>18-08-1996</t>
+  </si>
+  <si>
+    <t>15-09-1973</t>
+  </si>
+  <si>
+    <t>17-07-1971</t>
+  </si>
+  <si>
+    <t>25-08-1998</t>
   </si>
   <si>
     <t>09-08-1976</t>
@@ -889,37 +1129,52 @@
     <t>15-09-1996</t>
   </si>
   <si>
-    <t>18-08-1996</t>
+    <t>27-04-1993</t>
+  </si>
+  <si>
+    <t>17-10-2002</t>
   </si>
   <si>
     <t>11-12-2004</t>
   </si>
   <si>
+    <t>30-07-1996</t>
+  </si>
+  <si>
     <t>03-12-1981</t>
   </si>
   <si>
+    <t>12-02-2006</t>
+  </si>
+  <si>
     <t>12-05-2006</t>
   </si>
   <si>
+    <t>03-11-1994</t>
+  </si>
+  <si>
+    <t>27-03-1998</t>
+  </si>
+  <si>
+    <t>18-03-1995</t>
+  </si>
+  <si>
+    <t>25-04-1979</t>
+  </si>
+  <si>
     <t>25-07-1987</t>
   </si>
   <si>
-    <t>27-04-1993</t>
-  </si>
-  <si>
-    <t>17-10-2002</t>
-  </si>
-  <si>
-    <t>25-10-2003</t>
-  </si>
-  <si>
-    <t>15-09-1973</t>
-  </si>
-  <si>
-    <t>30-07-1996</t>
-  </si>
-  <si>
-    <t>25-04-1979</t>
+    <t>04-08-2006</t>
+  </si>
+  <si>
+    <t>15-12-1987</t>
+  </si>
+  <si>
+    <t>01-01-2000</t>
+  </si>
+  <si>
+    <t>18-01-2006</t>
   </si>
   <si>
     <t>09-11-1973</t>
@@ -928,37 +1183,25 @@
     <t>06-08-2002</t>
   </si>
   <si>
-    <t>27-03-1998</t>
-  </si>
-  <si>
-    <t>25-08-1998</t>
+    <t>26-11-1989</t>
+  </si>
+  <si>
+    <t>08-11-1989</t>
   </si>
   <si>
     <t>08-03-1971</t>
   </si>
   <si>
-    <t>17-07-1971</t>
-  </si>
-  <si>
-    <t>12-02-2006</t>
-  </si>
-  <si>
-    <t>18-03-1995</t>
-  </si>
-  <si>
-    <t>01-01-2000</t>
-  </si>
-  <si>
-    <t>26-11-1989</t>
-  </si>
-  <si>
-    <t>08-11-1989</t>
-  </si>
-  <si>
-    <t>18-01-2006</t>
-  </si>
-  <si>
-    <t>03-11-1994</t>
+    <t>20-06-2006</t>
+  </si>
+  <si>
+    <t>18-04-1977</t>
+  </si>
+  <si>
+    <t>18-06-1985</t>
+  </si>
+  <si>
+    <t>28-10-1986</t>
   </si>
   <si>
     <t>03-08-2006</t>
@@ -967,6 +1210,21 @@
     <t>03-03-2001</t>
   </si>
   <si>
+    <t>06-09-2006</t>
+  </si>
+  <si>
+    <t>09-02-1992</t>
+  </si>
+  <si>
+    <t>11-08-1951</t>
+  </si>
+  <si>
+    <t>24-09-1981</t>
+  </si>
+  <si>
+    <t>SAMUELSESS32@GMAIL.COM</t>
+  </si>
+  <si>
     <t>OAMEZQUITA@GMAIL.COM</t>
   </si>
   <si>
@@ -976,34 +1234,55 @@
     <t>HIGUERAROSAV@GMAIL.COM</t>
   </si>
   <si>
+    <t>AKYDANIELLA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SILVIAPAYAN009@GMAIL.COM</t>
+  </si>
+  <si>
     <t>JEVE0336@GMAIL.COM</t>
   </si>
   <si>
-    <t>SILVIAPAYAN009@GMAIL.COM</t>
-  </si>
-  <si>
     <t>EUNICE.LOPEZ5@UABC.EDU.MX</t>
   </si>
   <si>
+    <t>FANNYBEJARANO904@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>LICMERCADOSUNA.10@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>YADIRA_1290@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>CRISTIAN.TORRES@GCADENA.COM</t>
+  </si>
+  <si>
     <t>MARTHAELENAMG@GMAIL.COM</t>
   </si>
   <si>
-    <t>FANNYBEJARANO904@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>YADIRA_1290@HOTMAIL.COM</t>
+    <t>DANIELA.SANCHEZ.MORENO.89@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>CARLOS8A2510@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>VERONIKAPALAFOX@GMAIL.COM</t>
   </si>
   <si>
     <t>NOTIERERER@TYU.COM</t>
   </si>
   <si>
-    <t>LICMERCADOSUNA.10@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>DANIELA.SANCHEZ.MORENO.89@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>CRISTIAN.TORRES@GCADENA.COM</t>
+    <t>ESTEFANIAMTALAMANTESX@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>FIERRO_PACO@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>LEOPOLDOLOYO@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>JOSECACEREZ98@GMAIL.COM</t>
   </si>
   <si>
     <t>MACALVMAIL@GMAIL.COM</t>
@@ -1012,37 +1291,49 @@
     <t>RENEGONZALEZ1@GMAIL.COM</t>
   </si>
   <si>
-    <t>ESTEFANIAMTALAMANTESX@GMAIL.COM</t>
+    <t>IVANRNAVARRO12@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>NOTIENE11112222@FFFFDDD.COM</t>
   </si>
   <si>
     <t>KARYMEMACLOP@GMAIL.COM</t>
   </si>
   <si>
+    <t>SHES.MEZAGTZ@GMAIL.COM</t>
+  </si>
+  <si>
     <t>LOPEZDARIANA780@GMAIL.COM</t>
   </si>
   <si>
+    <t>GNAVARROGASCA@GMAIL.COM</t>
+  </si>
+  <si>
     <t>6MALLISME9@GMAIL.COM</t>
   </si>
   <si>
+    <t>IZAGUIRREARELI@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>JOSETAPIAGUAYO@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>YAAS.LOPEZ18@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MOPILLO@GMAIL.COM</t>
+  </si>
+  <si>
     <t>YLEM51@GMAIL.COM</t>
   </si>
   <si>
-    <t>IVANRNAVARRO12@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>NOTIENE11112222@FFFFDDD.COM</t>
-  </si>
-  <si>
-    <t>CARLOS8A2510@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>FIERRO_PACO@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>SHES.MEZAGTZ@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>MOPILLO@GMAIL.COM</t>
+    <t>ANGELESWCARMONA763@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>CHUYANTONT@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>JESSICAA.GUTIERREZ@CETYS.EDU.MX</t>
   </si>
   <si>
     <t>NOCUENTACON1@GMAIL.COM</t>
@@ -1051,34 +1342,25 @@
     <t>DYLANMTZM.26@GMAIL.COM</t>
   </si>
   <si>
-    <t>JOSETAPIAGUAYO@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>JOSECACEREZ98@GMAIL.COM</t>
+    <t>JOSUEBRMUSIC@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>VANESSAGALVANR250210@GMAIL.COM</t>
   </si>
   <si>
     <t>JUANCARLORIOS1422@GMAIL.COM</t>
   </si>
   <si>
-    <t>LEOPOLDOLOYO@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>GNAVARROGASCA@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>YAAS.LOPEZ18@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>JOSUEBRMUSIC@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>VANESSAGALVANR250210@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>JESSICAA.GUTIERREZ@CETYS.EDU.MX</t>
-  </si>
-  <si>
-    <t>IZAGUIRREARELI@GMAIL.COM</t>
+    <t>MOLINAARROYODANNAPAOLA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MASTERBOY1930@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>COLORGRAFICO@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>JESUSLEONEL@GMAIL.COM</t>
   </si>
   <si>
     <t>OR629395@GMAIL.COM</t>
@@ -1087,6 +1369,21 @@
     <t>OLVIAHU18@GMAIL.COM</t>
   </si>
   <si>
+    <t>NOTIENEEE@SSS.COM</t>
+  </si>
+  <si>
+    <t>MICHELLE.RLEYVA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>NOTIENE23445@DFDF.COM</t>
+  </si>
+  <si>
+    <t>KRISS0024@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>02-10-2024 22:01:32</t>
+  </si>
+  <si>
     <t>22-10-2025 15:17:42</t>
   </si>
   <si>
@@ -1096,34 +1393,55 @@
     <t>28-04-2025 19:34:24</t>
   </si>
   <si>
+    <t>19-09-2022 16:35:13</t>
+  </si>
+  <si>
+    <t>05-06-2024 18:12:25</t>
+  </si>
+  <si>
     <t>14-03-2023 12:55:14</t>
   </si>
   <si>
-    <t>05-06-2024 18:12:25</t>
-  </si>
-  <si>
     <t>23-06-2025 18:39:49</t>
   </si>
   <si>
+    <t>02-02-2026 16:15:36</t>
+  </si>
+  <si>
+    <t>03-02-2026 17:15:35</t>
+  </si>
+  <si>
+    <t>03-02-2026 15:56:48</t>
+  </si>
+  <si>
+    <t>03-02-2026 17:02:34</t>
+  </si>
+  <si>
     <t>23-01-2026 12:52:24</t>
   </si>
   <si>
-    <t>02-02-2026 16:15:36</t>
-  </si>
-  <si>
-    <t>03-02-2026 15:56:48</t>
+    <t>03-02-2026 18:45:03</t>
+  </si>
+  <si>
+    <t>09-02-2026 16:59:55</t>
+  </si>
+  <si>
+    <t>09-02-2026 10:07:36</t>
   </si>
   <si>
     <t>03-02-2026 08:55:15</t>
   </si>
   <si>
-    <t>03-02-2026 17:15:35</t>
-  </si>
-  <si>
-    <t>03-02-2026 18:45:03</t>
-  </si>
-  <si>
-    <t>03-02-2026 17:02:34</t>
+    <t>04-02-2026 18:08:31</t>
+  </si>
+  <si>
+    <t>09-02-2026 19:49:15</t>
+  </si>
+  <si>
+    <t>10-02-2026 19:02:43</t>
+  </si>
+  <si>
+    <t>09-02-2026 20:20:01</t>
   </si>
   <si>
     <t>03-02-2026 18:47:52</t>
@@ -1132,37 +1450,52 @@
     <t>03-02-2026 19:14:48</t>
   </si>
   <si>
-    <t>04-02-2026 18:08:31</t>
+    <t>09-02-2026 20:13:50</t>
+  </si>
+  <si>
+    <t>10-02-2026 10:48:52</t>
   </si>
   <si>
     <t>07-02-2026 12:03:12</t>
   </si>
   <si>
+    <t>10-02-2026 11:28:40</t>
+  </si>
+  <si>
     <t>07-02-2026 13:31:41</t>
   </si>
   <si>
+    <t>12-02-2026 19:16:27</t>
+  </si>
+  <si>
     <t>09-02-2026 17:35:12</t>
   </si>
   <si>
+    <t>11-02-2026 20:53:07</t>
+  </si>
+  <si>
+    <t>10-02-2026 18:11:07</t>
+  </si>
+  <si>
+    <t>11-02-2026 14:53:46</t>
+  </si>
+  <si>
+    <t>09-02-2026 17:27:09</t>
+  </si>
+  <si>
     <t>09-02-2026 20:08:06</t>
   </si>
   <si>
-    <t>09-02-2026 20:13:50</t>
-  </si>
-  <si>
-    <t>10-02-2026 10:48:52</t>
-  </si>
-  <si>
-    <t>09-02-2026 16:59:55</t>
-  </si>
-  <si>
-    <t>09-02-2026 19:49:15</t>
-  </si>
-  <si>
-    <t>10-02-2026 11:28:40</t>
-  </si>
-  <si>
-    <t>09-02-2026 17:27:09</t>
+    <t>16-02-2026 15:44:25</t>
+  </si>
+  <si>
+    <t>16-02-2026 19:42:11</t>
+  </si>
+  <si>
+    <t>11-02-2026 20:34:48</t>
+  </si>
+  <si>
+    <t>14-02-2026 11:38:52</t>
   </si>
   <si>
     <t>10-02-2026 18:03:21</t>
@@ -1171,37 +1504,25 @@
     <t>11-02-2026 15:49:14</t>
   </si>
   <si>
-    <t>10-02-2026 18:11:07</t>
-  </si>
-  <si>
-    <t>09-02-2026 20:20:01</t>
+    <t>10-02-2026 18:25:08</t>
+  </si>
+  <si>
+    <t>11-02-2026 20:55:11</t>
   </si>
   <si>
     <t>13-02-2026 17:19:49</t>
   </si>
   <si>
-    <t>10-02-2026 19:02:43</t>
-  </si>
-  <si>
-    <t>12-02-2026 19:16:27</t>
-  </si>
-  <si>
-    <t>11-02-2026 14:53:46</t>
-  </si>
-  <si>
-    <t>11-02-2026 20:34:48</t>
-  </si>
-  <si>
-    <t>10-02-2026 18:25:08</t>
-  </si>
-  <si>
-    <t>11-02-2026 20:55:11</t>
-  </si>
-  <si>
-    <t>14-02-2026 11:38:52</t>
-  </si>
-  <si>
-    <t>11-02-2026 20:53:07</t>
+    <t>16-02-2026 15:47:17</t>
+  </si>
+  <si>
+    <t>17-02-2026 08:06:52</t>
+  </si>
+  <si>
+    <t>17-02-2026 07:06:31</t>
+  </si>
+  <si>
+    <t>17-02-2026 17:54:18</t>
   </si>
   <si>
     <t>13-02-2026 20:02:16</t>
@@ -1210,13 +1531,34 @@
     <t>14-02-2026 11:45:34</t>
   </si>
   <si>
+    <t>17-02-2026 11:29:05</t>
+  </si>
+  <si>
+    <t>17-02-2026 12:06:32</t>
+  </si>
+  <si>
+    <t>17-02-2026 11:34:41</t>
+  </si>
+  <si>
+    <t>17-02-2026 14:43:35</t>
+  </si>
+  <si>
     <t>Tarifas 2026 LE</t>
   </si>
   <si>
+    <t>inscripcion promo 199</t>
+  </si>
+  <si>
+    <t>Sin contrato</t>
+  </si>
+  <si>
     <t>Forzoso</t>
   </si>
   <si>
-    <t>Sin contrato</t>
+    <t>No Forzoso</t>
+  </si>
+  <si>
+    <t>CONVENIOS $549</t>
   </si>
   <si>
     <t>PROMO FEBRERO 12 MESES</t>
@@ -1225,24 +1567,30 @@
     <t>1 MES $899</t>
   </si>
   <si>
-    <t>CONVENIOS $549</t>
+    <t>RECURRENTE $649 LE</t>
   </si>
   <si>
     <t>3 MESES $1,899</t>
   </si>
   <si>
+    <t>549</t>
+  </si>
+  <si>
     <t>499</t>
   </si>
   <si>
     <t>899</t>
   </si>
   <si>
-    <t>549</t>
+    <t>649</t>
   </si>
   <si>
     <t>633</t>
   </si>
   <si>
+    <t>17-02-2026 17:05:51</t>
+  </si>
+  <si>
     <t>11-02-2026 18:22:11</t>
   </si>
   <si>
@@ -1252,34 +1600,55 @@
     <t>14-02-2026 15:01:10</t>
   </si>
   <si>
+    <t>17-02-2026 06:58:58</t>
+  </si>
+  <si>
+    <t>10-02-2026 05:33:30</t>
+  </si>
+  <si>
     <t>14-02-2026 09:55:56</t>
   </si>
   <si>
-    <t>10-02-2026 05:33:30</t>
-  </si>
-  <si>
     <t>09-02-2026 08:55:34</t>
   </si>
   <si>
+    <t>02-02-2026 16:21:03</t>
+  </si>
+  <si>
+    <t>03-02-2026 17:19:02</t>
+  </si>
+  <si>
+    <t>05-02-2026 16:33:17</t>
+  </si>
+  <si>
+    <t>03-02-2026 17:06:48</t>
+  </si>
+  <si>
     <t>03-02-2026 08:23:40</t>
   </si>
   <si>
-    <t>02-02-2026 16:21:03</t>
-  </si>
-  <si>
-    <t>05-02-2026 16:33:17</t>
+    <t>03-02-2026 19:05:49</t>
+  </si>
+  <si>
+    <t>09-02-2026 17:01:28</t>
+  </si>
+  <si>
+    <t>16-02-2026 08:19:11</t>
   </si>
   <si>
     <t>04-02-2026 10:23:34</t>
   </si>
   <si>
-    <t>03-02-2026 17:19:02</t>
-  </si>
-  <si>
-    <t>03-02-2026 19:05:49</t>
-  </si>
-  <si>
-    <t>03-02-2026 17:06:48</t>
+    <t>10-02-2026 16:06:43</t>
+  </si>
+  <si>
+    <t>09-02-2026 19:51:47</t>
+  </si>
+  <si>
+    <t>14-02-2026 13:28:02</t>
+  </si>
+  <si>
+    <t>09-02-2026 20:21:16</t>
   </si>
   <si>
     <t>03-02-2026 19:09:42</t>
@@ -1288,37 +1657,52 @@
     <t>05-02-2026 19:04:55</t>
   </si>
   <si>
-    <t>10-02-2026 16:06:43</t>
+    <t>09-02-2026 20:16:34</t>
+  </si>
+  <si>
+    <t>10-02-2026 10:50:12</t>
   </si>
   <si>
     <t>07-02-2026 12:05:36</t>
   </si>
   <si>
+    <t>10-02-2026 11:31:11</t>
+  </si>
+  <si>
     <t>07-02-2026 13:38:04</t>
   </si>
   <si>
+    <t>12-02-2026 19:22:02</t>
+  </si>
+  <si>
     <t>09-02-2026 17:38:30</t>
   </si>
   <si>
+    <t>13-02-2026 18:50:54</t>
+  </si>
+  <si>
+    <t>10-02-2026 18:12:38</t>
+  </si>
+  <si>
+    <t>12-02-2026 12:36:52</t>
+  </si>
+  <si>
+    <t>09-02-2026 17:33:13</t>
+  </si>
+  <si>
     <t>09-02-2026 20:12:28</t>
   </si>
   <si>
-    <t>09-02-2026 20:16:34</t>
-  </si>
-  <si>
-    <t>10-02-2026 10:50:12</t>
-  </si>
-  <si>
-    <t>09-02-2026 17:01:28</t>
-  </si>
-  <si>
-    <t>09-02-2026 19:51:47</t>
-  </si>
-  <si>
-    <t>10-02-2026 11:31:11</t>
-  </si>
-  <si>
-    <t>09-02-2026 17:33:13</t>
+    <t>16-02-2026 15:45:32</t>
+  </si>
+  <si>
+    <t>16-02-2026 19:43:34</t>
+  </si>
+  <si>
+    <t>13-02-2026 16:04:20</t>
+  </si>
+  <si>
+    <t>14-02-2026 11:41:20</t>
   </si>
   <si>
     <t>10-02-2026 18:35:28</t>
@@ -1327,37 +1711,25 @@
     <t>11-02-2026 15:52:21</t>
   </si>
   <si>
-    <t>10-02-2026 18:12:38</t>
-  </si>
-  <si>
-    <t>09-02-2026 20:21:16</t>
+    <t>10-02-2026 18:27:56</t>
+  </si>
+  <si>
+    <t>13-02-2026 18:56:17</t>
   </si>
   <si>
     <t>13-02-2026 17:24:13</t>
   </si>
   <si>
-    <t>14-02-2026 13:28:02</t>
-  </si>
-  <si>
-    <t>12-02-2026 19:22:02</t>
-  </si>
-  <si>
-    <t>12-02-2026 12:36:52</t>
-  </si>
-  <si>
-    <t>13-02-2026 16:04:20</t>
-  </si>
-  <si>
-    <t>10-02-2026 18:27:56</t>
-  </si>
-  <si>
-    <t>13-02-2026 18:56:17</t>
-  </si>
-  <si>
-    <t>14-02-2026 11:41:20</t>
-  </si>
-  <si>
-    <t>13-02-2026 18:50:54</t>
+    <t>16-02-2026 15:49:00</t>
+  </si>
+  <si>
+    <t>17-02-2026 08:09:37</t>
+  </si>
+  <si>
+    <t>17-02-2026 07:07:36</t>
+  </si>
+  <si>
+    <t>17-02-2026 17:56:16</t>
   </si>
   <si>
     <t>13-02-2026 20:03:49</t>
@@ -1366,6 +1738,21 @@
     <t>14-02-2026 11:48:11</t>
   </si>
   <si>
+    <t>17-02-2026 11:32:47</t>
+  </si>
+  <si>
+    <t>17-02-2026 12:07:57</t>
+  </si>
+  <si>
+    <t>17-02-2026 11:37:38</t>
+  </si>
+  <si>
+    <t>17-02-2026 14:52:04</t>
+  </si>
+  <si>
+    <t>17-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>11-03-2026 23:59:59</t>
   </si>
   <si>
@@ -1378,28 +1765,34 @@
     <t>09-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>02-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>03-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>02-03-2026 23:59:59</t>
-  </si>
-  <si>
     <t>05-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>16-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>04-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>10-05-2026 23:59:59</t>
+  </si>
+  <si>
     <t>07-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>10-05-2026 23:59:59</t>
+    <t>12-03-2026 23:59:59</t>
   </si>
   <si>
     <t>13-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>12-03-2026 23:59:59</t>
+    <t>17-05-2026 23:59:59</t>
   </si>
   <si>
     <t>11-02-2026 18:18:44</t>
@@ -1411,6 +1804,9 @@
     <t>14-02-2026 15:00:36</t>
   </si>
   <si>
+    <t>17-02-2026 06:58:23</t>
+  </si>
+  <si>
     <t>10-02-2026 05:32:15</t>
   </si>
   <si>
@@ -1420,19 +1816,31 @@
     <t>02-02-2026 16:20:43</t>
   </si>
   <si>
+    <t>03-02-2026 17:18:43</t>
+  </si>
+  <si>
     <t>05-02-2026 16:30:37</t>
   </si>
   <si>
+    <t>03-02-2026 17:06:13</t>
+  </si>
+  <si>
+    <t>03-02-2026 19:04:34</t>
+  </si>
+  <si>
+    <t>16-02-2026 08:18:23</t>
+  </si>
+  <si>
     <t>04-02-2026 10:22:30</t>
   </si>
   <si>
-    <t>03-02-2026 17:18:43</t>
-  </si>
-  <si>
-    <t>03-02-2026 19:04:34</t>
-  </si>
-  <si>
-    <t>03-02-2026 17:06:13</t>
+    <t>10-02-2026 16:05:59</t>
+  </si>
+  <si>
+    <t>09-02-2026 19:50:53</t>
+  </si>
+  <si>
+    <t>14-02-2026 13:27:04</t>
   </si>
   <si>
     <t>03-02-2026 19:09:20</t>
@@ -1441,66 +1849,69 @@
     <t>05-02-2026 19:03:37</t>
   </si>
   <si>
-    <t>10-02-2026 16:05:59</t>
+    <t>09-02-2026 20:16:03</t>
+  </si>
+  <si>
+    <t>10-02-2026 11:30:36</t>
   </si>
   <si>
     <t>07-02-2026 13:35:50</t>
   </si>
   <si>
+    <t>12-02-2026 19:21:22</t>
+  </si>
+  <si>
     <t>09-02-2026 17:38:05</t>
   </si>
   <si>
+    <t>13-02-2026 18:49:33</t>
+  </si>
+  <si>
+    <t>12-02-2026 12:36:23</t>
+  </si>
+  <si>
+    <t>09-02-2026 17:32:43</t>
+  </si>
+  <si>
     <t>09-02-2026 20:10:07</t>
   </si>
   <si>
-    <t>09-02-2026 20:16:03</t>
-  </si>
-  <si>
-    <t>09-02-2026 19:50:53</t>
-  </si>
-  <si>
-    <t>10-02-2026 11:30:36</t>
-  </si>
-  <si>
-    <t>09-02-2026 17:32:43</t>
+    <t>14-02-2026 11:40:29</t>
   </si>
   <si>
     <t>10-02-2026 18:35:08</t>
   </si>
   <si>
+    <t>10-02-2026 18:27:24</t>
+  </si>
+  <si>
+    <t>13-02-2026 18:55:42</t>
+  </si>
+  <si>
     <t>13-02-2026 17:22:41</t>
   </si>
   <si>
-    <t>14-02-2026 13:27:04</t>
-  </si>
-  <si>
-    <t>12-02-2026 19:21:22</t>
-  </si>
-  <si>
-    <t>12-02-2026 12:36:23</t>
-  </si>
-  <si>
-    <t>10-02-2026 18:27:24</t>
-  </si>
-  <si>
-    <t>13-02-2026 18:55:42</t>
-  </si>
-  <si>
-    <t>14-02-2026 11:40:29</t>
-  </si>
-  <si>
-    <t>13-02-2026 18:49:33</t>
+    <t>17-02-2026 08:08:58</t>
   </si>
   <si>
     <t>14-02-2026 11:47:29</t>
   </si>
   <si>
+    <t>17-02-2026 11:32:10</t>
+  </si>
+  <si>
+    <t>17-02-2026 14:49:23</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
+    <t>26030522436260002152</t>
+  </si>
+  <si>
     <t>26160522273890001965</t>
   </si>
   <si>
@@ -1510,34 +1921,55 @@
     <t>26160522349780002121</t>
   </si>
   <si>
+    <t>26160522419880002224</t>
+  </si>
+  <si>
+    <t>26160522222220001861</t>
+  </si>
+  <si>
     <t>26160522345220002100</t>
   </si>
   <si>
-    <t>26160522222220001861</t>
-  </si>
-  <si>
     <t>26160522185470001787</t>
   </si>
   <si>
+    <t>26160522016270001486</t>
+  </si>
+  <si>
+    <t>26160522048750001552</t>
+  </si>
+  <si>
+    <t>26160522110560001680</t>
+  </si>
+  <si>
+    <t>26160522047970001551</t>
+  </si>
+  <si>
     <t>26160522033610001514</t>
   </si>
   <si>
-    <t>26160522016270001486</t>
-  </si>
-  <si>
-    <t>26160522110560001680</t>
+    <t>26160522055070001567</t>
+  </si>
+  <si>
+    <t>26160522200300001806</t>
+  </si>
+  <si>
+    <t>26160522380750002134</t>
   </si>
   <si>
     <t>26160522071550001606</t>
   </si>
   <si>
-    <t>26160522048750001552</t>
-  </si>
-  <si>
-    <t>26160522055070001567</t>
-  </si>
-  <si>
-    <t>26160522047970001551</t>
+    <t>26130522235720002570</t>
+  </si>
+  <si>
+    <t>26160522212280001839</t>
+  </si>
+  <si>
+    <t>26160522349290002113</t>
+  </si>
+  <si>
+    <t>26160522213460001843</t>
   </si>
   <si>
     <t>26160522055330001568</t>
@@ -1546,37 +1978,52 @@
     <t>26160522117360001694</t>
   </si>
   <si>
-    <t>26130522235720002570</t>
+    <t>26160522213270001841</t>
+  </si>
+  <si>
+    <t>26160522228650001872</t>
   </si>
   <si>
     <t>26160522160500001761</t>
   </si>
   <si>
+    <t>26160522229140001874</t>
+  </si>
+  <si>
     <t>26160522161810001766</t>
   </si>
   <si>
+    <t>26160522304540002036</t>
+  </si>
+  <si>
     <t>26160522203170001811</t>
   </si>
   <si>
+    <t>26170522328830002369</t>
+  </si>
+  <si>
+    <t>26160522242690001898</t>
+  </si>
+  <si>
+    <t>26180522292630004399</t>
+  </si>
+  <si>
+    <t>26160522202710001810</t>
+  </si>
+  <si>
     <t>26160522213110001840</t>
   </si>
   <si>
-    <t>26160522213270001841</t>
-  </si>
-  <si>
-    <t>26160522228650001872</t>
-  </si>
-  <si>
-    <t>26160522200300001806</t>
-  </si>
-  <si>
-    <t>26160522212280001839</t>
-  </si>
-  <si>
-    <t>26160522229140001874</t>
-  </si>
-  <si>
-    <t>26160522202710001810</t>
+    <t>26160522393400002157</t>
+  </si>
+  <si>
+    <t>26160522409070002196</t>
+  </si>
+  <si>
+    <t>26160522323640002074</t>
+  </si>
+  <si>
+    <t>26160522347590002106</t>
   </si>
   <si>
     <t>26160522243990001903</t>
@@ -1585,37 +2032,25 @@
     <t>26160522267270001952</t>
   </si>
   <si>
-    <t>26160522242690001898</t>
-  </si>
-  <si>
-    <t>26160522213460001843</t>
+    <t>26160522243630001901</t>
+  </si>
+  <si>
+    <t>26170522329060002370</t>
   </si>
   <si>
     <t>26160522326350002078</t>
   </si>
   <si>
-    <t>26160522349290002113</t>
-  </si>
-  <si>
-    <t>26160522304540002036</t>
-  </si>
-  <si>
-    <t>26180522292630004399</t>
-  </si>
-  <si>
-    <t>26160522323640002074</t>
-  </si>
-  <si>
-    <t>26160522243630001901</t>
-  </si>
-  <si>
-    <t>26170522329060002370</t>
-  </si>
-  <si>
-    <t>26160522347590002106</t>
-  </si>
-  <si>
-    <t>26170522328830002369</t>
+    <t>26160522393690002158</t>
+  </si>
+  <si>
+    <t>26160522421530002234</t>
+  </si>
+  <si>
+    <t>26160522420050002226</t>
+  </si>
+  <si>
+    <t>26160522439290002266</t>
   </si>
   <si>
     <t>26160522330930002093</t>
@@ -1624,6 +2059,18 @@
     <t>26160522347720002107</t>
   </si>
   <si>
+    <t>26160522425100002242</t>
+  </si>
+  <si>
+    <t>26160522425750002244</t>
+  </si>
+  <si>
+    <t>26160522425250002243</t>
+  </si>
+  <si>
+    <t>26160522430130002253</t>
+  </si>
+  <si>
     <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
   </si>
   <si>
@@ -1646,6 +2093,9 @@
   </si>
   <si>
     <t>N/D</t>
+  </si>
+  <si>
+    <t>Ricardo Alexis Alvarez Camarena</t>
   </si>
   <si>
     <t>Kevin Daniel Gonzalez Vasquez</t>
@@ -2021,7 +2471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
@@ -2118,85 +2568,73 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="F2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G2" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H2" t="s">
-        <v>212</v>
-      </c>
-      <c r="I2" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="J2" t="s">
-        <v>274</v>
+        <v>346</v>
       </c>
       <c r="K2" t="s">
-        <v>276</v>
+        <v>348</v>
       </c>
       <c r="L2" t="s">
-        <v>317</v>
+        <v>402</v>
       </c>
       <c r="M2" t="s">
-        <v>357</v>
+        <v>455</v>
+      </c>
+      <c r="N2" t="s">
+        <v>509</v>
       </c>
       <c r="O2" t="s">
-        <v>399</v>
+        <v>511</v>
       </c>
       <c r="P2" t="s">
-        <v>401</v>
+        <v>514</v>
       </c>
       <c r="Q2" t="s">
-        <v>405</v>
+        <v>519</v>
       </c>
       <c r="R2" t="s">
-        <v>409</v>
+        <v>524</v>
       </c>
       <c r="S2" t="s">
-        <v>450</v>
-      </c>
-      <c r="T2" t="s">
-        <v>462</v>
+        <v>578</v>
       </c>
       <c r="U2" t="s">
-        <v>493</v>
-      </c>
-      <c r="V2" t="s">
-        <v>494</v>
+        <v>629</v>
       </c>
       <c r="W2" t="s">
         <v>2</v>
       </c>
       <c r="X2" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>536</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>539</v>
+        <v>631</v>
       </c>
       <c r="AA2" t="s">
-        <v>405</v>
+        <v>519</v>
       </c>
       <c r="AB2" t="s">
-        <v>543</v>
+        <v>692</v>
       </c>
       <c r="AC2" t="s">
-        <v>548</v>
+        <v>698</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -2204,79 +2642,85 @@
         <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
       <c r="F3" t="s">
-        <v>174</v>
+        <v>236</v>
       </c>
       <c r="G3" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H3" t="s">
-        <v>213</v>
+        <v>268</v>
       </c>
       <c r="I3" t="s">
-        <v>111</v>
+        <v>321</v>
       </c>
       <c r="J3" t="s">
-        <v>275</v>
+        <v>346</v>
       </c>
       <c r="K3" t="s">
-        <v>277</v>
+        <v>349</v>
       </c>
       <c r="L3" t="s">
-        <v>318</v>
+        <v>403</v>
       </c>
       <c r="M3" t="s">
-        <v>358</v>
+        <v>456</v>
       </c>
       <c r="O3" t="s">
-        <v>399</v>
+        <v>512</v>
       </c>
       <c r="P3" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="Q3" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="R3" t="s">
-        <v>410</v>
+        <v>525</v>
       </c>
       <c r="S3" t="s">
-        <v>450</v>
+        <v>579</v>
       </c>
       <c r="T3" t="s">
-        <v>463</v>
+        <v>593</v>
       </c>
       <c r="U3" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V3" t="s">
-        <v>493</v>
+        <v>630</v>
       </c>
       <c r="W3" t="s">
         <v>2</v>
       </c>
       <c r="X3" t="s">
-        <v>496</v>
+        <v>632</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>685</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>688</v>
       </c>
       <c r="AA3" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="AB3" t="s">
-        <v>543</v>
+        <v>693</v>
       </c>
       <c r="AC3" t="s">
-        <v>548</v>
+        <v>699</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -2284,82 +2728,79 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
-        <v>154</v>
+        <v>193</v>
       </c>
       <c r="F4" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="G4" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H4" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
       <c r="I4" t="s">
-        <v>253</v>
+        <v>137</v>
       </c>
       <c r="J4" t="s">
-        <v>274</v>
+        <v>347</v>
       </c>
       <c r="K4" t="s">
-        <v>278</v>
+        <v>350</v>
       </c>
       <c r="L4" t="s">
-        <v>319</v>
+        <v>404</v>
       </c>
       <c r="M4" t="s">
-        <v>359</v>
+        <v>457</v>
       </c>
       <c r="O4" t="s">
-        <v>399</v>
+        <v>512</v>
       </c>
       <c r="P4" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="Q4" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="R4" t="s">
-        <v>411</v>
+        <v>526</v>
       </c>
       <c r="S4" t="s">
-        <v>451</v>
+        <v>579</v>
       </c>
       <c r="T4" t="s">
-        <v>464</v>
+        <v>594</v>
       </c>
       <c r="U4" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V4" t="s">
-        <v>494</v>
+        <v>629</v>
       </c>
       <c r="W4" t="s">
         <v>2</v>
       </c>
       <c r="X4" t="s">
-        <v>497</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>537</v>
+        <v>633</v>
       </c>
       <c r="AA4" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="AB4" t="s">
-        <v>544</v>
+        <v>693</v>
       </c>
       <c r="AC4" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -2367,73 +2808,82 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="E5" t="s">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="F5" t="s">
-        <v>187</v>
+        <v>237</v>
       </c>
       <c r="G5" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H5" t="s">
-        <v>215</v>
+        <v>270</v>
+      </c>
+      <c r="I5" t="s">
+        <v>321</v>
       </c>
       <c r="J5" t="s">
-        <v>274</v>
+        <v>346</v>
       </c>
       <c r="K5" t="s">
-        <v>279</v>
+        <v>351</v>
       </c>
       <c r="L5" t="s">
-        <v>320</v>
+        <v>405</v>
       </c>
       <c r="M5" t="s">
-        <v>360</v>
-      </c>
-      <c r="N5" t="s">
-        <v>398</v>
+        <v>458</v>
       </c>
       <c r="O5" t="s">
-        <v>400</v>
+        <v>512</v>
       </c>
       <c r="P5" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="Q5" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
       <c r="R5" t="s">
-        <v>412</v>
+        <v>527</v>
       </c>
       <c r="S5" t="s">
-        <v>451</v>
+        <v>580</v>
+      </c>
+      <c r="T5" t="s">
+        <v>595</v>
       </c>
       <c r="U5" t="s">
-        <v>493</v>
+        <v>629</v>
+      </c>
+      <c r="V5" t="s">
+        <v>630</v>
       </c>
       <c r="W5" t="s">
         <v>2</v>
       </c>
       <c r="X5" t="s">
-        <v>498</v>
+        <v>634</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>686</v>
       </c>
       <c r="AA5" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
       <c r="AB5" t="s">
-        <v>543</v>
+        <v>694</v>
       </c>
       <c r="AC5" t="s">
-        <v>548</v>
+        <v>699</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -2441,85 +2891,88 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="F6" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="G6" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H6" t="s">
-        <v>216</v>
+        <v>271</v>
       </c>
       <c r="I6" t="s">
-        <v>254</v>
+        <v>322</v>
       </c>
       <c r="J6" t="s">
-        <v>275</v>
+        <v>347</v>
       </c>
       <c r="K6" t="s">
-        <v>280</v>
+        <v>352</v>
       </c>
       <c r="L6" t="s">
-        <v>321</v>
+        <v>406</v>
       </c>
       <c r="M6" t="s">
-        <v>361</v>
+        <v>459</v>
+      </c>
+      <c r="N6" t="s">
+        <v>510</v>
       </c>
       <c r="O6" t="s">
-        <v>399</v>
+        <v>512</v>
       </c>
       <c r="P6" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="Q6" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="R6" t="s">
-        <v>413</v>
+        <v>528</v>
       </c>
       <c r="S6" t="s">
-        <v>452</v>
+        <v>578</v>
       </c>
       <c r="T6" t="s">
-        <v>465</v>
+        <v>596</v>
       </c>
       <c r="U6" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V6" t="s">
-        <v>494</v>
+        <v>630</v>
       </c>
       <c r="W6" t="s">
         <v>2</v>
       </c>
       <c r="X6" t="s">
-        <v>499</v>
+        <v>635</v>
       </c>
       <c r="Y6" t="s">
-        <v>536</v>
+        <v>685</v>
       </c>
       <c r="Z6" t="s">
-        <v>539</v>
+        <v>689</v>
       </c>
       <c r="AA6" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="AB6" t="s">
-        <v>544</v>
+        <v>692</v>
       </c>
       <c r="AC6" t="s">
-        <v>549</v>
+        <v>698</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -2527,82 +2980,85 @@
         <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="E7" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="F7" t="s">
-        <v>176</v>
+        <v>238</v>
       </c>
       <c r="G7" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H7" t="s">
-        <v>217</v>
+        <v>272</v>
       </c>
       <c r="I7" t="s">
-        <v>254</v>
+        <v>323</v>
       </c>
       <c r="J7" t="s">
-        <v>275</v>
+        <v>347</v>
       </c>
       <c r="K7" t="s">
-        <v>281</v>
+        <v>353</v>
       </c>
       <c r="L7" t="s">
-        <v>322</v>
+        <v>407</v>
       </c>
       <c r="M7" t="s">
-        <v>362</v>
+        <v>460</v>
       </c>
       <c r="O7" t="s">
-        <v>399</v>
+        <v>512</v>
       </c>
       <c r="P7" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="Q7" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="R7" t="s">
-        <v>414</v>
+        <v>529</v>
       </c>
       <c r="S7" t="s">
-        <v>453</v>
+        <v>581</v>
       </c>
       <c r="T7" t="s">
-        <v>466</v>
+        <v>597</v>
       </c>
       <c r="U7" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V7" t="s">
-        <v>494</v>
+        <v>630</v>
       </c>
       <c r="W7" t="s">
         <v>2</v>
       </c>
       <c r="X7" t="s">
-        <v>500</v>
+        <v>636</v>
       </c>
       <c r="Y7" t="s">
-        <v>536</v>
+        <v>685</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>688</v>
       </c>
       <c r="AA7" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="AB7" t="s">
-        <v>545</v>
+        <v>694</v>
       </c>
       <c r="AC7" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -2610,73 +3066,73 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="E8" t="s">
-        <v>158</v>
+        <v>197</v>
       </c>
       <c r="F8" t="s">
-        <v>189</v>
+        <v>239</v>
       </c>
       <c r="G8" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H8" t="s">
-        <v>218</v>
+        <v>273</v>
       </c>
       <c r="J8" t="s">
-        <v>275</v>
+        <v>346</v>
       </c>
       <c r="K8" t="s">
-        <v>282</v>
+        <v>354</v>
       </c>
       <c r="L8" t="s">
-        <v>323</v>
+        <v>408</v>
       </c>
       <c r="M8" t="s">
-        <v>363</v>
+        <v>461</v>
       </c>
       <c r="N8" t="s">
-        <v>398</v>
+        <v>509</v>
       </c>
       <c r="O8" t="s">
-        <v>400</v>
+        <v>511</v>
       </c>
       <c r="P8" t="s">
-        <v>402</v>
+        <v>516</v>
       </c>
       <c r="Q8" t="s">
-        <v>406</v>
+        <v>521</v>
       </c>
       <c r="R8" t="s">
-        <v>415</v>
+        <v>530</v>
       </c>
       <c r="S8" t="s">
-        <v>454</v>
+        <v>580</v>
       </c>
       <c r="U8" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="W8" t="s">
         <v>2</v>
       </c>
       <c r="X8" t="s">
-        <v>501</v>
+        <v>637</v>
       </c>
       <c r="AA8" t="s">
-        <v>406</v>
+        <v>521</v>
       </c>
       <c r="AB8" t="s">
-        <v>546</v>
+        <v>693</v>
       </c>
       <c r="AC8" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -2684,79 +3140,82 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="E9" t="s">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="F9" t="s">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="G9" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H9" t="s">
-        <v>219</v>
+        <v>274</v>
       </c>
       <c r="I9" t="s">
-        <v>255</v>
+        <v>323</v>
       </c>
       <c r="J9" t="s">
-        <v>275</v>
+        <v>347</v>
       </c>
       <c r="K9" t="s">
-        <v>283</v>
+        <v>355</v>
       </c>
       <c r="L9" t="s">
-        <v>324</v>
+        <v>409</v>
       </c>
       <c r="M9" t="s">
-        <v>364</v>
+        <v>462</v>
       </c>
       <c r="O9" t="s">
-        <v>399</v>
+        <v>512</v>
       </c>
       <c r="P9" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="Q9" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="R9" t="s">
-        <v>416</v>
+        <v>531</v>
       </c>
       <c r="S9" t="s">
-        <v>455</v>
+        <v>582</v>
       </c>
       <c r="T9" t="s">
-        <v>467</v>
+        <v>598</v>
       </c>
       <c r="U9" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V9" t="s">
-        <v>494</v>
+        <v>630</v>
       </c>
       <c r="W9" t="s">
         <v>2</v>
       </c>
       <c r="X9" t="s">
-        <v>502</v>
+        <v>638</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>685</v>
       </c>
       <c r="AA9" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="AB9" t="s">
-        <v>546</v>
+        <v>695</v>
       </c>
       <c r="AC9" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -2764,85 +3223,79 @@
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="E10" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="F10" t="s">
-        <v>191</v>
+        <v>240</v>
       </c>
       <c r="G10" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H10" t="s">
-        <v>220</v>
+        <v>275</v>
       </c>
       <c r="I10" t="s">
-        <v>256</v>
+        <v>324</v>
       </c>
       <c r="J10" t="s">
-        <v>275</v>
+        <v>347</v>
       </c>
       <c r="K10" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
       <c r="L10" t="s">
-        <v>325</v>
+        <v>410</v>
       </c>
       <c r="M10" t="s">
-        <v>365</v>
+        <v>463</v>
       </c>
       <c r="O10" t="s">
-        <v>399</v>
+        <v>512</v>
       </c>
       <c r="P10" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="Q10" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="R10" t="s">
-        <v>417</v>
+        <v>532</v>
       </c>
       <c r="S10" t="s">
-        <v>456</v>
+        <v>583</v>
       </c>
       <c r="T10" t="s">
-        <v>468</v>
+        <v>599</v>
       </c>
       <c r="U10" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V10" t="s">
-        <v>494</v>
+        <v>630</v>
       </c>
       <c r="W10" t="s">
         <v>2</v>
       </c>
       <c r="X10" t="s">
-        <v>503</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>536</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>539</v>
+        <v>639</v>
       </c>
       <c r="AA10" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="AB10" t="s">
-        <v>544</v>
+        <v>696</v>
       </c>
       <c r="AC10" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -2850,85 +3303,79 @@
         <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="E11" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="F11" t="s">
-        <v>192</v>
+        <v>241</v>
       </c>
       <c r="G11" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H11" t="s">
-        <v>221</v>
+        <v>276</v>
       </c>
       <c r="I11" t="s">
-        <v>257</v>
+        <v>325</v>
       </c>
       <c r="J11" t="s">
-        <v>275</v>
+        <v>347</v>
       </c>
       <c r="K11" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="L11" t="s">
-        <v>326</v>
+        <v>411</v>
       </c>
       <c r="M11" t="s">
-        <v>366</v>
+        <v>464</v>
       </c>
       <c r="O11" t="s">
-        <v>399</v>
+        <v>512</v>
       </c>
       <c r="P11" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="Q11" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="R11" t="s">
-        <v>418</v>
+        <v>533</v>
       </c>
       <c r="S11" t="s">
-        <v>457</v>
+        <v>584</v>
       </c>
       <c r="T11" t="s">
-        <v>469</v>
+        <v>600</v>
       </c>
       <c r="U11" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V11" t="s">
-        <v>494</v>
+        <v>629</v>
       </c>
       <c r="W11" t="s">
         <v>2</v>
       </c>
       <c r="X11" t="s">
-        <v>504</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>536</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>540</v>
+        <v>640</v>
       </c>
       <c r="AA11" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="AB11" t="s">
-        <v>545</v>
+        <v>697</v>
       </c>
       <c r="AC11" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -2936,79 +3383,85 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="E12" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="F12" t="s">
-        <v>193</v>
+        <v>242</v>
       </c>
       <c r="G12" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H12" t="s">
-        <v>222</v>
+        <v>277</v>
       </c>
       <c r="I12" t="s">
-        <v>258</v>
+        <v>326</v>
       </c>
       <c r="J12" t="s">
-        <v>275</v>
+        <v>347</v>
       </c>
       <c r="K12" t="s">
-        <v>286</v>
+        <v>358</v>
       </c>
       <c r="L12" t="s">
-        <v>327</v>
+        <v>412</v>
       </c>
       <c r="M12" t="s">
-        <v>367</v>
+        <v>465</v>
       </c>
       <c r="O12" t="s">
-        <v>399</v>
+        <v>512</v>
       </c>
       <c r="P12" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="Q12" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="R12" t="s">
-        <v>419</v>
+        <v>534</v>
       </c>
       <c r="S12" t="s">
-        <v>454</v>
+        <v>585</v>
       </c>
       <c r="T12" t="s">
-        <v>470</v>
+        <v>601</v>
       </c>
       <c r="U12" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V12" t="s">
-        <v>493</v>
+        <v>630</v>
       </c>
       <c r="W12" t="s">
         <v>2</v>
       </c>
       <c r="X12" t="s">
-        <v>505</v>
+        <v>641</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>685</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>688</v>
       </c>
       <c r="AA12" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="AB12" t="s">
-        <v>547</v>
+        <v>694</v>
       </c>
       <c r="AC12" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -3016,82 +3469,79 @@
         <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="E13" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="F13" t="s">
-        <v>194</v>
+        <v>243</v>
       </c>
       <c r="G13" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H13" t="s">
-        <v>223</v>
+        <v>278</v>
       </c>
       <c r="I13" t="s">
-        <v>259</v>
+        <v>327</v>
       </c>
       <c r="J13" t="s">
-        <v>275</v>
+        <v>346</v>
       </c>
       <c r="K13" t="s">
-        <v>287</v>
+        <v>359</v>
       </c>
       <c r="L13" t="s">
-        <v>328</v>
+        <v>413</v>
       </c>
       <c r="M13" t="s">
-        <v>368</v>
+        <v>466</v>
       </c>
       <c r="O13" t="s">
-        <v>399</v>
+        <v>512</v>
       </c>
       <c r="P13" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="Q13" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="R13" t="s">
-        <v>420</v>
+        <v>535</v>
       </c>
       <c r="S13" t="s">
-        <v>454</v>
+        <v>584</v>
       </c>
       <c r="T13" t="s">
-        <v>471</v>
+        <v>602</v>
       </c>
       <c r="U13" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V13" t="s">
-        <v>494</v>
+        <v>629</v>
       </c>
       <c r="W13" t="s">
         <v>2</v>
       </c>
       <c r="X13" t="s">
-        <v>506</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>538</v>
+        <v>642</v>
       </c>
       <c r="AA13" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="AB13" t="s">
-        <v>543</v>
+        <v>697</v>
       </c>
       <c r="AC13" t="s">
-        <v>548</v>
+        <v>699</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -3099,79 +3549,73 @@
         <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="E14" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="F14" t="s">
-        <v>195</v>
+        <v>244</v>
       </c>
       <c r="G14" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H14" t="s">
-        <v>224</v>
-      </c>
-      <c r="I14" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="J14" t="s">
-        <v>274</v>
+        <v>347</v>
       </c>
       <c r="K14" t="s">
-        <v>288</v>
+        <v>360</v>
       </c>
       <c r="L14" t="s">
-        <v>329</v>
+        <v>414</v>
       </c>
       <c r="M14" t="s">
-        <v>369</v>
+        <v>467</v>
+      </c>
+      <c r="N14" t="s">
+        <v>509</v>
       </c>
       <c r="O14" t="s">
-        <v>399</v>
+        <v>511</v>
       </c>
       <c r="P14" t="s">
-        <v>401</v>
+        <v>516</v>
       </c>
       <c r="Q14" t="s">
-        <v>405</v>
+        <v>521</v>
       </c>
       <c r="R14" t="s">
-        <v>421</v>
+        <v>536</v>
       </c>
       <c r="S14" t="s">
-        <v>454</v>
-      </c>
-      <c r="T14" t="s">
-        <v>472</v>
+        <v>584</v>
       </c>
       <c r="U14" t="s">
-        <v>493</v>
-      </c>
-      <c r="V14" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="W14" t="s">
         <v>2</v>
       </c>
       <c r="X14" t="s">
-        <v>507</v>
+        <v>643</v>
       </c>
       <c r="AA14" t="s">
-        <v>405</v>
+        <v>521</v>
       </c>
       <c r="AB14" t="s">
-        <v>547</v>
+        <v>696</v>
       </c>
       <c r="AC14" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -3179,82 +3623,82 @@
         <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="E15" t="s">
-        <v>165</v>
+        <v>204</v>
       </c>
       <c r="F15" t="s">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="G15" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H15" t="s">
-        <v>225</v>
+        <v>280</v>
       </c>
       <c r="I15" t="s">
-        <v>259</v>
+        <v>328</v>
       </c>
       <c r="J15" t="s">
-        <v>274</v>
+        <v>347</v>
       </c>
       <c r="K15" t="s">
-        <v>289</v>
+        <v>361</v>
       </c>
       <c r="L15" t="s">
-        <v>330</v>
+        <v>415</v>
       </c>
       <c r="M15" t="s">
-        <v>370</v>
+        <v>468</v>
       </c>
       <c r="O15" t="s">
-        <v>399</v>
+        <v>512</v>
       </c>
       <c r="P15" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="Q15" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="R15" t="s">
-        <v>422</v>
+        <v>537</v>
       </c>
       <c r="S15" t="s">
-        <v>454</v>
+        <v>584</v>
       </c>
       <c r="T15" t="s">
-        <v>473</v>
+        <v>603</v>
       </c>
       <c r="U15" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V15" t="s">
-        <v>494</v>
+        <v>630</v>
       </c>
       <c r="W15" t="s">
         <v>2</v>
       </c>
       <c r="X15" t="s">
-        <v>508</v>
+        <v>644</v>
       </c>
       <c r="Y15" t="s">
-        <v>538</v>
+        <v>687</v>
       </c>
       <c r="AA15" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="AB15" t="s">
-        <v>547</v>
+        <v>692</v>
       </c>
       <c r="AC15" t="s">
-        <v>549</v>
+        <v>698</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -3262,85 +3706,73 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="E16" t="s">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="F16" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G16" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H16" t="s">
-        <v>226</v>
-      </c>
-      <c r="I16" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J16" t="s">
-        <v>274</v>
+        <v>346</v>
       </c>
       <c r="K16" t="s">
-        <v>290</v>
+        <v>362</v>
       </c>
       <c r="L16" t="s">
-        <v>331</v>
+        <v>416</v>
       </c>
       <c r="M16" t="s">
-        <v>371</v>
+        <v>469</v>
+      </c>
+      <c r="N16" t="s">
+        <v>509</v>
       </c>
       <c r="O16" t="s">
-        <v>399</v>
+        <v>511</v>
       </c>
       <c r="P16" t="s">
-        <v>401</v>
+        <v>514</v>
       </c>
       <c r="Q16" t="s">
-        <v>405</v>
+        <v>519</v>
       </c>
       <c r="R16" t="s">
-        <v>423</v>
+        <v>538</v>
       </c>
       <c r="S16" t="s">
-        <v>456</v>
-      </c>
-      <c r="T16" t="s">
-        <v>474</v>
+        <v>582</v>
       </c>
       <c r="U16" t="s">
-        <v>493</v>
-      </c>
-      <c r="V16" t="s">
-        <v>494</v>
+        <v>629</v>
       </c>
       <c r="W16" t="s">
         <v>2</v>
       </c>
       <c r="X16" t="s">
-        <v>509</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>536</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>539</v>
+        <v>645</v>
       </c>
       <c r="AA16" t="s">
-        <v>405</v>
+        <v>519</v>
       </c>
       <c r="AB16" t="s">
-        <v>545</v>
+        <v>696</v>
       </c>
       <c r="AC16" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -3348,85 +3780,88 @@
         <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E17" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="F17" t="s">
-        <v>198</v>
+        <v>246</v>
       </c>
       <c r="G17" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H17" t="s">
-        <v>227</v>
+        <v>282</v>
       </c>
       <c r="I17" t="s">
-        <v>262</v>
+        <v>329</v>
       </c>
       <c r="J17" t="s">
-        <v>275</v>
+        <v>347</v>
       </c>
       <c r="K17" t="s">
-        <v>291</v>
+        <v>363</v>
       </c>
       <c r="L17" t="s">
-        <v>332</v>
+        <v>417</v>
       </c>
       <c r="M17" t="s">
-        <v>372</v>
+        <v>470</v>
+      </c>
+      <c r="N17" t="s">
+        <v>509</v>
       </c>
       <c r="O17" t="s">
-        <v>399</v>
+        <v>513</v>
       </c>
       <c r="P17" t="s">
-        <v>401</v>
+        <v>517</v>
       </c>
       <c r="Q17" t="s">
-        <v>405</v>
+        <v>522</v>
       </c>
       <c r="R17" t="s">
-        <v>424</v>
+        <v>539</v>
       </c>
       <c r="S17" t="s">
-        <v>452</v>
+        <v>586</v>
       </c>
       <c r="T17" t="s">
-        <v>475</v>
+        <v>604</v>
       </c>
       <c r="U17" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V17" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="W17" t="s">
         <v>2</v>
       </c>
       <c r="X17" t="s">
-        <v>510</v>
+        <v>646</v>
       </c>
       <c r="Y17" t="s">
-        <v>536</v>
+        <v>685</v>
       </c>
       <c r="Z17" t="s">
-        <v>541</v>
+        <v>689</v>
       </c>
       <c r="AA17" t="s">
-        <v>405</v>
+        <v>522</v>
       </c>
       <c r="AB17" t="s">
-        <v>545</v>
+        <v>693</v>
       </c>
       <c r="AC17" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -3434,73 +3869,85 @@
         <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="E18" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="F18" t="s">
-        <v>157</v>
+        <v>247</v>
       </c>
       <c r="G18" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H18" t="s">
-        <v>228</v>
+        <v>283</v>
+      </c>
+      <c r="I18" t="s">
+        <v>330</v>
       </c>
       <c r="J18" t="s">
-        <v>275</v>
+        <v>347</v>
       </c>
       <c r="K18" t="s">
-        <v>292</v>
+        <v>364</v>
       </c>
       <c r="L18" t="s">
-        <v>333</v>
+        <v>418</v>
       </c>
       <c r="M18" t="s">
-        <v>373</v>
-      </c>
-      <c r="N18" t="s">
-        <v>398</v>
+        <v>471</v>
       </c>
       <c r="O18" t="s">
-        <v>400</v>
+        <v>512</v>
       </c>
       <c r="P18" t="s">
-        <v>403</v>
+        <v>515</v>
       </c>
       <c r="Q18" t="s">
-        <v>407</v>
+        <v>520</v>
       </c>
       <c r="R18" t="s">
-        <v>425</v>
+        <v>540</v>
       </c>
       <c r="S18" t="s">
-        <v>458</v>
+        <v>587</v>
+      </c>
+      <c r="T18" t="s">
+        <v>605</v>
       </c>
       <c r="U18" t="s">
-        <v>493</v>
+        <v>629</v>
+      </c>
+      <c r="V18" t="s">
+        <v>630</v>
       </c>
       <c r="W18" t="s">
         <v>2</v>
       </c>
       <c r="X18" t="s">
-        <v>511</v>
+        <v>647</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>685</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>689</v>
       </c>
       <c r="AA18" t="s">
-        <v>407</v>
+        <v>520</v>
       </c>
       <c r="AB18" t="s">
-        <v>546</v>
+        <v>695</v>
       </c>
       <c r="AC18" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -3508,79 +3955,85 @@
         <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="E19" t="s">
-        <v>157</v>
+        <v>208</v>
       </c>
       <c r="F19" t="s">
-        <v>199</v>
+        <v>248</v>
       </c>
       <c r="G19" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H19" t="s">
-        <v>229</v>
+        <v>284</v>
       </c>
       <c r="I19" t="s">
-        <v>263</v>
+        <v>331</v>
       </c>
       <c r="J19" t="s">
-        <v>275</v>
+        <v>347</v>
       </c>
       <c r="K19" t="s">
-        <v>293</v>
+        <v>365</v>
       </c>
       <c r="L19" t="s">
-        <v>334</v>
+        <v>419</v>
       </c>
       <c r="M19" t="s">
-        <v>374</v>
+        <v>472</v>
       </c>
       <c r="O19" t="s">
-        <v>399</v>
+        <v>512</v>
       </c>
       <c r="P19" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="Q19" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="R19" t="s">
-        <v>426</v>
+        <v>541</v>
       </c>
       <c r="S19" t="s">
-        <v>458</v>
+        <v>581</v>
       </c>
       <c r="T19" t="s">
-        <v>476</v>
+        <v>606</v>
       </c>
       <c r="U19" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V19" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="W19" t="s">
         <v>2</v>
       </c>
       <c r="X19" t="s">
-        <v>512</v>
+        <v>648</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>685</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>690</v>
       </c>
       <c r="AA19" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="AB19" t="s">
-        <v>546</v>
+        <v>695</v>
       </c>
       <c r="AC19" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -3588,79 +4041,79 @@
         <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="E20" t="s">
-        <v>157</v>
+        <v>209</v>
       </c>
       <c r="F20" t="s">
-        <v>157</v>
+        <v>249</v>
       </c>
       <c r="G20" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H20" t="s">
-        <v>230</v>
+        <v>285</v>
       </c>
       <c r="I20" t="s">
-        <v>264</v>
+        <v>332</v>
       </c>
       <c r="J20" t="s">
-        <v>274</v>
+        <v>346</v>
       </c>
       <c r="K20" t="s">
-        <v>294</v>
+        <v>366</v>
       </c>
       <c r="L20" t="s">
-        <v>335</v>
+        <v>420</v>
       </c>
       <c r="M20" t="s">
-        <v>375</v>
+        <v>473</v>
       </c>
       <c r="O20" t="s">
-        <v>399</v>
+        <v>512</v>
       </c>
       <c r="P20" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="Q20" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="R20" t="s">
-        <v>427</v>
+        <v>542</v>
       </c>
       <c r="S20" t="s">
-        <v>453</v>
+        <v>582</v>
       </c>
       <c r="T20" t="s">
-        <v>477</v>
+        <v>607</v>
       </c>
       <c r="U20" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V20" t="s">
-        <v>493</v>
+        <v>630</v>
       </c>
       <c r="W20" t="s">
         <v>2</v>
       </c>
       <c r="X20" t="s">
-        <v>513</v>
+        <v>649</v>
       </c>
       <c r="AA20" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="AB20" t="s">
-        <v>546</v>
+        <v>696</v>
       </c>
       <c r="AC20" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -3668,79 +4121,82 @@
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="E21" t="s">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="F21" t="s">
-        <v>195</v>
+        <v>250</v>
       </c>
       <c r="G21" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H21" t="s">
-        <v>231</v>
+        <v>286</v>
       </c>
       <c r="I21" t="s">
-        <v>264</v>
+        <v>325</v>
       </c>
       <c r="J21" t="s">
-        <v>275</v>
+        <v>346</v>
       </c>
       <c r="K21" t="s">
-        <v>295</v>
+        <v>367</v>
       </c>
       <c r="L21" t="s">
-        <v>336</v>
+        <v>421</v>
       </c>
       <c r="M21" t="s">
-        <v>376</v>
+        <v>474</v>
       </c>
       <c r="O21" t="s">
-        <v>399</v>
+        <v>512</v>
       </c>
       <c r="P21" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="Q21" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="R21" t="s">
-        <v>428</v>
+        <v>543</v>
       </c>
       <c r="S21" t="s">
-        <v>453</v>
+        <v>580</v>
       </c>
       <c r="T21" t="s">
-        <v>478</v>
+        <v>608</v>
       </c>
       <c r="U21" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V21" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="W21" t="s">
         <v>2</v>
       </c>
       <c r="X21" t="s">
-        <v>514</v>
+        <v>650</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>687</v>
       </c>
       <c r="AA21" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="AB21" t="s">
-        <v>546</v>
+        <v>694</v>
       </c>
       <c r="AC21" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -3748,79 +4204,73 @@
         <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D22" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="E22" t="s">
-        <v>170</v>
+        <v>211</v>
       </c>
       <c r="F22" t="s">
-        <v>195</v>
+        <v>251</v>
       </c>
       <c r="G22" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H22" t="s">
-        <v>232</v>
-      </c>
-      <c r="I22" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="J22" t="s">
-        <v>274</v>
+        <v>346</v>
       </c>
       <c r="K22" t="s">
-        <v>296</v>
+        <v>368</v>
       </c>
       <c r="L22" t="s">
-        <v>337</v>
+        <v>422</v>
       </c>
       <c r="M22" t="s">
-        <v>377</v>
+        <v>475</v>
+      </c>
+      <c r="N22" t="s">
+        <v>509</v>
       </c>
       <c r="O22" t="s">
-        <v>399</v>
+        <v>511</v>
       </c>
       <c r="P22" t="s">
-        <v>401</v>
+        <v>516</v>
       </c>
       <c r="Q22" t="s">
-        <v>405</v>
+        <v>521</v>
       </c>
       <c r="R22" t="s">
-        <v>429</v>
+        <v>544</v>
       </c>
       <c r="S22" t="s">
-        <v>453</v>
-      </c>
-      <c r="T22" t="s">
-        <v>479</v>
+        <v>582</v>
       </c>
       <c r="U22" t="s">
-        <v>493</v>
-      </c>
-      <c r="V22" t="s">
-        <v>493</v>
+        <v>630</v>
       </c>
       <c r="W22" t="s">
         <v>2</v>
       </c>
       <c r="X22" t="s">
-        <v>515</v>
+        <v>651</v>
       </c>
       <c r="AA22" t="s">
-        <v>405</v>
+        <v>521</v>
       </c>
       <c r="AB22" t="s">
-        <v>546</v>
+        <v>696</v>
       </c>
       <c r="AC22" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -3828,73 +4278,82 @@
         <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="E23" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="F23" t="s">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="G23" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H23" t="s">
-        <v>233</v>
+        <v>288</v>
+      </c>
+      <c r="I23" t="s">
+        <v>328</v>
       </c>
       <c r="J23" t="s">
-        <v>274</v>
+        <v>346</v>
       </c>
       <c r="K23" t="s">
-        <v>297</v>
+        <v>369</v>
       </c>
       <c r="L23" t="s">
-        <v>338</v>
+        <v>423</v>
       </c>
       <c r="M23" t="s">
-        <v>378</v>
-      </c>
-      <c r="N23" t="s">
-        <v>398</v>
+        <v>476</v>
       </c>
       <c r="O23" t="s">
-        <v>400</v>
+        <v>512</v>
       </c>
       <c r="P23" t="s">
-        <v>404</v>
+        <v>515</v>
       </c>
       <c r="Q23" t="s">
-        <v>408</v>
+        <v>520</v>
       </c>
       <c r="R23" t="s">
-        <v>430</v>
+        <v>545</v>
       </c>
       <c r="S23" t="s">
-        <v>459</v>
+        <v>584</v>
+      </c>
+      <c r="T23" t="s">
+        <v>609</v>
       </c>
       <c r="U23" t="s">
-        <v>494</v>
+        <v>629</v>
+      </c>
+      <c r="V23" t="s">
+        <v>630</v>
       </c>
       <c r="W23" t="s">
         <v>2</v>
       </c>
       <c r="X23" t="s">
-        <v>516</v>
+        <v>652</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>687</v>
       </c>
       <c r="AA23" t="s">
-        <v>542</v>
+        <v>520</v>
       </c>
       <c r="AB23" t="s">
-        <v>546</v>
+        <v>697</v>
       </c>
       <c r="AC23" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -3902,73 +4361,85 @@
         <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D24" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="E24" t="s">
-        <v>172</v>
+        <v>213</v>
       </c>
       <c r="F24" t="s">
-        <v>153</v>
+        <v>233</v>
       </c>
       <c r="G24" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H24" t="s">
-        <v>234</v>
+        <v>289</v>
+      </c>
+      <c r="I24" t="s">
+        <v>333</v>
       </c>
       <c r="J24" t="s">
-        <v>274</v>
+        <v>346</v>
       </c>
       <c r="K24" t="s">
-        <v>298</v>
+        <v>370</v>
       </c>
       <c r="L24" t="s">
-        <v>339</v>
+        <v>424</v>
       </c>
       <c r="M24" t="s">
-        <v>379</v>
-      </c>
-      <c r="N24" t="s">
-        <v>398</v>
+        <v>477</v>
       </c>
       <c r="O24" t="s">
-        <v>400</v>
+        <v>512</v>
       </c>
       <c r="P24" t="s">
-        <v>403</v>
+        <v>515</v>
       </c>
       <c r="Q24" t="s">
-        <v>407</v>
+        <v>520</v>
       </c>
       <c r="R24" t="s">
-        <v>431</v>
+        <v>546</v>
       </c>
       <c r="S24" t="s">
-        <v>453</v>
+        <v>585</v>
+      </c>
+      <c r="T24" t="s">
+        <v>610</v>
       </c>
       <c r="U24" t="s">
-        <v>493</v>
+        <v>629</v>
+      </c>
+      <c r="V24" t="s">
+        <v>630</v>
       </c>
       <c r="W24" t="s">
         <v>2</v>
       </c>
       <c r="X24" t="s">
-        <v>517</v>
+        <v>653</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>685</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>688</v>
       </c>
       <c r="AA24" t="s">
-        <v>407</v>
+        <v>520</v>
       </c>
       <c r="AB24" t="s">
-        <v>546</v>
+        <v>695</v>
       </c>
       <c r="AC24" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -3976,79 +4447,79 @@
         <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="E25" t="s">
-        <v>173</v>
+        <v>214</v>
       </c>
       <c r="F25" t="s">
-        <v>201</v>
+        <v>243</v>
       </c>
       <c r="G25" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H25" t="s">
-        <v>235</v>
+        <v>290</v>
       </c>
       <c r="I25" t="s">
-        <v>265</v>
+        <v>334</v>
       </c>
       <c r="J25" t="s">
-        <v>274</v>
+        <v>346</v>
       </c>
       <c r="K25" t="s">
-        <v>299</v>
+        <v>371</v>
       </c>
       <c r="L25" t="s">
-        <v>340</v>
+        <v>425</v>
       </c>
       <c r="M25" t="s">
-        <v>380</v>
+        <v>478</v>
       </c>
       <c r="O25" t="s">
-        <v>399</v>
+        <v>512</v>
       </c>
       <c r="P25" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="Q25" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="R25" t="s">
-        <v>432</v>
+        <v>547</v>
       </c>
       <c r="S25" t="s">
-        <v>453</v>
+        <v>582</v>
       </c>
       <c r="T25" t="s">
-        <v>480</v>
+        <v>611</v>
       </c>
       <c r="U25" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V25" t="s">
-        <v>494</v>
+        <v>629</v>
       </c>
       <c r="W25" t="s">
         <v>2</v>
       </c>
       <c r="X25" t="s">
-        <v>518</v>
+        <v>654</v>
       </c>
       <c r="AA25" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="AB25" t="s">
-        <v>546</v>
+        <v>696</v>
       </c>
       <c r="AC25" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -4056,79 +4527,73 @@
         <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="E26" t="s">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="F26" t="s">
-        <v>199</v>
+        <v>253</v>
       </c>
       <c r="G26" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H26" t="s">
-        <v>236</v>
-      </c>
-      <c r="I26" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="J26" t="s">
-        <v>275</v>
+        <v>346</v>
       </c>
       <c r="K26" t="s">
-        <v>300</v>
+        <v>372</v>
       </c>
       <c r="L26" t="s">
-        <v>341</v>
+        <v>426</v>
       </c>
       <c r="M26" t="s">
-        <v>381</v>
+        <v>479</v>
+      </c>
+      <c r="N26" t="s">
+        <v>509</v>
       </c>
       <c r="O26" t="s">
-        <v>399</v>
+        <v>511</v>
       </c>
       <c r="P26" t="s">
-        <v>401</v>
+        <v>518</v>
       </c>
       <c r="Q26" t="s">
-        <v>405</v>
+        <v>523</v>
       </c>
       <c r="R26" t="s">
-        <v>433</v>
+        <v>548</v>
       </c>
       <c r="S26" t="s">
-        <v>452</v>
-      </c>
-      <c r="T26" t="s">
-        <v>481</v>
+        <v>588</v>
       </c>
       <c r="U26" t="s">
-        <v>493</v>
-      </c>
-      <c r="V26" t="s">
-        <v>494</v>
+        <v>630</v>
       </c>
       <c r="W26" t="s">
         <v>2</v>
       </c>
       <c r="X26" t="s">
-        <v>519</v>
+        <v>655</v>
       </c>
       <c r="AA26" t="s">
-        <v>405</v>
+        <v>691</v>
       </c>
       <c r="AB26" t="s">
-        <v>545</v>
+        <v>696</v>
       </c>
       <c r="AC26" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -4136,79 +4601,73 @@
         <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="E27" t="s">
-        <v>157</v>
+        <v>216</v>
       </c>
       <c r="F27" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G27" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H27" t="s">
-        <v>237</v>
-      </c>
-      <c r="I27" t="s">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="J27" t="s">
-        <v>274</v>
+        <v>347</v>
       </c>
       <c r="K27" t="s">
-        <v>301</v>
+        <v>373</v>
       </c>
       <c r="L27" t="s">
-        <v>342</v>
+        <v>427</v>
       </c>
       <c r="M27" t="s">
-        <v>382</v>
+        <v>480</v>
+      </c>
+      <c r="N27" t="s">
+        <v>509</v>
       </c>
       <c r="O27" t="s">
-        <v>399</v>
+        <v>511</v>
       </c>
       <c r="P27" t="s">
-        <v>401</v>
+        <v>514</v>
       </c>
       <c r="Q27" t="s">
-        <v>405</v>
+        <v>519</v>
       </c>
       <c r="R27" t="s">
-        <v>434</v>
+        <v>549</v>
       </c>
       <c r="S27" t="s">
-        <v>453</v>
-      </c>
-      <c r="T27" t="s">
-        <v>482</v>
+        <v>589</v>
       </c>
       <c r="U27" t="s">
-        <v>493</v>
-      </c>
-      <c r="V27" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="W27" t="s">
         <v>2</v>
       </c>
       <c r="X27" t="s">
-        <v>520</v>
+        <v>656</v>
       </c>
       <c r="AA27" t="s">
-        <v>405</v>
+        <v>519</v>
       </c>
       <c r="AB27" t="s">
-        <v>544</v>
+        <v>696</v>
       </c>
       <c r="AC27" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -4216,79 +4675,79 @@
         <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="E28" t="s">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="F28" t="s">
-        <v>195</v>
+        <v>254</v>
       </c>
       <c r="G28" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H28" t="s">
-        <v>238</v>
+        <v>293</v>
       </c>
       <c r="I28" t="s">
-        <v>258</v>
+        <v>335</v>
       </c>
       <c r="J28" t="s">
-        <v>274</v>
+        <v>347</v>
       </c>
       <c r="K28" t="s">
-        <v>302</v>
+        <v>374</v>
       </c>
       <c r="L28" t="s">
-        <v>343</v>
+        <v>428</v>
       </c>
       <c r="M28" t="s">
-        <v>383</v>
+        <v>481</v>
       </c>
       <c r="O28" t="s">
-        <v>399</v>
+        <v>512</v>
       </c>
       <c r="P28" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="Q28" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="R28" t="s">
-        <v>435</v>
+        <v>550</v>
       </c>
       <c r="S28" t="s">
-        <v>452</v>
+        <v>581</v>
       </c>
       <c r="T28" t="s">
-        <v>483</v>
+        <v>612</v>
       </c>
       <c r="U28" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V28" t="s">
-        <v>494</v>
+        <v>630</v>
       </c>
       <c r="W28" t="s">
         <v>2</v>
       </c>
       <c r="X28" t="s">
-        <v>521</v>
+        <v>657</v>
       </c>
       <c r="AA28" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="AB28" t="s">
-        <v>544</v>
+        <v>695</v>
       </c>
       <c r="AC28" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -4296,73 +4755,79 @@
         <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D29" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="E29" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="F29" t="s">
-        <v>203</v>
+        <v>254</v>
       </c>
       <c r="G29" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H29" t="s">
-        <v>239</v>
+        <v>294</v>
+      </c>
+      <c r="I29" t="s">
+        <v>336</v>
       </c>
       <c r="J29" t="s">
-        <v>274</v>
+        <v>347</v>
       </c>
       <c r="K29" t="s">
-        <v>303</v>
+        <v>375</v>
       </c>
       <c r="L29" t="s">
-        <v>344</v>
+        <v>429</v>
       </c>
       <c r="M29" t="s">
-        <v>384</v>
-      </c>
-      <c r="N29" t="s">
-        <v>398</v>
+        <v>482</v>
       </c>
       <c r="O29" t="s">
-        <v>400</v>
+        <v>512</v>
       </c>
       <c r="P29" t="s">
-        <v>403</v>
+        <v>515</v>
       </c>
       <c r="Q29" t="s">
-        <v>407</v>
+        <v>520</v>
       </c>
       <c r="R29" t="s">
-        <v>436</v>
+        <v>551</v>
       </c>
       <c r="S29" t="s">
-        <v>450</v>
+        <v>589</v>
+      </c>
+      <c r="T29" t="s">
+        <v>613</v>
       </c>
       <c r="U29" t="s">
-        <v>494</v>
+        <v>629</v>
+      </c>
+      <c r="V29" t="s">
+        <v>629</v>
       </c>
       <c r="W29" t="s">
         <v>2</v>
       </c>
       <c r="X29" t="s">
-        <v>522</v>
+        <v>658</v>
       </c>
       <c r="AA29" t="s">
-        <v>407</v>
+        <v>520</v>
       </c>
       <c r="AB29" t="s">
-        <v>543</v>
+        <v>696</v>
       </c>
       <c r="AC29" t="s">
-        <v>548</v>
+        <v>699</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -4370,73 +4835,79 @@
         <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="C30" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="E30" t="s">
-        <v>177</v>
+        <v>217</v>
       </c>
       <c r="F30" t="s">
-        <v>204</v>
+        <v>243</v>
       </c>
       <c r="G30" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H30" t="s">
-        <v>240</v>
+        <v>295</v>
+      </c>
+      <c r="I30" t="s">
+        <v>325</v>
       </c>
       <c r="J30" t="s">
-        <v>274</v>
+        <v>347</v>
       </c>
       <c r="K30" t="s">
-        <v>304</v>
+        <v>376</v>
       </c>
       <c r="L30" t="s">
-        <v>345</v>
+        <v>430</v>
       </c>
       <c r="M30" t="s">
-        <v>385</v>
-      </c>
-      <c r="N30" t="s">
-        <v>398</v>
+        <v>483</v>
       </c>
       <c r="O30" t="s">
-        <v>400</v>
+        <v>512</v>
       </c>
       <c r="P30" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="Q30" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
       <c r="R30" t="s">
-        <v>437</v>
+        <v>552</v>
       </c>
       <c r="S30" t="s">
-        <v>452</v>
+        <v>590</v>
+      </c>
+      <c r="T30" t="s">
+        <v>614</v>
       </c>
       <c r="U30" t="s">
-        <v>494</v>
+        <v>629</v>
+      </c>
+      <c r="V30" t="s">
+        <v>630</v>
       </c>
       <c r="W30" t="s">
         <v>2</v>
       </c>
       <c r="X30" t="s">
-        <v>523</v>
+        <v>659</v>
       </c>
       <c r="AA30" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
       <c r="AB30" t="s">
-        <v>546</v>
+        <v>694</v>
       </c>
       <c r="AC30" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -4444,73 +4915,79 @@
         <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D31" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="E31" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="F31" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="G31" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H31" t="s">
-        <v>241</v>
+        <v>296</v>
+      </c>
+      <c r="I31" t="s">
+        <v>334</v>
       </c>
       <c r="J31" t="s">
-        <v>274</v>
+        <v>346</v>
       </c>
       <c r="K31" t="s">
-        <v>305</v>
+        <v>377</v>
       </c>
       <c r="L31" t="s">
-        <v>346</v>
+        <v>431</v>
       </c>
       <c r="M31" t="s">
-        <v>386</v>
-      </c>
-      <c r="N31" t="s">
-        <v>398</v>
+        <v>484</v>
       </c>
       <c r="O31" t="s">
-        <v>400</v>
+        <v>512</v>
       </c>
       <c r="P31" t="s">
-        <v>402</v>
+        <v>515</v>
       </c>
       <c r="Q31" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
       <c r="R31" t="s">
-        <v>438</v>
+        <v>553</v>
       </c>
       <c r="S31" t="s">
-        <v>453</v>
+        <v>582</v>
+      </c>
+      <c r="T31" t="s">
+        <v>615</v>
       </c>
       <c r="U31" t="s">
-        <v>494</v>
+        <v>629</v>
+      </c>
+      <c r="V31" t="s">
+        <v>629</v>
       </c>
       <c r="W31" t="s">
         <v>2</v>
       </c>
       <c r="X31" t="s">
-        <v>524</v>
+        <v>660</v>
       </c>
       <c r="AA31" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
       <c r="AB31" t="s">
-        <v>546</v>
+        <v>696</v>
       </c>
       <c r="AC31" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -4518,79 +4995,82 @@
         <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C32" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="E32" t="s">
-        <v>178</v>
+        <v>218</v>
       </c>
       <c r="F32" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="G32" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H32" t="s">
-        <v>242</v>
+        <v>297</v>
       </c>
       <c r="I32" t="s">
-        <v>258</v>
+        <v>337</v>
       </c>
       <c r="J32" t="s">
-        <v>275</v>
+        <v>347</v>
       </c>
       <c r="K32" t="s">
-        <v>306</v>
+        <v>378</v>
       </c>
       <c r="L32" t="s">
-        <v>347</v>
+        <v>432</v>
       </c>
       <c r="M32" t="s">
-        <v>387</v>
+        <v>485</v>
       </c>
       <c r="O32" t="s">
-        <v>399</v>
+        <v>512</v>
       </c>
       <c r="P32" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="Q32" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="R32" t="s">
-        <v>439</v>
+        <v>554</v>
       </c>
       <c r="S32" t="s">
-        <v>460</v>
+        <v>591</v>
       </c>
       <c r="T32" t="s">
-        <v>484</v>
+        <v>616</v>
       </c>
       <c r="U32" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V32" t="s">
-        <v>494</v>
+        <v>630</v>
       </c>
       <c r="W32" t="s">
         <v>2</v>
       </c>
       <c r="X32" t="s">
-        <v>525</v>
+        <v>661</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>687</v>
       </c>
       <c r="AA32" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="AB32" t="s">
-        <v>544</v>
+        <v>693</v>
       </c>
       <c r="AC32" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -4598,82 +5078,73 @@
         <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C33" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D33" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="E33" t="s">
-        <v>179</v>
+        <v>219</v>
       </c>
       <c r="F33" t="s">
-        <v>206</v>
+        <v>256</v>
       </c>
       <c r="G33" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H33" t="s">
-        <v>243</v>
-      </c>
-      <c r="I33" t="s">
-        <v>258</v>
+        <v>298</v>
       </c>
       <c r="J33" t="s">
-        <v>274</v>
+        <v>346</v>
       </c>
       <c r="K33" t="s">
-        <v>307</v>
+        <v>379</v>
       </c>
       <c r="L33" t="s">
-        <v>348</v>
+        <v>433</v>
       </c>
       <c r="M33" t="s">
-        <v>388</v>
+        <v>486</v>
+      </c>
+      <c r="N33" t="s">
+        <v>509</v>
       </c>
       <c r="O33" t="s">
-        <v>399</v>
+        <v>511</v>
       </c>
       <c r="P33" t="s">
-        <v>401</v>
+        <v>516</v>
       </c>
       <c r="Q33" t="s">
-        <v>405</v>
+        <v>521</v>
       </c>
       <c r="R33" t="s">
-        <v>440</v>
+        <v>555</v>
       </c>
       <c r="S33" t="s">
-        <v>451</v>
-      </c>
-      <c r="T33" t="s">
-        <v>485</v>
+        <v>581</v>
       </c>
       <c r="U33" t="s">
-        <v>493</v>
-      </c>
-      <c r="V33" t="s">
-        <v>493</v>
+        <v>630</v>
       </c>
       <c r="W33" t="s">
         <v>2</v>
       </c>
       <c r="X33" t="s">
-        <v>526</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>538</v>
+        <v>662</v>
       </c>
       <c r="AA33" t="s">
-        <v>405</v>
+        <v>521</v>
       </c>
       <c r="AB33" t="s">
-        <v>544</v>
+        <v>696</v>
       </c>
       <c r="AC33" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -4681,79 +5152,79 @@
         <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C34" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D34" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="E34" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="F34" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G34" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H34" t="s">
-        <v>244</v>
+        <v>299</v>
       </c>
       <c r="I34" t="s">
-        <v>258</v>
+        <v>338</v>
       </c>
       <c r="J34" t="s">
-        <v>275</v>
+        <v>347</v>
       </c>
       <c r="K34" t="s">
-        <v>308</v>
+        <v>380</v>
       </c>
       <c r="L34" t="s">
-        <v>349</v>
+        <v>434</v>
       </c>
       <c r="M34" t="s">
-        <v>389</v>
+        <v>487</v>
       </c>
       <c r="O34" t="s">
-        <v>399</v>
+        <v>512</v>
       </c>
       <c r="P34" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="Q34" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="R34" t="s">
-        <v>441</v>
+        <v>556</v>
       </c>
       <c r="S34" t="s">
-        <v>461</v>
+        <v>590</v>
       </c>
       <c r="T34" t="s">
-        <v>486</v>
+        <v>617</v>
       </c>
       <c r="U34" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V34" t="s">
-        <v>494</v>
+        <v>630</v>
       </c>
       <c r="W34" t="s">
         <v>2</v>
       </c>
       <c r="X34" t="s">
-        <v>527</v>
+        <v>663</v>
       </c>
       <c r="AA34" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="AB34" t="s">
-        <v>544</v>
+        <v>693</v>
       </c>
       <c r="AC34" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -4761,79 +5232,79 @@
         <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C35" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D35" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="E35" t="s">
-        <v>157</v>
+        <v>198</v>
       </c>
       <c r="F35" t="s">
-        <v>157</v>
+        <v>257</v>
       </c>
       <c r="G35" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H35" t="s">
-        <v>245</v>
+        <v>300</v>
       </c>
       <c r="I35" t="s">
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="J35" t="s">
-        <v>275</v>
+        <v>346</v>
       </c>
       <c r="K35" t="s">
-        <v>309</v>
+        <v>381</v>
       </c>
       <c r="L35" t="s">
-        <v>350</v>
+        <v>435</v>
       </c>
       <c r="M35" t="s">
-        <v>390</v>
+        <v>488</v>
       </c>
       <c r="O35" t="s">
-        <v>399</v>
+        <v>512</v>
       </c>
       <c r="P35" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="Q35" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="R35" t="s">
-        <v>442</v>
+        <v>557</v>
       </c>
       <c r="S35" t="s">
-        <v>461</v>
+        <v>582</v>
       </c>
       <c r="T35" t="s">
-        <v>487</v>
+        <v>618</v>
       </c>
       <c r="U35" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V35" t="s">
-        <v>494</v>
+        <v>629</v>
       </c>
       <c r="W35" t="s">
         <v>2</v>
       </c>
       <c r="X35" t="s">
-        <v>528</v>
+        <v>664</v>
       </c>
       <c r="AA35" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="AB35" t="s">
-        <v>543</v>
+        <v>694</v>
       </c>
       <c r="AC35" t="s">
-        <v>548</v>
+        <v>699</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -4841,76 +5312,79 @@
         <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C36" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="E36" t="s">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="F36" t="s">
-        <v>195</v>
+        <v>243</v>
       </c>
       <c r="G36" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H36" t="s">
-        <v>246</v>
+        <v>301</v>
+      </c>
+      <c r="I36" t="s">
+        <v>334</v>
       </c>
       <c r="J36" t="s">
-        <v>274</v>
+        <v>347</v>
       </c>
       <c r="K36" t="s">
-        <v>310</v>
+        <v>382</v>
+      </c>
+      <c r="L36" t="s">
+        <v>436</v>
       </c>
       <c r="M36" t="s">
-        <v>391</v>
-      </c>
-      <c r="N36" t="s">
-        <v>398</v>
+        <v>489</v>
       </c>
       <c r="O36" t="s">
-        <v>400</v>
+        <v>512</v>
       </c>
       <c r="P36" t="s">
-        <v>403</v>
+        <v>515</v>
       </c>
       <c r="Q36" t="s">
-        <v>407</v>
+        <v>520</v>
       </c>
       <c r="R36" t="s">
-        <v>443</v>
+        <v>558</v>
       </c>
       <c r="S36" t="s">
-        <v>460</v>
+        <v>582</v>
+      </c>
+      <c r="T36" t="s">
+        <v>619</v>
       </c>
       <c r="U36" t="s">
-        <v>493</v>
+        <v>629</v>
+      </c>
+      <c r="V36" t="s">
+        <v>629</v>
       </c>
       <c r="W36" t="s">
         <v>2</v>
       </c>
       <c r="X36" t="s">
-        <v>529</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>536</v>
-      </c>
-      <c r="Z36" t="s">
-        <v>539</v>
+        <v>665</v>
       </c>
       <c r="AA36" t="s">
-        <v>407</v>
+        <v>520</v>
       </c>
       <c r="AB36" t="s">
-        <v>543</v>
+        <v>696</v>
       </c>
       <c r="AC36" t="s">
-        <v>548</v>
+        <v>699</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -4918,79 +5392,73 @@
         <v>64</v>
       </c>
       <c r="B37" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C37" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D37" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="E37" t="s">
-        <v>157</v>
+        <v>221</v>
       </c>
       <c r="F37" t="s">
-        <v>207</v>
+        <v>258</v>
       </c>
       <c r="G37" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H37" t="s">
-        <v>247</v>
-      </c>
-      <c r="I37" t="s">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="J37" t="s">
-        <v>274</v>
+        <v>347</v>
       </c>
       <c r="K37" t="s">
-        <v>311</v>
+        <v>383</v>
       </c>
       <c r="L37" t="s">
-        <v>351</v>
+        <v>437</v>
       </c>
       <c r="M37" t="s">
-        <v>392</v>
+        <v>490</v>
+      </c>
+      <c r="N37" t="s">
+        <v>509</v>
       </c>
       <c r="O37" t="s">
-        <v>399</v>
+        <v>511</v>
       </c>
       <c r="P37" t="s">
-        <v>401</v>
+        <v>514</v>
       </c>
       <c r="Q37" t="s">
-        <v>405</v>
+        <v>519</v>
       </c>
       <c r="R37" t="s">
-        <v>444</v>
+        <v>559</v>
       </c>
       <c r="S37" t="s">
-        <v>452</v>
-      </c>
-      <c r="T37" t="s">
-        <v>488</v>
+        <v>586</v>
       </c>
       <c r="U37" t="s">
-        <v>493</v>
-      </c>
-      <c r="V37" t="s">
-        <v>494</v>
+        <v>630</v>
       </c>
       <c r="W37" t="s">
         <v>2</v>
       </c>
       <c r="X37" t="s">
-        <v>530</v>
+        <v>666</v>
       </c>
       <c r="AA37" t="s">
-        <v>405</v>
+        <v>519</v>
       </c>
       <c r="AB37" t="s">
-        <v>546</v>
+        <v>694</v>
       </c>
       <c r="AC37" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -4998,82 +5466,73 @@
         <v>65</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C38" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D38" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="E38" t="s">
-        <v>182</v>
+        <v>222</v>
       </c>
       <c r="F38" t="s">
-        <v>178</v>
+        <v>255</v>
       </c>
       <c r="G38" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H38" t="s">
-        <v>248</v>
-      </c>
-      <c r="I38" t="s">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c r="J38" t="s">
-        <v>275</v>
+        <v>346</v>
       </c>
       <c r="K38" t="s">
-        <v>312</v>
+        <v>384</v>
       </c>
       <c r="L38" t="s">
-        <v>352</v>
+        <v>438</v>
       </c>
       <c r="M38" t="s">
-        <v>393</v>
+        <v>491</v>
+      </c>
+      <c r="N38" t="s">
+        <v>509</v>
       </c>
       <c r="O38" t="s">
-        <v>399</v>
+        <v>511</v>
       </c>
       <c r="P38" t="s">
-        <v>401</v>
+        <v>514</v>
       </c>
       <c r="Q38" t="s">
-        <v>405</v>
+        <v>519</v>
       </c>
       <c r="R38" t="s">
-        <v>445</v>
+        <v>560</v>
       </c>
       <c r="S38" t="s">
-        <v>460</v>
-      </c>
-      <c r="T38" t="s">
-        <v>489</v>
+        <v>586</v>
       </c>
       <c r="U38" t="s">
-        <v>493</v>
-      </c>
-      <c r="V38" t="s">
-        <v>494</v>
+        <v>629</v>
       </c>
       <c r="W38" t="s">
         <v>2</v>
       </c>
       <c r="X38" t="s">
-        <v>531</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>538</v>
+        <v>667</v>
       </c>
       <c r="AA38" t="s">
-        <v>405</v>
+        <v>519</v>
       </c>
       <c r="AB38" t="s">
-        <v>543</v>
+        <v>694</v>
       </c>
       <c r="AC38" t="s">
-        <v>548</v>
+        <v>699</v>
       </c>
     </row>
     <row r="39" spans="1:29">
@@ -5081,79 +5540,76 @@
         <v>66</v>
       </c>
       <c r="B39" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="C39" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D39" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="E39" t="s">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="F39" t="s">
-        <v>176</v>
+        <v>243</v>
       </c>
       <c r="G39" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H39" t="s">
-        <v>249</v>
-      </c>
-      <c r="I39" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="J39" t="s">
-        <v>275</v>
+        <v>346</v>
       </c>
       <c r="K39" t="s">
-        <v>313</v>
-      </c>
-      <c r="L39" t="s">
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="M39" t="s">
-        <v>394</v>
+        <v>492</v>
+      </c>
+      <c r="N39" t="s">
+        <v>509</v>
       </c>
       <c r="O39" t="s">
-        <v>399</v>
+        <v>511</v>
       </c>
       <c r="P39" t="s">
-        <v>401</v>
+        <v>514</v>
       </c>
       <c r="Q39" t="s">
-        <v>405</v>
+        <v>519</v>
       </c>
       <c r="R39" t="s">
-        <v>446</v>
+        <v>561</v>
       </c>
       <c r="S39" t="s">
-        <v>451</v>
-      </c>
-      <c r="T39" t="s">
-        <v>490</v>
+        <v>591</v>
       </c>
       <c r="U39" t="s">
-        <v>493</v>
-      </c>
-      <c r="V39" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="W39" t="s">
         <v>2</v>
       </c>
       <c r="X39" t="s">
-        <v>532</v>
+        <v>668</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>685</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>688</v>
       </c>
       <c r="AA39" t="s">
-        <v>405</v>
+        <v>519</v>
       </c>
       <c r="AB39" t="s">
-        <v>544</v>
+        <v>692</v>
       </c>
       <c r="AC39" t="s">
-        <v>549</v>
+        <v>698</v>
       </c>
     </row>
     <row r="40" spans="1:29">
@@ -5161,82 +5617,79 @@
         <v>67</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D40" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="E40" t="s">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="F40" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="G40" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H40" t="s">
-        <v>250</v>
+        <v>305</v>
       </c>
       <c r="I40" t="s">
-        <v>272</v>
+        <v>340</v>
       </c>
       <c r="J40" t="s">
-        <v>275</v>
+        <v>347</v>
       </c>
       <c r="K40" t="s">
-        <v>314</v>
+        <v>386</v>
       </c>
       <c r="L40" t="s">
-        <v>354</v>
+        <v>439</v>
       </c>
       <c r="M40" t="s">
-        <v>395</v>
+        <v>493</v>
       </c>
       <c r="O40" t="s">
-        <v>399</v>
+        <v>512</v>
       </c>
       <c r="P40" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="Q40" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="R40" t="s">
-        <v>447</v>
+        <v>562</v>
       </c>
       <c r="S40" t="s">
-        <v>460</v>
+        <v>580</v>
       </c>
       <c r="T40" t="s">
-        <v>491</v>
+        <v>620</v>
       </c>
       <c r="U40" t="s">
-        <v>493</v>
+        <v>629</v>
       </c>
       <c r="V40" t="s">
-        <v>494</v>
+        <v>629</v>
       </c>
       <c r="W40" t="s">
         <v>2</v>
       </c>
       <c r="X40" t="s">
-        <v>533</v>
-      </c>
-      <c r="Y40" t="s">
-        <v>538</v>
+        <v>669</v>
       </c>
       <c r="AA40" t="s">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="AB40" t="s">
-        <v>543</v>
+        <v>694</v>
       </c>
       <c r="AC40" t="s">
-        <v>548</v>
+        <v>699</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -5244,73 +5697,79 @@
         <v>68</v>
       </c>
       <c r="B41" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="C41" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D41" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="E41" t="s">
-        <v>178</v>
+        <v>224</v>
       </c>
       <c r="F41" t="s">
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="G41" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H41" t="s">
-        <v>251</v>
+        <v>306</v>
+      </c>
+      <c r="I41" t="s">
+        <v>325</v>
       </c>
       <c r="J41" t="s">
-        <v>274</v>
+        <v>346</v>
       </c>
       <c r="K41" t="s">
-        <v>315</v>
+        <v>387</v>
       </c>
       <c r="L41" t="s">
-        <v>355</v>
+        <v>440</v>
       </c>
       <c r="M41" t="s">
-        <v>396</v>
-      </c>
-      <c r="N41" t="s">
-        <v>398</v>
+        <v>494</v>
       </c>
       <c r="O41" t="s">
-        <v>400</v>
+        <v>512</v>
       </c>
       <c r="P41" t="s">
-        <v>403</v>
+        <v>515</v>
       </c>
       <c r="Q41" t="s">
-        <v>407</v>
+        <v>520</v>
       </c>
       <c r="R41" t="s">
-        <v>448</v>
+        <v>563</v>
       </c>
       <c r="S41" t="s">
-        <v>460</v>
+        <v>581</v>
+      </c>
+      <c r="T41" t="s">
+        <v>621</v>
       </c>
       <c r="U41" t="s">
-        <v>493</v>
+        <v>629</v>
+      </c>
+      <c r="V41" t="s">
+        <v>630</v>
       </c>
       <c r="W41" t="s">
         <v>2</v>
       </c>
       <c r="X41" t="s">
-        <v>534</v>
+        <v>670</v>
       </c>
       <c r="AA41" t="s">
-        <v>407</v>
+        <v>520</v>
       </c>
       <c r="AB41" t="s">
-        <v>544</v>
+        <v>694</v>
       </c>
       <c r="AC41" t="s">
-        <v>549</v>
+        <v>699</v>
       </c>
     </row>
     <row r="42" spans="1:29">
@@ -5318,79 +5777,1089 @@
         <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D42" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="E42" t="s">
-        <v>184</v>
+        <v>225</v>
       </c>
       <c r="F42" t="s">
-        <v>210</v>
+        <v>259</v>
       </c>
       <c r="G42" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="H42" t="s">
-        <v>252</v>
-      </c>
-      <c r="I42" t="s">
-        <v>273</v>
+        <v>307</v>
       </c>
       <c r="J42" t="s">
-        <v>275</v>
+        <v>346</v>
       </c>
       <c r="K42" t="s">
-        <v>316</v>
+        <v>388</v>
       </c>
       <c r="L42" t="s">
-        <v>356</v>
+        <v>441</v>
       </c>
       <c r="M42" t="s">
-        <v>397</v>
+        <v>495</v>
+      </c>
+      <c r="N42" t="s">
+        <v>509</v>
       </c>
       <c r="O42" t="s">
-        <v>399</v>
+        <v>511</v>
       </c>
       <c r="P42" t="s">
-        <v>401</v>
+        <v>514</v>
       </c>
       <c r="Q42" t="s">
-        <v>405</v>
+        <v>519</v>
       </c>
       <c r="R42" t="s">
-        <v>449</v>
+        <v>564</v>
       </c>
       <c r="S42" t="s">
-        <v>451</v>
-      </c>
-      <c r="T42" t="s">
-        <v>492</v>
+        <v>579</v>
       </c>
       <c r="U42" t="s">
-        <v>493</v>
-      </c>
-      <c r="V42" t="s">
-        <v>494</v>
+        <v>630</v>
       </c>
       <c r="W42" t="s">
         <v>2</v>
       </c>
       <c r="X42" t="s">
-        <v>535</v>
+        <v>671</v>
       </c>
       <c r="AA42" t="s">
-        <v>405</v>
+        <v>519</v>
       </c>
       <c r="AB42" t="s">
-        <v>544</v>
+        <v>693</v>
       </c>
       <c r="AC42" t="s">
-        <v>549</v>
+        <v>699</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29">
+      <c r="A43" t="s">
+        <v>70</v>
+      </c>
+      <c r="B43" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43" t="s">
+        <v>137</v>
+      </c>
+      <c r="D43" t="s">
+        <v>178</v>
+      </c>
+      <c r="E43" t="s">
+        <v>198</v>
+      </c>
+      <c r="F43" t="s">
+        <v>235</v>
+      </c>
+      <c r="G43" t="s">
+        <v>266</v>
+      </c>
+      <c r="H43" t="s">
+        <v>308</v>
+      </c>
+      <c r="I43" t="s">
+        <v>341</v>
+      </c>
+      <c r="J43" t="s">
+        <v>346</v>
+      </c>
+      <c r="K43" t="s">
+        <v>389</v>
+      </c>
+      <c r="L43" t="s">
+        <v>442</v>
+      </c>
+      <c r="M43" t="s">
+        <v>496</v>
+      </c>
+      <c r="O43" t="s">
+        <v>512</v>
+      </c>
+      <c r="P43" t="s">
+        <v>515</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>520</v>
+      </c>
+      <c r="R43" t="s">
+        <v>565</v>
+      </c>
+      <c r="S43" t="s">
+        <v>581</v>
+      </c>
+      <c r="T43" t="s">
+        <v>622</v>
+      </c>
+      <c r="U43" t="s">
+        <v>629</v>
+      </c>
+      <c r="V43" t="s">
+        <v>630</v>
+      </c>
+      <c r="W43" t="s">
+        <v>2</v>
+      </c>
+      <c r="X43" t="s">
+        <v>672</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>520</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>696</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29">
+      <c r="A44" t="s">
+        <v>71</v>
+      </c>
+      <c r="B44" t="s">
+        <v>125</v>
+      </c>
+      <c r="C44" t="s">
+        <v>137</v>
+      </c>
+      <c r="D44" t="s">
+        <v>179</v>
+      </c>
+      <c r="E44" t="s">
+        <v>226</v>
+      </c>
+      <c r="F44" t="s">
+        <v>227</v>
+      </c>
+      <c r="G44" t="s">
+        <v>266</v>
+      </c>
+      <c r="H44" t="s">
+        <v>309</v>
+      </c>
+      <c r="I44" t="s">
+        <v>342</v>
+      </c>
+      <c r="J44" t="s">
+        <v>347</v>
+      </c>
+      <c r="K44" t="s">
+        <v>390</v>
+      </c>
+      <c r="L44" t="s">
+        <v>443</v>
+      </c>
+      <c r="M44" t="s">
+        <v>497</v>
+      </c>
+      <c r="O44" t="s">
+        <v>512</v>
+      </c>
+      <c r="P44" t="s">
+        <v>515</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>520</v>
+      </c>
+      <c r="R44" t="s">
+        <v>566</v>
+      </c>
+      <c r="S44" t="s">
+        <v>591</v>
+      </c>
+      <c r="T44" t="s">
+        <v>623</v>
+      </c>
+      <c r="U44" t="s">
+        <v>629</v>
+      </c>
+      <c r="V44" t="s">
+        <v>630</v>
+      </c>
+      <c r="W44" t="s">
+        <v>2</v>
+      </c>
+      <c r="X44" t="s">
+        <v>673</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>687</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>520</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>693</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29">
+      <c r="A45" t="s">
+        <v>72</v>
+      </c>
+      <c r="B45" t="s">
+        <v>126</v>
+      </c>
+      <c r="C45" t="s">
+        <v>137</v>
+      </c>
+      <c r="D45" t="s">
+        <v>180</v>
+      </c>
+      <c r="E45" t="s">
+        <v>227</v>
+      </c>
+      <c r="F45" t="s">
+        <v>243</v>
+      </c>
+      <c r="G45" t="s">
+        <v>266</v>
+      </c>
+      <c r="H45" t="s">
+        <v>310</v>
+      </c>
+      <c r="I45" t="s">
+        <v>325</v>
+      </c>
+      <c r="J45" t="s">
+        <v>347</v>
+      </c>
+      <c r="K45" t="s">
+        <v>391</v>
+      </c>
+      <c r="L45" t="s">
+        <v>444</v>
+      </c>
+      <c r="M45" t="s">
+        <v>498</v>
+      </c>
+      <c r="O45" t="s">
+        <v>512</v>
+      </c>
+      <c r="P45" t="s">
+        <v>515</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>520</v>
+      </c>
+      <c r="R45" t="s">
+        <v>567</v>
+      </c>
+      <c r="S45" t="s">
+        <v>591</v>
+      </c>
+      <c r="T45" t="s">
+        <v>624</v>
+      </c>
+      <c r="U45" t="s">
+        <v>629</v>
+      </c>
+      <c r="V45" t="s">
+        <v>630</v>
+      </c>
+      <c r="W45" t="s">
+        <v>2</v>
+      </c>
+      <c r="X45" t="s">
+        <v>674</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>520</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>694</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="46" spans="1:29">
+      <c r="A46" t="s">
+        <v>73</v>
+      </c>
+      <c r="B46" t="s">
+        <v>127</v>
+      </c>
+      <c r="C46" t="s">
+        <v>137</v>
+      </c>
+      <c r="D46" t="s">
+        <v>181</v>
+      </c>
+      <c r="E46" t="s">
+        <v>228</v>
+      </c>
+      <c r="F46" t="s">
+        <v>260</v>
+      </c>
+      <c r="G46" t="s">
+        <v>266</v>
+      </c>
+      <c r="H46" t="s">
+        <v>311</v>
+      </c>
+      <c r="J46" t="s">
+        <v>347</v>
+      </c>
+      <c r="K46" t="s">
+        <v>392</v>
+      </c>
+      <c r="L46" t="s">
+        <v>445</v>
+      </c>
+      <c r="M46" t="s">
+        <v>499</v>
+      </c>
+      <c r="N46" t="s">
+        <v>509</v>
+      </c>
+      <c r="O46" t="s">
+        <v>511</v>
+      </c>
+      <c r="P46" t="s">
+        <v>514</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>519</v>
+      </c>
+      <c r="R46" t="s">
+        <v>568</v>
+      </c>
+      <c r="S46" t="s">
+        <v>586</v>
+      </c>
+      <c r="U46" t="s">
+        <v>630</v>
+      </c>
+      <c r="W46" t="s">
+        <v>2</v>
+      </c>
+      <c r="X46" t="s">
+        <v>675</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>519</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>694</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="47" spans="1:29">
+      <c r="A47" t="s">
+        <v>74</v>
+      </c>
+      <c r="B47" t="s">
+        <v>128</v>
+      </c>
+      <c r="C47" t="s">
+        <v>137</v>
+      </c>
+      <c r="D47" t="s">
+        <v>182</v>
+      </c>
+      <c r="E47" t="s">
+        <v>229</v>
+      </c>
+      <c r="F47" t="s">
+        <v>261</v>
+      </c>
+      <c r="G47" t="s">
+        <v>266</v>
+      </c>
+      <c r="H47" t="s">
+        <v>312</v>
+      </c>
+      <c r="I47" t="s">
+        <v>343</v>
+      </c>
+      <c r="J47" t="s">
+        <v>346</v>
+      </c>
+      <c r="K47" t="s">
+        <v>393</v>
+      </c>
+      <c r="L47" t="s">
+        <v>446</v>
+      </c>
+      <c r="M47" t="s">
+        <v>500</v>
+      </c>
+      <c r="N47" t="s">
+        <v>510</v>
+      </c>
+      <c r="O47" t="s">
+        <v>512</v>
+      </c>
+      <c r="P47" t="s">
+        <v>515</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>520</v>
+      </c>
+      <c r="R47" t="s">
+        <v>569</v>
+      </c>
+      <c r="S47" t="s">
+        <v>578</v>
+      </c>
+      <c r="T47" t="s">
+        <v>625</v>
+      </c>
+      <c r="U47" t="s">
+        <v>629</v>
+      </c>
+      <c r="V47" t="s">
+        <v>630</v>
+      </c>
+      <c r="W47" t="s">
+        <v>2</v>
+      </c>
+      <c r="X47" t="s">
+        <v>676</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>520</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>693</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="48" spans="1:29">
+      <c r="A48" t="s">
+        <v>75</v>
+      </c>
+      <c r="B48" t="s">
+        <v>129</v>
+      </c>
+      <c r="C48" t="s">
+        <v>137</v>
+      </c>
+      <c r="D48" t="s">
+        <v>183</v>
+      </c>
+      <c r="E48" t="s">
+        <v>230</v>
+      </c>
+      <c r="F48" t="s">
+        <v>262</v>
+      </c>
+      <c r="G48" t="s">
+        <v>266</v>
+      </c>
+      <c r="H48" t="s">
+        <v>313</v>
+      </c>
+      <c r="J48" t="s">
+        <v>346</v>
+      </c>
+      <c r="K48" t="s">
+        <v>394</v>
+      </c>
+      <c r="L48" t="s">
+        <v>447</v>
+      </c>
+      <c r="M48" t="s">
+        <v>501</v>
+      </c>
+      <c r="N48" t="s">
+        <v>509</v>
+      </c>
+      <c r="O48" t="s">
+        <v>511</v>
+      </c>
+      <c r="P48" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>523</v>
+      </c>
+      <c r="R48" t="s">
+        <v>570</v>
+      </c>
+      <c r="S48" t="s">
+        <v>592</v>
+      </c>
+      <c r="U48" t="s">
+        <v>630</v>
+      </c>
+      <c r="W48" t="s">
+        <v>2</v>
+      </c>
+      <c r="X48" t="s">
+        <v>677</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>691</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>692</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29">
+      <c r="A49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B49" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" t="s">
+        <v>137</v>
+      </c>
+      <c r="D49" t="s">
+        <v>184</v>
+      </c>
+      <c r="E49" t="s">
+        <v>231</v>
+      </c>
+      <c r="F49" t="s">
+        <v>243</v>
+      </c>
+      <c r="G49" t="s">
+        <v>266</v>
+      </c>
+      <c r="H49" t="s">
+        <v>314</v>
+      </c>
+      <c r="J49" t="s">
+        <v>346</v>
+      </c>
+      <c r="K49" t="s">
+        <v>395</v>
+      </c>
+      <c r="L49" t="s">
+        <v>448</v>
+      </c>
+      <c r="M49" t="s">
+        <v>502</v>
+      </c>
+      <c r="N49" t="s">
+        <v>509</v>
+      </c>
+      <c r="O49" t="s">
+        <v>511</v>
+      </c>
+      <c r="P49" t="s">
+        <v>516</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>521</v>
+      </c>
+      <c r="R49" t="s">
+        <v>571</v>
+      </c>
+      <c r="S49" t="s">
+        <v>578</v>
+      </c>
+      <c r="U49" t="s">
+        <v>630</v>
+      </c>
+      <c r="W49" t="s">
+        <v>2</v>
+      </c>
+      <c r="X49" t="s">
+        <v>678</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>521</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>692</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29">
+      <c r="A50" t="s">
+        <v>77</v>
+      </c>
+      <c r="B50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C50" t="s">
+        <v>137</v>
+      </c>
+      <c r="D50" t="s">
+        <v>185</v>
+      </c>
+      <c r="E50" t="s">
+        <v>227</v>
+      </c>
+      <c r="F50" t="s">
+        <v>263</v>
+      </c>
+      <c r="G50" t="s">
+        <v>266</v>
+      </c>
+      <c r="H50" t="s">
+        <v>315</v>
+      </c>
+      <c r="J50" t="s">
+        <v>346</v>
+      </c>
+      <c r="K50" t="s">
+        <v>396</v>
+      </c>
+      <c r="L50" t="s">
+        <v>449</v>
+      </c>
+      <c r="M50" t="s">
+        <v>503</v>
+      </c>
+      <c r="N50" t="s">
+        <v>509</v>
+      </c>
+      <c r="O50" t="s">
+        <v>511</v>
+      </c>
+      <c r="P50" t="s">
+        <v>514</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>519</v>
+      </c>
+      <c r="R50" t="s">
+        <v>572</v>
+      </c>
+      <c r="S50" t="s">
+        <v>591</v>
+      </c>
+      <c r="U50" t="s">
+        <v>629</v>
+      </c>
+      <c r="W50" t="s">
+        <v>2</v>
+      </c>
+      <c r="X50" t="s">
+        <v>679</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>519</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>694</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="51" spans="1:29">
+      <c r="A51" t="s">
+        <v>78</v>
+      </c>
+      <c r="B51" t="s">
+        <v>132</v>
+      </c>
+      <c r="C51" t="s">
+        <v>137</v>
+      </c>
+      <c r="D51" t="s">
+        <v>186</v>
+      </c>
+      <c r="E51" t="s">
+        <v>232</v>
+      </c>
+      <c r="F51" t="s">
+        <v>230</v>
+      </c>
+      <c r="G51" t="s">
+        <v>266</v>
+      </c>
+      <c r="H51" t="s">
+        <v>316</v>
+      </c>
+      <c r="I51" t="s">
+        <v>344</v>
+      </c>
+      <c r="J51" t="s">
+        <v>347</v>
+      </c>
+      <c r="K51" t="s">
+        <v>397</v>
+      </c>
+      <c r="L51" t="s">
+        <v>450</v>
+      </c>
+      <c r="M51" t="s">
+        <v>504</v>
+      </c>
+      <c r="O51" t="s">
+        <v>512</v>
+      </c>
+      <c r="P51" t="s">
+        <v>515</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>520</v>
+      </c>
+      <c r="R51" t="s">
+        <v>573</v>
+      </c>
+      <c r="S51" t="s">
+        <v>580</v>
+      </c>
+      <c r="T51" t="s">
+        <v>626</v>
+      </c>
+      <c r="U51" t="s">
+        <v>629</v>
+      </c>
+      <c r="V51" t="s">
+        <v>630</v>
+      </c>
+      <c r="W51" t="s">
+        <v>2</v>
+      </c>
+      <c r="X51" t="s">
+        <v>680</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>520</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>694</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29">
+      <c r="A52" t="s">
+        <v>79</v>
+      </c>
+      <c r="B52" t="s">
+        <v>133</v>
+      </c>
+      <c r="C52" t="s">
+        <v>137</v>
+      </c>
+      <c r="D52" t="s">
+        <v>187</v>
+      </c>
+      <c r="E52" t="s">
+        <v>233</v>
+      </c>
+      <c r="F52" t="s">
+        <v>264</v>
+      </c>
+      <c r="G52" t="s">
+        <v>266</v>
+      </c>
+      <c r="H52" t="s">
+        <v>317</v>
+      </c>
+      <c r="I52" t="s">
+        <v>345</v>
+      </c>
+      <c r="J52" t="s">
+        <v>346</v>
+      </c>
+      <c r="K52" t="s">
+        <v>398</v>
+      </c>
+      <c r="L52" t="s">
+        <v>451</v>
+      </c>
+      <c r="M52" t="s">
+        <v>505</v>
+      </c>
+      <c r="N52" t="s">
+        <v>510</v>
+      </c>
+      <c r="O52" t="s">
+        <v>512</v>
+      </c>
+      <c r="P52" t="s">
+        <v>515</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>520</v>
+      </c>
+      <c r="R52" t="s">
+        <v>574</v>
+      </c>
+      <c r="S52" t="s">
+        <v>578</v>
+      </c>
+      <c r="T52" t="s">
+        <v>627</v>
+      </c>
+      <c r="U52" t="s">
+        <v>629</v>
+      </c>
+      <c r="V52" t="s">
+        <v>630</v>
+      </c>
+      <c r="W52" t="s">
+        <v>2</v>
+      </c>
+      <c r="X52" t="s">
+        <v>681</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>520</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>693</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="53" spans="1:29">
+      <c r="A53" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" t="s">
+        <v>134</v>
+      </c>
+      <c r="C53" t="s">
+        <v>137</v>
+      </c>
+      <c r="D53" t="s">
+        <v>188</v>
+      </c>
+      <c r="E53" t="s">
+        <v>234</v>
+      </c>
+      <c r="F53" t="s">
+        <v>265</v>
+      </c>
+      <c r="G53" t="s">
+        <v>266</v>
+      </c>
+      <c r="H53" t="s">
+        <v>318</v>
+      </c>
+      <c r="J53" t="s">
+        <v>347</v>
+      </c>
+      <c r="K53" t="s">
+        <v>399</v>
+      </c>
+      <c r="L53" t="s">
+        <v>452</v>
+      </c>
+      <c r="M53" t="s">
+        <v>506</v>
+      </c>
+      <c r="N53" t="s">
+        <v>509</v>
+      </c>
+      <c r="O53" t="s">
+        <v>511</v>
+      </c>
+      <c r="P53" t="s">
+        <v>514</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>519</v>
+      </c>
+      <c r="R53" t="s">
+        <v>575</v>
+      </c>
+      <c r="S53" t="s">
+        <v>578</v>
+      </c>
+      <c r="U53" t="s">
+        <v>629</v>
+      </c>
+      <c r="W53" t="s">
+        <v>2</v>
+      </c>
+      <c r="X53" t="s">
+        <v>682</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>519</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>694</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="54" spans="1:29">
+      <c r="A54" t="s">
+        <v>81</v>
+      </c>
+      <c r="B54" t="s">
+        <v>135</v>
+      </c>
+      <c r="C54" t="s">
+        <v>137</v>
+      </c>
+      <c r="D54" t="s">
+        <v>189</v>
+      </c>
+      <c r="E54" t="s">
+        <v>233</v>
+      </c>
+      <c r="F54" t="s">
+        <v>198</v>
+      </c>
+      <c r="G54" t="s">
+        <v>266</v>
+      </c>
+      <c r="H54" t="s">
+        <v>319</v>
+      </c>
+      <c r="J54" t="s">
+        <v>346</v>
+      </c>
+      <c r="K54" t="s">
+        <v>400</v>
+      </c>
+      <c r="L54" t="s">
+        <v>453</v>
+      </c>
+      <c r="M54" t="s">
+        <v>507</v>
+      </c>
+      <c r="N54" t="s">
+        <v>509</v>
+      </c>
+      <c r="O54" t="s">
+        <v>511</v>
+      </c>
+      <c r="P54" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>523</v>
+      </c>
+      <c r="R54" t="s">
+        <v>576</v>
+      </c>
+      <c r="S54" t="s">
+        <v>592</v>
+      </c>
+      <c r="U54" t="s">
+        <v>629</v>
+      </c>
+      <c r="W54" t="s">
+        <v>2</v>
+      </c>
+      <c r="X54" t="s">
+        <v>683</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>691</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>692</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="55" spans="1:29">
+      <c r="A55" t="s">
+        <v>82</v>
+      </c>
+      <c r="B55" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55" t="s">
+        <v>137</v>
+      </c>
+      <c r="D55" t="s">
+        <v>190</v>
+      </c>
+      <c r="E55" t="s">
+        <v>235</v>
+      </c>
+      <c r="F55" t="s">
+        <v>243</v>
+      </c>
+      <c r="G55" t="s">
+        <v>266</v>
+      </c>
+      <c r="H55" t="s">
+        <v>320</v>
+      </c>
+      <c r="I55" t="s">
+        <v>325</v>
+      </c>
+      <c r="J55" t="s">
+        <v>347</v>
+      </c>
+      <c r="K55" t="s">
+        <v>401</v>
+      </c>
+      <c r="L55" t="s">
+        <v>454</v>
+      </c>
+      <c r="M55" t="s">
+        <v>508</v>
+      </c>
+      <c r="N55" t="s">
+        <v>510</v>
+      </c>
+      <c r="O55" t="s">
+        <v>512</v>
+      </c>
+      <c r="P55" t="s">
+        <v>515</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>520</v>
+      </c>
+      <c r="R55" t="s">
+        <v>577</v>
+      </c>
+      <c r="S55" t="s">
+        <v>578</v>
+      </c>
+      <c r="T55" t="s">
+        <v>628</v>
+      </c>
+      <c r="U55" t="s">
+        <v>629</v>
+      </c>
+      <c r="V55" t="s">
+        <v>629</v>
+      </c>
+      <c r="W55" t="s">
+        <v>2</v>
+      </c>
+      <c r="X55" t="s">
+        <v>684</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>520</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>694</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>699</v>
       </c>
     </row>
   </sheetData>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,12 +713,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>290316</t>
+          <t>123833</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>87814</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VANESSA</t>
+          <t>AKYEL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HIGUERA</t>
+          <t>CASTANEDO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -748,35 +748,39 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6861744727</t>
+          <t>6531131589</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 1</t>
+          <t>DEL CARRIZO 3015</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>22-07-1992</t>
+          <t>01-10-2003</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>HIGUERAROSAV@GMAIL.COM</t>
+          <t>AKYDANIELLA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>28-04-2025 19:34:24</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>19-09-2022 16:35:13</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -794,17 +798,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>14-02-2026 15:01:10</t>
+          <t>17-02-2026 06:58:58</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>14-02-2026 15:00:36</t>
+          <t>17-02-2026 06:58:23</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -824,15 +828,19 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26160522349780002121</t>
+          <t>26160522419880002224</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>499</t>
@@ -840,7 +848,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -967,12 +975,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1114,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>123833</t>
+          <t>320033</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>17530</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1121,17 +1129,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AKYEL</t>
+          <t>OMAR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CASTANEDO</t>
+          <t>AMEZQUITA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MENDIETA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1141,39 +1149,35 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6531131589</t>
+          <t>6863074437</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DEL CARRIZO 3015</t>
+          <t>INDEPENDENCIA 1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>01-10-2003</t>
+          <t>21-10-1966</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>AKYDANIELLA@GMAIL.COM</t>
+          <t>OAMEZQUITA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>19-09-2022 16:35:13</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>22-10-2025 15:17:42</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1191,17 +1195,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>17-02-2026 06:58:58</t>
+          <t>11-02-2026 18:22:11</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>17-02-2026 06:58:23</t>
+          <t>11-02-2026 18:18:44</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1221,7 +1225,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26160522419880002224</t>
+          <t>26160522273890001965</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1231,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1241,24 +1245,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>238288</t>
+          <t>340481</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35793</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1268,17 +1272,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SILVIA PAOLA</t>
+          <t>HILDA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PAYAN</t>
+          <t>BENAVIDEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1288,12 +1292,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6864629400</t>
+          <t>6864150761</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IND123</t>
+          <t>LINEZO1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1303,17 +1307,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>18-02-2009</t>
+          <t>21-07-1961</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>SILVIAPAYAN009@GMAIL.COM</t>
+          <t>NOTIERERER@TYU.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>05-06-2024 18:12:25</t>
+          <t>03-02-2026 08:55:15</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1334,17 +1338,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10-02-2026 05:33:30</t>
+          <t>04-02-2026 10:23:34</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>10-02-2026 05:32:15</t>
+          <t>04-02-2026 10:22:30</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1364,7 +1368,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26160522222220001861</t>
+          <t>26160522071550001606</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1374,7 +1378,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1384,7 +1388,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1396,12 +1400,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>320033</t>
+          <t>337242</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17530</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1411,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OMAR</t>
+          <t xml:space="preserve">MARTHA ELENA </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AMEZQUITA</t>
+          <t>MAEDA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MENDIETA</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1431,75 +1435,67 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6863074437</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA 1</t>
-        </is>
-      </c>
+          <t>6861253578</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>21-10-1966</t>
+          <t>06-10-1952</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>OAMEZQUITA@GMAIL.COM</t>
+          <t>MARTHAELENAMG@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>22-10-2025 15:17:42</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>23-01-2026 12:52:24</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>11-02-2026 18:22:11</t>
+          <t>03-02-2026 08:23:40</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>11-02-2026 18:18:44</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1507,27 +1503,19 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26160522273890001965</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26160522033610001514</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1539,12 +1527,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>340255</t>
+          <t>340791</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18073</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1554,17 +1542,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>STEPHANY</t>
+          <t>HECTOR MANUEL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BEJARANO</t>
+          <t>ALVARADO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ENRIQUEZ</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1574,32 +1562,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6865923181</t>
+          <t>5628369350</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 38</t>
+          <t>MAYA CAMPESTRE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>18-01-1995</t>
+          <t>09-08-1976</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>FANNYBEJARANO904@GMAIL.COM</t>
+          <t>MACALVMAIL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-02-2026 16:15:36</t>
+          <t>03-02-2026 18:47:52</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1620,17 +1608,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-02-2026 16:21:03</t>
+          <t>03-02-2026 19:09:42</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-02-2026 16:20:43</t>
+          <t>03-02-2026 19:09:20</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1650,10 +1638,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26160522016270001486</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
+          <t>26160522055330001568</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1662,7 +1654,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1674,12 +1666,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>340481</t>
+          <t>340808</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1689,17 +1681,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HILDA</t>
+          <t>RENE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BENAVIDEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PEÑA</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1709,32 +1701,32 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6864150761</t>
+          <t>6863485358</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LINEZO1</t>
+          <t>INDEPENDENCIA 23</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>21-07-1961</t>
+          <t>15-09-1996</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>NOTIERERER@TYU.COM</t>
+          <t>RENEGONZALEZ1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>03-02-2026 08:55:15</t>
+          <t>03-02-2026 19:14:48</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1755,17 +1747,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>04-02-2026 10:23:34</t>
+          <t>05-02-2026 19:04:55</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>04-02-2026 10:22:30</t>
+          <t>05-02-2026 19:03:37</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1785,7 +1777,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26160522071550001606</t>
+          <t>26160522117360001694</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1795,7 +1787,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1817,12 +1809,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>340641</t>
+          <t>340713</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1832,17 +1824,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LUCIA YADIRA</t>
+          <t>LESLIE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>VELARDE</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1852,12 +1844,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6861822416</t>
+          <t>6865257334</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CULTURA OLMECA 3608</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1867,17 +1859,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>13-12-1990</t>
+          <t>10-06-1994</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>YADIRA_1290@HOTMAIL.COM</t>
+          <t>LICMERCADOSUNA.10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-02-2026 15:56:48</t>
+          <t>03-02-2026 17:15:35</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1898,17 +1890,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>05-02-2026 16:33:17</t>
+          <t>03-02-2026 17:19:02</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>05-02-2026 16:30:37</t>
+          <t>03-02-2026 17:18:43</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1918,7 +1910,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1928,19 +1920,11 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26160522110560001680</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26160522048750001552</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
           <t>499</t>
@@ -1948,7 +1932,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1960,12 +1944,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>340697</t>
+          <t>290316</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>87814</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1975,17 +1959,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRISTIAN ISMAEL</t>
+          <t>VANESSA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>HIGUERA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1995,12 +1979,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6863537341</t>
+          <t>6861744727</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA3</t>
+          <t>INDEPENDENCIA 1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2010,17 +1994,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>22-06-1995</t>
+          <t>22-07-1992</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CRISTIAN.TORRES@GCADENA.COM</t>
+          <t>HIGUERAROSAV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>03-02-2026 17:02:34</t>
+          <t>28-04-2025 19:34:24</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2041,17 +2025,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-02-2026 17:06:48</t>
+          <t>14-02-2026 15:01:10</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>03-02-2026 17:06:13</t>
+          <t>14-02-2026 15:00:36</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2061,7 +2045,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2071,10 +2055,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26160522047970001551</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
+          <t>26160522349780002121</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
@@ -2083,7 +2071,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2095,12 +2083,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>340791</t>
+          <t>341834</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2110,17 +2098,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HECTOR MANUEL</t>
+          <t>DARIANA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ALVARADO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2130,32 +2118,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5628369350</t>
+          <t>6862489316</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MAYA CAMPESTRE</t>
+          <t>SAN CARLO1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>09-08-1976</t>
+          <t>03-12-1981</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>MACALVMAIL@GMAIL.COM</t>
+          <t>LOPEZDARIANA780@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-02-2026 18:47:52</t>
+          <t>07-02-2026 13:31:41</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2176,17 +2164,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-02-2026 19:09:42</t>
+          <t>07-02-2026 13:38:04</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>03-02-2026 19:09:20</t>
+          <t>07-02-2026 13:35:50</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2196,7 +2184,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2206,14 +2194,10 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26160522055330001568</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26160522161810001766</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
@@ -2222,7 +2206,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2234,12 +2218,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>340808</t>
+          <t>339686</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18626</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2249,17 +2233,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>RENE</t>
+          <t>EDUARDO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2269,12 +2253,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6863485358</t>
+          <t>6862121992</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 23</t>
+          <t>I988</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2284,20 +2268,24 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>15-09-1996</t>
+          <t>06-05-1992</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>RENEGONZALEZ1@GMAIL.COM</t>
+          <t>POLOEGARCIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-02-2026 19:14:48</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>31-01-2026 12:59:25</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2315,17 +2303,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>05-02-2026 19:04:55</t>
+          <t>18-02-2026 13:22:14</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>05-02-2026 19:03:37</t>
+          <t>18-02-2026 13:21:09</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2335,7 +2323,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2345,7 +2333,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26160522117360001694</t>
+          <t>26160522461460002325</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2355,7 +2343,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+          <t>auxiliar independencia mexicali</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2365,24 +2353,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>337242</t>
+          <t>341132</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2392,17 +2380,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTHA ELENA </t>
+          <t xml:space="preserve">NAHOMI ESTEFANIA </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MAEDA</t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>TALAMANTES</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2412,10 +2400,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6861253578</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>6643120858</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2423,56 +2415,60 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>06-10-1952</t>
+          <t>18-08-1996</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>MARTHAELENAMG@GMAIL.COM</t>
+          <t>ESTEFANIAMTALAMANTESX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>23-01-2026 12:52:24</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 18:08:31</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-02-2026 08:23:40</t>
+          <t>10-02-2026 16:06:43</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>10-02-2026 16:05:59</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2480,19 +2476,27 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26160522033610001514</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+          <t>26130522235720002570</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>MARIA CANDELARIA LARA AVILA</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2504,12 +2508,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>339686</t>
+          <t>238288</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17504</t>
+          <t>35793</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2519,17 +2523,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EDUARDO</t>
+          <t>SILVIA PAOLA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>PAYAN</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2539,39 +2543,35 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6862121992</t>
+          <t>6864629400</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>I988</t>
+          <t>IND123</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>06-05-1992</t>
+          <t>18-02-2009</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>POLOEGARCIA@GMAIL.COM</t>
+          <t>SILVIAPAYAN009@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>31-01-2026 12:59:25</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>05-06-2024 18:12:25</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2589,17 +2589,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>18-02-2026 13:22:14</t>
+          <t>10-02-2026 05:33:30</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>18-02-2026 13:21:09</t>
+          <t>10-02-2026 05:32:15</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26160522461460002325</t>
+          <t>26160522222220001861</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>auxiliar independencia mexicali</t>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2639,24 +2639,24 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>340713</t>
+          <t>299954</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>97452</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LESLIE</t>
+          <t>EUNICE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2686,12 +2686,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6865257334</t>
+          <t>6865848338</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>IND123</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>10-06-1994</t>
+          <t>11-06-2001</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>LICMERCADOSUNA.10@GMAIL.COM</t>
+          <t>EUNICE.LOPEZ5@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>03-02-2026 17:15:35</t>
+          <t>23-06-2025 18:39:49</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2732,17 +2732,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03-02-2026 17:19:02</t>
+          <t>09-02-2026 08:55:34</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>03-02-2026 17:18:43</t>
+          <t>09-02-2026 08:54:52</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2762,10 +2762,14 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26160522048750001552</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
+          <t>26160522185470001787</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2774,7 +2778,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2786,12 +2790,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>340789</t>
+          <t>341819</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18607</t>
+          <t>19637</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2801,17 +2805,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIELA </t>
+          <t>KARYME</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2821,14 +2825,10 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6861739204</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>MAYA CAMPESTRE</t>
-        </is>
-      </c>
+          <t>6861351566</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2836,60 +2836,56 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>06-09-1989</t>
+          <t>11-12-2004</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>DANIELA.SANCHEZ.MORENO.89@GMAIL.COM</t>
+          <t>KARYMEMACLOP@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-02-2026 18:45:03</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>07-02-2026 12:03:12</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-02-2026 19:05:49</t>
+          <t>07-02-2026 12:05:36</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>03-02-2026 19:04:34</t>
-        </is>
-      </c>
+          <t>07-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2897,23 +2893,19 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26160522055070001567</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26160522160500001761</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2925,12 +2917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>341834</t>
+          <t>342323</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19652</t>
+          <t>20141</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2940,7 +2932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DARIANA</t>
+          <t>MARCO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2950,7 +2942,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>ORDUÑO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2960,32 +2952,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6862489316</t>
+          <t>6861601599</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SAN CARLO1</t>
+          <t>INDEPENDENCIA0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>03-12-1981</t>
+          <t>25-04-1979</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>LOPEZDARIANA780@GMAIL.COM</t>
+          <t>MOPILLO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>07-02-2026 13:31:41</t>
+          <t>09-02-2026 17:27:09</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3006,17 +2998,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>07-02-2026 13:38:04</t>
+          <t>09-02-2026 17:33:13</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>07-02-2026 13:35:50</t>
+          <t>09-02-2026 17:32:43</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3036,7 +3028,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26160522161810001766</t>
+          <t>26160522202710001810</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -3048,7 +3040,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3060,12 +3052,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>341132</t>
+          <t>340255</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>18073</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3075,17 +3067,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAHOMI ESTEFANIA </t>
+          <t>STEPHANY</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t>BEJARANO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TALAMANTES</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3095,12 +3087,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6643120858</t>
+          <t>6865923181</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>INDEPENDENCIA 38</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3110,17 +3102,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>18-08-1996</t>
+          <t>18-01-1995</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ESTEFANIAMTALAMANTESX@GMAIL.COM</t>
+          <t>FANNYBEJARANO904@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>04-02-2026 18:08:31</t>
+          <t>02-02-2026 16:15:36</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3141,17 +3133,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>10-02-2026 16:06:43</t>
+          <t>02-02-2026 16:21:03</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>10-02-2026 16:05:59</t>
+          <t>02-02-2026 16:20:43</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3161,7 +3153,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3171,19 +3163,11 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26130522235720002570</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>MARIA CANDELARIA LARA AVILA</t>
-        </is>
-      </c>
+          <t>26160522016270001486</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
           <t>499</t>
@@ -3191,7 +3175,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3330,12 +3314,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>341819</t>
+          <t>342087</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19637</t>
+          <t>19905</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3345,17 +3329,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KARYME</t>
+          <t>KARLA VERÓNICA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>PALAFOX</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3365,10 +3349,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6861351566</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>6861244927</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>IND111111</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3376,17 +3364,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>11-12-2004</t>
+          <t>26-05-1986</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>KARYMEMACLOP@GMAIL.COM</t>
+          <t>VERONIKAPALAFOX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>07-02-2026 12:03:12</t>
+          <t>09-02-2026 10:07:36</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3396,36 +3384,44 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>07-02-2026 12:05:36</t>
+          <t>16-02-2026 08:19:11</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:18:23</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3433,19 +3429,27 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26160522160500001761</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
+          <t>26160522380750002134</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3457,12 +3461,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>299954</t>
+          <t>342336</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>97452</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3472,7 +3476,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EUNICE</t>
+          <t>MARCO ALEJANDRO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3482,7 +3486,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3492,32 +3496,32 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6865848338</t>
+          <t>6861632588</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>IND123</t>
+          <t>INDEPENDENCIA01</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>11-06-2001</t>
+          <t>12-05-2006</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>EUNICE.LOPEZ5@UABC.EDU.MX</t>
+          <t>6MALLISME9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>23-06-2025 18:39:49</t>
+          <t>09-02-2026 17:35:12</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3538,7 +3542,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>09-02-2026 08:55:34</t>
+          <t>09-02-2026 17:38:30</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3548,7 +3552,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>09-02-2026 08:54:52</t>
+          <t>09-02-2026 17:38:05</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3558,7 +3562,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3568,14 +3572,10 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26160522185470001787</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26160522203170001811</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3596,12 +3596,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>343384</t>
+          <t>342474</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21201</t>
+          <t>20291</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>BRISA</t>
+          <t>MELISSA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GASCA</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6863912198</t>
+          <t>6863242180</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>INDEPENDENCIA01</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3646,17 +3646,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>12-02-2006</t>
+          <t>25-07-1987</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>GNAVARROGASCA@GMAIL.COM</t>
+          <t>YLEM51@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>12-02-2026 19:16:27</t>
+          <t>09-02-2026 20:08:06</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3677,17 +3677,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>12-02-2026 19:22:02</t>
+          <t>09-02-2026 20:12:28</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>12-02-2026 19:21:22</t>
+          <t>09-02-2026 20:10:07</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26160522304540002036</t>
+          <t>26160522213110001840</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3731,12 +3731,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>342087</t>
+          <t>342794</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19905</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KARLA VERÓNICA</t>
+          <t>JOSUE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PALAFOX</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3766,67 +3766,63 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6861244927</t>
+          <t>6861127057</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>IND111111</t>
+          <t>INDEPENDENCI1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>26-05-1986</t>
+          <t>26-11-1989</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>VERONIKAPALAFOX@GMAIL.COM</t>
+          <t>JOSUEBRMUSIC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>09-02-2026 10:07:36</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 18:25:08</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>16-02-2026 08:19:11</t>
+          <t>10-02-2026 18:27:56</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>16-02-2026 08:18:23</t>
+          <t>10-02-2026 18:27:24</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3836,7 +3832,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3846,27 +3842,19 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26160522380750002134</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
-        </is>
-      </c>
+          <t>26160522243630001901</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3878,12 +3866,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>342323</t>
+          <t>343140</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3893,17 +3881,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MARCO</t>
+          <t xml:space="preserve">VANESSA </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ORDUÑO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3913,32 +3901,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6861601599</t>
+          <t>6864164007</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA0</t>
+          <t>AV TORRE LAS ARCAS 2045</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>25-04-1979</t>
+          <t>08-11-1989</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>MOPILLO@GMAIL.COM</t>
+          <t>VANESSAGALVANR250210@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>09-02-2026 17:27:09</t>
+          <t>11-02-2026 20:55:11</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3959,17 +3947,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>09-02-2026 17:33:13</t>
+          <t>13-02-2026 18:56:17</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>09-02-2026 17:32:43</t>
+          <t>13-02-2026 18:55:42</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3979,7 +3967,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3989,10 +3977,14 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26160522202710001810</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
+          <t>26170522329060002370</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
@@ -4001,7 +3993,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4013,12 +4005,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>344132</t>
+          <t>342478</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21949</t>
+          <t>20295</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4028,17 +4020,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGELES </t>
+          <t>FERNANDO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CARMONA</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SIQUEIROS</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4048,67 +4040,75 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6863378715</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>6861146223</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA01</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>04-08-2006</t>
+          <t>27-04-1993</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ANGELESWCARMONA763@GMAIL.COM</t>
+          <t>IVANRNAVARRO12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>16-02-2026 15:44:25</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 20:13:50</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>16-02-2026 15:45:32</t>
+          <t>09-02-2026 20:16:34</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>09-02-2026 20:16:03</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4116,19 +4116,19 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26160522393400002157</t>
+          <t>26160522213270001841</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4140,12 +4140,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>342794</t>
+          <t>340789</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4155,17 +4155,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>JOSUE</t>
+          <t xml:space="preserve">DANIELA </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4175,32 +4175,32 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6861127057</t>
+          <t>6861739204</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>INDEPENDENCI1</t>
+          <t>MAYA CAMPESTRE</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>26-11-1989</t>
+          <t>06-09-1989</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>JOSUEBRMUSIC@GMAIL.COM</t>
+          <t>DANIELA.SANCHEZ.MORENO.89@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>10-02-2026 18:25:08</t>
+          <t>03-02-2026 18:45:03</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4221,17 +4221,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>10-02-2026 18:27:56</t>
+          <t>03-02-2026 19:05:49</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>10-02-2026 18:27:24</t>
+          <t>03-02-2026 19:04:34</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4251,10 +4251,14 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26160522243630001901</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr"/>
+          <t>26160522055070001567</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
@@ -4263,7 +4267,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4275,12 +4279,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>342822</t>
+          <t>340641</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20639</t>
+          <t>18459</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4290,17 +4294,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LEOPOLDO</t>
+          <t>LUCIA YADIRA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LOYO</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>COBO</t>
+          <t>VELARDE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4310,32 +4314,32 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6862120595</t>
+          <t>6861822416</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>CULTURA OLMECA 3608</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>17-07-1971</t>
+          <t>13-12-1990</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>LEOPOLDOLOYO@GMAIL.COM</t>
+          <t>YADIRA_1290@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10-02-2026 19:02:43</t>
+          <t>03-02-2026 15:56:48</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4356,17 +4360,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>14-02-2026 13:28:02</t>
+          <t>05-02-2026 16:33:17</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>14-02-2026 13:27:04</t>
+          <t>05-02-2026 16:30:37</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4376,7 +4380,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4386,15 +4390,19 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26160522349290002113</t>
+          <t>26160522110560001680</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>499</t>
@@ -4414,12 +4422,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>342336</t>
+          <t>340697</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4429,17 +4437,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MARCO ALEJANDRO</t>
+          <t>CRISTIAN ISMAEL</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4449,12 +4457,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6861632588</t>
+          <t>6863537341</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA01</t>
+          <t>INDEPENDENCIA3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4464,17 +4472,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>12-05-2006</t>
+          <t>22-06-1995</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6MALLISME9@GMAIL.COM</t>
+          <t>CRISTIAN.TORRES@GCADENA.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>09-02-2026 17:35:12</t>
+          <t>03-02-2026 17:02:34</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4495,17 +4503,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>09-02-2026 17:38:30</t>
+          <t>03-02-2026 17:06:48</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>09-02-2026 17:38:05</t>
+          <t>03-02-2026 17:06:13</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4525,7 +4533,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26160522203170001811</t>
+          <t>26160522047970001551</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4537,7 +4545,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4549,12 +4557,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342474</t>
+          <t>342822</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4564,17 +4572,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MELISSA</t>
+          <t>LEOPOLDO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>LOYO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>COBO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4584,32 +4592,32 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6863242180</t>
+          <t>6862120595</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA01</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>25-07-1987</t>
+          <t>17-07-1971</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>YLEM51@GMAIL.COM</t>
+          <t>LEOPOLDOLOYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>09-02-2026 20:08:06</t>
+          <t>10-02-2026 19:02:43</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4630,17 +4638,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>09-02-2026 20:12:28</t>
+          <t>14-02-2026 13:28:02</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>09-02-2026 20:10:07</t>
+          <t>14-02-2026 13:27:04</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4660,10 +4668,14 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26160522213110001840</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr"/>
+          <t>26160522349290002113</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
@@ -4672,7 +4684,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4684,12 +4696,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>344345</t>
+          <t>342776</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>22162</t>
+          <t>20593</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4699,17 +4711,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>JESUS ANTONIO</t>
+          <t>JUAN MANUEL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TOPETE</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4719,10 +4731,14 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6865890812</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>6867292744</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4730,56 +4746,60 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>15-12-1987</t>
+          <t>09-11-1973</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CHUYANTONT@GMAIL.COM</t>
+          <t>NOCUENTACON1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>16-02-2026 19:42:11</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 18:03:21</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>16-02-2026 19:43:34</t>
+          <t>10-02-2026 18:35:28</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>10-02-2026 18:35:08</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4787,14 +4807,14 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26160522409070002196</t>
+          <t>26160522243990001903</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4811,12 +4831,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>343140</t>
+          <t>342580</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>20397</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4826,17 +4846,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">VANESSA </t>
+          <t>HECTOR MANUEL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t>PIÑA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>OLIVEROS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4846,75 +4866,67 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6864164007</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>AV TORRE LAS ARCAS 2045</t>
-        </is>
-      </c>
+          <t>6865895862</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>08-11-1989</t>
+          <t>17-10-2002</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>VANESSAGALVANR250210@GMAIL.COM</t>
+          <t>NOTIENE11112222@FFFFDDD.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>11-02-2026 20:55:11</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>10-02-2026 10:48:52</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>13-02-2026 18:56:17</t>
+          <t>10-02-2026 10:50:12</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>13-02-2026 18:55:42</t>
-        </is>
-      </c>
+          <t>10-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4922,23 +4934,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26170522329060002370</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26160522228650001872</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4950,12 +4958,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>343713</t>
+          <t>343612</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>21429</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4965,17 +4973,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>JESSICA ALEJANDRA</t>
+          <t>OSCAR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CARRERA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4985,75 +4993,67 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6863648770</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>JOSE MARIA AGUAYO 506</t>
-        </is>
-      </c>
+          <t>6865906261</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>18-01-2006</t>
+          <t>03-08-2006</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>JESSICAA.GUTIERREZ@CETYS.EDU.MX</t>
+          <t>OR629395@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>14-02-2026 11:38:52</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>13-02-2026 20:02:16</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>14-02-2026 11:41:20</t>
+          <t>13-02-2026 20:03:49</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>14-02-2026 11:40:29</t>
-        </is>
-      </c>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5061,14 +5061,14 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26160522347590002106</t>
+          <t>26160522330930002093</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342776</t>
+          <t>343714</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20593</t>
+          <t>21531</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>JUAN MANUEL</t>
+          <t>OLVIA YISEL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5120,32 +5120,32 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6867292744</t>
+          <t>6863667098</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>AV LAGO BAHIJASH 634</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>09-11-1973</t>
+          <t>03-03-2001</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>NOCUENTACON1@GMAIL.COM</t>
+          <t>OLVIAHU18@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>10-02-2026 18:03:21</t>
+          <t>14-02-2026 11:45:34</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5166,17 +5166,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>10-02-2026 18:35:28</t>
+          <t>14-02-2026 11:48:11</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>10-02-2026 18:35:08</t>
+          <t>14-02-2026 11:47:29</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26160522243990001903</t>
+          <t>26160522347720002107</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5220,12 +5220,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>342478</t>
+          <t>343025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20295</t>
+          <t>20842</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FERNANDO</t>
+          <t>DYLAN</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5255,14 +5255,10 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6861146223</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA01</t>
-        </is>
-      </c>
+          <t>6861698256</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5270,60 +5266,56 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>27-04-1993</t>
+          <t>06-08-2002</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>IVANRNAVARRO12@GMAIL.COM</t>
+          <t>DYLANMTZM.26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>09-02-2026 20:13:50</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>11-02-2026 15:49:14</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>09-02-2026 20:16:34</t>
+          <t>11-02-2026 15:52:21</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>09-02-2026 20:16:03</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5331,19 +5323,19 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26160522213270001841</t>
+          <t>26160522267270001952</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5355,12 +5347,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>342580</t>
+          <t>343713</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20397</t>
+          <t>21530</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5370,17 +5362,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>HECTOR MANUEL</t>
+          <t>JESSICA ALEJANDRA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>PIÑA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>OLIVEROS</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5390,67 +5382,75 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6865895862</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>6863648770</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>JOSE MARIA AGUAYO 506</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>17-10-2002</t>
+          <t>18-01-2006</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>NOTIENE11112222@FFFFDDD.COM</t>
+          <t>JESSICAA.GUTIERREZ@CETYS.EDU.MX</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>10-02-2026 10:48:52</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>14-02-2026 11:38:52</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>10-02-2026 10:50:12</t>
+          <t>14-02-2026 11:41:20</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>10-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>14-02-2026 11:40:29</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5458,19 +5458,19 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26160522228650001872</t>
+          <t>26160522347590002106</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5482,12 +5482,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>342457</t>
+          <t>343557</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20274</t>
+          <t>21374</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5497,17 +5497,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE </t>
+          <t>JUAN CARLOS</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FRANCISCO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FIERRO</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5517,32 +5517,32 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6861575086</t>
+          <t>6863903522</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA02</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>15-09-1973</t>
+          <t>08-03-1971</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>FIERRO_PACO@HOTMAIL.COM</t>
+          <t>JUANCARLORIOS1422@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>09-02-2026 19:49:15</t>
+          <t>13-02-2026 17:19:49</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5563,17 +5563,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>09-02-2026 19:51:47</t>
+          <t>13-02-2026 17:24:13</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>09-02-2026 19:50:53</t>
+          <t>13-02-2026 17:22:41</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26160522212280001839</t>
+          <t>26160522326350002078</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5617,12 +5617,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>342583</t>
+          <t>344453</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20400</t>
+          <t>22270</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5632,17 +5632,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SHESLY DENNIS</t>
+          <t>JESUS</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5652,75 +5652,67 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6861234727</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>PRESA DE LA ANGOSURA 1491</t>
-        </is>
-      </c>
+          <t>6861762359</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>30-07-1996</t>
+          <t>11-08-1951</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>SHES.MEZAGTZ@GMAIL.COM</t>
+          <t>NOTIENE23445@DFDF.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>10-02-2026 11:28:40</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>17-02-2026 11:34:41</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>10-02-2026 11:31:11</t>
+          <t>17-02-2026 11:37:38</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>10-02-2026 11:30:36</t>
-        </is>
-      </c>
+          <t>17-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5728,19 +5720,19 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26160522229140001874</t>
+          <t>26160522425250002243</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5752,12 +5744,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>343612</t>
+          <t>344505</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21429</t>
+          <t>22322</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5767,17 +5759,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>OSCAR</t>
+          <t>KENIA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CARRERA</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5787,67 +5779,79 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6865906261</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>6869460269</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>03-08-2006</t>
+          <t>24-09-1981</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>OR629395@GMAIL.COM</t>
+          <t>KRISS0024@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>13-02-2026 20:02:16</t>
+          <t>17-02-2026 14:43:35</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>13-02-2026 20:03:49</t>
+          <t>17-02-2026 14:52:04</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>17-02-2026 14:49:23</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5855,14 +5859,14 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26160522330930002093</t>
+          <t>26160522430130002253</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5879,12 +5883,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>343714</t>
+          <t>342457</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21531</t>
+          <t>20274</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5894,17 +5898,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>OLVIA YISEL</t>
+          <t xml:space="preserve">JOSE </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>FRANCISCO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>FIERRO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5914,32 +5918,32 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6863667098</t>
+          <t>6861575086</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AV LAGO BAHIJASH 634</t>
+          <t>INDEPENDENCIA02</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>03-03-2001</t>
+          <t>15-09-1973</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>OLVIAHU18@GMAIL.COM</t>
+          <t>FIERRO_PACO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>14-02-2026 11:45:34</t>
+          <t>09-02-2026 19:49:15</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5960,17 +5964,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>14-02-2026 11:48:11</t>
+          <t>09-02-2026 19:51:47</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>14-02-2026 11:47:29</t>
+          <t>09-02-2026 19:50:53</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5990,7 +5994,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26160522347720002107</t>
+          <t>26160522212280001839</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -6002,7 +6006,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6014,12 +6018,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>343025</t>
+          <t>342583</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20842</t>
+          <t>20400</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6029,17 +6033,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DYLAN</t>
+          <t>SHESLY DENNIS</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6049,67 +6053,75 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6861698256</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>6861234727</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>PRESA DE LA ANGOSURA 1491</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>06-08-2002</t>
+          <t>30-07-1996</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>DYLANMTZM.26@GMAIL.COM</t>
+          <t>SHES.MEZAGTZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>11-02-2026 15:49:14</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 11:28:40</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>11-02-2026 15:52:21</t>
+          <t>10-02-2026 11:31:11</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>10-02-2026 11:30:36</t>
+        </is>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6117,19 +6129,19 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26160522267270001952</t>
+          <t>26160522229140001874</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6141,12 +6153,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>342783</t>
+          <t>344451</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20600</t>
+          <t>22268</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6156,17 +6168,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>TIFFANY JAZMIN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TAPIA</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AGUAYO</t>
+          <t>HOPKINS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6176,10 +6188,14 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6623654956</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>6866190407</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>IND22222</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6187,56 +6203,64 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>27-03-1998</t>
+          <t>06-09-2006</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>JOSETAPIAGUAYO@GMAIL.COM</t>
+          <t>NOTIENEEE@SSS.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>10-02-2026 18:11:07</t>
+          <t>17-02-2026 11:29:05</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>10-02-2026 18:12:38</t>
+          <t>17-02-2026 11:32:47</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>17-02-2026 11:32:10</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6244,19 +6268,19 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26160522242690001898</t>
+          <t>26160522425100002242</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6268,12 +6292,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>343557</t>
+          <t>344464</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21374</t>
+          <t>22281</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6283,17 +6307,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>JUAN CARLOS</t>
+          <t>MICHELLE JAZLIM</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>LEYVA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>RICO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6303,14 +6327,10 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6863903522</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6865111469</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6318,60 +6338,56 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>08-03-1971</t>
+          <t>09-02-1992</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>JUANCARLORIOS1422@GMAIL.COM</t>
+          <t>MICHELLE.RLEYVA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>13-02-2026 17:19:49</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>17-02-2026 12:06:32</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>13-02-2026 17:24:13</t>
+          <t>17-02-2026 12:07:57</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>13-02-2026 17:22:41</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6379,14 +6395,14 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26160522326350002078</t>
+          <t>26160522425750002244</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -6403,12 +6419,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>342997</t>
+          <t>344134</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20814</t>
+          <t>21951</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6418,17 +6434,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>JAZMIN</t>
+          <t>DANNA PAOLA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MOLINA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>ARROYO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6438,14 +6454,10 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8130964314</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>CERRO DEL POTOSI 1119</t>
-        </is>
-      </c>
+          <t>6531662052</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6453,60 +6465,56 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>18-03-1995</t>
+          <t>20-06-2006</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>YAAS.LOPEZ18@GMAIL.COM</t>
+          <t>MOLINAARROYODANNAPAOLA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>11-02-2026 14:53:46</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>16-02-2026 15:47:17</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>12-02-2026 12:36:52</t>
+          <t>16-02-2026 15:49:00</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>12-02-2026 12:36:23</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6514,19 +6522,19 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26180522292630004399</t>
+          <t>26160522393690002158</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6538,12 +6546,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>343135</t>
+          <t>344409</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20952</t>
+          <t>22226</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6553,17 +6561,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>JAIME</t>
+          <t>ISRAEL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>VELAZQUEZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>LIAÑO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6573,10 +6581,14 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6862316574</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>6863940285</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>EEEE12</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6584,52 +6596,64 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+          <t>18-04-1977</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>MASTERBOY1930@GMAIL.COM</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>11-02-2026 20:34:48</t>
+          <t>17-02-2026 08:06:52</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>13-02-2026 16:04:20</t>
+          <t>17-02-2026 08:09:37</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>17-02-2026 08:08:58</t>
+        </is>
+      </c>
       <c r="U46" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr"/>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6637,44 +6661,36 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26160522323640002074</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26160522421530002234</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>344451</t>
+          <t>344948</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>22268</t>
+          <t>22765</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6684,17 +6700,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>TIFFANY JAZMIN</t>
+          <t>KENIA LORENA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>HOPKINS</t>
+          <t>BATISTA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6704,67 +6720,67 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6866190407</t>
+          <t>6862417380</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>IND22222</t>
+          <t>INDEPENDENCIA 1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>06-09-2006</t>
+          <t>10-06-1998</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>NOTIENEEE@SSS.COM</t>
+          <t>KENIAMB98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>17-02-2026 11:29:05</t>
+          <t>18-02-2026 19:27:03</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>17-02-2026 11:32:47</t>
+          <t>18-02-2026 19:31:59</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>17-02-2026 11:32:10</t>
+          <t>18-02-2026 19:30:17</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6784,19 +6800,19 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26160522425100002242</t>
+          <t>26160522475220002354</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -6808,12 +6824,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>344464</t>
+          <t>342783</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22281</t>
+          <t>20600</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6823,17 +6839,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>MICHELLE JAZLIM</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t>TAPIA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RICO</t>
+          <t>AGUAYO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6843,28 +6859,28 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6865111469</t>
+          <t>6623654956</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>09-02-1992</t>
+          <t>27-03-1998</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>MICHELLE.RLEYVA@GMAIL.COM</t>
+          <t>JOSETAPIAGUAYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>17-02-2026 12:06:32</t>
+          <t>10-02-2026 18:11:07</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6879,28 +6895,28 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>17-02-2026 12:07:57</t>
+          <t>10-02-2026 18:12:38</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V48" t="inlineStr"/>
@@ -6911,19 +6927,19 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26160522425750002244</t>
+          <t>26160522242690001898</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6935,12 +6951,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>344453</t>
+          <t>342482</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>22270</t>
+          <t>20299</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6950,17 +6966,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>JESUS</t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>CACERES</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6970,7 +6986,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6861762359</t>
+          <t>6867220400</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6981,17 +6997,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>11-08-1951</t>
+          <t>25-08-1998</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>NOTIENE23445@DFDF.COM</t>
+          <t>JOSECACEREZ98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>17-02-2026 11:34:41</t>
+          <t>09-02-2026 20:20:01</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -7006,28 +7022,28 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>17-02-2026 11:37:38</t>
+          <t>09-02-2026 20:21:16</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V49" t="inlineStr"/>
@@ -7038,19 +7054,19 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26160522425250002243</t>
+          <t>26160522213460001843</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7062,12 +7078,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>344505</t>
+          <t>342997</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>20814</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7077,17 +7093,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KENIA</t>
+          <t>JAZMIN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7097,12 +7113,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6869460269</t>
+          <t>8130964314</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>CERRO DEL POTOSI 1119</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7112,24 +7128,20 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>24-09-1981</t>
+          <t>18-03-1995</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>KRISS0024@GMAIL.COM</t>
+          <t>YAAS.LOPEZ18@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>17-02-2026 14:43:35</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>11-02-2026 14:53:46</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7147,17 +7159,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>17-02-2026 14:52:04</t>
+          <t>12-02-2026 12:36:52</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>17-02-2026 14:49:23</t>
+          <t>12-02-2026 12:36:23</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7167,7 +7179,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -7177,7 +7189,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26160522430130002253</t>
+          <t>26180522292630004399</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
@@ -7189,7 +7201,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7201,12 +7213,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>344948</t>
+          <t>343135</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>22765</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7216,17 +7228,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>KENIA LORENA</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>OLIVAS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>BATISTA</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7236,32 +7248,24 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6862417380</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA 1</t>
-        </is>
-      </c>
+          <t>6862316574</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>10-06-1998</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>KENIAMB98@GMAIL.COM</t>
-        </is>
-      </c>
+          <t>01-01-2000</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>18-02-2026 19:27:03</t>
+          <t>11-02-2026 20:34:48</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7271,44 +7275,36 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>18-02-2026 19:31:59</t>
+          <t>13-02-2026 16:04:20</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>18-02-2026 19:30:17</t>
-        </is>
-      </c>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7316,14 +7312,22 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26160522475220002354</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
+          <t>26160522323640002074</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -7340,12 +7344,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>344134</t>
+          <t>343384</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21951</t>
+          <t>21201</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7355,17 +7359,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DANNA PAOLA</t>
+          <t>BRISA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MOLINA</t>
+          <t>GASCA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ARROYO</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7375,10 +7379,14 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6531662052</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>6863912198</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7386,56 +7394,60 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>20-06-2006</t>
+          <t>12-02-2006</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>MOLINAARROYODANNAPAOLA@GMAIL.COM</t>
+          <t>GNAVARROGASCA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>16-02-2026 15:47:17</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 19:16:27</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>16-02-2026 15:49:00</t>
+          <t>12-02-2026 19:22:02</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>12-02-2026 19:21:22</t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7443,14 +7455,14 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26160522393690002158</t>
+          <t>26160522304540002036</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -7467,12 +7479,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>344391</t>
+          <t>344132</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7482,17 +7494,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t xml:space="preserve">ANGELES </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>CARMONA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ARTEAGA</t>
+          <t>SIQUEIROS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7502,28 +7514,28 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6311261612</t>
+          <t>6863378715</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>18-06-1985</t>
+          <t>04-08-2006</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>COLORGRAFICO@HOTMAIL.COM</t>
+          <t>ANGELESWCARMONA763@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>17-02-2026 07:06:31</t>
+          <t>16-02-2026 15:44:25</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7538,22 +7550,22 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>17-02-2026 07:07:36</t>
+          <t>16-02-2026 15:45:32</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -7570,36 +7582,36 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26160522420050002226</t>
+          <t>26160522393400002157</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>344409</t>
+          <t>343139</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22226</t>
+          <t>20956</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7609,17 +7621,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ISRAEL</t>
+          <t>NICZA ARELI</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t>IZAGUIRRE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LIAÑO</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7629,39 +7641,35 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6863940285</t>
+          <t>6864650098</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>EEEE12</t>
+          <t xml:space="preserve">TORRE LAS ARCAS </t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>18-04-1977</t>
+          <t>03-11-1994</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>MASTERBOY1930@GMAIL.COM</t>
+          <t>IZAGUIRREARELI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>17-02-2026 08:06:52</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>11-02-2026 20:53:07</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7679,17 +7687,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>17-02-2026 08:09:37</t>
+          <t>13-02-2026 18:50:54</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>17-02-2026 08:08:58</t>
+          <t>13-02-2026 18:49:33</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7709,10 +7717,14 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26160522421530002234</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr"/>
+          <t>26170522328830002369</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
@@ -7721,7 +7733,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7733,12 +7745,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>344630</t>
+          <t>344345</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>22162</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7748,17 +7760,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>JESUS LEONEL</t>
+          <t>JESUS ANTONIO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>GALAVIZ</t>
+          <t>TOPETE</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7768,7 +7780,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6865866356</t>
+          <t>6865890812</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7779,17 +7791,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>28-10-1986</t>
+          <t>15-12-1987</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>JESUSLEONEL@GMAIL.COM</t>
+          <t>CHUYANTONT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>17-02-2026 17:54:18</t>
+          <t>16-02-2026 19:42:11</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7804,28 +7816,28 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>17-02-2026 17:56:16</t>
+          <t>16-02-2026 19:43:34</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V55" t="inlineStr"/>
@@ -7836,14 +7848,14 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26160522439290002266</t>
+          <t>26160522409070002196</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -7860,12 +7872,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>344929</t>
+          <t>344391</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22746</t>
+          <t>22208</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7875,17 +7887,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>ARTEAGA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7895,14 +7907,10 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>9371155830</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6311261612</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7910,64 +7918,56 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>18-06-1991</t>
+          <t>18-06-1985</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>ANGELMORENOOCHOA@GMAIL.COM</t>
+          <t>COLORGRAFICO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>18-02-2026 18:36:12</t>
+          <t>17-02-2026 07:06:31</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>18-02-2026 18:47:06</t>
+          <t>17-02-2026 07:07:36</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>18-02-2026 18:46:16</t>
-        </is>
-      </c>
+          <t>17-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7975,36 +7975,36 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26160522473470002345</t>
+          <t>26160522420050002226</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>342482</t>
+          <t>344630</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20299</t>
+          <t>22447</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8014,17 +8014,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>JESUS LEONEL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>GALAVIZ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CACERES</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6867220400</t>
+          <t>6865866356</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8045,17 +8045,17 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>25-08-1998</t>
+          <t>28-10-1986</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>JOSECACEREZ98@GMAIL.COM</t>
+          <t>JESUSLEONEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>09-02-2026 20:20:01</t>
+          <t>17-02-2026 17:54:18</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>09-02-2026 20:21:16</t>
+          <t>17-02-2026 17:56:16</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26160522213460001843</t>
+          <t>26160522439290002266</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -8126,12 +8126,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>343139</t>
+          <t>345376</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20956</t>
+          <t>87541</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8141,17 +8141,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NICZA ARELI</t>
+          <t>SOPHIA</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IZAGUIRRE</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6864650098</t>
+          <t>6865307488</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRE LAS ARCAS </t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8176,20 +8176,24 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>03-11-1994</t>
+          <t>26-06-1993</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>IZAGUIRREARELI@GMAIL.COM</t>
+          <t>SOPHIA.QUINDI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>11-02-2026 20:53:07</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>20-02-2026 17:55:33</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8207,17 +8211,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>13-02-2026 18:50:54</t>
+          <t>20-02-2026 18:01:22</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>13-02-2026 18:49:33</t>
+          <t>20-02-2026 18:00:10</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -8237,14 +8241,10 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26170522328830002369</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26160522533220002443</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -8265,145 +8265,562 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>345386</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>87551</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALEJANDRO </t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>LAURIAS</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>6866441611</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>10-08-1994</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>ALGSMQD26@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:13:38</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:16:09</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:15:32</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>26160522533690002445</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Sergio  Cordova Hernandez</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>345399</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>87564</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NATALIA</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>CASAREZ</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>VALLE</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>6861221578</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>09-11-1995</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NATALIACASAREZVALLE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:53:23</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:57:38</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:56:28</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>26160522534930002446</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>344929</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>22746</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ANGEL</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>OCHOA</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>9371155830</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>18-06-1991</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>ANGELMORENOOCHOA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>18-02-2026 18:36:12</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>18-02-2026 18:47:06</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>18-02-2026 18:46:16</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>26160522473470002345</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>344197</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>22014</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>INDEPENDENCIA</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>SILVIA</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>RODRIGUEZ</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>GARCIA</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>6863845214</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>INDEPENDENCIA1</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>01-01-2000</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>MARIA.932573@GMAIL.COM</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>16-02-2026 17:11:26</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>Tarifas 2026 LE</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>No Forzoso</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>RECURRENTE $649 LE</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>649</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>18-02-2026 17:47:52</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>18-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>18-02-2026 17:43:52</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>26160522470320002337</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>GUILLERMO  PALMA Y MEZA OTERO</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>649</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
+      <c r="AC62" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,12 +713,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>123833</t>
+          <t>158386</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>55922</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AKYEL</t>
+          <t xml:space="preserve">JESUS </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CASTANEDO</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -748,79 +748,67 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6531131589</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>DEL CARRIZO 3015</t>
-        </is>
-      </c>
+          <t>6861480734</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>01-10-2003</t>
+          <t>14-03-1988</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>AKYDANIELLA@GMAIL.COM</t>
+          <t>JEVE0336@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>19-09-2022 16:35:13</t>
+          <t>14-03-2023 12:55:14</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>17-02-2026 06:58:58</t>
+          <t>14-02-2026 09:55:56</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>17-02-2026 06:58:23</t>
-        </is>
-      </c>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -828,27 +816,19 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26160522419880002224</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
-        </is>
-      </c>
+          <t>26160522345220002100</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -860,12 +840,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>260403</t>
+          <t>123833</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>57907</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -875,17 +855,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAMUEL ESTEBAN</t>
+          <t>AKYEL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SERRANO</t>
+          <t>CASTANEDO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SERRANO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -895,53 +875,57 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6862393566</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6531131589</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>DEL CARRIZO 3015</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>28-05-2001</t>
+          <t>01-10-2003</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>SAMUELSESS32@GMAIL.COM</t>
+          <t>AKYDANIELLA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-10-2024 22:01:32</t>
+          <t>19-09-2022 16:35:13</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17-02-2026 17:05:51</t>
+          <t>17-02-2026 06:58:58</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -949,13 +933,21 @@
           <t>17-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>17-02-2026 06:58:23</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -963,14 +955,22 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26030522436260002152</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26160522419880002224</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -987,12 +987,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>158386</t>
+          <t>260403</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>55922</t>
+          <t>57907</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS </t>
+          <t>SAMUEL ESTEBAN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>SERRANO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>SERRANO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6861480734</t>
+          <t>6862393566</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,17 +1033,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>14-03-1988</t>
+          <t>28-05-2001</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>JEVE0336@GMAIL.COM</t>
+          <t>SAMUELSESS32@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>14-03-2023 12:55:14</t>
+          <t>02-10-2024 22:01:32</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1058,22 +1058,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14-02-2026 09:55:56</t>
+          <t>17-02-2026 17:05:51</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1090,19 +1090,19 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26160522345220002100</t>
+          <t>26030522436260002152</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1257,12 +1257,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>340481</t>
+          <t>73864</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>71680</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1272,17 +1272,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HILDA</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BENAVIDEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PEÑA</t>
+          <t xml:space="preserve">MONTESINOS </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1292,75 +1292,71 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6864150761</t>
+          <t>6862338385</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>LINEZO1</t>
+          <t>MISION SAN ISIDRO 338</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>21-07-1961</t>
+          <t>26-02-1982</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>NOTIERERER@TYU.COM</t>
+          <t>ALEXMONTECINOS7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>03-02-2026 08:55:15</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>21-02-2022 06:55:54</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>04-02-2026 10:23:34</t>
+          <t>23-02-2026 16:06:04</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>04-02-2026 10:22:30</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1368,44 +1364,36 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26160522071550001606</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
-        </is>
-      </c>
+          <t>26160522586190002504</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>337242</t>
+          <t>340481</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1403,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTHA ELENA </t>
+          <t>HILDA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MAEDA</t>
+          <t>BENAVIDEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,10 +1423,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6861253578</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>6864150761</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LINEZO1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1446,56 +1438,60 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>06-10-1952</t>
+          <t>21-07-1961</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>MARTHAELENAMG@GMAIL.COM</t>
+          <t>NOTIERERER@TYU.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>23-01-2026 12:52:24</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 08:55:15</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-02-2026 08:23:40</t>
+          <t>04-02-2026 10:23:34</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>04-02-2026 10:22:30</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1503,19 +1499,27 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26160522033610001514</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+          <t>26160522071550001606</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1527,12 +1531,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>340791</t>
+          <t>340713</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1542,17 +1546,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HECTOR MANUEL</t>
+          <t>LESLIE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ALVARADO</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1562,32 +1566,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5628369350</t>
+          <t>6865257334</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MAYA CAMPESTRE</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>09-08-1976</t>
+          <t>10-06-1994</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>MACALVMAIL@GMAIL.COM</t>
+          <t>LICMERCADOSUNA.10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>03-02-2026 18:47:52</t>
+          <t>03-02-2026 17:15:35</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1608,7 +1612,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-02-2026 19:09:42</t>
+          <t>03-02-2026 17:19:02</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1618,7 +1622,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>03-02-2026 19:09:20</t>
+          <t>03-02-2026 17:18:43</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1628,7 +1632,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1638,14 +1642,10 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26160522055330001568</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26160522048750001552</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1666,12 +1666,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>340808</t>
+          <t>337242</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18626</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1681,17 +1681,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>RENE</t>
+          <t xml:space="preserve">MARTHA ELENA </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MAEDA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1701,75 +1701,67 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6863485358</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA 23</t>
-        </is>
-      </c>
+          <t>6861253578</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>15-09-1996</t>
+          <t>06-10-1952</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>RENEGONZALEZ1@GMAIL.COM</t>
+          <t>MARTHAELENAMG@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>03-02-2026 19:14:48</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>23-01-2026 12:52:24</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>05-02-2026 19:04:55</t>
+          <t>03-02-2026 08:23:40</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>05-02-2026 19:03:37</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1777,27 +1769,19 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26160522117360001694</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26160522033610001514</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1809,12 +1793,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>340713</t>
+          <t>340791</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1824,17 +1808,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LESLIE</t>
+          <t>HECTOR MANUEL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>ALVARADO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1844,32 +1828,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6865257334</t>
+          <t>5628369350</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>MAYA CAMPESTRE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>10-06-1994</t>
+          <t>09-08-1976</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>LICMERCADOSUNA.10@GMAIL.COM</t>
+          <t>MACALVMAIL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-02-2026 17:15:35</t>
+          <t>03-02-2026 18:47:52</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1890,7 +1874,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-02-2026 17:19:02</t>
+          <t>03-02-2026 19:09:42</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1900,7 +1884,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>03-02-2026 17:18:43</t>
+          <t>03-02-2026 19:09:20</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1910,7 +1894,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1920,10 +1904,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26160522048750001552</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
+          <t>26160522055330001568</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1944,12 +1932,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>290316</t>
+          <t>340808</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>87814</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1959,17 +1947,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VANESSA</t>
+          <t>RENE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HIGUERA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1979,12 +1967,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6861744727</t>
+          <t>6863485358</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 1</t>
+          <t>INDEPENDENCIA 23</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1994,17 +1982,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>22-07-1992</t>
+          <t>15-09-1996</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>HIGUERAROSAV@GMAIL.COM</t>
+          <t>RENEGONZALEZ1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>28-04-2025 19:34:24</t>
+          <t>03-02-2026 19:14:48</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2025,17 +2013,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>14-02-2026 15:01:10</t>
+          <t>05-02-2026 19:04:55</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>14-02-2026 15:00:36</t>
+          <t>05-02-2026 19:03:37</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2055,15 +2043,19 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26160522349780002121</t>
+          <t>26160522117360001694</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>499</t>
@@ -2071,7 +2063,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2083,12 +2075,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>341834</t>
+          <t>290316</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19652</t>
+          <t>87814</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2098,17 +2090,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DARIANA</t>
+          <t>VANESSA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>HIGUERA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2118,32 +2110,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6862489316</t>
+          <t>6861744727</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SAN CARLO1</t>
+          <t>INDEPENDENCIA 1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>03-12-1981</t>
+          <t>22-07-1992</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>LOPEZDARIANA780@GMAIL.COM</t>
+          <t>HIGUERAROSAV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>07-02-2026 13:31:41</t>
+          <t>28-04-2025 19:34:24</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2164,17 +2156,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>07-02-2026 13:38:04</t>
+          <t>14-02-2026 15:01:10</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>07-02-2026 13:35:50</t>
+          <t>14-02-2026 15:00:36</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2184,7 +2176,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2194,10 +2186,14 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26160522161810001766</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
+          <t>26160522349780002121</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
@@ -2206,7 +2202,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2218,12 +2214,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>339686</t>
+          <t>341132</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17504</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2233,17 +2229,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EDUARDO</t>
+          <t xml:space="preserve">NAHOMI ESTEFANIA </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>TALAMANTES</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2253,39 +2249,35 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6862121992</t>
+          <t>6643120858</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>I988</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>06-05-1992</t>
+          <t>18-08-1996</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>POLOEGARCIA@GMAIL.COM</t>
+          <t>ESTEFANIAMTALAMANTESX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>31-01-2026 12:59:25</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>04-02-2026 18:08:31</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2303,17 +2295,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>18-02-2026 13:22:14</t>
+          <t>10-02-2026 16:06:43</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>18-02-2026 13:21:09</t>
+          <t>10-02-2026 16:05:59</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2333,7 +2325,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26160522461460002325</t>
+          <t>26130522235720002570</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2343,7 +2335,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>auxiliar independencia mexicali</t>
+          <t>MARIA CANDELARIA LARA AVILA</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2353,24 +2345,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>341132</t>
+          <t>341834</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2380,17 +2372,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAHOMI ESTEFANIA </t>
+          <t>DARIANA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TALAMANTES</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2400,12 +2392,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6643120858</t>
+          <t>6862489316</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>SAN CARLO1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2415,17 +2407,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>18-08-1996</t>
+          <t>03-12-1981</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ESTEFANIAMTALAMANTESX@GMAIL.COM</t>
+          <t>LOPEZDARIANA780@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>04-02-2026 18:08:31</t>
+          <t>07-02-2026 13:31:41</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2446,17 +2438,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>10-02-2026 16:06:43</t>
+          <t>07-02-2026 13:38:04</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>10-02-2026 16:05:59</t>
+          <t>07-02-2026 13:35:50</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2476,19 +2468,11 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26130522235720002570</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>MARIA CANDELARIA LARA AVILA</t>
-        </is>
-      </c>
+          <t>26160522161810001766</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
           <t>499</t>
@@ -2496,7 +2480,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2508,12 +2492,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>238288</t>
+          <t>342294</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>35793</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2523,17 +2507,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SILVIA PAOLA</t>
+          <t>CARLOS ANTONIO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PAYAN</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2543,75 +2527,67 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6864629400</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>IND123</t>
-        </is>
-      </c>
+          <t>6863473949</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>18-02-2009</t>
+          <t>25-10-2003</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>SILVIAPAYAN009@GMAIL.COM</t>
+          <t>CARLOS8A2510@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>05-06-2024 18:12:25</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>09-02-2026 16:59:55</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>10-02-2026 05:33:30</t>
+          <t>09-02-2026 17:01:28</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>10-02-2026 05:32:15</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2619,27 +2595,19 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26160522222220001861</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26160522200300001806</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2651,12 +2619,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>299954</t>
+          <t>341819</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>97452</t>
+          <t>19637</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2666,19 +2634,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EUNICE</t>
+          <t>KARYME</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>MACIAS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>LOPEZ</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>MARTINEZ</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>52</t>
@@ -2686,14 +2654,10 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6865848338</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>IND123</t>
-        </is>
-      </c>
+          <t>6861351566</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2701,60 +2665,56 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>11-06-2001</t>
+          <t>11-12-2004</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>EUNICE.LOPEZ5@UABC.EDU.MX</t>
+          <t>KARYMEMACLOP@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>23-06-2025 18:39:49</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>07-02-2026 12:03:12</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>09-02-2026 08:55:34</t>
+          <t>07-02-2026 12:05:36</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>09-02-2026 08:54:52</t>
-        </is>
-      </c>
+          <t>07-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2762,23 +2722,19 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26160522185470001787</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26160522160500001761</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2790,12 +2746,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>341819</t>
+          <t>238288</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19637</t>
+          <t>35793</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2805,17 +2761,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KARYME</t>
+          <t>SILVIA PAOLA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>PAYAN</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2825,10 +2781,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6861351566</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>6864629400</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>IND123</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2836,56 +2796,60 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>11-12-2004</t>
+          <t>18-02-2009</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>KARYMEMACLOP@GMAIL.COM</t>
+          <t>SILVIAPAYAN009@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>07-02-2026 12:03:12</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-06-2024 18:12:25</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>07-02-2026 12:05:36</t>
+          <t>10-02-2026 05:33:30</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>10-02-2026 05:32:15</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2893,19 +2857,27 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26160522160500001761</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>26160522222220001861</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2917,12 +2889,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>342323</t>
+          <t>299954</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>97452</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2932,7 +2904,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MARCO</t>
+          <t>EUNICE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2942,7 +2914,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ORDUÑO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2952,32 +2924,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6861601599</t>
+          <t>6865848338</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA0</t>
+          <t>IND123</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>25-04-1979</t>
+          <t>11-06-2001</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>MOPILLO@GMAIL.COM</t>
+          <t>EUNICE.LOPEZ5@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>09-02-2026 17:27:09</t>
+          <t>23-06-2025 18:39:49</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2998,7 +2970,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>09-02-2026 17:33:13</t>
+          <t>09-02-2026 08:55:34</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -3008,7 +2980,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>09-02-2026 17:32:43</t>
+          <t>09-02-2026 08:54:52</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3018,7 +2990,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -3028,10 +3000,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26160522202710001810</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
+          <t>26160522185470001787</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
@@ -3040,7 +3016,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3052,12 +3028,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>340255</t>
+          <t>342323</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18073</t>
+          <t>20141</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3067,17 +3043,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>STEPHANY</t>
+          <t>MARCO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BEJARANO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ENRIQUEZ</t>
+          <t>ORDUÑO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3087,32 +3063,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6865923181</t>
+          <t>6861601599</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 38</t>
+          <t>INDEPENDENCIA0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>18-01-1995</t>
+          <t>25-04-1979</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>FANNYBEJARANO904@GMAIL.COM</t>
+          <t>MOPILLO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-02-2026 16:15:36</t>
+          <t>09-02-2026 17:27:09</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3133,17 +3109,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-02-2026 16:21:03</t>
+          <t>09-02-2026 17:33:13</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>02-02-2026 16:20:43</t>
+          <t>09-02-2026 17:32:43</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3153,7 +3129,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3163,7 +3139,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26160522016270001486</t>
+          <t>26160522202710001810</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3175,7 +3151,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3187,12 +3163,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>342294</t>
+          <t>339686</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3202,17 +3178,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CARLOS ANTONIO</t>
+          <t>EDUARDO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3222,10 +3198,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6863473949</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>6862121992</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>I988</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3233,56 +3213,64 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>25-10-2003</t>
+          <t>06-05-1992</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CARLOS8A2510@GMAIL.COM</t>
+          <t>POLOEGARCIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>09-02-2026 16:59:55</t>
+          <t>31-01-2026 12:59:25</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>09-02-2026 17:01:28</t>
+          <t>18-02-2026 13:22:14</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>18-02-2026 13:21:09</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3290,36 +3278,44 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26160522200300001806</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+          <t>26160522461460002325</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>auxiliar independencia mexicali</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>342087</t>
+          <t>340255</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19905</t>
+          <t>18073</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3329,17 +3325,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KARLA VERÓNICA</t>
+          <t>STEPHANY</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>BEJARANO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PALAFOX</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3349,12 +3345,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6861244927</t>
+          <t>6865923181</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>IND111111</t>
+          <t>INDEPENDENCIA 38</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3364,52 +3360,48 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>26-05-1986</t>
+          <t>18-01-1995</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>VERONIKAPALAFOX@GMAIL.COM</t>
+          <t>FANNYBEJARANO904@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>09-02-2026 10:07:36</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 16:15:36</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>16-02-2026 08:19:11</t>
+          <t>02-02-2026 16:21:03</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>16-02-2026 08:18:23</t>
+          <t>02-02-2026 16:20:43</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3419,7 +3411,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3429,27 +3421,19 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26160522380750002134</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
-        </is>
-      </c>
+          <t>26160522016270001486</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3461,12 +3445,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>342336</t>
+          <t>342822</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3476,17 +3460,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MARCO ALEJANDRO</t>
+          <t>LEOPOLDO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>LOYO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>COBO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3496,12 +3480,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6861632588</t>
+          <t>6862120595</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA01</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3511,17 +3495,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>12-05-2006</t>
+          <t>17-07-1971</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>6MALLISME9@GMAIL.COM</t>
+          <t>LEOPOLDOLOYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>09-02-2026 17:35:12</t>
+          <t>10-02-2026 19:02:43</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3542,17 +3526,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>09-02-2026 17:38:30</t>
+          <t>14-02-2026 13:28:02</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>09-02-2026 17:38:05</t>
+          <t>14-02-2026 13:27:04</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3572,10 +3556,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26160522203170001811</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr"/>
+          <t>26160522349290002113</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
@@ -3584,7 +3572,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3596,12 +3584,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>342474</t>
+          <t>342336</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3611,17 +3599,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MELISSA</t>
+          <t>MARCO ALEJANDRO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3631,7 +3619,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6863242180</t>
+          <t>6861632588</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3641,22 +3629,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>25-07-1987</t>
+          <t>12-05-2006</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>YLEM51@GMAIL.COM</t>
+          <t>6MALLISME9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>09-02-2026 20:08:06</t>
+          <t>09-02-2026 17:35:12</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3677,7 +3665,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>09-02-2026 20:12:28</t>
+          <t>09-02-2026 17:38:30</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3687,7 +3675,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>09-02-2026 20:10:07</t>
+          <t>09-02-2026 17:38:05</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3707,7 +3695,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26160522213110001840</t>
+          <t>26160522203170001811</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3731,12 +3719,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>342794</t>
+          <t>342087</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>19905</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3746,17 +3734,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>JOSUE</t>
+          <t>KARLA VERÓNICA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>PALAFOX</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3766,63 +3754,67 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6861127057</t>
+          <t>6861244927</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>INDEPENDENCI1</t>
+          <t>IND111111</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>26-11-1989</t>
+          <t>26-05-1986</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>JOSUEBRMUSIC@GMAIL.COM</t>
+          <t>VERONIKAPALAFOX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>10-02-2026 18:25:08</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>09-02-2026 10:07:36</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>10-02-2026 18:27:56</t>
+          <t>16-02-2026 08:19:11</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>10-02-2026 18:27:24</t>
+          <t>16-02-2026 08:18:23</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3832,7 +3824,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3842,19 +3834,27 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26160522243630001901</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+          <t>26160522380750002134</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3866,12 +3866,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>343140</t>
+          <t>340641</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>18459</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">VANESSA </t>
+          <t>LUCIA YADIRA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>VELARDE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3901,12 +3901,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6864164007</t>
+          <t>6861822416</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AV TORRE LAS ARCAS 2045</t>
+          <t>CULTURA OLMECA 3608</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3916,17 +3916,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>08-11-1989</t>
+          <t>13-12-1990</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>VANESSAGALVANR250210@GMAIL.COM</t>
+          <t>YADIRA_1290@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>11-02-2026 20:55:11</t>
+          <t>03-02-2026 15:56:48</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3947,17 +3947,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>13-02-2026 18:56:17</t>
+          <t>05-02-2026 16:33:17</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>13-02-2026 18:55:42</t>
+          <t>05-02-2026 16:30:37</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3977,15 +3977,19 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26170522329060002370</t>
+          <t>26160522110560001680</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>499</t>
@@ -3993,7 +3997,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4005,12 +4009,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>342478</t>
+          <t>340697</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20295</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4020,12 +4024,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FERNANDO</t>
+          <t>CRISTIAN ISMAEL</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4040,12 +4044,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6861146223</t>
+          <t>6863537341</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA01</t>
+          <t>INDEPENDENCIA3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4055,17 +4059,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>27-04-1993</t>
+          <t>22-06-1995</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>IVANRNAVARRO12@GMAIL.COM</t>
+          <t>CRISTIAN.TORRES@GCADENA.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>09-02-2026 20:13:50</t>
+          <t>03-02-2026 17:02:34</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4086,17 +4090,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>09-02-2026 20:16:34</t>
+          <t>03-02-2026 17:06:48</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>09-02-2026 20:16:03</t>
+          <t>03-02-2026 17:06:13</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4116,7 +4120,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26160522213270001841</t>
+          <t>26160522047970001551</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
@@ -4128,7 +4132,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4140,12 +4144,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>340789</t>
+          <t>342474</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>18607</t>
+          <t>20291</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4155,17 +4159,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIELA </t>
+          <t>MELISSA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4175,12 +4179,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6861739204</t>
+          <t>6863242180</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MAYA CAMPESTRE</t>
+          <t>INDEPENDENCIA01</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4190,17 +4194,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>06-09-1989</t>
+          <t>25-07-1987</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>DANIELA.SANCHEZ.MORENO.89@GMAIL.COM</t>
+          <t>YLEM51@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>03-02-2026 18:45:03</t>
+          <t>09-02-2026 20:08:06</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4221,17 +4225,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>03-02-2026 19:05:49</t>
+          <t>09-02-2026 20:12:28</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>03-02-2026 19:04:34</t>
+          <t>09-02-2026 20:10:07</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4241,7 +4245,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4251,14 +4255,10 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26160522055070001567</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26160522213110001840</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4279,12 +4279,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>340641</t>
+          <t>342794</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4294,17 +4294,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LUCIA YADIRA</t>
+          <t>JOSUE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>VELARDE</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6861822416</t>
+          <t>6861127057</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CULTURA OLMECA 3608</t>
+          <t>INDEPENDENCI1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>13-12-1990</t>
+          <t>26-11-1989</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>YADIRA_1290@HOTMAIL.COM</t>
+          <t>JOSUEBRMUSIC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>03-02-2026 15:56:48</t>
+          <t>10-02-2026 18:25:08</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4360,17 +4360,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>05-02-2026 16:33:17</t>
+          <t>10-02-2026 18:27:56</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>05-02-2026 16:30:37</t>
+          <t>10-02-2026 18:27:24</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4390,19 +4390,11 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26160522110560001680</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26160522243630001901</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
           <t>499</t>
@@ -4410,7 +4402,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4422,12 +4414,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>340697</t>
+          <t>343713</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>21530</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4437,17 +4429,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CRISTIAN ISMAEL</t>
+          <t>JESSICA ALEJANDRA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4457,32 +4449,32 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6863537341</t>
+          <t>6863648770</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA3</t>
+          <t>JOSE MARIA AGUAYO 506</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>22-06-1995</t>
+          <t>18-01-2006</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CRISTIAN.TORRES@GCADENA.COM</t>
+          <t>JESSICAA.GUTIERREZ@CETYS.EDU.MX</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>03-02-2026 17:02:34</t>
+          <t>14-02-2026 11:38:52</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4503,17 +4495,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>03-02-2026 17:06:48</t>
+          <t>14-02-2026 11:41:20</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>03-02-2026 17:06:13</t>
+          <t>14-02-2026 11:40:29</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4533,7 +4525,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26160522047970001551</t>
+          <t>26160522347590002106</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4545,7 +4537,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4557,12 +4549,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342822</t>
+          <t>342776</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20639</t>
+          <t>20593</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4572,17 +4564,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LEOPOLDO</t>
+          <t>JUAN MANUEL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LOYO</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>COBO</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4592,7 +4584,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6862120595</t>
+          <t>6867292744</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4607,17 +4599,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>17-07-1971</t>
+          <t>09-11-1973</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>LEOPOLDOLOYO@GMAIL.COM</t>
+          <t>NOCUENTACON1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10-02-2026 19:02:43</t>
+          <t>10-02-2026 18:03:21</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4638,17 +4630,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>14-02-2026 13:28:02</t>
+          <t>10-02-2026 18:35:28</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>14-02-2026 13:27:04</t>
+          <t>10-02-2026 18:35:08</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4658,7 +4650,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4668,14 +4660,10 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26160522349290002113</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26160522243990001903</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
@@ -4696,12 +4684,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>342776</t>
+          <t>343025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20593</t>
+          <t>20842</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4711,17 +4699,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>JUAN MANUEL</t>
+          <t>DYLAN</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4731,14 +4719,10 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6867292744</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6861698256</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4746,60 +4730,56 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>09-11-1973</t>
+          <t>06-08-2002</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>NOCUENTACON1@GMAIL.COM</t>
+          <t>DYLANMTZM.26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>10-02-2026 18:03:21</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>11-02-2026 15:49:14</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>10-02-2026 18:35:28</t>
+          <t>11-02-2026 15:52:21</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>10-02-2026 18:35:08</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4807,19 +4787,19 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26160522243990001903</t>
+          <t>26160522267270001952</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4831,12 +4811,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>342580</t>
+          <t>343140</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20397</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4846,17 +4826,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>HECTOR MANUEL</t>
+          <t xml:space="preserve">VANESSA </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PIÑA</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OLIVEROS</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4866,67 +4846,75 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6865895862</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>6864164007</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>AV TORRE LAS ARCAS 2045</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>17-10-2002</t>
+          <t>08-11-1989</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>NOTIENE11112222@FFFFDDD.COM</t>
+          <t>VANESSAGALVANR250210@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>10-02-2026 10:48:52</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>11-02-2026 20:55:11</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>10-02-2026 10:50:12</t>
+          <t>13-02-2026 18:56:17</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>10-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>13-02-2026 18:55:42</t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4934,19 +4922,23 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26160522228650001872</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
+          <t>26170522329060002370</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4958,12 +4950,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>343612</t>
+          <t>342478</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21429</t>
+          <t>20295</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4973,17 +4965,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>OSCAR</t>
+          <t>FERNANDO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CARRERA</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4993,10 +4985,14 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6865906261</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>6861146223</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA01</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5004,56 +5000,60 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>03-08-2006</t>
+          <t>27-04-1993</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>OR629395@GMAIL.COM</t>
+          <t>IVANRNAVARRO12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>13-02-2026 20:02:16</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 20:13:50</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>13-02-2026 20:03:49</t>
+          <t>09-02-2026 20:16:34</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>09-02-2026 20:16:03</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5061,19 +5061,19 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26160522330930002093</t>
+          <t>26160522213270001841</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>343714</t>
+          <t>342580</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21531</t>
+          <t>20397</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OLVIA YISEL</t>
+          <t>HECTOR MANUEL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>PIÑA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>OLIVEROS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5120,75 +5120,67 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6863667098</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>AV LAGO BAHIJASH 634</t>
-        </is>
-      </c>
+          <t>6865895862</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>03-03-2001</t>
+          <t>17-10-2002</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>OLVIAHU18@GMAIL.COM</t>
+          <t>NOTIENE11112222@FFFFDDD.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>14-02-2026 11:45:34</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>10-02-2026 10:48:52</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>14-02-2026 11:48:11</t>
+          <t>10-02-2026 10:50:12</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>14-02-2026 11:47:29</t>
-        </is>
-      </c>
+          <t>10-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5196,19 +5188,19 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26160522347720002107</t>
+          <t>26160522228650001872</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5220,12 +5212,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>343025</t>
+          <t>343612</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20842</t>
+          <t>21429</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5235,17 +5227,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DYLAN</t>
+          <t>OSCAR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t>CARRERA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5255,7 +5247,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6861698256</t>
+          <t>6865906261</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5266,17 +5258,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>06-08-2002</t>
+          <t>03-08-2006</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>DYLANMTZM.26@GMAIL.COM</t>
+          <t>OR629395@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>11-02-2026 15:49:14</t>
+          <t>13-02-2026 20:02:16</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5301,18 +5293,18 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>11-02-2026 15:52:21</t>
+          <t>13-02-2026 20:03:49</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V36" t="inlineStr"/>
@@ -5323,7 +5315,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26160522267270001952</t>
+          <t>26160522330930002093</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
@@ -5335,7 +5327,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5347,12 +5339,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>343713</t>
+          <t>343714</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>21531</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5362,17 +5354,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JESSICA ALEJANDRA</t>
+          <t>OLVIA YISEL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5382,12 +5374,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6863648770</t>
+          <t>6863667098</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>JOSE MARIA AGUAYO 506</t>
+          <t>AV LAGO BAHIJASH 634</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5397,17 +5389,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>18-01-2006</t>
+          <t>03-03-2001</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>JESSICAA.GUTIERREZ@CETYS.EDU.MX</t>
+          <t>OLVIAHU18@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>14-02-2026 11:38:52</t>
+          <t>14-02-2026 11:45:34</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5428,7 +5420,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>14-02-2026 11:41:20</t>
+          <t>14-02-2026 11:48:11</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -5438,7 +5430,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>14-02-2026 11:40:29</t>
+          <t>14-02-2026 11:47:29</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5448,7 +5440,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5458,7 +5450,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26160522347590002106</t>
+          <t>26160522347720002107</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -5482,12 +5474,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>343557</t>
+          <t>340789</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21374</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5497,17 +5489,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>JUAN CARLOS</t>
+          <t xml:space="preserve">DANIELA </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5517,12 +5509,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6863903522</t>
+          <t>6861739204</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>MAYA CAMPESTRE</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5532,17 +5524,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>08-03-1971</t>
+          <t>06-09-1989</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>JUANCARLORIOS1422@GMAIL.COM</t>
+          <t>DANIELA.SANCHEZ.MORENO.89@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>13-02-2026 17:19:49</t>
+          <t>03-02-2026 18:45:03</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5563,17 +5555,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>13-02-2026 17:24:13</t>
+          <t>03-02-2026 19:05:49</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>13-02-2026 17:22:41</t>
+          <t>03-02-2026 19:04:34</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5593,10 +5585,14 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26160522326350002078</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr"/>
+          <t>26160522055070001567</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
@@ -5605,7 +5601,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5617,12 +5613,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>344453</t>
+          <t>343557</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22270</t>
+          <t>21374</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5632,17 +5628,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>JESUS</t>
+          <t>JUAN CARLOS</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5652,67 +5648,75 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6861762359</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>6863903522</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>11-08-1951</t>
+          <t>08-03-1971</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>NOTIENE23445@DFDF.COM</t>
+          <t>JUANCARLORIOS1422@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>17-02-2026 11:34:41</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>13-02-2026 17:19:49</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>17-02-2026 11:37:38</t>
+          <t>13-02-2026 17:24:13</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>13-02-2026 17:22:41</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5720,19 +5724,19 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26160522425250002243</t>
+          <t>26160522326350002078</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5744,12 +5748,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>344505</t>
+          <t>345721</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>87886</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5759,17 +5763,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KENIA</t>
+          <t>J ASUNCION</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5779,32 +5783,32 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6869460269</t>
+          <t>6861754997</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>RIO AMECA 1896</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>24-09-1981</t>
+          <t>14-01-1981</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>KRISS0024@GMAIL.COM</t>
+          <t>RODRILOVEMX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>17-02-2026 14:43:35</t>
+          <t>23-02-2026 12:02:31</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5829,17 +5833,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>17-02-2026 14:52:04</t>
+          <t>23-02-2026 12:11:56</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>17-02-2026 14:49:23</t>
+          <t>23-02-2026 12:08:50</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5849,7 +5853,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5859,7 +5863,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26160522430130002253</t>
+          <t>26160522578360002492</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -5871,7 +5875,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5883,12 +5887,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>342457</t>
+          <t>344453</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20274</t>
+          <t>22270</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5898,17 +5902,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE </t>
+          <t>JESUS</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FRANCISCO</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FIERRO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5918,14 +5922,10 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6861575086</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA02</t>
-        </is>
-      </c>
+          <t>6861762359</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5933,60 +5933,56 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>15-09-1973</t>
+          <t>11-08-1951</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>FIERRO_PACO@HOTMAIL.COM</t>
+          <t>NOTIENE23445@DFDF.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>09-02-2026 19:49:15</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>17-02-2026 11:34:41</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>09-02-2026 19:51:47</t>
+          <t>17-02-2026 11:37:38</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>09-02-2026 19:50:53</t>
-        </is>
-      </c>
+          <t>17-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5994,19 +5990,19 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26160522212280001839</t>
+          <t>26160522425250002243</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6018,12 +6014,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>342583</t>
+          <t>344505</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20400</t>
+          <t>22322</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6033,17 +6029,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SHESLY DENNIS</t>
+          <t>KENIA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6053,12 +6049,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6861234727</t>
+          <t>6869460269</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>PRESA DE LA ANGOSURA 1491</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6068,20 +6064,24 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>30-07-1996</t>
+          <t>24-09-1981</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>SHES.MEZAGTZ@GMAIL.COM</t>
+          <t>KRISS0024@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>10-02-2026 11:28:40</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>17-02-2026 14:43:35</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6099,17 +6099,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>10-02-2026 11:31:11</t>
+          <t>17-02-2026 14:52:04</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>10-02-2026 11:30:36</t>
+          <t>17-02-2026 14:49:23</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26160522229140001874</t>
+          <t>26160522430130002253</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6292,12 +6292,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>344464</t>
+          <t>344042</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>22281</t>
+          <t>21859</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6307,17 +6307,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MICHELLE JAZLIM</t>
+          <t xml:space="preserve">FELISA </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t>ANGUAMEA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>RICO</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6865111469</t>
+          <t>6442161660</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6338,24 +6338,20 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>09-02-1992</t>
+          <t>01-01-2000</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>MICHELLE.RLEYVA@GMAIL.COM</t>
+          <t>FELISAANGUAMEAVALENZUELA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>17-02-2026 12:06:32</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>16-02-2026 12:24:29</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -6363,22 +6359,22 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>17-02-2026 12:07:57</t>
+          <t>23-02-2026 18:27:10</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>23-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -6395,36 +6391,44 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26160522425750002244</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
+          <t>26060522595620004368</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>344134</t>
+          <t>344464</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21951</t>
+          <t>22281</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6434,17 +6438,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DANNA PAOLA</t>
+          <t>MICHELLE JAZLIM</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MOLINA</t>
+          <t>LEYVA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ARROYO</t>
+          <t>RICO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6454,7 +6458,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6531662052</t>
+          <t>6865111469</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6465,17 +6469,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>20-06-2006</t>
+          <t>09-02-1992</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>MOLINAARROYODANNAPAOLA@GMAIL.COM</t>
+          <t>MICHELLE.RLEYVA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>16-02-2026 15:47:17</t>
+          <t>17-02-2026 12:06:32</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6500,18 +6504,18 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>16-02-2026 15:49:00</t>
+          <t>17-02-2026 12:07:57</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V45" t="inlineStr"/>
@@ -6522,7 +6526,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26160522393690002158</t>
+          <t>26160522425750002244</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
@@ -6546,12 +6550,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>344409</t>
+          <t>344948</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>22226</t>
+          <t>22765</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6561,17 +6565,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ISRAEL</t>
+          <t>KENIA LORENA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>LIAÑO</t>
+          <t>BATISTA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6581,67 +6585,67 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6863940285</t>
+          <t>6862417380</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>EEEE12</t>
+          <t>INDEPENDENCIA 1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>18-04-1977</t>
+          <t>10-06-1998</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>MASTERBOY1930@GMAIL.COM</t>
+          <t>KENIAMB98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>17-02-2026 08:06:52</t>
+          <t>18-02-2026 19:27:03</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>17-02-2026 08:09:37</t>
+          <t>18-02-2026 19:31:59</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>17-02-2026 08:08:58</t>
+          <t>18-02-2026 19:30:17</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6661,19 +6665,19 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26160522421530002234</t>
+          <t>26160522475220002354</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6685,12 +6689,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>344948</t>
+          <t>344134</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>22765</t>
+          <t>21951</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6700,17 +6704,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KENIA LORENA</t>
+          <t>DANNA PAOLA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MOLINA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BATISTA</t>
+          <t>ARROYO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6720,14 +6724,10 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6862417380</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA 1</t>
-        </is>
-      </c>
+          <t>6531662052</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6735,17 +6735,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>10-06-1998</t>
+          <t>20-06-2006</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>KENIAMB98@GMAIL.COM</t>
+          <t>MOLINAARROYODANNAPAOLA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>18-02-2026 19:27:03</t>
+          <t>16-02-2026 15:47:17</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6755,44 +6755,36 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>18-02-2026 19:31:59</t>
+          <t>16-02-2026 15:49:00</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>18-02-2026 19:30:17</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6800,14 +6792,14 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26160522475220002354</t>
+          <t>26160522393690002158</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6824,12 +6816,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>342783</t>
+          <t>344409</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20600</t>
+          <t>22226</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6839,17 +6831,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>ISRAEL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TAPIA</t>
+          <t>VELAZQUEZ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AGUAYO</t>
+          <t>LIAÑO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6859,10 +6851,14 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6623654956</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>6863940285</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>EEEE12</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6870,56 +6866,64 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>27-03-1998</t>
+          <t>18-04-1977</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>JOSETAPIAGUAYO@GMAIL.COM</t>
+          <t>MASTERBOY1930@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>10-02-2026 18:11:07</t>
+          <t>17-02-2026 08:06:52</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>10-02-2026 18:12:38</t>
+          <t>17-02-2026 08:09:37</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>17-02-2026 08:08:58</t>
+        </is>
+      </c>
       <c r="U48" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6927,19 +6931,19 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26160522242690001898</t>
+          <t>26160522421530002234</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6951,12 +6955,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>342482</t>
+          <t>342457</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20299</t>
+          <t>20274</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6966,17 +6970,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t xml:space="preserve">JOSE </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>FRANCISCO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CACERES</t>
+          <t>FIERRO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6986,10 +6990,14 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6867220400</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>6861575086</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA02</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6997,42 +7005,38 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>25-08-1998</t>
+          <t>15-09-1973</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>JOSECACEREZ98@GMAIL.COM</t>
+          <t>FIERRO_PACO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>09-02-2026 20:20:01</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 19:49:15</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>09-02-2026 20:21:16</t>
+          <t>09-02-2026 19:51:47</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -7040,13 +7044,21 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr"/>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>09-02-2026 19:50:53</t>
+        </is>
+      </c>
       <c r="U49" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7054,14 +7066,14 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26160522213460001843</t>
+          <t>26160522212280001839</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -7078,12 +7090,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>342997</t>
+          <t>342583</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20814</t>
+          <t>20400</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7093,17 +7105,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>JAZMIN</t>
+          <t>SHESLY DENNIS</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7113,12 +7125,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8130964314</t>
+          <t>6861234727</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CERRO DEL POTOSI 1119</t>
+          <t>PRESA DE LA ANGOSURA 1491</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7128,17 +7140,17 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>18-03-1995</t>
+          <t>30-07-1996</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>YAAS.LOPEZ18@GMAIL.COM</t>
+          <t>SHES.MEZAGTZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>11-02-2026 14:53:46</t>
+          <t>10-02-2026 11:28:40</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -7159,17 +7171,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>12-02-2026 12:36:52</t>
+          <t>10-02-2026 11:31:11</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>12-02-2026 12:36:23</t>
+          <t>10-02-2026 11:30:36</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7189,7 +7201,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26180522292630004399</t>
+          <t>26160522229140001874</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
@@ -7201,7 +7213,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7213,12 +7225,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>343135</t>
+          <t>343384</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20952</t>
+          <t>21201</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7228,12 +7240,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>JAIME</t>
+          <t>BRISA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>GASCA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -7248,63 +7260,75 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6862316574</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>6863912198</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
+          <t>12-02-2006</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>GNAVARROGASCA@GMAIL.COM</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>11-02-2026 20:34:48</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 19:16:27</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>13-02-2026 16:04:20</t>
+          <t>12-02-2026 19:22:02</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>12-02-2026 19:21:22</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7312,44 +7336,36 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26160522323640002074</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26160522304540002036</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>343384</t>
+          <t>342482</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21201</t>
+          <t>20299</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7359,17 +7375,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BRISA</t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>GASCA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>CACERES</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7379,75 +7395,67 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6863912198</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6867220400</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>12-02-2006</t>
+          <t>25-08-1998</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>GNAVARROGASCA@GMAIL.COM</t>
+          <t>JOSECACEREZ98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>12-02-2026 19:16:27</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>09-02-2026 20:20:01</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>12-02-2026 19:22:02</t>
+          <t>09-02-2026 20:21:16</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>12-02-2026 19:21:22</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7455,19 +7463,19 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26160522304540002036</t>
+          <t>26160522213460001843</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7479,12 +7487,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>344132</t>
+          <t>342783</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21949</t>
+          <t>20600</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7494,17 +7502,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGELES </t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CARMONA</t>
+          <t>TAPIA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SIQUEIROS</t>
+          <t>AGUAYO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7514,28 +7522,28 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6863378715</t>
+          <t>6623654956</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>04-08-2006</t>
+          <t>27-03-1998</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>ANGELESWCARMONA763@GMAIL.COM</t>
+          <t>JOSETAPIAGUAYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>16-02-2026 15:44:25</t>
+          <t>10-02-2026 18:11:07</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7550,22 +7558,22 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>16-02-2026 15:45:32</t>
+          <t>10-02-2026 18:12:38</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -7582,19 +7590,19 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26160522393400002157</t>
+          <t>26160522242690001898</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7606,12 +7614,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>343139</t>
+          <t>344132</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20956</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7621,17 +7629,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NICZA ARELI</t>
+          <t xml:space="preserve">ANGELES </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IZAGUIRRE</t>
+          <t>CARMONA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>SIQUEIROS</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7641,14 +7649,10 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6864650098</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TORRE LAS ARCAS </t>
-        </is>
-      </c>
+          <t>6863378715</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7656,60 +7660,56 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>03-11-1994</t>
+          <t>04-08-2006</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>IZAGUIRREARELI@GMAIL.COM</t>
+          <t>ANGELESWCARMONA763@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>11-02-2026 20:53:07</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>16-02-2026 15:44:25</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>13-02-2026 18:50:54</t>
+          <t>16-02-2026 15:45:32</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>13-02-2026 18:49:33</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7717,23 +7717,19 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26170522328830002369</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26160522393400002157</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7745,12 +7741,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>344345</t>
+          <t>345809</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22162</t>
+          <t>87974</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7760,17 +7756,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>JESUS ANTONIO</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>TOPETE</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>HARO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7780,10 +7776,14 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6865890812</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>6863504737</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7791,17 +7791,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>15-12-1987</t>
+          <t>08-04-2000</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CHUYANTONT@GMAIL.COM</t>
+          <t>ALETSMIRANDA7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>16-02-2026 19:42:11</t>
+          <t>23-02-2026 14:46:02</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7811,36 +7811,44 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>16-02-2026 19:43:34</t>
+          <t>23-02-2026 15:06:54</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>23-02-2026 14:52:57</t>
+        </is>
+      </c>
       <c r="U55" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W55" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7848,14 +7856,14 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26160522409070002196</t>
+          <t>26160522583760002502</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -7872,12 +7880,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>344391</t>
+          <t>342997</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>20814</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7887,17 +7895,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t>JAZMIN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ARTEAGA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7907,67 +7915,75 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6311261612</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>8130964314</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>CERRO DEL POTOSI 1119</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>18-06-1985</t>
+          <t>18-03-1995</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>COLORGRAFICO@HOTMAIL.COM</t>
+          <t>YAAS.LOPEZ18@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>17-02-2026 07:06:31</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>11-02-2026 14:53:46</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>17-02-2026 07:07:36</t>
+          <t>12-02-2026 12:36:52</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>12-02-2026 12:36:23</t>
+        </is>
+      </c>
       <c r="U56" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7975,19 +7991,19 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26160522420050002226</t>
+          <t>26180522292630004399</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7999,12 +8015,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>344630</t>
+          <t>343135</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8014,12 +8030,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>JESUS LEONEL</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>GALAVIZ</t>
+          <t>OLIVAS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -8034,7 +8050,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6865866356</t>
+          <t>6862316574</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8045,17 +8061,13 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>28-10-1986</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>JESUSLEONEL@GMAIL.COM</t>
-        </is>
-      </c>
+          <t>01-01-2000</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>17-02-2026 17:54:18</t>
+          <t>11-02-2026 20:34:48</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -8070,28 +8082,28 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>17-02-2026 17:56:16</t>
+          <t>13-02-2026 16:04:20</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V57" t="inlineStr"/>
@@ -8102,36 +8114,44 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26160522439290002266</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
+          <t>26160522323640002074</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>345376</t>
+          <t>344345</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>87541</t>
+          <t>22162</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8141,17 +8161,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SOPHIA</t>
+          <t>JESUS ANTONIO</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>TOPETE</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8161,79 +8181,67 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6865307488</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6865890812</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>26-06-1993</t>
+          <t>15-12-1987</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>SOPHIA.QUINDI@GMAIL.COM</t>
+          <t>CHUYANTONT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>20-02-2026 17:55:33</t>
+          <t>16-02-2026 19:42:11</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>20-02-2026 18:01:22</t>
+          <t>16-02-2026 19:43:34</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>20-02-2026 18:00:10</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8241,19 +8249,19 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26160522533220002443</t>
+          <t>26160522409070002196</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -8265,12 +8273,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>345386</t>
+          <t>343139</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>87551</t>
+          <t>20956</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8280,17 +8288,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEJANDRO </t>
+          <t>NICZA ARELI</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>LAURIAS</t>
+          <t>IZAGUIRRE</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8300,39 +8308,35 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6866441611</t>
+          <t>6864650098</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t xml:space="preserve">TORRE LAS ARCAS </t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>10-08-1994</t>
+          <t>03-11-1994</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>ALGSMQD26@GMAIL.COM</t>
+          <t>IZAGUIRREARELI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>20-02-2026 18:13:38</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>11-02-2026 20:53:07</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8350,17 +8354,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>20-02-2026 18:16:09</t>
+          <t>13-02-2026 18:50:54</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>20-02-2026 18:15:32</t>
+          <t>13-02-2026 18:49:33</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8380,10 +8384,14 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26160522533690002445</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr"/>
+          <t>26170522328830002369</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
@@ -8392,7 +8400,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -8404,12 +8412,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>345399</t>
+          <t>344515</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>87564</t>
+          <t>22332</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8419,17 +8427,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NATALIA</t>
+          <t>ASTRID AITANA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CASAREZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>VALLE</t>
+          <t>HIDALGO</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8439,12 +8447,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6861221578</t>
+          <t>5522151079</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>RIO TULA 12</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8454,17 +8462,17 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>09-11-1995</t>
+          <t>19-10-2006</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>NATALIACASAREZVALLE@GMAIL.COM</t>
+          <t>AITANAHIDALGO0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>20-02-2026 18:53:23</t>
+          <t>17-02-2026 15:10:23</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -8474,32 +8482,32 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>20-02-2026 18:57:38</t>
+          <t>23-02-2026 15:56:01</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>20-02-2026 18:56:28</t>
+          <t>23-02-2026 15:54:51</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -8509,7 +8517,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -8519,36 +8527,36 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26160522534930002446</t>
+          <t>26290522585740002451</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>344929</t>
+          <t>345376</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>22746</t>
+          <t>87541</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8558,17 +8566,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>SOPHIA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8578,7 +8586,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>9371155830</t>
+          <t>6865307488</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -8588,22 +8596,22 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>18-06-1991</t>
+          <t>26-06-1993</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>ANGELMORENOOCHOA@GMAIL.COM</t>
+          <t>SOPHIA.QUINDI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>18-02-2026 18:36:12</t>
+          <t>20-02-2026 17:55:33</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -8628,17 +8636,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>18-02-2026 18:47:06</t>
+          <t>20-02-2026 18:01:22</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>18-02-2026 18:46:16</t>
+          <t>20-02-2026 18:00:10</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -8658,7 +8666,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26160522473470002345</t>
+          <t>26160522533220002443</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
@@ -8670,7 +8678,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -8682,145 +8690,1197 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>345386</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>87551</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALEJANDRO </t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>LAURIAS</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>6866441611</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>10-08-1994</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>ALGSMQD26@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:13:38</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:16:09</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:15:32</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>26160522533690002445</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>Sergio  Cordova Hernandez</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>345399</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>87564</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NATALIA</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>CASAREZ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>VALLE</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>6861221578</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>09-11-1995</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NATALIACASAREZVALLE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:53:23</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:57:38</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:56:28</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>26160522534930002446</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>345976</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>88141</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>JOAQUIN</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RUIZ</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>COTA</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>6861822047</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>10-06-1982</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>JOTAQN.RUIZ@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:22:36</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:24:38</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>26160522595470002522</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>344197</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>22014</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>INDEPENDENCIA</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>SILVIA</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>RODRIGUEZ</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>GARCIA</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>6863845214</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>INDEPENDENCIA1</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>01-01-2000</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>MARIA.932573@GMAIL.COM</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>16-02-2026 17:11:26</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>Tarifas 2026 LE</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>No Forzoso</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>RECURRENTE $649 LE</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>649</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>18-02-2026 17:47:52</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>18-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>18-02-2026 17:43:52</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>26160522470320002337</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>GUILLERMO  PALMA Y MEZA OTERO</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>649</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>344391</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>22208</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ERNESTO</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>BELTRAN</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ARTEAGA</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>6311261612</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>18-06-1985</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>COLORGRAFICO@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>17-02-2026 07:06:31</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>17-02-2026 07:07:36</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>17-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>26160522420050002226</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Julio Alonso Lerma Sanchez</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>344630</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>22447</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>JESUS LEONEL</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>GALAVIZ</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>6865866356</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>28-10-1986</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>JESUSLEONEL@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>17-02-2026 17:54:18</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>17-02-2026 17:56:16</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>26160522439290002266</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>344929</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>22746</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ANGEL</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>OCHOA</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>9371155830</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>18-06-1991</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>ANGELMORENOOCHOA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>18-02-2026 18:36:12</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>18-02-2026 18:47:06</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>18-02-2026 18:46:16</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>26160522473470002345</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>345971</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>88136</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>JOAQUIN</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RUIZ</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>IBAÑEZ</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>6862034774</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>21-03-2009</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>RUIZIBAÑEZJQN@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:17:27</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:19:45</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>26160522595030002521</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>346049</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>88214</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>JONAS</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>MEZA</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>6862765318</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>19-07-1999</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>LABAJAMXLI@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>23-02-2026 20:45:09</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>23-02-2026 20:46:28</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>26160522602060002551</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -840,12 +840,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>123833</t>
+          <t>260403</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>57907</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,17 +855,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AKYEL</t>
+          <t>SAMUEL ESTEBAN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CASTANEDO</t>
+          <t>SERRANO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>SERRANO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -875,57 +875,53 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6531131589</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>DEL CARRIZO 3015</t>
-        </is>
-      </c>
+          <t>6862393566</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>01-10-2003</t>
+          <t>28-05-2001</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>AKYDANIELLA@GMAIL.COM</t>
+          <t>SAMUELSESS32@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>19-09-2022 16:35:13</t>
+          <t>02-10-2024 22:01:32</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17-02-2026 06:58:58</t>
+          <t>17-02-2026 17:05:51</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -933,21 +929,13 @@
           <t>17-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>17-02-2026 06:58:23</t>
-        </is>
-      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -955,22 +943,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26160522419880002224</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
-        </is>
-      </c>
+          <t>26030522436260002152</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -987,12 +967,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>260403</t>
+          <t>123833</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>57907</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1002,17 +982,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAMUEL ESTEBAN</t>
+          <t>AKYEL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SERRANO</t>
+          <t>CASTANEDO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SERRANO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1022,53 +1002,57 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6862393566</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>6531131589</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>DEL CARRIZO 3015</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>28-05-2001</t>
+          <t>01-10-2003</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>SAMUELSESS32@GMAIL.COM</t>
+          <t>AKYDANIELLA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-10-2024 22:01:32</t>
+          <t>19-09-2022 16:35:13</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>17-02-2026 17:05:51</t>
+          <t>17-02-2026 06:58:58</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1076,13 +1060,21 @@
           <t>17-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>17-02-2026 06:58:23</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1090,14 +1082,22 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26030522436260002152</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>26160522419880002224</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1376,24 +1376,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>340481</t>
+          <t>340713</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HILDA</t>
+          <t>LESLIE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BENAVIDEZ</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PEÑA</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6864150761</t>
+          <t>6865257334</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>LINEZO1</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>21-07-1961</t>
+          <t>10-06-1994</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>NOTIERERER@TYU.COM</t>
+          <t>LICMERCADOSUNA.10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>03-02-2026 08:55:15</t>
+          <t>03-02-2026 17:15:35</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1469,17 +1469,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>04-02-2026 10:23:34</t>
+          <t>03-02-2026 17:19:02</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>04-02-2026 10:22:30</t>
+          <t>03-02-2026 17:18:43</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1499,19 +1499,11 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26160522071550001606</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
-        </is>
-      </c>
+          <t>26160522048750001552</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
           <t>499</t>
@@ -1519,7 +1511,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1531,12 +1523,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>340713</t>
+          <t>290316</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>87814</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,17 +1538,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LESLIE</t>
+          <t>VANESSA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>HIGUERA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1566,32 +1558,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6865257334</t>
+          <t>6861744727</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>INDEPENDENCIA 1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>10-06-1994</t>
+          <t>22-07-1992</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>LICMERCADOSUNA.10@GMAIL.COM</t>
+          <t>HIGUERAROSAV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>03-02-2026 17:15:35</t>
+          <t>28-04-2025 19:34:24</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1612,17 +1604,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-02-2026 17:19:02</t>
+          <t>14-02-2026 15:01:10</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>03-02-2026 17:18:43</t>
+          <t>14-02-2026 15:00:36</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1632,7 +1624,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1642,10 +1634,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26160522048750001552</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
+          <t>26160522349780002121</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1654,7 +1650,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1666,12 +1662,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>337242</t>
+          <t>340481</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1681,17 +1677,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTHA ELENA </t>
+          <t>HILDA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MAEDA</t>
+          <t>BENAVIDEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1701,10 +1697,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6861253578</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>6864150761</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LINEZO1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1712,56 +1712,60 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>06-10-1952</t>
+          <t>21-07-1961</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>MARTHAELENAMG@GMAIL.COM</t>
+          <t>NOTIERERER@TYU.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>23-01-2026 12:52:24</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 08:55:15</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-02-2026 08:23:40</t>
+          <t>04-02-2026 10:23:34</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>04-02-2026 10:22:30</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1769,19 +1773,27 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26160522033610001514</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>26160522071550001606</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2075,12 +2087,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>290316</t>
+          <t>342294</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>87814</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2090,17 +2102,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VANESSA</t>
+          <t>CARLOS ANTONIO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HIGUERA</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2110,14 +2122,10 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6861744727</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA 1</t>
-        </is>
-      </c>
+          <t>6863473949</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2125,60 +2133,56 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>22-07-1992</t>
+          <t>25-10-2003</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>HIGUERAROSAV@GMAIL.COM</t>
+          <t>CARLOS8A2510@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>28-04-2025 19:34:24</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>09-02-2026 16:59:55</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>14-02-2026 15:01:10</t>
+          <t>09-02-2026 17:01:28</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>14-02-2026 15:00:36</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2186,23 +2190,19 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26160522349780002121</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26160522200300001806</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2214,12 +2214,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>341132</t>
+          <t>341834</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2229,17 +2229,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAHOMI ESTEFANIA </t>
+          <t>DARIANA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TALAMANTES</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6643120858</t>
+          <t>6862489316</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>SAN CARLO1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2264,17 +2264,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>18-08-1996</t>
+          <t>03-12-1981</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ESTEFANIAMTALAMANTESX@GMAIL.COM</t>
+          <t>LOPEZDARIANA780@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>04-02-2026 18:08:31</t>
+          <t>07-02-2026 13:31:41</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2295,17 +2295,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>10-02-2026 16:06:43</t>
+          <t>07-02-2026 13:38:04</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>10-02-2026 16:05:59</t>
+          <t>07-02-2026 13:35:50</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2325,19 +2325,11 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26130522235720002570</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>MARIA CANDELARIA LARA AVILA</t>
-        </is>
-      </c>
+          <t>26160522161810001766</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
           <t>499</t>
@@ -2345,7 +2337,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2357,12 +2349,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>341834</t>
+          <t>342323</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19652</t>
+          <t>20141</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2372,7 +2364,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DARIANA</t>
+          <t>MARCO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2382,7 +2374,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>ORDUÑO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2392,32 +2384,32 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6862489316</t>
+          <t>6861601599</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SAN CARLO1</t>
+          <t>INDEPENDENCIA0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>03-12-1981</t>
+          <t>25-04-1979</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>LOPEZDARIANA780@GMAIL.COM</t>
+          <t>MOPILLO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>07-02-2026 13:31:41</t>
+          <t>09-02-2026 17:27:09</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2438,17 +2430,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>07-02-2026 13:38:04</t>
+          <t>09-02-2026 17:33:13</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>07-02-2026 13:35:50</t>
+          <t>09-02-2026 17:32:43</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2468,7 +2460,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26160522161810001766</t>
+          <t>26160522202710001810</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2480,7 +2472,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2492,12 +2484,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>342294</t>
+          <t>238288</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>35793</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2507,17 +2499,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CARLOS ANTONIO</t>
+          <t>SILVIA PAOLA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>PAYAN</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2527,67 +2519,75 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6863473949</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>6864629400</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>IND123</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>25-10-2003</t>
+          <t>18-02-2009</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CARLOS8A2510@GMAIL.COM</t>
+          <t>SILVIAPAYAN009@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>09-02-2026 16:59:55</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-06-2024 18:12:25</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>09-02-2026 17:01:28</t>
+          <t>10-02-2026 05:33:30</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>10-02-2026 05:32:15</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2595,19 +2595,27 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26160522200300001806</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+          <t>26160522222220001861</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2619,12 +2627,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>341819</t>
+          <t>299954</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19637</t>
+          <t>97452</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2634,17 +2642,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KARYME</t>
+          <t>EUNICE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2654,10 +2662,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6861351566</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>6865848338</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>IND123</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2665,56 +2677,60 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>11-12-2004</t>
+          <t>11-06-2001</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>KARYMEMACLOP@GMAIL.COM</t>
+          <t>EUNICE.LOPEZ5@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>07-02-2026 12:03:12</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>23-06-2025 18:39:49</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>07-02-2026 12:05:36</t>
+          <t>09-02-2026 08:55:34</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>09-02-2026 08:54:52</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2722,19 +2738,23 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26160522160500001761</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
+          <t>26160522185470001787</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2746,12 +2766,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>238288</t>
+          <t>339686</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>35793</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2761,17 +2781,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SILVIA PAOLA</t>
+          <t>EDUARDO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PAYAN</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2781,35 +2801,39 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6864629400</t>
+          <t>6862121992</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>IND123</t>
+          <t>I988</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18-02-2009</t>
+          <t>06-05-1992</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>SILVIAPAYAN009@GMAIL.COM</t>
+          <t>POLOEGARCIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>05-06-2024 18:12:25</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>31-01-2026 12:59:25</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2827,17 +2851,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>10-02-2026 05:33:30</t>
+          <t>18-02-2026 13:22:14</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>10-02-2026 05:32:15</t>
+          <t>18-02-2026 13:21:09</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2847,7 +2871,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2857,7 +2881,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26160522222220001861</t>
+          <t>26160522461460002325</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2867,7 +2891,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+          <t>auxiliar independencia mexicali</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2877,7 +2901,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2889,12 +2913,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>299954</t>
+          <t>342822</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>97452</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2904,17 +2928,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EUNICE</t>
+          <t>LEOPOLDO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>LOYO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>COBO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2924,32 +2948,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6865848338</t>
+          <t>6862120595</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>IND123</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>11-06-2001</t>
+          <t>17-07-1971</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>EUNICE.LOPEZ5@UABC.EDU.MX</t>
+          <t>LEOPOLDOLOYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>23-06-2025 18:39:49</t>
+          <t>10-02-2026 19:02:43</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2970,17 +2994,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>09-02-2026 08:55:34</t>
+          <t>14-02-2026 13:28:02</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>09-02-2026 08:54:52</t>
+          <t>14-02-2026 13:27:04</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2990,7 +3014,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -3000,12 +3024,12 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26160522185470001787</t>
+          <t>26160522349290002113</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+          <t>PASE RECORRIDO</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr"/>
@@ -3016,7 +3040,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3028,12 +3052,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>342323</t>
+          <t>342087</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>19905</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3043,17 +3067,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MARCO</t>
+          <t>KARLA VERÓNICA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ORDUÑO</t>
+          <t>PALAFOX</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3063,63 +3087,67 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6861601599</t>
+          <t>6861244927</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA0</t>
+          <t>IND111111</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>25-04-1979</t>
+          <t>26-05-1986</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>MOPILLO@GMAIL.COM</t>
+          <t>VERONIKAPALAFOX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>09-02-2026 17:27:09</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>09-02-2026 10:07:36</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>09-02-2026 17:33:13</t>
+          <t>16-02-2026 08:19:11</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>09-02-2026 17:32:43</t>
+          <t>16-02-2026 08:18:23</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3139,19 +3167,27 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26160522202710001810</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+          <t>26160522380750002134</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3163,12 +3199,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>339686</t>
+          <t>337242</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17504</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3178,17 +3214,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EDUARDO</t>
+          <t xml:space="preserve">MARTHA ELENA </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MAEDA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3198,79 +3234,67 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6862121992</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>I988</t>
-        </is>
-      </c>
+          <t>6861253578</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>06-05-1992</t>
+          <t>06-10-1952</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>POLOEGARCIA@GMAIL.COM</t>
+          <t>MARTHAELENAMG@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>31-01-2026 12:59:25</t>
+          <t>23-01-2026 12:52:24</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>18-02-2026 13:22:14</t>
+          <t>03-02-2026 08:23:40</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>18-02-2026 13:21:09</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3278,32 +3302,24 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26160522461460002325</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>auxiliar independencia mexicali</t>
-        </is>
-      </c>
+          <t>26160522033610001514</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -3445,12 +3461,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>342822</t>
+          <t>342794</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20639</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3460,17 +3476,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LEOPOLDO</t>
+          <t>JOSUE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LOYO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>COBO</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3480,12 +3496,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6862120595</t>
+          <t>6861127057</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>INDEPENDENCI1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3495,17 +3511,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>17-07-1971</t>
+          <t>26-11-1989</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>LEOPOLDOLOYO@GMAIL.COM</t>
+          <t>JOSUEBRMUSIC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>10-02-2026 19:02:43</t>
+          <t>10-02-2026 18:25:08</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3526,17 +3542,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>14-02-2026 13:28:02</t>
+          <t>10-02-2026 18:27:56</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>14-02-2026 13:27:04</t>
+          <t>10-02-2026 18:27:24</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3546,7 +3562,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3556,14 +3572,10 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26160522349290002113</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26160522243630001901</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
@@ -3572,7 +3584,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3584,12 +3596,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>342336</t>
+          <t>340641</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>18459</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3599,17 +3611,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MARCO ALEJANDRO</t>
+          <t>LUCIA YADIRA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>VELARDE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3619,32 +3631,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6861632588</t>
+          <t>6861822416</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA01</t>
+          <t>CULTURA OLMECA 3608</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>12-05-2006</t>
+          <t>13-12-1990</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>6MALLISME9@GMAIL.COM</t>
+          <t>YADIRA_1290@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>09-02-2026 17:35:12</t>
+          <t>03-02-2026 15:56:48</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3665,17 +3677,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>09-02-2026 17:38:30</t>
+          <t>05-02-2026 16:33:17</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>09-02-2026 17:38:05</t>
+          <t>05-02-2026 16:30:37</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3685,7 +3697,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3695,11 +3707,19 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26160522203170001811</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
+          <t>26160522110560001680</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>499</t>
@@ -3707,7 +3727,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3719,12 +3739,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>342087</t>
+          <t>343713</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19905</t>
+          <t>21530</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3734,17 +3754,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KARLA VERÓNICA</t>
+          <t>JESSICA ALEJANDRA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PALAFOX</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3754,12 +3774,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6861244927</t>
+          <t>6863648770</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>IND111111</t>
+          <t>JOSE MARIA AGUAYO 506</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3769,52 +3789,48 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>26-05-1986</t>
+          <t>18-01-2006</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>VERONIKAPALAFOX@GMAIL.COM</t>
+          <t>JESSICAA.GUTIERREZ@CETYS.EDU.MX</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>09-02-2026 10:07:36</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>14-02-2026 11:38:52</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>16-02-2026 08:19:11</t>
+          <t>14-02-2026 11:41:20</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>16-02-2026 08:18:23</t>
+          <t>14-02-2026 11:40:29</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3834,27 +3850,19 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26160522380750002134</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
-        </is>
-      </c>
+          <t>26160522347590002106</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3866,12 +3874,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>340641</t>
+          <t>342478</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>20295</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3881,17 +3889,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LUCIA YADIRA</t>
+          <t>FERNANDO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VELARDE</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3901,32 +3909,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6861822416</t>
+          <t>6861146223</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CULTURA OLMECA 3608</t>
+          <t>INDEPENDENCIA01</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>13-12-1990</t>
+          <t>27-04-1993</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>YADIRA_1290@HOTMAIL.COM</t>
+          <t>IVANRNAVARRO12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>03-02-2026 15:56:48</t>
+          <t>09-02-2026 20:13:50</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3947,17 +3955,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>05-02-2026 16:33:17</t>
+          <t>09-02-2026 20:16:34</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>05-02-2026 16:30:37</t>
+          <t>09-02-2026 20:16:03</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3967,7 +3975,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3977,19 +3985,11 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26160522110560001680</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26160522213270001841</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
           <t>499</t>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4009,12 +4009,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>340697</t>
+          <t>342580</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>20397</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4024,17 +4024,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CRISTIAN ISMAEL</t>
+          <t>HECTOR MANUEL</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>PIÑA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>OLIVEROS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4044,14 +4044,10 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6863537341</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA3</t>
-        </is>
-      </c>
+          <t>6865895862</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4059,60 +4055,56 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>22-06-1995</t>
+          <t>17-10-2002</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CRISTIAN.TORRES@GCADENA.COM</t>
+          <t>NOTIENE11112222@FFFFDDD.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>03-02-2026 17:02:34</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>10-02-2026 10:48:52</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>03-02-2026 17:06:48</t>
+          <t>10-02-2026 10:50:12</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>03-02-2026 17:06:13</t>
-        </is>
-      </c>
+          <t>10-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4120,19 +4112,19 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26160522047970001551</t>
+          <t>26160522228650001872</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4144,12 +4136,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>342474</t>
+          <t>343140</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4159,17 +4151,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MELISSA</t>
+          <t xml:space="preserve">VANESSA </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4179,12 +4171,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6863242180</t>
+          <t>6864164007</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA01</t>
+          <t>AV TORRE LAS ARCAS 2045</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4194,17 +4186,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>25-07-1987</t>
+          <t>08-11-1989</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>YLEM51@GMAIL.COM</t>
+          <t>VANESSAGALVANR250210@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>09-02-2026 20:08:06</t>
+          <t>11-02-2026 20:55:11</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4225,17 +4217,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>09-02-2026 20:12:28</t>
+          <t>13-02-2026 18:56:17</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>09-02-2026 20:10:07</t>
+          <t>13-02-2026 18:55:42</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4245,7 +4237,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4255,10 +4247,14 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26160522213110001840</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr"/>
+          <t>26170522329060002370</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
@@ -4267,7 +4263,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4279,12 +4275,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>342794</t>
+          <t>340697</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4294,17 +4290,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>JOSUE</t>
+          <t>CRISTIAN ISMAEL</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4314,12 +4310,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6861127057</t>
+          <t>6863537341</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>INDEPENDENCI1</t>
+          <t>INDEPENDENCIA3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4329,17 +4325,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>26-11-1989</t>
+          <t>22-06-1995</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>JOSUEBRMUSIC@GMAIL.COM</t>
+          <t>CRISTIAN.TORRES@GCADENA.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10-02-2026 18:25:08</t>
+          <t>03-02-2026 17:02:34</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4360,17 +4356,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>10-02-2026 18:27:56</t>
+          <t>03-02-2026 17:06:48</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>10-02-2026 18:27:24</t>
+          <t>03-02-2026 17:06:13</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4380,7 +4376,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4390,7 +4386,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26160522243630001901</t>
+          <t>26160522047970001551</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4402,7 +4398,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4414,12 +4410,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>343713</t>
+          <t>343612</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>21429</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4429,17 +4425,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>JESSICA ALEJANDRA</t>
+          <t>OSCAR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CARRERA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4449,75 +4445,67 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6863648770</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>JOSE MARIA AGUAYO 506</t>
-        </is>
-      </c>
+          <t>6865906261</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>18-01-2006</t>
+          <t>03-08-2006</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>JESSICAA.GUTIERREZ@CETYS.EDU.MX</t>
+          <t>OR629395@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>14-02-2026 11:38:52</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>13-02-2026 20:02:16</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>14-02-2026 11:41:20</t>
+          <t>13-02-2026 20:03:49</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>14-02-2026 11:40:29</t>
-        </is>
-      </c>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4525,14 +4513,14 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26160522347590002106</t>
+          <t>26160522330930002093</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4549,12 +4537,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342776</t>
+          <t>343714</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20593</t>
+          <t>21531</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4564,17 +4552,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>JUAN MANUEL</t>
+          <t>OLVIA YISEL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4584,32 +4572,32 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6867292744</t>
+          <t>6863667098</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>AV LAGO BAHIJASH 634</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>09-11-1973</t>
+          <t>03-03-2001</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>NOCUENTACON1@GMAIL.COM</t>
+          <t>OLVIAHU18@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10-02-2026 18:03:21</t>
+          <t>14-02-2026 11:45:34</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4630,17 +4618,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>10-02-2026 18:35:28</t>
+          <t>14-02-2026 11:48:11</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>10-02-2026 18:35:08</t>
+          <t>14-02-2026 11:47:29</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4660,7 +4648,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26160522243990001903</t>
+          <t>26160522347720002107</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4684,12 +4672,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>343025</t>
+          <t>340789</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20842</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4699,17 +4687,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DYLAN</t>
+          <t xml:space="preserve">DANIELA </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4719,67 +4707,75 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6861698256</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>6861739204</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>MAYA CAMPESTRE</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>06-08-2002</t>
+          <t>06-09-1989</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>DYLANMTZM.26@GMAIL.COM</t>
+          <t>DANIELA.SANCHEZ.MORENO.89@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>11-02-2026 15:49:14</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 18:45:03</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>11-02-2026 15:52:21</t>
+          <t>03-02-2026 19:05:49</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>03-02-2026 19:04:34</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4787,14 +4783,18 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26160522267270001952</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
+          <t>26160522055070001567</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4811,12 +4811,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>343140</t>
+          <t>341132</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4826,17 +4826,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">VANESSA </t>
+          <t xml:space="preserve">NAHOMI ESTEFANIA </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>TALAMANTES</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4846,12 +4846,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6864164007</t>
+          <t>6643120858</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>AV TORRE LAS ARCAS 2045</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4861,17 +4861,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>08-11-1989</t>
+          <t>18-08-1996</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>VANESSAGALVANR250210@GMAIL.COM</t>
+          <t>ESTEFANIAMTALAMANTESX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>11-02-2026 20:55:11</t>
+          <t>04-02-2026 18:08:31</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4892,17 +4892,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>13-02-2026 18:56:17</t>
+          <t>10-02-2026 16:06:43</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>13-02-2026 18:55:42</t>
+          <t>10-02-2026 16:05:59</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4922,15 +4922,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26170522329060002370</t>
+          <t>26130522235720002570</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>MARIA CANDELARIA LARA AVILA</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>499</t>
@@ -4938,7 +4942,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4950,12 +4954,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>342478</t>
+          <t>345721</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20295</t>
+          <t>87886</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4965,17 +4969,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FERNANDO</t>
+          <t>J ASUNCION</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4985,12 +4989,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6861146223</t>
+          <t>6861754997</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA01</t>
+          <t>RIO AMECA 1896</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5000,20 +5004,24 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>27-04-1993</t>
+          <t>14-01-1981</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>IVANRNAVARRO12@GMAIL.COM</t>
+          <t>RODRILOVEMX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>09-02-2026 20:13:50</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>23-02-2026 12:02:31</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5031,17 +5039,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>09-02-2026 20:16:34</t>
+          <t>23-02-2026 12:11:56</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>09-02-2026 20:16:03</t>
+          <t>23-02-2026 12:08:50</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5051,7 +5059,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -5061,7 +5069,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26160522213270001841</t>
+          <t>26160522578360002492</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -5085,12 +5093,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342580</t>
+          <t>341819</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20397</t>
+          <t>19637</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5100,17 +5108,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HECTOR MANUEL</t>
+          <t>KARYME</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PIÑA</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>OLIVEROS</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5120,28 +5128,28 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6865895862</t>
+          <t>6861351566</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>17-10-2002</t>
+          <t>11-12-2004</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>NOTIENE11112222@FFFFDDD.COM</t>
+          <t>KARYMEMACLOP@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>10-02-2026 10:48:52</t>
+          <t>07-02-2026 12:03:12</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5156,28 +5164,28 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>10-02-2026 10:50:12</t>
+          <t>07-02-2026 12:05:36</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>10-05-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V35" t="inlineStr"/>
@@ -5188,14 +5196,14 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26160522228650001872</t>
+          <t>26160522160500001761</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5212,12 +5220,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>343612</t>
+          <t>344453</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21429</t>
+          <t>22270</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5227,17 +5235,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>OSCAR</t>
+          <t>JESUS</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CARRERA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5247,7 +5255,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6865906261</t>
+          <t>6861762359</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5258,17 +5266,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>03-08-2006</t>
+          <t>11-08-1951</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>OR629395@GMAIL.COM</t>
+          <t>NOTIENE23445@DFDF.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>13-02-2026 20:02:16</t>
+          <t>17-02-2026 11:34:41</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5283,22 +5291,22 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>13-02-2026 20:03:49</t>
+          <t>17-02-2026 11:37:38</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>17-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -5315,19 +5323,19 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26160522330930002093</t>
+          <t>26160522425250002243</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5339,12 +5347,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>343714</t>
+          <t>344505</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21531</t>
+          <t>22322</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5354,17 +5362,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>OLVIA YISEL</t>
+          <t>KENIA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5374,12 +5382,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6863667098</t>
+          <t>6869460269</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>AV LAGO BAHIJASH 634</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5389,20 +5397,24 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>03-03-2001</t>
+          <t>24-09-1981</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>OLVIAHU18@GMAIL.COM</t>
+          <t>KRISS0024@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>14-02-2026 11:45:34</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>17-02-2026 14:43:35</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5420,17 +5432,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>14-02-2026 11:48:11</t>
+          <t>17-02-2026 14:52:04</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>14-02-2026 11:47:29</t>
+          <t>17-02-2026 14:49:23</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5440,7 +5452,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5450,7 +5462,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26160522347720002107</t>
+          <t>26160522430130002253</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -5474,12 +5486,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>340789</t>
+          <t>344042</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18607</t>
+          <t>21859</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5489,17 +5501,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIELA </t>
+          <t xml:space="preserve">FELISA </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ANGUAMEA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5509,14 +5521,10 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6861739204</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>MAYA CAMPESTRE</t>
-        </is>
-      </c>
+          <t>6442161660</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5524,60 +5532,52 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>06-09-1989</t>
+          <t>01-01-2000</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>DANIELA.SANCHEZ.MORENO.89@GMAIL.COM</t>
+          <t>FELISAANGUAMEAVALENZUELA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>03-02-2026 18:45:03</t>
+          <t>16-02-2026 12:24:29</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>03-02-2026 19:05:49</t>
+          <t>23-02-2026 18:27:10</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>03-02-2026 19:04:34</t>
-        </is>
-      </c>
+          <t>23-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5585,18 +5585,22 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26160522055070001567</t>
+          <t>26060522595620004368</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5613,12 +5617,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>343557</t>
+          <t>344134</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21374</t>
+          <t>21951</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5628,17 +5632,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>JUAN CARLOS</t>
+          <t>DANNA PAOLA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MOLINA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>ARROYO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5648,14 +5652,10 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6863903522</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6531662052</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5663,60 +5663,56 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>08-03-1971</t>
+          <t>20-06-2006</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>JUANCARLORIOS1422@GMAIL.COM</t>
+          <t>MOLINAARROYODANNAPAOLA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>13-02-2026 17:19:49</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>16-02-2026 15:47:17</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>13-02-2026 17:24:13</t>
+          <t>16-02-2026 15:49:00</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>13-02-2026 17:22:41</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5724,14 +5720,14 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26160522326350002078</t>
+          <t>26160522393690002158</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5748,12 +5744,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>345721</t>
+          <t>344409</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>87886</t>
+          <t>22226</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5763,17 +5759,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>J ASUNCION</t>
+          <t>ISRAEL</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>VELAZQUEZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>LIAÑO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5783,12 +5779,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6861754997</t>
+          <t>6863940285</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>RIO AMECA 1896</t>
+          <t>EEEE12</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5798,17 +5794,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>14-01-1981</t>
+          <t>18-04-1977</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>RODRILOVEMX@GMAIL.COM</t>
+          <t>MASTERBOY1930@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>23-02-2026 12:02:31</t>
+          <t>17-02-2026 08:06:52</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5833,17 +5829,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>23-02-2026 12:11:56</t>
+          <t>17-02-2026 08:09:37</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>23-02-2026 12:08:50</t>
+          <t>17-02-2026 08:08:58</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5863,7 +5859,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26160522578360002492</t>
+          <t>26160522421530002234</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -5875,7 +5871,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5887,12 +5883,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>344453</t>
+          <t>346370</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>22270</t>
+          <t>88535</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5902,17 +5898,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>JESUS</t>
+          <t>JOSE ALBERTO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>PAEZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>FRANCISCO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5922,10 +5918,14 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6861762359</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>7123435473</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>VILLAFONTANA</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5933,56 +5933,64 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>11-08-1951</t>
+          <t>26-06-2000</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>NOTIENE23445@DFDF.COM</t>
+          <t>JOSE5535072149@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>17-02-2026 11:34:41</t>
+          <t>25-02-2026 07:44:10</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>17-02-2026 11:37:38</t>
+          <t>25-02-2026 07:47:45</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr"/>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>25-02-2026 07:46:50</t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5990,36 +5998,36 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26160522425250002243</t>
+          <t>26160522646040002634</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>344505</t>
+          <t>342336</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6029,17 +6037,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>KENIA</t>
+          <t>MARCO ALEJANDRO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6049,39 +6057,35 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6869460269</t>
+          <t>6861632588</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>INDEPENDENCIA01</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>24-09-1981</t>
+          <t>12-05-2006</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>KRISS0024@GMAIL.COM</t>
+          <t>6MALLISME9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>17-02-2026 14:43:35</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:35:12</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6099,17 +6103,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>17-02-2026 14:52:04</t>
+          <t>09-02-2026 17:38:30</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>17-02-2026 14:49:23</t>
+          <t>09-02-2026 17:38:05</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6129,7 +6133,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26160522430130002253</t>
+          <t>26160522203170001811</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6141,7 +6145,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6153,12 +6157,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>344451</t>
+          <t>342474</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>22268</t>
+          <t>20291</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6168,17 +6172,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TIFFANY JAZMIN</t>
+          <t>MELISSA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>HOPKINS</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6188,39 +6192,35 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6866190407</t>
+          <t>6863242180</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>IND22222</t>
+          <t>INDEPENDENCIA01</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>06-09-2006</t>
+          <t>25-07-1987</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>NOTIENEEE@SSS.COM</t>
+          <t>YLEM51@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>17-02-2026 11:29:05</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 20:08:06</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6238,17 +6238,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>17-02-2026 11:32:47</t>
+          <t>09-02-2026 20:12:28</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>17-02-2026 11:32:10</t>
+          <t>09-02-2026 20:10:07</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26160522425100002242</t>
+          <t>26160522213110001840</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6292,12 +6292,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>344042</t>
+          <t>342776</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21859</t>
+          <t>20593</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6307,17 +6307,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">FELISA </t>
+          <t>JUAN MANUEL</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ANGUAMEA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t>X</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6327,63 +6327,75 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6442161660</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>6867292744</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
+          <t>09-11-1973</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>FELISAANGUAMEAVALENZUELA@GMAIL.COM</t>
+          <t>NOCUENTACON1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>16-02-2026 12:24:29</t>
+          <t>10-02-2026 18:03:21</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>23-02-2026 18:27:10</t>
+          <t>10-02-2026 18:35:28</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>10-02-2026 18:35:08</t>
+        </is>
+      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6391,44 +6403,36 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26060522595620004368</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>LIZBETH  SALDIVAR MONTES</t>
-        </is>
-      </c>
+          <t>26160522243990001903</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>344464</t>
+          <t>342457</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>22281</t>
+          <t>20274</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6438,17 +6442,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MICHELLE JAZLIM</t>
+          <t xml:space="preserve">JOSE </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t>FRANCISCO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>RICO</t>
+          <t>FIERRO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6458,67 +6462,75 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6865111469</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>6861575086</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA02</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>09-02-1992</t>
+          <t>15-09-1973</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>MICHELLE.RLEYVA@GMAIL.COM</t>
+          <t>FIERRO_PACO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>17-02-2026 12:06:32</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 19:49:15</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>17-02-2026 12:07:57</t>
+          <t>09-02-2026 19:51:47</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>09-02-2026 19:50:53</t>
+        </is>
+      </c>
       <c r="U45" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6526,19 +6538,19 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26160522425750002244</t>
+          <t>26160522212280001839</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6550,12 +6562,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>344948</t>
+          <t>342583</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>22765</t>
+          <t>20400</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6565,17 +6577,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KENIA LORENA</t>
+          <t>SHESLY DENNIS</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>BATISTA</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6585,12 +6597,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6862417380</t>
+          <t>6861234727</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 1</t>
+          <t>PRESA DE LA ANGOSURA 1491</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6600,52 +6612,48 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>10-06-1998</t>
+          <t>30-07-1996</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>KENIAMB98@GMAIL.COM</t>
+          <t>SHES.MEZAGTZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>18-02-2026 19:27:03</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 11:28:40</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>18-02-2026 19:31:59</t>
+          <t>10-02-2026 11:31:11</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>18-02-2026 19:30:17</t>
+          <t>10-02-2026 11:30:36</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6665,19 +6673,19 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26160522475220002354</t>
+          <t>26160522229140001874</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6689,12 +6697,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>344134</t>
+          <t>343025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21951</t>
+          <t>20842</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6704,17 +6712,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DANNA PAOLA</t>
+          <t>DYLAN</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MOLINA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ARROYO</t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6724,28 +6732,28 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6531662052</t>
+          <t>6861698256</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>20-06-2006</t>
+          <t>06-08-2002</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>MOLINAARROYODANNAPAOLA@GMAIL.COM</t>
+          <t>DYLANMTZM.26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>16-02-2026 15:47:17</t>
+          <t>11-02-2026 15:49:14</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6770,12 +6778,12 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>16-02-2026 15:49:00</t>
+          <t>11-02-2026 15:52:21</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -6792,7 +6800,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26160522393690002158</t>
+          <t>26160522267270001952</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -6804,7 +6812,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -6816,12 +6824,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>344409</t>
+          <t>343384</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22226</t>
+          <t>21201</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6831,17 +6839,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ISRAEL</t>
+          <t>BRISA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t>GASCA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LIAÑO</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6851,39 +6859,35 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6863940285</t>
+          <t>6863912198</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>EEEE12</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>18-04-1977</t>
+          <t>12-02-2006</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>MASTERBOY1930@GMAIL.COM</t>
+          <t>GNAVARROGASCA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>17-02-2026 08:06:52</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>12-02-2026 19:16:27</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6901,17 +6905,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>17-02-2026 08:09:37</t>
+          <t>12-02-2026 19:22:02</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>17-02-2026 08:08:58</t>
+          <t>12-02-2026 19:21:22</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6931,7 +6935,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26160522421530002234</t>
+          <t>26160522304540002036</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
@@ -6943,7 +6947,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6955,12 +6959,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>342457</t>
+          <t>342482</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20274</t>
+          <t>20299</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6970,17 +6974,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE </t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FRANCISCO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FIERRO</t>
+          <t>CACERES</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6990,14 +6994,10 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6861575086</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA02</t>
-        </is>
-      </c>
+          <t>6867220400</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7005,38 +7005,42 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>15-09-1973</t>
+          <t>25-08-1998</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>FIERRO_PACO@HOTMAIL.COM</t>
+          <t>JOSECACEREZ98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>09-02-2026 19:49:15</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>09-02-2026 20:20:01</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>09-02-2026 19:51:47</t>
+          <t>09-02-2026 20:21:16</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -7044,21 +7048,13 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>09-02-2026 19:50:53</t>
-        </is>
-      </c>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7066,14 +7062,14 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26160522212280001839</t>
+          <t>26160522213460001843</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -7090,12 +7086,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>342583</t>
+          <t>342783</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20400</t>
+          <t>20600</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7105,17 +7101,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SHESLY DENNIS</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>TAPIA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>AGUAYO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7125,53 +7121,53 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6861234727</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>PRESA DE LA ANGOSURA 1491</t>
-        </is>
-      </c>
+          <t>6623654956</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>30-07-1996</t>
+          <t>27-03-1998</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>SHES.MEZAGTZ@GMAIL.COM</t>
+          <t>JOSETAPIAGUAYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>10-02-2026 11:28:40</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>10-02-2026 18:11:07</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>10-02-2026 11:31:11</t>
+          <t>10-02-2026 18:12:38</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -7179,21 +7175,13 @@
           <t>10-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>10-02-2026 11:30:36</t>
-        </is>
-      </c>
+      <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7201,19 +7189,19 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26160522229140001874</t>
+          <t>26160522242690001898</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7225,12 +7213,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>343384</t>
+          <t>343557</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21201</t>
+          <t>21374</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7240,12 +7228,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BRISA</t>
+          <t>JUAN CARLOS</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>GASCA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -7260,7 +7248,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6863912198</t>
+          <t>6863903522</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -7275,17 +7263,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>12-02-2006</t>
+          <t>08-03-1971</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>GNAVARROGASCA@GMAIL.COM</t>
+          <t>JUANCARLORIOS1422@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>12-02-2026 19:16:27</t>
+          <t>13-02-2026 17:19:49</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -7306,17 +7294,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>12-02-2026 19:22:02</t>
+          <t>13-02-2026 17:24:13</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>12-02-2026 19:21:22</t>
+          <t>13-02-2026 17:22:41</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -7336,7 +7324,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26160522304540002036</t>
+          <t>26160522326350002078</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
@@ -7360,12 +7348,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>342482</t>
+          <t>345809</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20299</t>
+          <t>87974</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7375,17 +7363,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CACERES</t>
+          <t>HARO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7395,10 +7383,14 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6867220400</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>6863504737</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7406,17 +7398,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>25-08-1998</t>
+          <t>08-04-2000</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>JOSECACEREZ98@GMAIL.COM</t>
+          <t>ALETSMIRANDA7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>09-02-2026 20:20:01</t>
+          <t>23-02-2026 14:46:02</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7426,36 +7418,44 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>09-02-2026 20:21:16</t>
+          <t>23-02-2026 15:06:54</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>23-02-2026 14:52:57</t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7463,19 +7463,19 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26160522213460001843</t>
+          <t>26160522583760002502</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7487,12 +7487,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>342783</t>
+          <t>342997</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20600</t>
+          <t>20814</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7502,17 +7502,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>JAZMIN</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>TAPIA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AGUAYO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7522,67 +7522,75 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6623654956</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>8130964314</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>CERRO DEL POTOSI 1119</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>27-03-1998</t>
+          <t>18-03-1995</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>JOSETAPIAGUAYO@GMAIL.COM</t>
+          <t>YAAS.LOPEZ18@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>10-02-2026 18:11:07</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>11-02-2026 14:53:46</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10-02-2026 18:12:38</t>
+          <t>12-02-2026 12:36:52</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>12-02-2026 12:36:23</t>
+        </is>
+      </c>
       <c r="U53" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7590,19 +7598,19 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26160522242690001898</t>
+          <t>26180522292630004399</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7614,12 +7622,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>344132</t>
+          <t>343135</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21949</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7629,17 +7637,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGELES </t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CARMONA</t>
+          <t>OLIVAS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SIQUEIROS</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7649,28 +7657,24 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6863378715</t>
+          <t>6862316574</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>04-08-2006</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>ANGELESWCARMONA763@GMAIL.COM</t>
-        </is>
-      </c>
+          <t>01-01-2000</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>16-02-2026 15:44:25</t>
+          <t>11-02-2026 20:34:48</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7695,18 +7699,18 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>16-02-2026 15:45:32</t>
+          <t>13-02-2026 16:04:20</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V54" t="inlineStr"/>
@@ -7717,11 +7721,19 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26160522393400002157</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
+          <t>26160522323640002074</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>549</t>
@@ -7729,24 +7741,24 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>345809</t>
+          <t>346272</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>87974</t>
+          <t>88437</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7756,17 +7768,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>ANGELA</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>OJEDA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>UREÑA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7776,32 +7788,28 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6863504737</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6461508837</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>08-04-2000</t>
+          <t>21-04-1999</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>ALETSMIRANDA7@GMAIL.COM</t>
+          <t>ANGELA.OJEDA0421@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>23-02-2026 14:46:02</t>
+          <t>24-02-2026 17:44:34</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7811,44 +7819,36 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>23-02-2026 15:06:54</t>
+          <t>24-02-2026 17:45:53</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>23-02-2026 14:52:57</t>
-        </is>
-      </c>
+          <t>24-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7856,14 +7856,14 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26160522583760002502</t>
+          <t>26160522628990002594</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -7880,12 +7880,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>342997</t>
+          <t>343139</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20814</t>
+          <t>20956</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7895,17 +7895,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>JAZMIN</t>
+          <t>NICZA ARELI</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>IZAGUIRRE</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>8130964314</t>
+          <t>6864650098</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CERRO DEL POTOSI 1119</t>
+          <t xml:space="preserve">TORRE LAS ARCAS </t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7930,17 +7930,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>18-03-1995</t>
+          <t>03-11-1994</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>YAAS.LOPEZ18@GMAIL.COM</t>
+          <t>IZAGUIRREARELI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>11-02-2026 14:53:46</t>
+          <t>11-02-2026 20:53:07</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7961,17 +7961,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>12-02-2026 12:36:52</t>
+          <t>13-02-2026 18:50:54</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>12-02-2026 12:36:23</t>
+          <t>13-02-2026 18:49:33</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7991,10 +7991,14 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26180522292630004399</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr"/>
+          <t>26170522328830002369</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
@@ -8003,7 +8007,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8015,12 +8019,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>343135</t>
+          <t>344132</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20952</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8030,17 +8034,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>JAIME</t>
+          <t xml:space="preserve">ANGELES </t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>CARMONA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>SIQUEIROS</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8050,24 +8054,28 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6862316574</t>
+          <t>6863378715</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
+          <t>04-08-2006</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>ANGELESWCARMONA763@GMAIL.COM</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>11-02-2026 20:34:48</t>
+          <t>16-02-2026 15:44:25</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -8092,18 +8100,18 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>13-02-2026 16:04:20</t>
+          <t>16-02-2026 15:45:32</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V57" t="inlineStr"/>
@@ -8114,19 +8122,11 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26160522323640002074</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26160522393400002157</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
           <t>549</t>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -8273,12 +8273,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>343139</t>
+          <t>344515</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20956</t>
+          <t>22332</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8288,17 +8288,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NICZA ARELI</t>
+          <t>ASTRID AITANA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IZAGUIRRE</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>HIDALGO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6864650098</t>
+          <t>5522151079</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRE LAS ARCAS </t>
+          <t>RIO TULA 12</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -8323,20 +8323,24 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>03-11-1994</t>
+          <t>19-10-2006</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>IZAGUIRREARELI@GMAIL.COM</t>
+          <t>AITANAHIDALGO0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>11-02-2026 20:53:07</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>17-02-2026 15:10:23</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8344,27 +8348,27 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>13-02-2026 18:50:54</t>
+          <t>23-02-2026 15:56:01</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>13-02-2026 18:49:33</t>
+          <t>23-02-2026 15:54:51</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8384,23 +8388,19 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26170522328830002369</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26290522585740002451</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -8412,12 +8412,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>344515</t>
+          <t>344451</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>22332</t>
+          <t>22268</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8427,17 +8427,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ASTRID AITANA</t>
+          <t>TIFFANY JAZMIN</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t>HOPKINS</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8447,37 +8447,37 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>5522151079</t>
+          <t>6866190407</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>RIO TULA 12</t>
+          <t>IND22222</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>19-10-2006</t>
+          <t>06-09-2006</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>AITANAHIDALGO0@GMAIL.COM</t>
+          <t>NOTIENEEE@SSS.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>17-02-2026 15:10:23</t>
+          <t>17-02-2026 11:29:05</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -8487,27 +8487,27 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>23-02-2026 15:56:01</t>
+          <t>17-02-2026 11:32:47</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>23-02-2026 15:54:51</t>
+          <t>17-02-2026 11:32:10</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -8527,36 +8527,36 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26290522585740002451</t>
+          <t>26160522425100002242</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>345376</t>
+          <t>344464</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>87541</t>
+          <t>22281</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8566,17 +8566,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SOPHIA</t>
+          <t>MICHELLE JAZLIM</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>LEYVA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>RICO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8586,14 +8586,10 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6865307488</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6865111469</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8601,64 +8597,56 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>26-06-1993</t>
+          <t>09-02-1992</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>SOPHIA.QUINDI@GMAIL.COM</t>
+          <t>MICHELLE.RLEYVA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>20-02-2026 17:55:33</t>
+          <t>17-02-2026 12:06:32</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>20-02-2026 18:01:22</t>
+          <t>17-02-2026 12:07:57</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>20-02-2026 18:00:10</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8666,19 +8654,19 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26160522533220002443</t>
+          <t>26160522425750002244</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -8690,12 +8678,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>345386</t>
+          <t>344948</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>87551</t>
+          <t>22765</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8705,17 +8693,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEJANDRO </t>
+          <t>KENIA LORENA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>LAURIAS</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>BATISTA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8725,67 +8713,67 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6866441611</t>
+          <t>6862417380</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>INDEPENDENCIA 1</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>10-08-1994</t>
+          <t>10-06-1998</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>ALGSMQD26@GMAIL.COM</t>
+          <t>KENIAMB98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>20-02-2026 18:13:38</t>
+          <t>18-02-2026 19:27:03</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>20-02-2026 18:16:09</t>
+          <t>18-02-2026 19:31:59</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>20-02-2026 18:15:32</t>
+          <t>18-02-2026 19:30:17</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -8805,19 +8793,19 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26160522533690002445</t>
+          <t>26160522475220002354</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -8829,12 +8817,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>345399</t>
+          <t>345376</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>87564</t>
+          <t>87541</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8844,17 +8832,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NATALIA</t>
+          <t>SOPHIA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CASAREZ</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>VALLE</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8864,7 +8852,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6861221578</t>
+          <t>6865307488</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -8879,42 +8867,42 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>09-11-1995</t>
+          <t>26-06-1993</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>NATALIACASAREZVALLE@GMAIL.COM</t>
+          <t>SOPHIA.QUINDI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>20-02-2026 18:53:23</t>
+          <t>20-02-2026 17:55:33</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>20-02-2026 18:57:38</t>
+          <t>20-02-2026 18:01:22</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -8924,7 +8912,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>20-02-2026 18:56:28</t>
+          <t>20-02-2026 18:00:10</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -8934,7 +8922,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -8944,19 +8932,19 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26160522534930002446</t>
+          <t>26160522533220002443</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -8968,12 +8956,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>345976</t>
+          <t>345386</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>88141</t>
+          <t>87551</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8983,17 +8971,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>JOAQUIN</t>
+          <t xml:space="preserve">ALEJANDRO </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>LAURIAS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -9003,10 +8991,14 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6861822047</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>6866441611</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -9014,56 +9006,64 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>10-06-1982</t>
+          <t>10-08-1994</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>JOTAQN.RUIZ@HOTMAIL.COM</t>
+          <t>ALGSMQD26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>23-02-2026 18:22:36</t>
+          <t>20-02-2026 18:13:38</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>23-02-2026 18:24:38</t>
+          <t>20-02-2026 18:16:09</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr"/>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:15:32</t>
+        </is>
+      </c>
       <c r="U64" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr"/>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W64" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9071,36 +9071,36 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26160522595470002522</t>
+          <t>26160522533690002445</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>344197</t>
+          <t>345399</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22014</t>
+          <t>87564</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9110,17 +9110,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SILVIA</t>
+          <t>NATALIA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>CASAREZ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>VALLE</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6863845214</t>
+          <t>6861221578</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -9145,17 +9145,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
+          <t>09-11-1995</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>MARIA.932573@GMAIL.COM</t>
+          <t>NATALIACASAREZVALLE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>16-02-2026 17:11:26</t>
+          <t>20-02-2026 18:53:23</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -9180,17 +9180,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>18-02-2026 17:47:52</t>
+          <t>20-02-2026 18:57:38</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>18-02-2026 17:43:52</t>
+          <t>20-02-2026 18:56:28</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -9210,19 +9210,11 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26160522470320002337</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26160522534930002446</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
           <t>649</t>
@@ -9230,24 +9222,24 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>344391</t>
+          <t>344197</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>22014</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9257,17 +9249,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t>SILVIA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ARTEAGA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9277,28 +9269,32 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6311261612</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>6863845214</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>18-06-1985</t>
+          <t>01-01-2000</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>COLORGRAFICO@HOTMAIL.COM</t>
+          <t>MARIA.932573@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>17-02-2026 07:06:31</t>
+          <t>16-02-2026 17:11:26</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -9308,36 +9304,44 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>17-02-2026 07:07:36</t>
+          <t>18-02-2026 17:47:52</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr"/>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>18-02-2026 17:43:52</t>
+        </is>
+      </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W66" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9345,19 +9349,27 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26160522420050002226</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
+          <t>26160522470320002337</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -9369,12 +9381,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>344630</t>
+          <t>344391</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>22208</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9384,17 +9396,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>JESUS LEONEL</t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>GALAVIZ</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>ARTEAGA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9404,7 +9416,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6865866356</t>
+          <t>6311261612</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9415,17 +9427,17 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>28-10-1986</t>
+          <t>18-06-1985</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>JESUSLEONEL@GMAIL.COM</t>
+          <t>COLORGRAFICO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>17-02-2026 17:54:18</t>
+          <t>17-02-2026 07:06:31</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -9440,22 +9452,22 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>17-02-2026 17:56:16</t>
+          <t>17-02-2026 07:07:36</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>17-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -9472,19 +9484,19 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26160522439290002266</t>
+          <t>26160522420050002226</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -9496,12 +9508,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>344929</t>
+          <t>344630</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22746</t>
+          <t>22447</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9511,17 +9523,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>JESUS LEONEL</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>GALAVIZ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9531,14 +9543,10 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>9371155830</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6865866356</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -9546,64 +9554,56 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>18-06-1991</t>
+          <t>28-10-1986</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>ANGELMORENOOCHOA@GMAIL.COM</t>
+          <t>JESUSLEONEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>18-02-2026 18:36:12</t>
+          <t>17-02-2026 17:54:18</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>18-02-2026 18:47:06</t>
+          <t>17-02-2026 17:56:16</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>18-02-2026 18:46:16</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9611,14 +9611,14 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26160522473470002345</t>
+          <t>26160522439290002266</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
@@ -9635,12 +9635,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>345971</t>
+          <t>345976</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>88136</t>
+          <t>88141</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>IBAÑEZ</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6862034774</t>
+          <t>6861822047</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9681,17 +9681,17 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>21-03-2009</t>
+          <t>10-06-1982</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>RUIZIBAÑEZJQN@OUTLOOK.COM</t>
+          <t>JOTAQN.RUIZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>23-02-2026 18:17:27</t>
+          <t>23-02-2026 18:22:36</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>23-02-2026 18:19:45</t>
+          <t>23-02-2026 18:24:38</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26160522595030002521</t>
+          <t>26160522595470002522</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr"/>
@@ -9750,24 +9750,24 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>346049</t>
+          <t>344929</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>88214</t>
+          <t>22746</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9777,17 +9777,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>JONAS</t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9797,10 +9797,14 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6862765318</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>9371155830</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -9808,56 +9812,64 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>19-07-1999</t>
+          <t>18-06-1991</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>LABAJAMXLI@GMAIL.COM</t>
+          <t>ANGELMORENOOCHOA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>23-02-2026 20:45:09</t>
+          <t>18-02-2026 18:36:12</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>23-02-2026 20:46:28</t>
+          <t>18-02-2026 18:47:06</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr"/>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>18-02-2026 18:46:16</t>
+        </is>
+      </c>
       <c r="U70" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9865,22 +9877,415 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26160522602060002551</t>
+          <t>26160522473470002345</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>345971</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>88136</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>JOAQUIN</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RUIZ</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>IBAÑEZ</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>6862034774</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>21-03-2009</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>RUIZIBAÑEZJQN@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:17:27</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:19:45</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>26160522595030002521</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>346049</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>88214</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>JONAS</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>MEZA</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>6862765318</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>19-07-1999</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>LABAJAMXLI@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>23-02-2026 20:45:09</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
           <t>899</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>23-02-2026 20:46:28</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>26160522602060002551</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>346604</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>88769</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ALVARADO</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>MOSQUERA</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>6862149610</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA 1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>23-06-1989</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>PEMOALJUL@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>25-02-2026 20:04:30</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>25-02-2026 20:10:08</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>25-02-2026 20:08:55</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>26160522667440002678</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
+      <c r="AC73" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
@@ -1388,12 +1388,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>340713</t>
+          <t>290316</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>87814</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LESLIE</t>
+          <t>VANESSA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>HIGUERA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1423,32 +1423,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6865257334</t>
+          <t>6861744727</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>INDEPENDENCIA 1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>10-06-1994</t>
+          <t>22-07-1992</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>LICMERCADOSUNA.10@GMAIL.COM</t>
+          <t>HIGUERAROSAV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>03-02-2026 17:15:35</t>
+          <t>28-04-2025 19:34:24</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1469,17 +1469,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-02-2026 17:19:02</t>
+          <t>14-02-2026 15:01:10</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>03-02-2026 17:18:43</t>
+          <t>14-02-2026 15:00:36</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1499,10 +1499,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26160522048750001552</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
+          <t>26160522349780002121</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1511,7 +1515,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1523,12 +1527,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>290316</t>
+          <t>340481</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>87814</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1538,17 +1542,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VANESSA</t>
+          <t>HILDA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HIGUERA</t>
+          <t>BENAVIDEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1558,32 +1562,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6861744727</t>
+          <t>6864150761</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 1</t>
+          <t>LINEZO1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>22-07-1992</t>
+          <t>21-07-1961</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>HIGUERAROSAV@GMAIL.COM</t>
+          <t>NOTIERERER@TYU.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>28-04-2025 19:34:24</t>
+          <t>03-02-2026 08:55:15</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1604,17 +1608,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>14-02-2026 15:01:10</t>
+          <t>04-02-2026 10:23:34</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>14-02-2026 15:00:36</t>
+          <t>04-02-2026 10:22:30</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1634,15 +1638,19 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26160522349780002121</t>
+          <t>26160522071550001606</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>499</t>
@@ -1650,7 +1658,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1662,12 +1670,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>340481</t>
+          <t>340791</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1677,17 +1685,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HILDA</t>
+          <t>HECTOR MANUEL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BENAVIDEZ</t>
+          <t>ALVARADO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PEÑA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1697,32 +1705,32 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6864150761</t>
+          <t>5628369350</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LINEZO1</t>
+          <t>MAYA CAMPESTRE</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>21-07-1961</t>
+          <t>09-08-1976</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>NOTIERERER@TYU.COM</t>
+          <t>MACALVMAIL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>03-02-2026 08:55:15</t>
+          <t>03-02-2026 18:47:52</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1743,17 +1751,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>04-02-2026 10:23:34</t>
+          <t>03-02-2026 19:09:42</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>04-02-2026 10:22:30</t>
+          <t>03-02-2026 19:09:20</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1773,19 +1781,15 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26160522071550001606</t>
+          <t>26160522055330001568</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
           <t>499</t>
@@ -1793,7 +1797,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1805,12 +1809,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>340791</t>
+          <t>340808</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1820,17 +1824,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HECTOR MANUEL</t>
+          <t>RENE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ALVARADO</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1840,12 +1844,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5628369350</t>
+          <t>6863485358</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MAYA CAMPESTRE</t>
+          <t>INDEPENDENCIA 23</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1855,17 +1859,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>09-08-1976</t>
+          <t>15-09-1996</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>MACALVMAIL@GMAIL.COM</t>
+          <t>RENEGONZALEZ1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-02-2026 18:47:52</t>
+          <t>03-02-2026 19:14:48</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1886,17 +1890,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-02-2026 19:09:42</t>
+          <t>05-02-2026 19:04:55</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>03-02-2026 19:09:20</t>
+          <t>05-02-2026 19:03:37</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1916,15 +1920,19 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26160522055330001568</t>
+          <t>26160522117360001694</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>499</t>
@@ -1932,7 +1940,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1944,12 +1952,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>340808</t>
+          <t>238288</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18626</t>
+          <t>35793</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1959,17 +1967,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>RENE</t>
+          <t>SILVIA PAOLA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>PAYAN</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1979,32 +1987,32 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6863485358</t>
+          <t>6864629400</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 23</t>
+          <t>IND123</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>15-09-1996</t>
+          <t>18-02-2009</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>RENEGONZALEZ1@GMAIL.COM</t>
+          <t>SILVIAPAYAN009@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>03-02-2026 19:14:48</t>
+          <t>05-06-2024 18:12:25</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2025,17 +2033,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>05-02-2026 19:04:55</t>
+          <t>10-02-2026 05:33:30</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>05-02-2026 19:03:37</t>
+          <t>10-02-2026 05:32:15</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2055,7 +2063,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26160522117360001694</t>
+          <t>26160522222220001861</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2075,7 +2083,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2087,12 +2095,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>342294</t>
+          <t>299954</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>97452</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2102,17 +2110,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CARLOS ANTONIO</t>
+          <t>EUNICE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2122,53 +2130,53 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6863473949</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>6865848338</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>IND123</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>25-10-2003</t>
+          <t>11-06-2001</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CARLOS8A2510@GMAIL.COM</t>
+          <t>EUNICE.LOPEZ5@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>09-02-2026 16:59:55</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>23-06-2025 18:39:49</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>09-02-2026 17:01:28</t>
+          <t>09-02-2026 08:55:34</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2176,13 +2184,21 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>09-02-2026 08:54:52</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2190,19 +2206,23 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26160522200300001806</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
+          <t>26160522185470001787</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2214,12 +2234,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>341834</t>
+          <t>340713</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19652</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2229,17 +2249,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DARIANA</t>
+          <t>LESLIE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2249,12 +2269,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6862489316</t>
+          <t>6865257334</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SAN CARLO1</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2264,17 +2284,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>03-12-1981</t>
+          <t>10-06-1994</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>LOPEZDARIANA780@GMAIL.COM</t>
+          <t>LICMERCADOSUNA.10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>07-02-2026 13:31:41</t>
+          <t>03-02-2026 17:15:35</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2295,17 +2315,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>07-02-2026 13:38:04</t>
+          <t>03-02-2026 17:19:02</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>07-02-2026 13:35:50</t>
+          <t>03-02-2026 17:18:43</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2325,7 +2345,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26160522161810001766</t>
+          <t>26160522048750001552</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2337,7 +2357,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2349,12 +2369,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>342323</t>
+          <t>339686</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2364,17 +2384,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MARCO</t>
+          <t>EDUARDO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ORDUÑO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2384,12 +2404,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6861601599</t>
+          <t>6862121992</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA0</t>
+          <t>I988</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2399,20 +2419,24 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>25-04-1979</t>
+          <t>06-05-1992</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>MOPILLO@GMAIL.COM</t>
+          <t>POLOEGARCIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>09-02-2026 17:27:09</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>31-01-2026 12:59:25</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2430,17 +2454,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>09-02-2026 17:33:13</t>
+          <t>18-02-2026 13:22:14</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>09-02-2026 17:32:43</t>
+          <t>18-02-2026 13:21:09</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2460,11 +2484,19 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26160522202710001810</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+          <t>26160522461460002325</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>auxiliar independencia mexicali</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>499</t>
@@ -2472,7 +2504,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2484,12 +2516,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>238288</t>
+          <t>337242</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>35793</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2499,17 +2531,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SILVIA PAOLA</t>
+          <t xml:space="preserve">MARTHA ELENA </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PAYAN</t>
+          <t>MAEDA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2519,14 +2551,10 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6864629400</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>IND123</t>
-        </is>
-      </c>
+          <t>6861253578</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2534,60 +2562,56 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>18-02-2009</t>
+          <t>06-10-1952</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>SILVIAPAYAN009@GMAIL.COM</t>
+          <t>MARTHAELENAMG@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>05-06-2024 18:12:25</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>23-01-2026 12:52:24</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>10-02-2026 05:33:30</t>
+          <t>03-02-2026 08:23:40</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>10-02-2026 05:32:15</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2595,27 +2619,19 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26160522222220001861</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26160522033610001514</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2627,12 +2643,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>299954</t>
+          <t>341834</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>97452</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2642,7 +2658,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EUNICE</t>
+          <t>DARIANA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2652,7 +2668,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2662,12 +2678,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6865848338</t>
+          <t>6862489316</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>IND123</t>
+          <t>SAN CARLO1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2677,17 +2693,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>11-06-2001</t>
+          <t>03-12-1981</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>EUNICE.LOPEZ5@UABC.EDU.MX</t>
+          <t>LOPEZDARIANA780@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>23-06-2025 18:39:49</t>
+          <t>07-02-2026 13:31:41</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2708,17 +2724,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>09-02-2026 08:55:34</t>
+          <t>07-02-2026 13:38:04</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>09-02-2026 08:54:52</t>
+          <t>07-02-2026 13:35:50</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2728,7 +2744,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2738,14 +2754,10 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26160522185470001787</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26160522161810001766</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2754,7 +2766,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2766,12 +2778,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>339686</t>
+          <t>340255</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17504</t>
+          <t>18073</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2781,17 +2793,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EDUARDO</t>
+          <t>STEPHANY</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>BEJARANO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2801,39 +2813,35 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6862121992</t>
+          <t>6865923181</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>I988</t>
+          <t>INDEPENDENCIA 38</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>06-05-1992</t>
+          <t>18-01-1995</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>POLOEGARCIA@GMAIL.COM</t>
+          <t>FANNYBEJARANO904@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>31-01-2026 12:59:25</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>02-02-2026 16:15:36</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2851,17 +2859,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>18-02-2026 13:22:14</t>
+          <t>02-02-2026 16:21:03</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>18-02-2026 13:21:09</t>
+          <t>02-02-2026 16:20:43</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2871,7 +2879,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2881,19 +2889,11 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26160522461460002325</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>auxiliar independencia mexicali</t>
-        </is>
-      </c>
+          <t>26160522016270001486</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
           <t>499</t>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2913,12 +2913,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>342822</t>
+          <t>342323</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20639</t>
+          <t>20141</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2928,17 +2928,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LEOPOLDO</t>
+          <t>MARCO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LOYO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>COBO</t>
+          <t>ORDUÑO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2948,12 +2948,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6862120595</t>
+          <t>6861601599</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>INDEPENDENCIA0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2963,17 +2963,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>17-07-1971</t>
+          <t>25-04-1979</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>LEOPOLDOLOYO@GMAIL.COM</t>
+          <t>MOPILLO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>10-02-2026 19:02:43</t>
+          <t>09-02-2026 17:27:09</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2994,17 +2994,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>14-02-2026 13:28:02</t>
+          <t>09-02-2026 17:33:13</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>14-02-2026 13:27:04</t>
+          <t>09-02-2026 17:32:43</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3024,14 +3024,10 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26160522349290002113</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26160522202710001810</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
@@ -3052,12 +3048,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>342087</t>
+          <t>340641</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19905</t>
+          <t>18459</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3067,17 +3063,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KARLA VERÓNICA</t>
+          <t>LUCIA YADIRA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PALAFOX</t>
+          <t>VELARDE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3087,12 +3083,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6861244927</t>
+          <t>6861822416</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>IND111111</t>
+          <t>CULTURA OLMECA 3608</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3102,52 +3098,48 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>26-05-1986</t>
+          <t>13-12-1990</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>VERONIKAPALAFOX@GMAIL.COM</t>
+          <t>YADIRA_1290@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>09-02-2026 10:07:36</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 15:56:48</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>16-02-2026 08:19:11</t>
+          <t>05-02-2026 16:33:17</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>16-02-2026 08:18:23</t>
+          <t>05-02-2026 16:30:37</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3157,7 +3149,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3167,7 +3159,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26160522380750002134</t>
+          <t>26160522110560001680</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3177,17 +3169,17 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3199,12 +3191,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>337242</t>
+          <t>340789</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3214,17 +3206,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTHA ELENA </t>
+          <t xml:space="preserve">DANIELA </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MAEDA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3234,10 +3226,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6861253578</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>6861739204</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MAYA CAMPESTRE</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3245,42 +3241,38 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>06-10-1952</t>
+          <t>06-09-1989</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>MARTHAELENAMG@GMAIL.COM</t>
+          <t>DANIELA.SANCHEZ.MORENO.89@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>23-01-2026 12:52:24</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 18:45:03</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>03-02-2026 08:23:40</t>
+          <t>03-02-2026 19:05:49</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -3288,13 +3280,21 @@
           <t>03-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>03-02-2026 19:04:34</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3302,19 +3302,23 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26160522033610001514</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
+          <t>26160522055070001567</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3326,12 +3330,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>340255</t>
+          <t>340697</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18073</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3341,17 +3345,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>STEPHANY</t>
+          <t>CRISTIAN ISMAEL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BEJARANO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ENRIQUEZ</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3361,32 +3365,32 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6865923181</t>
+          <t>6863537341</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 38</t>
+          <t>INDEPENDENCIA3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>18-01-1995</t>
+          <t>22-06-1995</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>FANNYBEJARANO904@GMAIL.COM</t>
+          <t>CRISTIAN.TORRES@GCADENA.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>02-02-2026 16:15:36</t>
+          <t>03-02-2026 17:02:34</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3407,17 +3411,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>02-02-2026 16:21:03</t>
+          <t>03-02-2026 17:06:48</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>02-02-2026 16:20:43</t>
+          <t>03-02-2026 17:06:13</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3427,7 +3431,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3437,7 +3441,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26160522016270001486</t>
+          <t>26160522047970001551</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3449,7 +3453,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3461,12 +3465,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>342794</t>
+          <t>342087</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>19905</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3476,17 +3480,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>JOSUE</t>
+          <t>KARLA VERÓNICA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>PALAFOX</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3496,63 +3500,67 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6861127057</t>
+          <t>6861244927</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>INDEPENDENCI1</t>
+          <t>IND111111</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>26-11-1989</t>
+          <t>26-05-1986</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>JOSUEBRMUSIC@GMAIL.COM</t>
+          <t>VERONIKAPALAFOX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>10-02-2026 18:25:08</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>09-02-2026 10:07:36</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>10-02-2026 18:27:56</t>
+          <t>16-02-2026 08:19:11</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>10-02-2026 18:27:24</t>
+          <t>16-02-2026 08:18:23</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3562,7 +3570,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3572,19 +3580,27 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26160522243630001901</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
+          <t>26160522380750002134</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3596,12 +3612,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>340641</t>
+          <t>342794</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3611,17 +3627,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LUCIA YADIRA</t>
+          <t>JOSUE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VELARDE</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3631,32 +3647,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6861822416</t>
+          <t>6861127057</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CULTURA OLMECA 3608</t>
+          <t>INDEPENDENCI1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>13-12-1990</t>
+          <t>26-11-1989</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>YADIRA_1290@HOTMAIL.COM</t>
+          <t>JOSUEBRMUSIC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>03-02-2026 15:56:48</t>
+          <t>10-02-2026 18:25:08</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3677,17 +3693,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>05-02-2026 16:33:17</t>
+          <t>10-02-2026 18:27:56</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>05-02-2026 16:30:37</t>
+          <t>10-02-2026 18:27:24</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3707,19 +3723,11 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26160522110560001680</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26160522243630001901</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
           <t>499</t>
@@ -3727,7 +3735,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3739,12 +3747,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>343713</t>
+          <t>341132</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3754,17 +3762,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>JESSICA ALEJANDRA</t>
+          <t xml:space="preserve">NAHOMI ESTEFANIA </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>TALAMANTES</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3774,12 +3782,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6863648770</t>
+          <t>6643120858</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>JOSE MARIA AGUAYO 506</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3789,17 +3797,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>18-01-2006</t>
+          <t>18-08-1996</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>JESSICAA.GUTIERREZ@CETYS.EDU.MX</t>
+          <t>ESTEFANIAMTALAMANTESX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>14-02-2026 11:38:52</t>
+          <t>04-02-2026 18:08:31</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3820,17 +3828,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>14-02-2026 11:41:20</t>
+          <t>10-02-2026 16:06:43</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>14-02-2026 11:40:29</t>
+          <t>10-02-2026 16:05:59</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3850,11 +3858,19 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26160522347590002106</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+          <t>26130522235720002570</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>MARIA CANDELARIA LARA AVILA</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>499</t>
@@ -3862,7 +3878,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3874,12 +3890,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>342478</t>
+          <t>343140</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20295</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3889,17 +3905,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FERNANDO</t>
+          <t xml:space="preserve">VANESSA </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3909,32 +3925,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6861146223</t>
+          <t>6864164007</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA01</t>
+          <t>AV TORRE LAS ARCAS 2045</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>27-04-1993</t>
+          <t>08-11-1989</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>IVANRNAVARRO12@GMAIL.COM</t>
+          <t>VANESSAGALVANR250210@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>09-02-2026 20:13:50</t>
+          <t>11-02-2026 20:55:11</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3955,17 +3971,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>09-02-2026 20:16:34</t>
+          <t>13-02-2026 18:56:17</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>09-02-2026 20:16:03</t>
+          <t>13-02-2026 18:55:42</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3975,7 +3991,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3985,10 +4001,14 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26160522213270001841</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
+          <t>26170522329060002370</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3997,7 +4017,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4009,12 +4029,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>342580</t>
+          <t>341819</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20397</t>
+          <t>19637</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4024,17 +4044,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>HECTOR MANUEL</t>
+          <t>KARYME</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PIÑA</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>OLIVEROS</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4044,28 +4064,28 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6865895862</t>
+          <t>6861351566</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>17-10-2002</t>
+          <t>11-12-2004</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>NOTIENE11112222@FFFFDDD.COM</t>
+          <t>KARYMEMACLOP@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>10-02-2026 10:48:52</t>
+          <t>07-02-2026 12:03:12</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4080,28 +4100,28 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>10-02-2026 10:50:12</t>
+          <t>07-02-2026 12:05:36</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>10-05-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V27" t="inlineStr"/>
@@ -4112,14 +4132,14 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26160522228650001872</t>
+          <t>26160522160500001761</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4136,12 +4156,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>343140</t>
+          <t>342478</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>20295</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4151,17 +4171,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">VANESSA </t>
+          <t>FERNANDO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4171,32 +4191,32 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6864164007</t>
+          <t>6861146223</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>AV TORRE LAS ARCAS 2045</t>
+          <t>INDEPENDENCIA01</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>08-11-1989</t>
+          <t>27-04-1993</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>VANESSAGALVANR250210@GMAIL.COM</t>
+          <t>IVANRNAVARRO12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>11-02-2026 20:55:11</t>
+          <t>09-02-2026 20:13:50</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4217,17 +4237,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>13-02-2026 18:56:17</t>
+          <t>09-02-2026 20:16:34</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>13-02-2026 18:55:42</t>
+          <t>09-02-2026 20:16:03</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4237,7 +4257,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4247,14 +4267,10 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26170522329060002370</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26160522213270001841</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
@@ -4263,7 +4279,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4275,12 +4291,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>340697</t>
+          <t>342580</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>20397</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4290,17 +4306,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CRISTIAN ISMAEL</t>
+          <t>HECTOR MANUEL</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>PIÑA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>OLIVEROS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4310,14 +4326,10 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6863537341</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA3</t>
-        </is>
-      </c>
+          <t>6865895862</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4325,60 +4337,56 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>22-06-1995</t>
+          <t>17-10-2002</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CRISTIAN.TORRES@GCADENA.COM</t>
+          <t>NOTIENE11112222@FFFFDDD.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>03-02-2026 17:02:34</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>10-02-2026 10:48:52</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>03-02-2026 17:06:48</t>
+          <t>10-02-2026 10:50:12</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>03-02-2026 17:06:13</t>
-        </is>
-      </c>
+          <t>10-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4386,19 +4394,19 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26160522047970001551</t>
+          <t>26160522228650001872</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4672,12 +4680,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>340789</t>
+          <t>342336</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18607</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4687,17 +4695,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIELA </t>
+          <t>MARCO ALEJANDRO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4707,32 +4715,32 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6861739204</t>
+          <t>6861632588</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>MAYA CAMPESTRE</t>
+          <t>INDEPENDENCIA01</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>06-09-1989</t>
+          <t>12-05-2006</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>DANIELA.SANCHEZ.MORENO.89@GMAIL.COM</t>
+          <t>6MALLISME9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>03-02-2026 18:45:03</t>
+          <t>09-02-2026 17:35:12</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4753,17 +4761,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>03-02-2026 19:05:49</t>
+          <t>09-02-2026 17:38:30</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>03-02-2026 19:04:34</t>
+          <t>09-02-2026 17:38:05</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4773,7 +4781,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4783,14 +4791,10 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26160522055070001567</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26160522203170001811</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4799,7 +4803,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4811,12 +4815,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>341132</t>
+          <t>342474</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>20291</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4826,17 +4830,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAHOMI ESTEFANIA </t>
+          <t>MELISSA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TALAMANTES</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4846,12 +4850,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6643120858</t>
+          <t>6863242180</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>INDEPENDENCIA01</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4861,17 +4865,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>18-08-1996</t>
+          <t>25-07-1987</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ESTEFANIAMTALAMANTESX@GMAIL.COM</t>
+          <t>YLEM51@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>04-02-2026 18:08:31</t>
+          <t>09-02-2026 20:08:06</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4892,17 +4896,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>10-02-2026 16:06:43</t>
+          <t>09-02-2026 20:12:28</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>10-02-2026 16:05:59</t>
+          <t>09-02-2026 20:10:07</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4922,19 +4926,11 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26130522235720002570</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>MARIA CANDELARIA LARA AVILA</t>
-        </is>
-      </c>
+          <t>26160522213110001840</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
           <t>499</t>
@@ -4942,7 +4938,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4954,12 +4950,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>345721</t>
+          <t>342457</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>87886</t>
+          <t>20274</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4969,17 +4965,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>J ASUNCION</t>
+          <t xml:space="preserve">JOSE </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>FRANCISCO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>FIERRO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4989,12 +4985,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6861754997</t>
+          <t>6861575086</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>RIO AMECA 1896</t>
+          <t>INDEPENDENCIA02</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5004,24 +5000,20 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>14-01-1981</t>
+          <t>15-09-1973</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>RODRILOVEMX@GMAIL.COM</t>
+          <t>FIERRO_PACO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>23-02-2026 12:02:31</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 19:49:15</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5039,17 +5031,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>23-02-2026 12:11:56</t>
+          <t>09-02-2026 19:51:47</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>23-02-2026 12:08:50</t>
+          <t>09-02-2026 19:50:53</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5069,7 +5061,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26160522578360002492</t>
+          <t>26160522212280001839</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -5093,12 +5085,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>341819</t>
+          <t>342583</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19637</t>
+          <t>20400</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5108,17 +5100,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>KARYME</t>
+          <t>SHESLY DENNIS</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5128,10 +5120,14 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6861351566</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>6861234727</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>PRESA DE LA ANGOSURA 1491</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5139,56 +5135,60 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>11-12-2004</t>
+          <t>30-07-1996</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>KARYMEMACLOP@GMAIL.COM</t>
+          <t>SHES.MEZAGTZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>07-02-2026 12:03:12</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 11:28:40</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>07-02-2026 12:05:36</t>
+          <t>10-02-2026 11:31:11</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>10-02-2026 11:30:36</t>
+        </is>
+      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5196,19 +5196,19 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26160522160500001761</t>
+          <t>26160522229140001874</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5220,12 +5220,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>344453</t>
+          <t>342776</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>22270</t>
+          <t>20593</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JESUS</t>
+          <t>JUAN MANUEL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5255,10 +5255,14 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6861762359</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>6867292744</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5266,56 +5270,60 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>11-08-1951</t>
+          <t>09-11-1973</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>NOTIENE23445@DFDF.COM</t>
+          <t>NOCUENTACON1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>17-02-2026 11:34:41</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 18:03:21</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>17-02-2026 11:37:38</t>
+          <t>10-02-2026 18:35:28</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>10-02-2026 18:35:08</t>
+        </is>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5323,19 +5331,19 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26160522425250002243</t>
+          <t>26160522243990001903</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5347,12 +5355,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>344505</t>
+          <t>344453</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>22270</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5362,17 +5370,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>KENIA</t>
+          <t>JESUS</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5382,79 +5390,67 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6869460269</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6861762359</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>24-09-1981</t>
+          <t>11-08-1951</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>KRISS0024@GMAIL.COM</t>
+          <t>NOTIENE23445@DFDF.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>17-02-2026 14:43:35</t>
+          <t>17-02-2026 11:34:41</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>17-02-2026 14:52:04</t>
+          <t>17-02-2026 11:37:38</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>17-02-2026 14:49:23</t>
-        </is>
-      </c>
+          <t>17-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5462,19 +5458,19 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26160522430130002253</t>
+          <t>26160522425250002243</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5486,12 +5482,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>344042</t>
+          <t>344505</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21859</t>
+          <t>22322</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5501,17 +5497,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">FELISA </t>
+          <t>KENIA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ANGUAMEA</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t>X</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5521,10 +5517,14 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6442161660</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>6869460269</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5532,52 +5532,64 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
+          <t>24-09-1981</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>FELISAANGUAMEAVALENZUELA@GMAIL.COM</t>
+          <t>KRISS0024@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>16-02-2026 12:24:29</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>17-02-2026 14:43:35</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>23-02-2026 18:27:10</t>
+          <t>17-02-2026 14:52:04</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>17-02-2026 14:49:23</t>
+        </is>
+      </c>
       <c r="U38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5585,27 +5597,19 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26060522595620004368</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>LIZBETH  SALDIVAR MONTES</t>
-        </is>
-      </c>
+          <t>26160522430130002253</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5617,12 +5621,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>344134</t>
+          <t>342294</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21951</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5632,17 +5636,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DANNA PAOLA</t>
+          <t>CARLOS ANTONIO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MOLINA</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ARROYO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5652,28 +5656,28 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6531662052</t>
+          <t>6863473949</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>20-06-2006</t>
+          <t>25-10-2003</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>MOLINAARROYODANNAPAOLA@GMAIL.COM</t>
+          <t>CARLOS8A2510@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>16-02-2026 15:47:17</t>
+          <t>09-02-2026 16:59:55</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5698,18 +5702,18 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>16-02-2026 15:49:00</t>
+          <t>09-02-2026 17:01:28</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V39" t="inlineStr"/>
@@ -5720,7 +5724,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26160522393690002158</t>
+          <t>26160522200300001806</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5732,7 +5736,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5744,12 +5748,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>344409</t>
+          <t>342482</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>22226</t>
+          <t>20299</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5759,17 +5763,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ISRAEL</t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LIAÑO</t>
+          <t>CACERES</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5779,14 +5783,10 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6863940285</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>EEEE12</t>
-        </is>
-      </c>
+          <t>6867220400</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5794,64 +5794,56 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>18-04-1977</t>
+          <t>25-08-1998</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>MASTERBOY1930@GMAIL.COM</t>
+          <t>JOSECACEREZ98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>17-02-2026 08:06:52</t>
+          <t>09-02-2026 20:20:01</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>17-02-2026 08:09:37</t>
+          <t>09-02-2026 20:21:16</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>17-02-2026 08:08:58</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5859,19 +5851,19 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26160522421530002234</t>
+          <t>26160522213460001843</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5883,12 +5875,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>346370</t>
+          <t>342783</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>88535</t>
+          <t>20600</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5898,17 +5890,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>JOSE ALBERTO</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PAEZ</t>
+          <t>TAPIA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FRANCISCO</t>
+          <t>AGUAYO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5918,14 +5910,10 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>7123435473</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>VILLAFONTANA</t>
-        </is>
-      </c>
+          <t>6623654956</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5933,64 +5921,56 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>26-06-2000</t>
+          <t>27-03-1998</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>JOSE5535072149@GMAIL.COM</t>
+          <t>JOSETAPIAGUAYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>25-02-2026 07:44:10</t>
+          <t>10-02-2026 18:11:07</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>25-02-2026 07:47:45</t>
+          <t>10-02-2026 18:12:38</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>25-02-2026 07:46:50</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5998,36 +5978,36 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26160522646040002634</t>
+          <t>26160522242690001898</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>342336</t>
+          <t>343025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>20842</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6037,17 +6017,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MARCO ALEJANDRO</t>
+          <t>DYLAN</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6057,14 +6037,10 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6861632588</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA01</t>
-        </is>
-      </c>
+          <t>6861698256</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6072,60 +6048,56 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>12-05-2006</t>
+          <t>06-08-2002</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>6MALLISME9@GMAIL.COM</t>
+          <t>DYLANMTZM.26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>09-02-2026 17:35:12</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>11-02-2026 15:49:14</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>09-02-2026 17:38:30</t>
+          <t>11-02-2026 15:52:21</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>09-02-2026 17:38:05</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6133,19 +6105,19 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26160522203170001811</t>
+          <t>26160522267270001952</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6157,12 +6129,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>342474</t>
+          <t>342997</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20814</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6172,17 +6144,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MELISSA</t>
+          <t>JAZMIN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6192,12 +6164,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6863242180</t>
+          <t>8130964314</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA01</t>
+          <t>CERRO DEL POTOSI 1119</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6207,17 +6179,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>25-07-1987</t>
+          <t>18-03-1995</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>YLEM51@GMAIL.COM</t>
+          <t>YAAS.LOPEZ18@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>09-02-2026 20:08:06</t>
+          <t>11-02-2026 14:53:46</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6238,17 +6210,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>09-02-2026 20:12:28</t>
+          <t>12-02-2026 12:36:52</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>09-02-2026 20:10:07</t>
+          <t>12-02-2026 12:36:23</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6258,7 +6230,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -6268,7 +6240,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26160522213110001840</t>
+          <t>26180522292630004399</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -6280,7 +6252,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6292,12 +6264,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>342776</t>
+          <t>343135</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20593</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6307,12 +6279,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>JUAN MANUEL</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>OLIVAS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -6327,14 +6299,10 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6867292744</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6862316574</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6342,60 +6310,52 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>09-11-1973</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>NOCUENTACON1@GMAIL.COM</t>
-        </is>
-      </c>
+          <t>01-01-2000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>10-02-2026 18:03:21</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>11-02-2026 20:34:48</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>10-02-2026 18:35:28</t>
+          <t>13-02-2026 16:04:20</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>10-02-2026 18:35:08</t>
-        </is>
-      </c>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6403,36 +6363,44 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26160522243990001903</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
+          <t>26160522323640002074</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>342457</t>
+          <t>343384</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20274</t>
+          <t>21201</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6442,17 +6410,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE </t>
+          <t>BRISA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FRANCISCO</t>
+          <t>GASCA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FIERRO</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6462,32 +6430,32 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6861575086</t>
+          <t>6863912198</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA02</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>15-09-1973</t>
+          <t>12-02-2006</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>FIERRO_PACO@HOTMAIL.COM</t>
+          <t>GNAVARROGASCA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>09-02-2026 19:49:15</t>
+          <t>12-02-2026 19:16:27</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6508,17 +6476,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>09-02-2026 19:51:47</t>
+          <t>12-02-2026 19:22:02</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>09-02-2026 19:50:53</t>
+          <t>12-02-2026 19:21:22</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6538,7 +6506,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26160522212280001839</t>
+          <t>26160522304540002036</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
@@ -6550,7 +6518,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6562,12 +6530,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>342583</t>
+          <t>343557</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20400</t>
+          <t>21374</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6577,17 +6545,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SHESLY DENNIS</t>
+          <t>JUAN CARLOS</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6597,12 +6565,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6861234727</t>
+          <t>6863903522</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>PRESA DE LA ANGOSURA 1491</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6612,17 +6580,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>30-07-1996</t>
+          <t>08-03-1971</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>SHES.MEZAGTZ@GMAIL.COM</t>
+          <t>JUANCARLORIOS1422@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>10-02-2026 11:28:40</t>
+          <t>13-02-2026 17:19:49</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6643,17 +6611,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>10-02-2026 11:31:11</t>
+          <t>13-02-2026 17:24:13</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>10-02-2026 11:30:36</t>
+          <t>13-02-2026 17:22:41</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6673,7 +6641,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26160522229140001874</t>
+          <t>26160522326350002078</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
@@ -6685,7 +6653,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6697,12 +6665,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>343025</t>
+          <t>344042</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20842</t>
+          <t>21859</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6712,17 +6680,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DYLAN</t>
+          <t xml:space="preserve">FELISA </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>ANGUAMEA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6732,35 +6700,31 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6861698256</t>
+          <t>6442161660</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>06-08-2002</t>
+          <t>01-01-2000</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>DYLANMTZM.26@GMAIL.COM</t>
+          <t>FELISAANGUAMEAVALENZUELA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>11-02-2026 15:49:14</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>16-02-2026 12:24:29</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -6768,28 +6732,28 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>11-02-2026 15:52:21</t>
+          <t>23-02-2026 18:27:10</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>23-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V47" t="inlineStr"/>
@@ -6800,14 +6764,22 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26160522267270001952</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
+          <t>26060522595620004368</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6824,12 +6796,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>343384</t>
+          <t>344134</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21201</t>
+          <t>21951</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6839,17 +6811,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BRISA</t>
+          <t>DANNA PAOLA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>GASCA</t>
+          <t>MOLINA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>ARROYO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6859,14 +6831,10 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6863912198</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6531662052</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6874,60 +6842,56 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>12-02-2006</t>
+          <t>20-06-2006</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>GNAVARROGASCA@GMAIL.COM</t>
+          <t>MOLINAARROYODANNAPAOLA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>12-02-2026 19:16:27</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>16-02-2026 15:47:17</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>12-02-2026 19:22:02</t>
+          <t>16-02-2026 15:49:00</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>12-02-2026 19:21:22</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6935,14 +6899,14 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26160522304540002036</t>
+          <t>26160522393690002158</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -6959,12 +6923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>342482</t>
+          <t>344409</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20299</t>
+          <t>22226</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6974,17 +6938,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>ISRAEL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>VELAZQUEZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CACERES</t>
+          <t>LIAÑO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6994,10 +6958,14 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6867220400</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>6863940285</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>EEEE12</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7005,56 +6973,64 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>25-08-1998</t>
+          <t>18-04-1977</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>JOSECACEREZ98@GMAIL.COM</t>
+          <t>MASTERBOY1930@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>09-02-2026 20:20:01</t>
+          <t>17-02-2026 08:06:52</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>09-02-2026 20:21:16</t>
+          <t>17-02-2026 08:09:37</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>17-02-2026 08:08:58</t>
+        </is>
+      </c>
       <c r="U49" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7062,19 +7038,19 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26160522213460001843</t>
+          <t>26160522421530002234</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7086,12 +7062,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>342783</t>
+          <t>343139</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20600</t>
+          <t>20956</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7101,17 +7077,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>NICZA ARELI</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>TAPIA</t>
+          <t>IZAGUIRRE</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AGUAYO</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7121,67 +7097,75 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6623654956</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>6864650098</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TORRE LAS ARCAS </t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>27-03-1998</t>
+          <t>03-11-1994</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>JOSETAPIAGUAYO@GMAIL.COM</t>
+          <t>IZAGUIRREARELI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>10-02-2026 18:11:07</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>11-02-2026 20:53:07</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>10-02-2026 18:12:38</t>
+          <t>13-02-2026 18:50:54</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>13-02-2026 18:49:33</t>
+        </is>
+      </c>
       <c r="U50" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7189,19 +7173,23 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26160522242690001898</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr"/>
+          <t>26170522328830002369</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7213,12 +7201,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>343557</t>
+          <t>344132</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21374</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7228,17 +7216,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>JUAN CARLOS</t>
+          <t xml:space="preserve">ANGELES </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>CARMONA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>SIQUEIROS</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7248,14 +7236,10 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6863903522</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6863378715</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7263,60 +7247,56 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>08-03-1971</t>
+          <t>04-08-2006</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>JUANCARLORIOS1422@GMAIL.COM</t>
+          <t>ANGELESWCARMONA763@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>13-02-2026 17:19:49</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>16-02-2026 15:44:25</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>13-02-2026 17:24:13</t>
+          <t>16-02-2026 15:45:32</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>13-02-2026 17:22:41</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7324,14 +7304,14 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26160522326350002078</t>
+          <t>26160522393400002157</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -7348,12 +7328,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>345809</t>
+          <t>342822</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>87974</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7363,17 +7343,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>LEOPOLDO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>LOYO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>COBO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7383,7 +7363,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6863504737</t>
+          <t>6862120595</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -7398,52 +7378,48 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>08-04-2000</t>
+          <t>17-07-1971</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>ALETSMIRANDA7@GMAIL.COM</t>
+          <t>LEOPOLDOLOYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>23-02-2026 14:46:02</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 19:02:43</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>23-02-2026 15:06:54</t>
+          <t>14-02-2026 13:28:02</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>23-02-2026 14:52:57</t>
+          <t>14-02-2026 13:27:04</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7453,7 +7429,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -7463,14 +7439,18 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26160522583760002502</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr"/>
+          <t>26160522349290002113</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -7487,12 +7467,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>342997</t>
+          <t>344345</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20814</t>
+          <t>22162</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7502,17 +7482,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>JAZMIN</t>
+          <t>JESUS ANTONIO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>TOPETE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7522,75 +7502,67 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>8130964314</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>CERRO DEL POTOSI 1119</t>
-        </is>
-      </c>
+          <t>6865890812</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>18-03-1995</t>
+          <t>15-12-1987</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>YAAS.LOPEZ18@GMAIL.COM</t>
+          <t>CHUYANTONT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>11-02-2026 14:53:46</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>16-02-2026 19:42:11</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>12-02-2026 12:36:52</t>
+          <t>16-02-2026 19:43:34</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>12-02-2026 12:36:23</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7598,19 +7570,19 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26180522292630004399</t>
+          <t>26160522409070002196</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7622,12 +7594,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>343135</t>
+          <t>344515</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20952</t>
+          <t>22332</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7637,17 +7609,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>JAIME</t>
+          <t>ASTRID AITANA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>HIDALGO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7657,24 +7629,32 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6862316574</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>5522151079</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>RIO TULA 12</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
+          <t>19-10-2006</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>AITANAHIDALGO0@GMAIL.COM</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>11-02-2026 20:34:48</t>
+          <t>17-02-2026 15:10:23</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7684,12 +7664,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -7699,21 +7679,29 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>13-02-2026 16:04:20</t>
+          <t>23-02-2026 15:56:01</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>23-02-2026 15:54:51</t>
+        </is>
+      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7721,19 +7709,11 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26160522323640002074</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26290522585740002451</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
           <t>549</t>
@@ -7741,24 +7721,24 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>346272</t>
+          <t>344197</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>88437</t>
+          <t>22014</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7768,17 +7748,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ANGELA</t>
+          <t>SILVIA</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OJEDA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UREÑA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7788,10 +7768,14 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6461508837</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>6863845214</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7799,17 +7783,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>21-04-1999</t>
+          <t>01-01-2000</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>ANGELA.OJEDA0421@GMAIL.COM</t>
+          <t>MARIA.932573@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>24-02-2026 17:44:34</t>
+          <t>16-02-2026 17:11:26</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7819,36 +7803,44 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>24-02-2026 17:45:53</t>
+          <t>18-02-2026 17:47:52</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>24-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr"/>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>18-02-2026 17:43:52</t>
+        </is>
+      </c>
       <c r="U55" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W55" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7856,19 +7848,27 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26160522628990002594</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
+          <t>26160522470320002337</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7880,12 +7880,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>343139</t>
+          <t>344391</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20956</t>
+          <t>22208</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7895,17 +7895,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NICZA ARELI</t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IZAGUIRRE</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>ARTEAGA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7915,75 +7915,67 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6864650098</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TORRE LAS ARCAS </t>
-        </is>
-      </c>
+          <t>6311261612</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>03-11-1994</t>
+          <t>18-06-1985</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>IZAGUIRREARELI@GMAIL.COM</t>
+          <t>COLORGRAFICO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>11-02-2026 20:53:07</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>17-02-2026 07:06:31</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>13-02-2026 18:50:54</t>
+          <t>17-02-2026 07:07:36</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>13-02-2026 18:49:33</t>
-        </is>
-      </c>
+          <t>17-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7991,23 +7983,19 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26170522328830002369</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26160522420050002226</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8019,12 +8007,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>344132</t>
+          <t>344630</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21949</t>
+          <t>22447</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8034,17 +8022,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGELES </t>
+          <t>JESUS LEONEL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CARMONA</t>
+          <t>GALAVIZ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SIQUEIROS</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8054,28 +8042,28 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6863378715</t>
+          <t>6865866356</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>04-08-2006</t>
+          <t>28-10-1986</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>ANGELESWCARMONA763@GMAIL.COM</t>
+          <t>JESUSLEONEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>16-02-2026 15:44:25</t>
+          <t>17-02-2026 17:54:18</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -8090,22 +8078,22 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>16-02-2026 15:45:32</t>
+          <t>17-02-2026 17:56:16</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -8122,14 +8110,14 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26160522393400002157</t>
+          <t>26160522439290002266</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
@@ -8146,12 +8134,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>344345</t>
+          <t>345809</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22162</t>
+          <t>87974</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8161,17 +8149,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>JESUS ANTONIO</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>TOPETE</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>HARO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8181,10 +8169,14 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6865890812</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>6863504737</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -8192,17 +8184,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>15-12-1987</t>
+          <t>08-04-2000</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CHUYANTONT@GMAIL.COM</t>
+          <t>ALETSMIRANDA7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>16-02-2026 19:42:11</t>
+          <t>23-02-2026 14:46:02</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8212,36 +8204,44 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>16-02-2026 19:43:34</t>
+          <t>23-02-2026 15:06:54</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>23-02-2026 14:52:57</t>
+        </is>
+      </c>
       <c r="U58" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr"/>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W58" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8249,14 +8249,14 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26160522409070002196</t>
+          <t>26160522583760002502</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
@@ -8273,12 +8273,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>344515</t>
+          <t>344451</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>22332</t>
+          <t>22268</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8288,17 +8288,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ASTRID AITANA</t>
+          <t>TIFFANY JAZMIN</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t>HOPKINS</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8308,37 +8308,37 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>5522151079</t>
+          <t>6866190407</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>RIO TULA 12</t>
+          <t>IND22222</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>19-10-2006</t>
+          <t>06-09-2006</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>AITANAHIDALGO0@GMAIL.COM</t>
+          <t>NOTIENEEE@SSS.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>17-02-2026 15:10:23</t>
+          <t>17-02-2026 11:29:05</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -8348,27 +8348,27 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>23-02-2026 15:56:01</t>
+          <t>17-02-2026 11:32:47</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>23-02-2026 15:54:51</t>
+          <t>17-02-2026 11:32:10</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8388,14 +8388,14 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26290522585740002451</t>
+          <t>26160522425100002242</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -8412,12 +8412,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>344451</t>
+          <t>344464</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>22268</t>
+          <t>22281</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8427,17 +8427,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>TIFFANY JAZMIN</t>
+          <t>MICHELLE JAZLIM</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>LEYVA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>HOPKINS</t>
+          <t>RICO</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8447,57 +8447,53 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6866190407</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>IND22222</t>
-        </is>
-      </c>
+          <t>6865111469</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>06-09-2006</t>
+          <t>09-02-1992</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>NOTIENEEE@SSS.COM</t>
+          <t>MICHELLE.RLEYVA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>17-02-2026 11:29:05</t>
+          <t>17-02-2026 12:06:32</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>17-02-2026 11:32:47</t>
+          <t>17-02-2026 12:07:57</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -8505,21 +8501,13 @@
           <t>17-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>17-02-2026 11:32:10</t>
-        </is>
-      </c>
+      <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8527,19 +8515,19 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26160522425100002242</t>
+          <t>26160522425750002244</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -8551,12 +8539,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>344464</t>
+          <t>345376</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>22281</t>
+          <t>87541</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8566,17 +8554,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>MICHELLE JAZLIM</t>
+          <t>SOPHIA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RICO</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8586,10 +8574,14 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6865111469</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>6865307488</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8597,56 +8589,64 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>09-02-1992</t>
+          <t>26-06-1993</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>MICHELLE.RLEYVA@GMAIL.COM</t>
+          <t>SOPHIA.QUINDI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>17-02-2026 12:06:32</t>
+          <t>20-02-2026 17:55:33</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>17-02-2026 12:07:57</t>
+          <t>20-02-2026 18:01:22</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr"/>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:00:10</t>
+        </is>
+      </c>
       <c r="U61" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr"/>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W61" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8654,19 +8654,19 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26160522425750002244</t>
+          <t>26160522533220002443</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -8678,12 +8678,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>344948</t>
+          <t>345386</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22765</t>
+          <t>87551</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8693,17 +8693,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KENIA LORENA</t>
+          <t xml:space="preserve">ALEJANDRO </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>LAURIAS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>BATISTA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8713,67 +8713,67 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6862417380</t>
+          <t>6866441611</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 1</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>10-06-1998</t>
+          <t>10-08-1994</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>KENIAMB98@GMAIL.COM</t>
+          <t>ALGSMQD26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>18-02-2026 19:27:03</t>
+          <t>20-02-2026 18:13:38</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>18-02-2026 19:31:59</t>
+          <t>20-02-2026 18:16:09</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>18-02-2026 19:30:17</t>
+          <t>20-02-2026 18:15:32</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -8793,19 +8793,19 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26160522475220002354</t>
+          <t>26160522533690002445</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -8817,12 +8817,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>345376</t>
+          <t>345399</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>87541</t>
+          <t>87564</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8832,17 +8832,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SOPHIA</t>
+          <t>NATALIA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>CASAREZ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>VALLE</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6865307488</t>
+          <t>6861221578</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -8867,42 +8867,42 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>26-06-1993</t>
+          <t>09-11-1995</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>SOPHIA.QUINDI@GMAIL.COM</t>
+          <t>NATALIACASAREZVALLE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>20-02-2026 17:55:33</t>
+          <t>20-02-2026 18:53:23</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>20-02-2026 18:01:22</t>
+          <t>20-02-2026 18:57:38</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>20-02-2026 18:00:10</t>
+          <t>20-02-2026 18:56:28</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -8932,19 +8932,19 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26160522533220002443</t>
+          <t>26160522534930002446</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -8956,12 +8956,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>345386</t>
+          <t>344929</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>87551</t>
+          <t>22746</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8971,17 +8971,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEJANDRO </t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>LAURIAS</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6866441611</t>
+          <t>9371155830</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>10-08-1994</t>
+          <t>18-06-1991</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>ALGSMQD26@GMAIL.COM</t>
+          <t>ANGELMORENOOCHOA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>20-02-2026 18:13:38</t>
+          <t>18-02-2026 18:36:12</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>20-02-2026 18:16:09</t>
+          <t>18-02-2026 18:47:06</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>20-02-2026 18:15:32</t>
+          <t>18-02-2026 18:46:16</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26160522533690002445</t>
+          <t>26160522473470002345</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr"/>
@@ -9083,7 +9083,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -9095,12 +9095,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>345399</t>
+          <t>346272</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>87564</t>
+          <t>88437</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9110,17 +9110,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NATALIA</t>
+          <t>ANGELA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CASAREZ</t>
+          <t>OJEDA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>VALLE</t>
+          <t>UREÑA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9130,14 +9130,10 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6861221578</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6461508837</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -9145,17 +9141,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>09-11-1995</t>
+          <t>21-04-1999</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>NATALIACASAREZVALLE@GMAIL.COM</t>
+          <t>ANGELA.OJEDA0421@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>20-02-2026 18:53:23</t>
+          <t>24-02-2026 17:44:34</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -9165,44 +9161,36 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>20-02-2026 18:57:38</t>
+          <t>24-02-2026 17:45:53</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>20-02-2026 18:56:28</t>
-        </is>
-      </c>
+          <t>24-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9210,14 +9198,14 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26160522534930002446</t>
+          <t>26160522628990002594</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
@@ -9234,12 +9222,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>344197</t>
+          <t>345976</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>22014</t>
+          <t>88141</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9249,17 +9237,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SILVIA</t>
+          <t>JOAQUIN</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9269,79 +9257,67 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6863845214</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6861822047</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
+          <t>10-06-1982</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>MARIA.932573@GMAIL.COM</t>
+          <t>JOTAQN.RUIZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>16-02-2026 17:11:26</t>
+          <t>23-02-2026 18:22:36</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>18-02-2026 17:47:52</t>
+          <t>23-02-2026 18:24:38</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>18-02-2026 17:43:52</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9349,27 +9325,19 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26160522470320002337</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26160522595470002522</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -9381,12 +9349,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>344391</t>
+          <t>344948</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>22765</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9396,17 +9364,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t>KENIA LORENA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ARTEAGA</t>
+          <t>BATISTA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9416,28 +9384,32 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6311261612</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>6862417380</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA 1</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>18-06-1985</t>
+          <t>10-06-1998</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>COLORGRAFICO@HOTMAIL.COM</t>
+          <t>KENIAMB98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>17-02-2026 07:06:31</t>
+          <t>18-02-2026 19:27:03</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -9447,36 +9419,44 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>17-02-2026 07:07:36</t>
+          <t>18-02-2026 19:31:59</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr"/>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>18-02-2026 19:30:17</t>
+        </is>
+      </c>
       <c r="U67" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9484,19 +9464,19 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26160522420050002226</t>
+          <t>26160522475220002354</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -9508,12 +9488,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>344630</t>
+          <t>343713</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>21530</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9523,17 +9503,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>JESUS LEONEL</t>
+          <t>JESSICA ALEJANDRA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>GALAVIZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9543,67 +9523,75 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6865866356</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>6863648770</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>JOSE MARIA AGUAYO 506</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>28-10-1986</t>
+          <t>18-01-2006</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>JESUSLEONEL@GMAIL.COM</t>
+          <t>JESSICAA.GUTIERREZ@CETYS.EDU.MX</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>17-02-2026 17:54:18</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>14-02-2026 11:38:52</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>17-02-2026 17:56:16</t>
+          <t>14-02-2026 11:41:20</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr"/>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>14-02-2026 11:40:29</t>
+        </is>
+      </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W68" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9611,14 +9599,14 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26160522439290002266</t>
+          <t>26160522347590002106</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
@@ -9635,12 +9623,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>345976</t>
+          <t>345971</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>88141</t>
+          <t>88136</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9660,7 +9648,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>IBAÑEZ</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9670,7 +9658,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6861822047</t>
+          <t>6862034774</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9681,17 +9669,17 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>10-06-1982</t>
+          <t>21-03-2009</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>JOTAQN.RUIZ@HOTMAIL.COM</t>
+          <t>RUIZIBAÑEZJQN@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>23-02-2026 18:22:36</t>
+          <t>23-02-2026 18:17:27</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -9716,7 +9704,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>23-02-2026 18:24:38</t>
+          <t>23-02-2026 18:19:45</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -9738,7 +9726,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26160522595470002522</t>
+          <t>26160522595030002521</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr"/>
@@ -9750,24 +9738,24 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>344929</t>
+          <t>346049</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>22746</t>
+          <t>88214</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9777,17 +9765,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>JONAS</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9797,14 +9785,10 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>9371155830</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6862765318</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -9812,64 +9796,56 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>18-06-1991</t>
+          <t>19-07-1999</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>ANGELMORENOOCHOA@GMAIL.COM</t>
+          <t>LABAJAMXLI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>18-02-2026 18:36:12</t>
+          <t>23-02-2026 20:45:09</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>18-02-2026 18:47:06</t>
+          <t>23-02-2026 20:46:28</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>18-02-2026 18:46:16</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9877,14 +9853,14 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26160522473470002345</t>
+          <t>26160522602060002551</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
@@ -9901,12 +9877,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>345971</t>
+          <t>346604</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>88136</t>
+          <t>88769</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9916,17 +9892,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>JOAQUIN</t>
+          <t>ALEJANDRA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>ALVARADO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>IBAÑEZ</t>
+          <t>MOSQUERA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9936,67 +9912,79 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>6862034774</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>6862149610</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA 1</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>21-03-2009</t>
+          <t>23-06-1989</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>RUIZIBAÑEZJQN@OUTLOOK.COM</t>
+          <t>PEMOALJUL@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>23-02-2026 18:17:27</t>
+          <t>25-02-2026 20:04:30</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>23-02-2026 18:19:45</t>
+          <t>25-02-2026 20:10:08</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr"/>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>25-02-2026 20:08:55</t>
+        </is>
+      </c>
       <c r="U71" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr"/>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W71" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10004,36 +9992,36 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26160522595030002521</t>
+          <t>26160522667440002678</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>346049</t>
+          <t>345721</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>88214</t>
+          <t>87886</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -10043,17 +10031,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>JONAS</t>
+          <t>J ASUNCION</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -10063,10 +10051,14 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>6862765318</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>6861754997</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>RIO AMECA 1896</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -10074,42 +10066,42 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>19-07-1999</t>
+          <t>14-01-1981</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>LABAJAMXLI@GMAIL.COM</t>
+          <t>RODRILOVEMX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>23-02-2026 20:45:09</t>
+          <t>23-02-2026 12:02:31</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>23-02-2026 20:46:28</t>
+          <t>23-02-2026 12:11:56</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -10117,13 +10109,21 @@
           <t>23-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr"/>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>23-02-2026 12:08:50</t>
+        </is>
+      </c>
       <c r="U72" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10131,19 +10131,19 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>26160522602060002551</t>
+          <t>26160522578360002492</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -10155,12 +10155,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>346604</t>
+          <t>346370</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>88769</t>
+          <t>88535</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ALEJANDRA</t>
+          <t>JOSE ALBERTO</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ALVARADO</t>
+          <t>PAEZ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MOSQUERA</t>
+          <t>FRANCISCO</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -10190,57 +10190,57 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>6862149610</t>
+          <t>7123435473</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 1</t>
+          <t>VILLAFONTANA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>23-06-1989</t>
+          <t>26-06-2000</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>PEMOALJUL@HOTMAIL.COM</t>
+          <t>JOSE5535072149@GMAIL.COM</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>25-02-2026 20:04:30</t>
+          <t>25-02-2026 07:44:10</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>25-02-2026 20:10:08</t>
+          <t>25-02-2026 07:47:45</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>25-02-2026 20:08:55</t>
+          <t>25-02-2026 07:46:50</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -10270,14 +10270,14 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>26160522667440002678</t>
+          <t>26160522646040002634</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC73"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -840,12 +840,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>260403</t>
+          <t>123833</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>57907</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,17 +855,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAMUEL ESTEBAN</t>
+          <t>AKYEL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SERRANO</t>
+          <t>CASTANEDO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SERRANO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -875,53 +875,57 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6862393566</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6531131589</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>DEL CARRIZO 3015</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>28-05-2001</t>
+          <t>01-10-2003</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>SAMUELSESS32@GMAIL.COM</t>
+          <t>AKYDANIELLA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-10-2024 22:01:32</t>
+          <t>19-09-2022 16:35:13</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17-02-2026 17:05:51</t>
+          <t>17-02-2026 06:58:58</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -929,13 +933,21 @@
           <t>17-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>17-02-2026 06:58:23</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -943,14 +955,22 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26030522436260002152</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26160522419880002224</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -967,12 +987,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>123833</t>
+          <t>260403</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>57907</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -982,17 +1002,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AKYEL</t>
+          <t>SAMUEL ESTEBAN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CASTANEDO</t>
+          <t>SERRANO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>SERRANO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1002,57 +1022,53 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6531131589</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>DEL CARRIZO 3015</t>
-        </is>
-      </c>
+          <t>6862393566</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>01-10-2003</t>
+          <t>28-05-2001</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>AKYDANIELLA@GMAIL.COM</t>
+          <t>SAMUELSESS32@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>19-09-2022 16:35:13</t>
+          <t>02-10-2024 22:01:32</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>17-02-2026 06:58:58</t>
+          <t>17-02-2026 17:05:51</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1060,21 +1076,13 @@
           <t>17-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>17-02-2026 06:58:23</t>
-        </is>
-      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1082,22 +1090,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26160522419880002224</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
-        </is>
-      </c>
+          <t>26030522436260002152</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1388,12 +1388,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>290316</t>
+          <t>340713</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>87814</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VANESSA</t>
+          <t>LESLIE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HIGUERA</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1423,32 +1423,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6861744727</t>
+          <t>6865257334</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 1</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>22-07-1992</t>
+          <t>10-06-1994</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>HIGUERAROSAV@GMAIL.COM</t>
+          <t>LICMERCADOSUNA.10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>28-04-2025 19:34:24</t>
+          <t>03-02-2026 17:15:35</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1469,17 +1469,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>14-02-2026 15:01:10</t>
+          <t>03-02-2026 17:19:02</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>14-02-2026 15:00:36</t>
+          <t>03-02-2026 17:18:43</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1499,14 +1499,10 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26160522349780002121</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26160522048750001552</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1515,7 +1511,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1527,12 +1523,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>340481</t>
+          <t>290316</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>87814</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1542,17 +1538,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HILDA</t>
+          <t>VANESSA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BENAVIDEZ</t>
+          <t>HIGUERA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PEÑA</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1562,32 +1558,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6864150761</t>
+          <t>6861744727</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>LINEZO1</t>
+          <t>INDEPENDENCIA 1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>21-07-1961</t>
+          <t>22-07-1992</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>NOTIERERER@TYU.COM</t>
+          <t>HIGUERAROSAV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>03-02-2026 08:55:15</t>
+          <t>28-04-2025 19:34:24</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1608,17 +1604,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>04-02-2026 10:23:34</t>
+          <t>14-02-2026 15:01:10</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>04-02-2026 10:22:30</t>
+          <t>14-02-2026 15:00:36</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1638,19 +1634,15 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26160522071550001606</t>
+          <t>26160522349780002121</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>499</t>
@@ -1658,7 +1650,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1670,12 +1662,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>340791</t>
+          <t>340481</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1685,17 +1677,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HECTOR MANUEL</t>
+          <t>HILDA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ALVARADO</t>
+          <t>BENAVIDEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1705,32 +1697,32 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5628369350</t>
+          <t>6864150761</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MAYA CAMPESTRE</t>
+          <t>LINEZO1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>09-08-1976</t>
+          <t>21-07-1961</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>MACALVMAIL@GMAIL.COM</t>
+          <t>NOTIERERER@TYU.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>03-02-2026 18:47:52</t>
+          <t>03-02-2026 08:55:15</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1751,17 +1743,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-02-2026 19:09:42</t>
+          <t>04-02-2026 10:23:34</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>03-02-2026 19:09:20</t>
+          <t>04-02-2026 10:22:30</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1781,15 +1773,19 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26160522055330001568</t>
+          <t>26160522071550001606</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>499</t>
@@ -1797,7 +1793,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1809,12 +1805,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>340808</t>
+          <t>341834</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18626</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1824,17 +1820,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RENE</t>
+          <t>DARIANA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1844,32 +1840,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6863485358</t>
+          <t>6862489316</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 23</t>
+          <t>SAN CARLO1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>15-09-1996</t>
+          <t>03-12-1981</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>RENEGONZALEZ1@GMAIL.COM</t>
+          <t>LOPEZDARIANA780@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-02-2026 19:14:48</t>
+          <t>07-02-2026 13:31:41</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1890,17 +1886,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>05-02-2026 19:04:55</t>
+          <t>07-02-2026 13:38:04</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>05-02-2026 19:03:37</t>
+          <t>07-02-2026 13:35:50</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1910,7 +1906,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1920,19 +1916,11 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26160522117360001694</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26160522161810001766</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
           <t>499</t>
@@ -1940,7 +1928,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2234,12 +2222,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>340713</t>
+          <t>342294</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2249,17 +2237,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LESLIE</t>
+          <t>CARLOS ANTONIO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2269,75 +2257,67 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6865257334</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6863473949</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>10-06-1994</t>
+          <t>25-10-2003</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>LICMERCADOSUNA.10@GMAIL.COM</t>
+          <t>CARLOS8A2510@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-02-2026 17:15:35</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>09-02-2026 16:59:55</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-02-2026 17:19:02</t>
+          <t>09-02-2026 17:01:28</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>03-02-2026 17:18:43</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2345,19 +2325,19 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26160522048750001552</t>
+          <t>26160522200300001806</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2516,12 +2496,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>337242</t>
+          <t>340791</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2531,17 +2511,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTHA ELENA </t>
+          <t>HECTOR MANUEL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MAEDA</t>
+          <t>ALVARADO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2551,53 +2531,53 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6861253578</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>5628369350</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MAYA CAMPESTRE</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>06-10-1952</t>
+          <t>09-08-1976</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>MARTHAELENAMG@GMAIL.COM</t>
+          <t>MACALVMAIL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>23-01-2026 12:52:24</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 18:47:52</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-02-2026 08:23:40</t>
+          <t>03-02-2026 19:09:42</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2605,13 +2585,21 @@
           <t>03-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>03-02-2026 19:09:20</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2619,19 +2607,23 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26160522033610001514</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
+          <t>26160522055330001568</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2643,12 +2635,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>341834</t>
+          <t>340808</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19652</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2658,17 +2650,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DARIANA</t>
+          <t>RENE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2678,32 +2670,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6862489316</t>
+          <t>6863485358</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SAN CARLO1</t>
+          <t>INDEPENDENCIA 23</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>03-12-1981</t>
+          <t>15-09-1996</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>LOPEZDARIANA780@GMAIL.COM</t>
+          <t>RENEGONZALEZ1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>07-02-2026 13:31:41</t>
+          <t>03-02-2026 19:14:48</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2724,17 +2716,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>07-02-2026 13:38:04</t>
+          <t>05-02-2026 19:04:55</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>07-02-2026 13:35:50</t>
+          <t>05-02-2026 19:03:37</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2744,7 +2736,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2754,11 +2746,19 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26160522161810001766</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>26160522117360001694</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>499</t>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2778,12 +2778,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>340255</t>
+          <t>342323</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18073</t>
+          <t>20141</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2793,17 +2793,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>STEPHANY</t>
+          <t>MARCO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BEJARANO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ENRIQUEZ</t>
+          <t>ORDUÑO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2813,32 +2813,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6865923181</t>
+          <t>6861601599</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 38</t>
+          <t>INDEPENDENCIA0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18-01-1995</t>
+          <t>25-04-1979</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>FANNYBEJARANO904@GMAIL.COM</t>
+          <t>MOPILLO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-02-2026 16:15:36</t>
+          <t>09-02-2026 17:27:09</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2859,17 +2859,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-02-2026 16:21:03</t>
+          <t>09-02-2026 17:33:13</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>02-02-2026 16:20:43</t>
+          <t>09-02-2026 17:32:43</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26160522016270001486</t>
+          <t>26160522202710001810</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2913,12 +2913,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>342323</t>
+          <t>337242</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2928,17 +2928,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MARCO</t>
+          <t xml:space="preserve">MARTHA ELENA </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MAEDA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ORDUÑO</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2948,75 +2948,67 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6861601599</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA0</t>
-        </is>
-      </c>
+          <t>6861253578</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>25-04-1979</t>
+          <t>06-10-1952</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>MOPILLO@GMAIL.COM</t>
+          <t>MARTHAELENAMG@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>09-02-2026 17:27:09</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>23-01-2026 12:52:24</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>09-02-2026 17:33:13</t>
+          <t>03-02-2026 08:23:40</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>09-02-2026 17:32:43</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3024,19 +3016,19 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26160522202710001810</t>
+          <t>26160522033610001514</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3048,12 +3040,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>340641</t>
+          <t>342822</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3063,17 +3055,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LUCIA YADIRA</t>
+          <t>LEOPOLDO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>LOYO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VELARDE</t>
+          <t>COBO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3083,32 +3075,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6861822416</t>
+          <t>6862120595</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CULTURA OLMECA 3608</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>13-12-1990</t>
+          <t>17-07-1971</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>YADIRA_1290@HOTMAIL.COM</t>
+          <t>LEOPOLDOLOYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>03-02-2026 15:56:48</t>
+          <t>10-02-2026 19:02:43</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3129,17 +3121,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>05-02-2026 16:33:17</t>
+          <t>14-02-2026 13:28:02</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>05-02-2026 16:30:37</t>
+          <t>14-02-2026 13:27:04</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3149,7 +3141,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3159,19 +3151,15 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26160522110560001680</t>
+          <t>26160522349290002113</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
           <t>499</t>
@@ -3191,12 +3179,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>340789</t>
+          <t>342794</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18607</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3206,17 +3194,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIELA </t>
+          <t>JOSUE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3226,32 +3214,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6861739204</t>
+          <t>6861127057</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MAYA CAMPESTRE</t>
+          <t>INDEPENDENCI1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>06-09-1989</t>
+          <t>26-11-1989</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>DANIELA.SANCHEZ.MORENO.89@GMAIL.COM</t>
+          <t>JOSUEBRMUSIC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>03-02-2026 18:45:03</t>
+          <t>10-02-2026 18:25:08</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3272,17 +3260,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>03-02-2026 19:05:49</t>
+          <t>10-02-2026 18:27:56</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>03-02-2026 19:04:34</t>
+          <t>10-02-2026 18:27:24</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3302,14 +3290,10 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26160522055070001567</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26160522243630001901</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
@@ -3318,7 +3302,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3330,12 +3314,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>340697</t>
+          <t>340255</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>18073</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3345,17 +3329,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CRISTIAN ISMAEL</t>
+          <t>STEPHANY</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>BEJARANO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3365,32 +3349,32 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6863537341</t>
+          <t>6865923181</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA3</t>
+          <t>INDEPENDENCIA 38</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>22-06-1995</t>
+          <t>18-01-1995</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CRISTIAN.TORRES@GCADENA.COM</t>
+          <t>FANNYBEJARANO904@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>03-02-2026 17:02:34</t>
+          <t>02-02-2026 16:15:36</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3411,17 +3395,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>03-02-2026 17:06:48</t>
+          <t>02-02-2026 16:21:03</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>03-02-2026 17:06:13</t>
+          <t>02-02-2026 16:20:43</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3431,7 +3415,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3441,7 +3425,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26160522047970001551</t>
+          <t>26160522016270001486</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3453,7 +3437,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3465,12 +3449,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>342087</t>
+          <t>343140</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19905</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3480,17 +3464,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>KARLA VERÓNICA</t>
+          <t xml:space="preserve">VANESSA </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PALAFOX</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3500,12 +3484,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6861244927</t>
+          <t>6864164007</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>IND111111</t>
+          <t>AV TORRE LAS ARCAS 2045</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3515,52 +3499,48 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>26-05-1986</t>
+          <t>08-11-1989</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>VERONIKAPALAFOX@GMAIL.COM</t>
+          <t>VANESSAGALVANR250210@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>09-02-2026 10:07:36</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>11-02-2026 20:55:11</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>16-02-2026 08:19:11</t>
+          <t>13-02-2026 18:56:17</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>16-02-2026 08:18:23</t>
+          <t>13-02-2026 18:55:42</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3570,7 +3550,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3580,27 +3560,23 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26160522380750002134</t>
+          <t>26170522329060002370</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3612,12 +3588,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>342794</t>
+          <t>340641</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>18459</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3627,17 +3603,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>JOSUE</t>
+          <t>LUCIA YADIRA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>VELARDE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3647,32 +3623,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6861127057</t>
+          <t>6861822416</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>INDEPENDENCI1</t>
+          <t>CULTURA OLMECA 3608</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>26-11-1989</t>
+          <t>13-12-1990</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>JOSUEBRMUSIC@GMAIL.COM</t>
+          <t>YADIRA_1290@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10-02-2026 18:25:08</t>
+          <t>03-02-2026 15:56:48</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3693,17 +3669,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>10-02-2026 18:27:56</t>
+          <t>05-02-2026 16:33:17</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>10-02-2026 18:27:24</t>
+          <t>05-02-2026 16:30:37</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3723,11 +3699,19 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26160522243630001901</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
+          <t>26160522110560001680</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>499</t>
@@ -3735,7 +3719,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3747,12 +3731,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>341132</t>
+          <t>343713</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>21530</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3762,17 +3746,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAHOMI ESTEFANIA </t>
+          <t>JESSICA ALEJANDRA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TALAMANTES</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3782,12 +3766,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6643120858</t>
+          <t>6863648770</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>JOSE MARIA AGUAYO 506</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3797,17 +3781,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>18-08-1996</t>
+          <t>18-01-2006</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ESTEFANIAMTALAMANTESX@GMAIL.COM</t>
+          <t>JESSICAA.GUTIERREZ@CETYS.EDU.MX</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>04-02-2026 18:08:31</t>
+          <t>14-02-2026 11:38:52</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3828,17 +3812,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>10-02-2026 16:06:43</t>
+          <t>14-02-2026 11:41:20</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>10-02-2026 16:05:59</t>
+          <t>14-02-2026 11:40:29</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3858,19 +3842,11 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26130522235720002570</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>MARIA CANDELARIA LARA AVILA</t>
-        </is>
-      </c>
+          <t>26160522347590002106</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
           <t>499</t>
@@ -3878,7 +3854,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3890,12 +3866,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>343140</t>
+          <t>343612</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>21429</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3905,17 +3881,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">VANESSA </t>
+          <t>OSCAR</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>CARRERA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3925,53 +3901,53 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6864164007</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>AV TORRE LAS ARCAS 2045</t>
-        </is>
-      </c>
+          <t>6865906261</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>08-11-1989</t>
+          <t>03-08-2006</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>VANESSAGALVANR250210@GMAIL.COM</t>
+          <t>OR629395@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>11-02-2026 20:55:11</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>13-02-2026 20:02:16</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>13-02-2026 18:56:17</t>
+          <t>13-02-2026 20:03:49</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3979,21 +3955,13 @@
           <t>13-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>13-02-2026 18:55:42</t>
-        </is>
-      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4001,23 +3969,19 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26170522329060002370</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26160522330930002093</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4029,12 +3993,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>341819</t>
+          <t>340697</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19637</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4044,17 +4008,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>KARYME</t>
+          <t>CRISTIAN ISMAEL</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4064,67 +4028,75 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6861351566</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>6863537341</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA3</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>11-12-2004</t>
+          <t>22-06-1995</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>KARYMEMACLOP@GMAIL.COM</t>
+          <t>CRISTIAN.TORRES@GCADENA.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>07-02-2026 12:03:12</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 17:02:34</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>07-02-2026 12:05:36</t>
+          <t>03-02-2026 17:06:48</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>03-02-2026 17:06:13</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4132,19 +4104,19 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26160522160500001761</t>
+          <t>26160522047970001551</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4156,12 +4128,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>342478</t>
+          <t>340789</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20295</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4171,17 +4143,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FERNANDO</t>
+          <t xml:space="preserve">DANIELA </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4191,32 +4163,32 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6861146223</t>
+          <t>6861739204</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA01</t>
+          <t>MAYA CAMPESTRE</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>27-04-1993</t>
+          <t>06-09-1989</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>IVANRNAVARRO12@GMAIL.COM</t>
+          <t>DANIELA.SANCHEZ.MORENO.89@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>09-02-2026 20:13:50</t>
+          <t>03-02-2026 18:45:03</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4237,17 +4209,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>09-02-2026 20:16:34</t>
+          <t>03-02-2026 19:05:49</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>09-02-2026 20:16:03</t>
+          <t>03-02-2026 19:04:34</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4257,7 +4229,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4267,10 +4239,14 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26160522213270001841</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr"/>
+          <t>26160522055070001567</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
@@ -4279,7 +4255,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4291,12 +4267,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>342580</t>
+          <t>343714</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20397</t>
+          <t>21531</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4306,17 +4282,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>HECTOR MANUEL</t>
+          <t>OLVIA YISEL</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PIÑA</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>OLIVEROS</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4326,67 +4302,75 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6865895862</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>6863667098</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>AV LAGO BAHIJASH 634</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>17-10-2002</t>
+          <t>03-03-2001</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>NOTIENE11112222@FFFFDDD.COM</t>
+          <t>OLVIAHU18@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10-02-2026 10:48:52</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>14-02-2026 11:45:34</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>10-02-2026 10:50:12</t>
+          <t>14-02-2026 11:48:11</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>10-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>14-02-2026 11:47:29</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4394,19 +4378,19 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26160522228650001872</t>
+          <t>26160522347720002107</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4418,12 +4402,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>343612</t>
+          <t>342087</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21429</t>
+          <t>19905</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4433,17 +4417,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>OSCAR</t>
+          <t>KARLA VERÓNICA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CARRERA</t>
+          <t>PALAFOX</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4453,28 +4437,32 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6865906261</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>6861244927</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>IND111111</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>03-08-2006</t>
+          <t>26-05-1986</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>OR629395@GMAIL.COM</t>
+          <t>VERONIKAPALAFOX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>13-02-2026 20:02:16</t>
+          <t>09-02-2026 10:07:36</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4484,36 +4472,44 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>13-02-2026 20:03:49</t>
+          <t>16-02-2026 08:19:11</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:18:23</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4521,19 +4517,27 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26160522330930002093</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
+          <t>26160522380750002134</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4545,12 +4549,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>343714</t>
+          <t>341132</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21531</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4560,17 +4564,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OLVIA YISEL</t>
+          <t xml:space="preserve">NAHOMI ESTEFANIA </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>TALAMANTES</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4580,12 +4584,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6863667098</t>
+          <t>6643120858</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>AV LAGO BAHIJASH 634</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4595,17 +4599,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>03-03-2001</t>
+          <t>18-08-1996</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>OLVIAHU18@GMAIL.COM</t>
+          <t>ESTEFANIAMTALAMANTESX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>14-02-2026 11:45:34</t>
+          <t>04-02-2026 18:08:31</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4626,17 +4630,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>14-02-2026 11:48:11</t>
+          <t>10-02-2026 16:06:43</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>14-02-2026 11:47:29</t>
+          <t>10-02-2026 16:05:59</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4646,7 +4650,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4656,11 +4660,19 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26160522347720002107</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
+          <t>26130522235720002570</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>MARIA CANDELARIA LARA AVILA</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>499</t>
@@ -4668,7 +4680,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4680,12 +4692,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>342336</t>
+          <t>341819</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>19637</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4695,19 +4707,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MARCO ALEJANDRO</t>
+          <t>KARYME</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>MACIAS</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>LOPEZ</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>LOPEZ</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>52</t>
@@ -4715,75 +4727,67 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6861632588</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA01</t>
-        </is>
-      </c>
+          <t>6861351566</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>12-05-2006</t>
+          <t>11-12-2004</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>6MALLISME9@GMAIL.COM</t>
+          <t>KARYMEMACLOP@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>09-02-2026 17:35:12</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>07-02-2026 12:03:12</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>09-02-2026 17:38:30</t>
+          <t>07-02-2026 12:05:36</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>09-02-2026 17:38:05</t>
-        </is>
-      </c>
+          <t>07-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4791,14 +4795,14 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26160522203170001811</t>
+          <t>26160522160500001761</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4815,12 +4819,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>342474</t>
+          <t>345721</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>87886</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4830,17 +4834,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MELISSA</t>
+          <t>J ASUNCION</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4850,35 +4854,39 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6863242180</t>
+          <t>6861754997</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA01</t>
+          <t>RIO AMECA 1896</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>25-07-1987</t>
+          <t>14-01-1981</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>YLEM51@GMAIL.COM</t>
+          <t>RODRILOVEMX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>09-02-2026 20:08:06</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>23-02-2026 12:02:31</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4896,17 +4904,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>09-02-2026 20:12:28</t>
+          <t>23-02-2026 12:11:56</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>09-02-2026 20:10:07</t>
+          <t>23-02-2026 12:08:50</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4916,7 +4924,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4926,7 +4934,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26160522213110001840</t>
+          <t>26160522578360002492</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -4950,12 +4958,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>342457</t>
+          <t>344453</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20274</t>
+          <t>22270</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4965,17 +4973,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE </t>
+          <t>JESUS</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FRANCISCO</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FIERRO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4985,14 +4993,10 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6861575086</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA02</t>
-        </is>
-      </c>
+          <t>6861762359</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5000,60 +5004,56 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>15-09-1973</t>
+          <t>11-08-1951</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>FIERRO_PACO@HOTMAIL.COM</t>
+          <t>NOTIENE23445@DFDF.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>09-02-2026 19:49:15</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>17-02-2026 11:34:41</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>09-02-2026 19:51:47</t>
+          <t>17-02-2026 11:37:38</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>09-02-2026 19:50:53</t>
-        </is>
-      </c>
+          <t>17-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5061,19 +5061,19 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26160522212280001839</t>
+          <t>26160522425250002243</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342583</t>
+          <t>344505</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20400</t>
+          <t>22322</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SHESLY DENNIS</t>
+          <t>KENIA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6861234727</t>
+          <t>6869460269</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>PRESA DE LA ANGOSURA 1491</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5135,20 +5135,24 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>30-07-1996</t>
+          <t>24-09-1981</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>SHES.MEZAGTZ@GMAIL.COM</t>
+          <t>KRISS0024@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>10-02-2026 11:28:40</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>17-02-2026 14:43:35</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5166,17 +5170,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>10-02-2026 11:31:11</t>
+          <t>17-02-2026 14:52:04</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>10-02-2026 11:30:36</t>
+          <t>17-02-2026 14:49:23</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5186,7 +5190,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5196,7 +5200,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26160522229140001874</t>
+          <t>26160522430130002253</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5208,7 +5212,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5220,12 +5224,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>342776</t>
+          <t>342478</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20593</t>
+          <t>20295</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5235,12 +5239,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JUAN MANUEL</t>
+          <t>FERNANDO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -5255,12 +5259,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6867292744</t>
+          <t>6861146223</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>INDEPENDENCIA01</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5270,17 +5274,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>09-11-1973</t>
+          <t>27-04-1993</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>NOCUENTACON1@GMAIL.COM</t>
+          <t>IVANRNAVARRO12@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>10-02-2026 18:03:21</t>
+          <t>09-02-2026 20:13:50</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5301,17 +5305,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>10-02-2026 18:35:28</t>
+          <t>09-02-2026 20:16:34</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>10-02-2026 18:35:08</t>
+          <t>09-02-2026 20:16:03</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5321,7 +5325,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5331,7 +5335,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26160522243990001903</t>
+          <t>26160522213270001841</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
@@ -5343,7 +5347,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5355,12 +5359,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>344453</t>
+          <t>342580</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22270</t>
+          <t>20397</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5370,17 +5374,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JESUS</t>
+          <t>HECTOR MANUEL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>PIÑA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>OLIVEROS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5390,7 +5394,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6861762359</t>
+          <t>6865895862</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5401,17 +5405,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>11-08-1951</t>
+          <t>17-10-2002</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>NOTIENE23445@DFDF.COM</t>
+          <t>NOTIENE11112222@FFFFDDD.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>17-02-2026 11:34:41</t>
+          <t>10-02-2026 10:48:52</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5436,18 +5440,18 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>17-02-2026 11:37:38</t>
+          <t>10-02-2026 10:50:12</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
+          <t>10-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V37" t="inlineStr"/>
@@ -5458,7 +5462,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26160522425250002243</t>
+          <t>26160522228650001872</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -5470,7 +5474,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5482,12 +5486,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>344505</t>
+          <t>342336</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5497,17 +5501,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KENIA</t>
+          <t>MARCO ALEJANDRO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5517,39 +5521,35 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6869460269</t>
+          <t>6861632588</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>INDEPENDENCIA01</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>24-09-1981</t>
+          <t>12-05-2006</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>KRISS0024@GMAIL.COM</t>
+          <t>6MALLISME9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>17-02-2026 14:43:35</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:35:12</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5567,17 +5567,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>17-02-2026 14:52:04</t>
+          <t>09-02-2026 17:38:30</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>17-02-2026 14:49:23</t>
+          <t>09-02-2026 17:38:05</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26160522430130002253</t>
+          <t>26160522203170001811</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5621,12 +5621,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>342294</t>
+          <t>342474</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>20291</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5636,17 +5636,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CARLOS ANTONIO</t>
+          <t>MELISSA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5656,53 +5656,53 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6863473949</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>6863242180</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA01</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>25-10-2003</t>
+          <t>25-07-1987</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CARLOS8A2510@GMAIL.COM</t>
+          <t>YLEM51@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>09-02-2026 16:59:55</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 20:08:06</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>09-02-2026 17:01:28</t>
+          <t>09-02-2026 20:12:28</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -5710,13 +5710,21 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr"/>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>09-02-2026 20:10:07</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5724,14 +5732,14 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26160522200300001806</t>
+          <t>26160522213110001840</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5748,12 +5756,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>342482</t>
+          <t>342457</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20299</t>
+          <t>20274</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5763,17 +5771,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t xml:space="preserve">JOSE </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>FRANCISCO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CACERES</t>
+          <t>FIERRO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5783,10 +5791,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6867220400</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>6861575086</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA02</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5794,42 +5806,38 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>25-08-1998</t>
+          <t>15-09-1973</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>JOSECACEREZ98@GMAIL.COM</t>
+          <t>FIERRO_PACO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>09-02-2026 20:20:01</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 19:49:15</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>09-02-2026 20:21:16</t>
+          <t>09-02-2026 19:51:47</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5837,13 +5845,21 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr"/>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>09-02-2026 19:50:53</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5851,14 +5867,14 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26160522213460001843</t>
+          <t>26160522212280001839</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5875,12 +5891,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>342783</t>
+          <t>342583</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20600</t>
+          <t>20400</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5890,17 +5906,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>SHESLY DENNIS</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TAPIA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AGUAYO</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5910,53 +5926,53 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6623654956</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>6861234727</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>PRESA DE LA ANGOSURA 1491</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>27-03-1998</t>
+          <t>30-07-1996</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>JOSETAPIAGUAYO@GMAIL.COM</t>
+          <t>SHES.MEZAGTZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>10-02-2026 18:11:07</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 11:28:40</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>10-02-2026 18:12:38</t>
+          <t>10-02-2026 11:31:11</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5964,13 +5980,21 @@
           <t>10-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr"/>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>10-02-2026 11:30:36</t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5978,19 +6002,19 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26160522242690001898</t>
+          <t>26160522229140001874</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6002,12 +6026,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>343025</t>
+          <t>346370</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20842</t>
+          <t>88535</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6017,17 +6041,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DYLAN</t>
+          <t>JOSE ALBERTO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>PAEZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t>FRANCISCO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6037,10 +6061,14 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6861698256</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>7123435473</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>VILLAFONTANA</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6048,56 +6076,64 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>06-08-2002</t>
+          <t>26-06-2000</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>DYLANMTZM.26@GMAIL.COM</t>
+          <t>JOSE5535072149@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>11-02-2026 15:49:14</t>
+          <t>25-02-2026 07:44:10</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>11-02-2026 15:52:21</t>
+          <t>25-02-2026 07:47:45</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr"/>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>25-02-2026 07:46:50</t>
+        </is>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6105,14 +6141,14 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26160522267270001952</t>
+          <t>26160522646040002634</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -6129,12 +6165,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>342997</t>
+          <t>342776</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20814</t>
+          <t>20593</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6144,17 +6180,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>JAZMIN</t>
+          <t>JUAN MANUEL</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6164,32 +6200,32 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8130964314</t>
+          <t>6867292744</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CERRO DEL POTOSI 1119</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>18-03-1995</t>
+          <t>09-11-1973</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>YAAS.LOPEZ18@GMAIL.COM</t>
+          <t>NOCUENTACON1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>11-02-2026 14:53:46</t>
+          <t>10-02-2026 18:03:21</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6210,17 +6246,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>12-02-2026 12:36:52</t>
+          <t>10-02-2026 18:35:28</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>12-02-2026 12:36:23</t>
+          <t>10-02-2026 18:35:08</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6240,7 +6276,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26180522292630004399</t>
+          <t>26160522243990001903</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -6252,7 +6288,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6264,12 +6300,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>343135</t>
+          <t>342783</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20952</t>
+          <t>20600</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6279,17 +6315,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>JAIME</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>TAPIA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>AGUAYO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6299,7 +6335,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6862316574</t>
+          <t>6623654956</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6310,13 +6346,17 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
+          <t>27-03-1998</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>JOSETAPIAGUAYO@GMAIL.COM</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>11-02-2026 20:34:48</t>
+          <t>10-02-2026 18:11:07</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6331,28 +6371,28 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>13-02-2026 16:04:20</t>
+          <t>10-02-2026 18:12:38</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V44" t="inlineStr"/>
@@ -6363,44 +6403,36 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26160522323640002074</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26160522242690001898</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>343384</t>
+          <t>342482</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21201</t>
+          <t>20299</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6410,17 +6442,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>BRISA</t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>GASCA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>CACERES</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6430,75 +6462,67 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6863912198</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6867220400</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>12-02-2006</t>
+          <t>25-08-1998</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>GNAVARROGASCA@GMAIL.COM</t>
+          <t>JOSECACEREZ98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>12-02-2026 19:16:27</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>09-02-2026 20:20:01</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>12-02-2026 19:22:02</t>
+          <t>09-02-2026 20:21:16</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>12-02-2026 19:21:22</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6506,19 +6530,19 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26160522304540002036</t>
+          <t>26160522213460001843</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6530,12 +6554,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>343557</t>
+          <t>343025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21374</t>
+          <t>20842</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6545,17 +6569,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>JUAN CARLOS</t>
+          <t>DYLAN</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6565,75 +6589,67 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6863903522</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6861698256</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>08-03-1971</t>
+          <t>06-08-2002</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>JUANCARLORIOS1422@GMAIL.COM</t>
+          <t>DYLANMTZM.26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>13-02-2026 17:19:49</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>11-02-2026 15:49:14</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>13-02-2026 17:24:13</t>
+          <t>11-02-2026 15:52:21</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>13-02-2026 17:22:41</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6641,19 +6657,19 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26160522326350002078</t>
+          <t>26160522267270001952</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6665,12 +6681,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>344042</t>
+          <t>342997</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21859</t>
+          <t>20814</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6680,17 +6696,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">FELISA </t>
+          <t>JAZMIN</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ANGUAMEA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6700,10 +6716,14 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6442161660</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>8130964314</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>CERRO DEL POTOSI 1119</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6711,52 +6731,60 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
+          <t>18-03-1995</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>FELISAANGUAMEAVALENZUELA@GMAIL.COM</t>
+          <t>YAAS.LOPEZ18@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>16-02-2026 12:24:29</t>
+          <t>11-02-2026 14:53:46</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>23-02-2026 18:27:10</t>
+          <t>12-02-2026 12:36:52</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>12-02-2026 12:36:23</t>
+        </is>
+      </c>
       <c r="U47" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6764,22 +6792,14 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26060522595620004368</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>LIZBETH  SALDIVAR MONTES</t>
-        </is>
-      </c>
+          <t>26180522292630004399</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6796,12 +6816,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>344134</t>
+          <t>343135</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21951</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6811,17 +6831,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DANNA PAOLA</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MOLINA</t>
+          <t>OLIVAS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ARROYO</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6831,28 +6851,24 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6531662052</t>
+          <t>6862316574</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>20-06-2006</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>MOLINAARROYODANNAPAOLA@GMAIL.COM</t>
-        </is>
-      </c>
+          <t>01-01-2000</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>16-02-2026 15:47:17</t>
+          <t>11-02-2026 20:34:48</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6877,18 +6893,18 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>16-02-2026 15:49:00</t>
+          <t>13-02-2026 16:04:20</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V48" t="inlineStr"/>
@@ -6899,11 +6915,19 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26160522393690002158</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
+          <t>26160522323640002074</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>549</t>
@@ -6911,24 +6935,24 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>344409</t>
+          <t>343384</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>22226</t>
+          <t>21201</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6938,17 +6962,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ISRAEL</t>
+          <t>BRISA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t>GASCA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LIAÑO</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6958,39 +6982,35 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6863940285</t>
+          <t>6863912198</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>EEEE12</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>18-04-1977</t>
+          <t>12-02-2006</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>MASTERBOY1930@GMAIL.COM</t>
+          <t>GNAVARROGASCA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>17-02-2026 08:06:52</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>12-02-2026 19:16:27</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7008,17 +7028,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>17-02-2026 08:09:37</t>
+          <t>12-02-2026 19:22:02</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>17-02-2026 08:08:58</t>
+          <t>12-02-2026 19:21:22</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -7038,7 +7058,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26160522421530002234</t>
+          <t>26160522304540002036</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
@@ -7050,7 +7070,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7062,12 +7082,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>343139</t>
+          <t>343557</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20956</t>
+          <t>21374</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7077,17 +7097,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NICZA ARELI</t>
+          <t>JUAN CARLOS</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IZAGUIRRE</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7097,12 +7117,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6864650098</t>
+          <t>6863903522</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRE LAS ARCAS </t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7112,17 +7132,17 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>03-11-1994</t>
+          <t>08-03-1971</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>IZAGUIRREARELI@GMAIL.COM</t>
+          <t>JUANCARLORIOS1422@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>11-02-2026 20:53:07</t>
+          <t>13-02-2026 17:19:49</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -7143,7 +7163,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>13-02-2026 18:50:54</t>
+          <t>13-02-2026 17:24:13</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -7153,7 +7173,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>13-02-2026 18:49:33</t>
+          <t>13-02-2026 17:22:41</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7173,14 +7193,10 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26170522328830002369</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26160522326350002078</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
@@ -7189,7 +7205,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7201,12 +7217,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>344132</t>
+          <t>343139</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21949</t>
+          <t>20956</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7216,17 +7232,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGELES </t>
+          <t>NICZA ARELI</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CARMONA</t>
+          <t>IZAGUIRRE</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SIQUEIROS</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7236,10 +7252,14 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6863378715</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>6864650098</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TORRE LAS ARCAS </t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7247,56 +7267,60 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>04-08-2006</t>
+          <t>03-11-1994</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>ANGELESWCARMONA763@GMAIL.COM</t>
+          <t>IZAGUIRREARELI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>16-02-2026 15:44:25</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>11-02-2026 20:53:07</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>16-02-2026 15:45:32</t>
+          <t>13-02-2026 18:50:54</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>13-02-2026 18:49:33</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7304,19 +7328,23 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26160522393400002157</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr"/>
+          <t>26170522328830002369</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -7328,12 +7356,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>342822</t>
+          <t>344132</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20639</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7343,17 +7371,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LEOPOLDO</t>
+          <t xml:space="preserve">ANGELES </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>LOYO</t>
+          <t>CARMONA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>COBO</t>
+          <t>SIQUEIROS</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7363,75 +7391,67 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6862120595</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6863378715</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>17-07-1971</t>
+          <t>04-08-2006</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>LEOPOLDOLOYO@GMAIL.COM</t>
+          <t>ANGELESWCARMONA763@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>10-02-2026 19:02:43</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>16-02-2026 15:44:25</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>14-02-2026 13:28:02</t>
+          <t>16-02-2026 15:45:32</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>14-02-2026 13:27:04</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7439,18 +7459,14 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26160522349290002113</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26160522393400002157</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -7467,12 +7483,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>344345</t>
+          <t>344042</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22162</t>
+          <t>21859</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7482,17 +7498,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>JESUS ANTONIO</t>
+          <t xml:space="preserve">FELISA </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>TOPETE</t>
+          <t>ANGUAMEA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7502,35 +7518,31 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6865890812</t>
+          <t>6442161660</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>15-12-1987</t>
+          <t>01-01-2000</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CHUYANTONT@GMAIL.COM</t>
+          <t>FELISAANGUAMEAVALENZUELA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>16-02-2026 19:42:11</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>16-02-2026 12:24:29</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -7538,22 +7550,22 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>16-02-2026 19:43:34</t>
+          <t>23-02-2026 18:27:10</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>23-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -7570,19 +7582,27 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26160522409070002196</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
+          <t>26060522595620004368</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>LIZBETH  SALDIVAR MONTES</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7594,12 +7614,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>344515</t>
+          <t>344134</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22332</t>
+          <t>21951</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7609,17 +7629,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ASTRID AITANA</t>
+          <t>DANNA PAOLA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>MOLINA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t>ARROYO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7629,14 +7649,10 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>5522151079</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>RIO TULA 12</t>
-        </is>
-      </c>
+          <t>6531662052</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7644,17 +7660,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>19-10-2006</t>
+          <t>20-06-2006</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>AITANAHIDALGO0@GMAIL.COM</t>
+          <t>MOLINAARROYODANNAPAOLA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>17-02-2026 15:10:23</t>
+          <t>16-02-2026 15:47:17</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7664,12 +7680,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -7679,29 +7695,21 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>23-02-2026 15:56:01</t>
+          <t>16-02-2026 15:49:00</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>23-02-2026 15:54:51</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7709,7 +7717,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26290522585740002451</t>
+          <t>26160522393690002158</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
@@ -7721,7 +7729,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7733,12 +7741,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>344197</t>
+          <t>344345</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22014</t>
+          <t>22162</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7748,17 +7756,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SILVIA</t>
+          <t>JESUS ANTONIO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>TOPETE</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7768,32 +7776,28 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6863845214</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6865890812</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
+          <t>15-12-1987</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>MARIA.932573@GMAIL.COM</t>
+          <t>CHUYANTONT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>16-02-2026 17:11:26</t>
+          <t>16-02-2026 19:42:11</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7803,44 +7807,36 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>18-02-2026 17:47:52</t>
+          <t>16-02-2026 19:43:34</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>18-02-2026 17:43:52</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7848,27 +7844,19 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26160522470320002337</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26160522409070002196</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7880,12 +7868,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>344391</t>
+          <t>344451</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>22268</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7895,17 +7883,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t>TIFFANY JAZMIN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ARTEAGA</t>
+          <t>HOPKINS</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7915,10 +7903,14 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6311261612</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>6866190407</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>IND22222</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7926,56 +7918,64 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>18-06-1985</t>
+          <t>06-09-2006</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>COLORGRAFICO@HOTMAIL.COM</t>
+          <t>NOTIENEEE@SSS.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>17-02-2026 07:06:31</t>
+          <t>17-02-2026 11:29:05</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>17-02-2026 07:07:36</t>
+          <t>17-02-2026 11:32:47</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>17-02-2026 11:32:10</t>
+        </is>
+      </c>
       <c r="U56" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7983,19 +7983,19 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26160522420050002226</t>
+          <t>26160522425100002242</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8007,12 +8007,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>344630</t>
+          <t>344464</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>22281</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8022,17 +8022,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>JESUS LEONEL</t>
+          <t>MICHELLE JAZLIM</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>GALAVIZ</t>
+          <t>LEYVA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>RICO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8042,28 +8042,28 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6865866356</t>
+          <t>6865111469</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>28-10-1986</t>
+          <t>09-02-1992</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>JESUSLEONEL@GMAIL.COM</t>
+          <t>MICHELLE.RLEYVA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>17-02-2026 17:54:18</t>
+          <t>17-02-2026 12:06:32</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -8078,17 +8078,17 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>17-02-2026 17:56:16</t>
+          <t>17-02-2026 12:07:57</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -8099,7 +8099,7 @@
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V57" t="inlineStr"/>
@@ -8110,14 +8110,14 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26160522439290002266</t>
+          <t>26160522425750002244</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
@@ -8134,12 +8134,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>345809</t>
+          <t>344409</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>87974</t>
+          <t>22226</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8149,17 +8149,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>ISRAEL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>VELAZQUEZ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>LIAÑO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6863504737</t>
+          <t>6863940285</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>EEEE12</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8184,52 +8184,52 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>08-04-2000</t>
+          <t>18-04-1977</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>ALETSMIRANDA7@GMAIL.COM</t>
+          <t>MASTERBOY1930@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>23-02-2026 14:46:02</t>
+          <t>17-02-2026 08:06:52</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>23-02-2026 15:06:54</t>
+          <t>17-02-2026 08:09:37</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>23-02-2026 14:52:57</t>
+          <t>17-02-2026 08:08:58</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -8249,19 +8249,19 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26160522583760002502</t>
+          <t>26160522421530002234</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -8273,12 +8273,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>344451</t>
+          <t>344515</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>22268</t>
+          <t>22332</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8288,17 +8288,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>TIFFANY JAZMIN</t>
+          <t>ASTRID AITANA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>HOPKINS</t>
+          <t>HIDALGO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8308,37 +8308,37 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6866190407</t>
+          <t>5522151079</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>IND22222</t>
+          <t>RIO TULA 12</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>06-09-2006</t>
+          <t>19-10-2006</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>NOTIENEEE@SSS.COM</t>
+          <t>AITANAHIDALGO0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>17-02-2026 11:29:05</t>
+          <t>17-02-2026 15:10:23</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -8348,27 +8348,27 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>17-02-2026 11:32:47</t>
+          <t>23-02-2026 15:56:01</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>17-02-2026 11:32:10</t>
+          <t>23-02-2026 15:54:51</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8388,14 +8388,14 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26160522425100002242</t>
+          <t>26290522585740002451</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -8412,12 +8412,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>344464</t>
+          <t>344391</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>22281</t>
+          <t>22208</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8427,17 +8427,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MICHELLE JAZLIM</t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>RICO</t>
+          <t>ARTEAGA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8447,28 +8447,28 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6865111469</t>
+          <t>6311261612</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>09-02-1992</t>
+          <t>18-06-1985</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>MICHELLE.RLEYVA@GMAIL.COM</t>
+          <t>COLORGRAFICO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>17-02-2026 12:06:32</t>
+          <t>17-02-2026 07:06:31</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -8483,28 +8483,28 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>17-02-2026 12:07:57</t>
+          <t>17-02-2026 07:07:36</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>17-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V60" t="inlineStr"/>
@@ -8515,19 +8515,19 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26160522425750002244</t>
+          <t>26160522420050002226</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -8539,12 +8539,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>345376</t>
+          <t>344630</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>87541</t>
+          <t>22447</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8554,17 +8554,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SOPHIA</t>
+          <t>JESUS LEONEL</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>GALAVIZ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8574,79 +8574,67 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6865307488</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6865866356</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>26-06-1993</t>
+          <t>28-10-1986</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>SOPHIA.QUINDI@GMAIL.COM</t>
+          <t>JESUSLEONEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>20-02-2026 17:55:33</t>
+          <t>17-02-2026 17:54:18</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>20-02-2026 18:01:22</t>
+          <t>17-02-2026 17:56:16</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>20-02-2026 18:00:10</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8654,19 +8642,19 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26160522533220002443</t>
+          <t>26160522439290002266</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -8678,12 +8666,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>345386</t>
+          <t>344948</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>87551</t>
+          <t>22765</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8693,17 +8681,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEJANDRO </t>
+          <t>KENIA LORENA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>LAURIAS</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>BATISTA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8713,67 +8701,67 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6866441611</t>
+          <t>6862417380</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>INDEPENDENCIA 1</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>10-08-1994</t>
+          <t>10-06-1998</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>ALGSMQD26@GMAIL.COM</t>
+          <t>KENIAMB98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>20-02-2026 18:13:38</t>
+          <t>18-02-2026 19:27:03</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>20-02-2026 18:16:09</t>
+          <t>18-02-2026 19:31:59</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>20-02-2026 18:15:32</t>
+          <t>18-02-2026 19:30:17</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -8793,19 +8781,19 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26160522533690002445</t>
+          <t>26160522475220002354</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -8817,12 +8805,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>345399</t>
+          <t>344197</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>87564</t>
+          <t>22014</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8832,17 +8820,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NATALIA</t>
+          <t>SILVIA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CASAREZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>VALLE</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8852,7 +8840,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6861221578</t>
+          <t>6863845214</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -8867,17 +8855,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>09-11-1995</t>
+          <t>01-01-2000</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>NATALIACASAREZVALLE@GMAIL.COM</t>
+          <t>MARIA.932573@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>20-02-2026 18:53:23</t>
+          <t>16-02-2026 17:11:26</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8902,17 +8890,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>20-02-2026 18:57:38</t>
+          <t>18-02-2026 17:47:52</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>20-02-2026 18:56:28</t>
+          <t>18-02-2026 17:43:52</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -8932,11 +8920,19 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26160522534930002446</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
+          <t>26160522470320002337</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>649</t>
@@ -8944,7 +8940,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -8956,12 +8952,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>344929</t>
+          <t>345376</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22746</t>
+          <t>87541</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8971,17 +8967,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>SOPHIA</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8991,7 +8987,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>9371155830</t>
+          <t>6865307488</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -9001,22 +8997,22 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>18-06-1991</t>
+          <t>26-06-1993</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>ANGELMORENOOCHOA@GMAIL.COM</t>
+          <t>SOPHIA.QUINDI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>18-02-2026 18:36:12</t>
+          <t>20-02-2026 17:55:33</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -9041,17 +9037,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>18-02-2026 18:47:06</t>
+          <t>20-02-2026 18:01:22</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>18-02-2026 18:46:16</t>
+          <t>20-02-2026 18:00:10</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -9071,7 +9067,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26160522473470002345</t>
+          <t>26160522533220002443</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr"/>
@@ -9083,7 +9079,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -9095,12 +9091,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>346272</t>
+          <t>345386</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>88437</t>
+          <t>87551</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9110,17 +9106,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ANGELA</t>
+          <t xml:space="preserve">ALEJANDRO </t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OJEDA</t>
+          <t>LAURIAS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>UREÑA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9130,67 +9126,79 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6461508837</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>6866441611</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>21-04-1999</t>
+          <t>10-08-1994</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>ANGELA.OJEDA0421@GMAIL.COM</t>
+          <t>ALGSMQD26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>24-02-2026 17:44:34</t>
+          <t>20-02-2026 18:13:38</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>24-02-2026 17:45:53</t>
+          <t>20-02-2026 18:16:09</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>24-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr"/>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:15:32</t>
+        </is>
+      </c>
       <c r="U65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr"/>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W65" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9198,19 +9206,19 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26160522628990002594</t>
+          <t>26160522533690002445</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -9222,12 +9230,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>345976</t>
+          <t>345399</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>88141</t>
+          <t>87564</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9237,17 +9245,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>JOAQUIN</t>
+          <t>NATALIA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>CASAREZ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>VALLE</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9257,67 +9265,79 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6861822047</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>6861221578</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>10-06-1982</t>
+          <t>09-11-1995</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>JOTAQN.RUIZ@HOTMAIL.COM</t>
+          <t>NATALIACASAREZVALLE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>23-02-2026 18:22:36</t>
+          <t>20-02-2026 18:53:23</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>23-02-2026 18:24:38</t>
+          <t>20-02-2026 18:57:38</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr"/>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:56:28</t>
+        </is>
+      </c>
       <c r="U66" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr"/>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W66" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9325,14 +9345,14 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26160522595470002522</t>
+          <t>26160522534930002446</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
@@ -9349,12 +9369,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>344948</t>
+          <t>344929</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22765</t>
+          <t>22746</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9364,17 +9384,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>KENIA LORENA</t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>BATISTA</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9384,57 +9404,57 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6862417380</t>
+          <t>9371155830</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 1</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>10-06-1998</t>
+          <t>18-06-1991</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>KENIAMB98@GMAIL.COM</t>
+          <t>ANGELMORENOOCHOA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>18-02-2026 19:27:03</t>
+          <t>18-02-2026 18:36:12</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>18-02-2026 19:31:59</t>
+          <t>18-02-2026 18:47:06</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -9444,7 +9464,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>18-02-2026 19:30:17</t>
+          <t>18-02-2026 18:46:16</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -9464,14 +9484,14 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26160522475220002354</t>
+          <t>26160522473470002345</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
@@ -9488,12 +9508,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>343713</t>
+          <t>345809</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>87974</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9503,17 +9523,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>JESSICA ALEJANDRA</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>HARO</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9523,63 +9543,67 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6863648770</t>
+          <t>6863504737</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>JOSE MARIA AGUAYO 506</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>18-01-2006</t>
+          <t>08-04-2000</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>JESSICAA.GUTIERREZ@CETYS.EDU.MX</t>
+          <t>ALETSMIRANDA7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>14-02-2026 11:38:52</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>23-02-2026 14:46:02</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>14-02-2026 11:41:20</t>
+          <t>23-02-2026 15:06:54</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>14-02-2026 11:40:29</t>
+          <t>23-02-2026 14:52:57</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -9589,7 +9613,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
@@ -9599,14 +9623,14 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26160522347590002106</t>
+          <t>26160522583760002502</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
@@ -9623,12 +9647,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>345971</t>
+          <t>345976</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>88136</t>
+          <t>88141</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9648,7 +9672,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>IBAÑEZ</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9658,7 +9682,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6862034774</t>
+          <t>6861822047</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9669,17 +9693,17 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>21-03-2009</t>
+          <t>10-06-1982</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>RUIZIBAÑEZJQN@OUTLOOK.COM</t>
+          <t>JOTAQN.RUIZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>23-02-2026 18:17:27</t>
+          <t>23-02-2026 18:22:36</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -9704,7 +9728,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>23-02-2026 18:19:45</t>
+          <t>23-02-2026 18:24:38</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -9726,7 +9750,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26160522595030002521</t>
+          <t>26160522595470002522</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr"/>
@@ -9738,24 +9762,24 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>346049</t>
+          <t>345971</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>88214</t>
+          <t>88136</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9765,17 +9789,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>JONAS</t>
+          <t>JOAQUIN</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>IBAÑEZ</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9785,7 +9809,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6862765318</t>
+          <t>6862034774</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9796,22 +9820,22 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>19-07-1999</t>
+          <t>21-03-2009</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>LABAJAMXLI@GMAIL.COM</t>
+          <t>RUIZIBAÑEZJQN@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>23-02-2026 20:45:09</t>
+          <t>23-02-2026 18:17:27</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -9821,17 +9845,17 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>23-02-2026 20:46:28</t>
+          <t>23-02-2026 18:19:45</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -9842,7 +9866,7 @@
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V70" t="inlineStr"/>
@@ -9853,36 +9877,36 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26160522602060002551</t>
+          <t>26160522595030002521</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>346604</t>
+          <t>346272</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>88769</t>
+          <t>88437</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9892,17 +9916,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ALEJANDRA</t>
+          <t>ANGELA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ALVARADO</t>
+          <t>OJEDA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MOSQUERA</t>
+          <t>UREÑA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9912,14 +9936,10 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>6862149610</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA 1</t>
-        </is>
-      </c>
+          <t>6461508837</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -9927,17 +9947,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>23-06-1989</t>
+          <t>21-04-1999</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>PEMOALJUL@HOTMAIL.COM</t>
+          <t>ANGELA.OJEDA0421@GMAIL.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>25-02-2026 20:04:30</t>
+          <t>24-02-2026 17:44:34</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -9947,44 +9967,36 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>25-02-2026 20:10:08</t>
+          <t>24-02-2026 17:45:53</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>25-02-2026 20:08:55</t>
-        </is>
-      </c>
+          <t>24-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9992,19 +10004,19 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26160522667440002678</t>
+          <t>26160522628990002594</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -10016,12 +10028,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>345721</t>
+          <t>346049</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>87886</t>
+          <t>88214</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -10031,17 +10043,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>J ASUNCION</t>
+          <t>JONAS</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -10051,14 +10063,10 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>6861754997</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>RIO AMECA 1896</t>
-        </is>
-      </c>
+          <t>6862765318</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -10066,42 +10074,42 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>14-01-1981</t>
+          <t>19-07-1999</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>RODRILOVEMX@GMAIL.COM</t>
+          <t>LABAJAMXLI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>23-02-2026 12:02:31</t>
+          <t>23-02-2026 20:45:09</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>23-02-2026 12:11:56</t>
+          <t>23-02-2026 20:46:28</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -10109,21 +10117,13 @@
           <t>23-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>23-02-2026 12:08:50</t>
-        </is>
-      </c>
+      <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10131,19 +10131,19 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>26160522578360002492</t>
+          <t>26160522602060002551</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -10155,12 +10155,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>346370</t>
+          <t>346604</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>88535</t>
+          <t>88769</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>JOSE ALBERTO</t>
+          <t>ALEJANDRA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PAEZ</t>
+          <t>ALVARADO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>FRANCISCO</t>
+          <t>MOSQUERA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -10190,57 +10190,57 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>7123435473</t>
+          <t>6862149610</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>VILLAFONTANA</t>
+          <t>INDEPENDENCIA 1</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>26-06-2000</t>
+          <t>23-06-1989</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>JOSE5535072149@GMAIL.COM</t>
+          <t>PEMOALJUL@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>25-02-2026 07:44:10</t>
+          <t>25-02-2026 20:04:30</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>25-02-2026 07:47:45</t>
+          <t>25-02-2026 20:10:08</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>25-02-2026 07:46:50</t>
+          <t>25-02-2026 20:08:55</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -10270,22 +10270,288 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>26160522646040002634</t>
+          <t>26160522667440002678</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
+          <t>Sergio  Cordova Hernandez</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>346933</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>89098</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA ELSY </t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAMOS</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>6862682248</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>IGNACIO ALLENDE 1006</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>28-02-2000</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>EELSY.RAMOS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>27-02-2026 12:42:34</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>27-02-2026 12:55:33</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>27-02-2026 12:54:47</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>26160522710730002759</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>346956</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>89121</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ISABELA</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>CHARLES</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6866483390</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>23-03-2011</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>ICHARLESD@EDUBC.MX</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>27-02-2026 14:11:58</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>27-02-2026 14:15:12</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>26160522712130002765</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
@@ -1662,12 +1662,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>340481</t>
+          <t>341834</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HILDA</t>
+          <t>DARIANA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BENAVIDEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PEÑA</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6864150761</t>
+          <t>6862489316</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LINEZO1</t>
+          <t>SAN CARLO1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1712,17 +1712,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>21-07-1961</t>
+          <t>03-12-1981</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>NOTIERERER@TYU.COM</t>
+          <t>LOPEZDARIANA780@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>03-02-2026 08:55:15</t>
+          <t>07-02-2026 13:31:41</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1743,17 +1743,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>04-02-2026 10:23:34</t>
+          <t>07-02-2026 13:38:04</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>04-02-2026 10:22:30</t>
+          <t>07-02-2026 13:35:50</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1773,19 +1773,11 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26160522071550001606</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
-        </is>
-      </c>
+          <t>26160522161810001766</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
           <t>499</t>
@@ -1793,7 +1785,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1805,12 +1797,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>341834</t>
+          <t>340481</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19652</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1820,17 +1812,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DARIANA</t>
+          <t>HILDA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>BENAVIDEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1840,12 +1832,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6862489316</t>
+          <t>6864150761</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SAN CARLO1</t>
+          <t>LINEZO1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1855,17 +1847,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>03-12-1981</t>
+          <t>21-07-1961</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>LOPEZDARIANA780@GMAIL.COM</t>
+          <t>NOTIERERER@TYU.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>07-02-2026 13:31:41</t>
+          <t>03-02-2026 08:55:15</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1886,17 +1878,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>07-02-2026 13:38:04</t>
+          <t>04-02-2026 10:23:34</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>07-02-2026 13:35:50</t>
+          <t>04-02-2026 10:22:30</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1906,7 +1898,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1916,11 +1908,19 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26160522161810001766</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+          <t>26160522071550001606</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>499</t>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -3040,12 +3040,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>342822</t>
+          <t>340255</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20639</t>
+          <t>18073</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3055,17 +3055,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LEOPOLDO</t>
+          <t>STEPHANY</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LOYO</t>
+          <t>BEJARANO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>COBO</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6862120595</t>
+          <t>6865923181</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>INDEPENDENCIA 38</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>17-07-1971</t>
+          <t>18-01-1995</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>LEOPOLDOLOYO@GMAIL.COM</t>
+          <t>FANNYBEJARANO904@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>10-02-2026 19:02:43</t>
+          <t>02-02-2026 16:15:36</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3121,17 +3121,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>14-02-2026 13:28:02</t>
+          <t>02-02-2026 16:21:03</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>14-02-2026 13:27:04</t>
+          <t>02-02-2026 16:20:43</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3151,14 +3151,10 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26160522349290002113</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26160522016270001486</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
@@ -3167,7 +3163,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3179,12 +3175,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>342794</t>
+          <t>342822</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3194,17 +3190,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>JOSUE</t>
+          <t>LEOPOLDO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>LOYO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>COBO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3214,12 +3210,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6861127057</t>
+          <t>6862120595</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>INDEPENDENCI1</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3229,17 +3225,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>26-11-1989</t>
+          <t>17-07-1971</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>JOSUEBRMUSIC@GMAIL.COM</t>
+          <t>LEOPOLDOLOYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>10-02-2026 18:25:08</t>
+          <t>10-02-2026 19:02:43</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3260,17 +3256,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>10-02-2026 18:27:56</t>
+          <t>14-02-2026 13:28:02</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>10-02-2026 18:27:24</t>
+          <t>14-02-2026 13:27:04</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3280,7 +3276,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3290,10 +3286,14 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26160522243630001901</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
+          <t>26160522349290002113</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3314,12 +3314,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>340255</t>
+          <t>342794</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18073</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3329,17 +3329,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>STEPHANY</t>
+          <t>JOSUE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BEJARANO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ENRIQUEZ</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3349,32 +3349,32 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6865923181</t>
+          <t>6861127057</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 38</t>
+          <t>INDEPENDENCI1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>18-01-1995</t>
+          <t>26-11-1989</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>FANNYBEJARANO904@GMAIL.COM</t>
+          <t>JOSUEBRMUSIC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>02-02-2026 16:15:36</t>
+          <t>10-02-2026 18:25:08</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3395,17 +3395,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>02-02-2026 16:21:03</t>
+          <t>10-02-2026 18:27:56</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>02-02-2026 16:20:43</t>
+          <t>10-02-2026 18:27:24</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26160522016270001486</t>
+          <t>26160522243630001901</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3449,12 +3449,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>343140</t>
+          <t>340641</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>18459</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3464,17 +3464,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">VANESSA </t>
+          <t>LUCIA YADIRA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>VELARDE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6864164007</t>
+          <t>6861822416</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AV TORRE LAS ARCAS 2045</t>
+          <t>CULTURA OLMECA 3608</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3499,17 +3499,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>08-11-1989</t>
+          <t>13-12-1990</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>VANESSAGALVANR250210@GMAIL.COM</t>
+          <t>YADIRA_1290@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>11-02-2026 20:55:11</t>
+          <t>03-02-2026 15:56:48</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3530,17 +3530,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>13-02-2026 18:56:17</t>
+          <t>05-02-2026 16:33:17</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>13-02-2026 18:55:42</t>
+          <t>05-02-2026 16:30:37</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3560,15 +3560,19 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26170522329060002370</t>
+          <t>26160522110560001680</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>499</t>
@@ -3576,7 +3580,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3588,12 +3592,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>340641</t>
+          <t>343140</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3603,17 +3607,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LUCIA YADIRA</t>
+          <t xml:space="preserve">VANESSA </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VELARDE</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3623,12 +3627,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6861822416</t>
+          <t>6864164007</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CULTURA OLMECA 3608</t>
+          <t>AV TORRE LAS ARCAS 2045</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3638,17 +3642,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>13-12-1990</t>
+          <t>08-11-1989</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>YADIRA_1290@HOTMAIL.COM</t>
+          <t>VANESSAGALVANR250210@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>03-02-2026 15:56:48</t>
+          <t>11-02-2026 20:55:11</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3669,17 +3673,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>05-02-2026 16:33:17</t>
+          <t>13-02-2026 18:56:17</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>05-02-2026 16:30:37</t>
+          <t>13-02-2026 18:55:42</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3699,19 +3703,15 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26160522110560001680</t>
+          <t>26170522329060002370</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
           <t>499</t>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3866,12 +3866,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>343612</t>
+          <t>340697</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21429</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>OSCAR</t>
+          <t>CRISTIAN ISMAEL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CARRERA</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3901,10 +3901,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6865906261</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>6863537341</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA3</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3912,56 +3916,60 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>03-08-2006</t>
+          <t>22-06-1995</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>OR629395@GMAIL.COM</t>
+          <t>CRISTIAN.TORRES@GCADENA.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>13-02-2026 20:02:16</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 17:02:34</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>13-02-2026 20:03:49</t>
+          <t>03-02-2026 17:06:48</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>03-02-2026 17:06:13</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3969,19 +3977,19 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26160522330930002093</t>
+          <t>26160522047970001551</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3993,12 +4001,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>340697</t>
+          <t>343612</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>21429</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4008,17 +4016,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CRISTIAN ISMAEL</t>
+          <t>OSCAR</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>CARRERA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4028,14 +4036,10 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6863537341</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA3</t>
-        </is>
-      </c>
+          <t>6865906261</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4043,60 +4047,56 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>22-06-1995</t>
+          <t>03-08-2006</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CRISTIAN.TORRES@GCADENA.COM</t>
+          <t>OR629395@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>03-02-2026 17:02:34</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>13-02-2026 20:02:16</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>03-02-2026 17:06:48</t>
+          <t>13-02-2026 20:03:49</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>03-02-2026 17:06:13</t>
-        </is>
-      </c>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4104,19 +4104,19 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26160522047970001551</t>
+          <t>26160522330930002093</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4402,12 +4402,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>342087</t>
+          <t>341132</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19905</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4417,17 +4417,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>KARLA VERÓNICA</t>
+          <t xml:space="preserve">NAHOMI ESTEFANIA </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PALAFOX</t>
+          <t>TALAMANTES</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6861244927</t>
+          <t>6643120858</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>IND111111</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4452,52 +4452,48 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>26-05-1986</t>
+          <t>18-08-1996</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>VERONIKAPALAFOX@GMAIL.COM</t>
+          <t>ESTEFANIAMTALAMANTESX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>09-02-2026 10:07:36</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 18:08:31</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>16-02-2026 08:19:11</t>
+          <t>10-02-2026 16:06:43</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>16-02-2026 08:18:23</t>
+          <t>10-02-2026 16:05:59</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4517,7 +4513,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26160522380750002134</t>
+          <t>26130522235720002570</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4527,17 +4523,17 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
+          <t>MARIA CANDELARIA LARA AVILA</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4549,12 +4545,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>341132</t>
+          <t>342087</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>19905</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4564,17 +4560,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAHOMI ESTEFANIA </t>
+          <t>KARLA VERÓNICA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TALAMANTES</t>
+          <t>PALAFOX</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4584,12 +4580,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6643120858</t>
+          <t>6861244927</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>IND111111</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4599,48 +4595,52 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>18-08-1996</t>
+          <t>26-05-1986</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ESTEFANIAMTALAMANTESX@GMAIL.COM</t>
+          <t>VERONIKAPALAFOX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>04-02-2026 18:08:31</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>09-02-2026 10:07:36</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>10-02-2026 16:06:43</t>
+          <t>16-02-2026 08:19:11</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>10-02-2026 16:05:59</t>
+          <t>16-02-2026 08:18:23</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26130522235720002570</t>
+          <t>26160522380750002134</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4670,17 +4670,17 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>MARIA CANDELARIA LARA AVILA</t>
+          <t>GERARDO ARTURO ALEJO OYARVIDE</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4819,12 +4819,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>345721</t>
+          <t>344453</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>87886</t>
+          <t>22270</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4834,12 +4834,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>J ASUNCION</t>
+          <t>JESUS</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4854,14 +4854,10 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6861754997</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>RIO AMECA 1896</t>
-        </is>
-      </c>
+          <t>6861762359</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4869,64 +4865,56 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>14-01-1981</t>
+          <t>11-08-1951</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>RODRILOVEMX@GMAIL.COM</t>
+          <t>NOTIENE23445@DFDF.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>23-02-2026 12:02:31</t>
+          <t>17-02-2026 11:34:41</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>23-02-2026 12:11:56</t>
+          <t>17-02-2026 11:37:38</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>23-02-2026 12:08:50</t>
-        </is>
-      </c>
+          <t>17-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4934,19 +4922,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26160522578360002492</t>
+          <t>26160522425250002243</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4958,12 +4946,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>344453</t>
+          <t>344505</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>22270</t>
+          <t>22322</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4973,17 +4961,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>JESUS</t>
+          <t>KENIA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4993,67 +4981,79 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6861762359</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>6869460269</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>11-08-1951</t>
+          <t>24-09-1981</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>NOTIENE23445@DFDF.COM</t>
+          <t>KRISS0024@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>17-02-2026 11:34:41</t>
+          <t>17-02-2026 14:43:35</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>17-02-2026 11:37:38</t>
+          <t>17-02-2026 14:52:04</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>17-02-2026 14:49:23</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5061,19 +5061,19 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26160522425250002243</t>
+          <t>26160522430130002253</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>344505</t>
+          <t>345721</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>87886</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>KENIA</t>
+          <t>J ASUNCION</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5120,32 +5120,32 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6869460269</t>
+          <t>6861754997</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>RIO AMECA 1896</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>24-09-1981</t>
+          <t>14-01-1981</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>KRISS0024@GMAIL.COM</t>
+          <t>RODRILOVEMX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>17-02-2026 14:43:35</t>
+          <t>23-02-2026 12:02:31</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5170,17 +5170,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>17-02-2026 14:52:04</t>
+          <t>23-02-2026 12:11:56</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>17-02-2026 14:49:23</t>
+          <t>23-02-2026 12:08:50</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26160522430130002253</t>
+          <t>26160522578360002492</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5486,12 +5486,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>342336</t>
+          <t>346370</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>88535</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5501,17 +5501,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MARCO ALEJANDRO</t>
+          <t>JOSE ALBERTO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>PAEZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>FRANCISCO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6861632588</t>
+          <t>7123435473</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA01</t>
+          <t>VILLAFONTANA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5536,20 +5536,24 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>12-05-2006</t>
+          <t>26-06-2000</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>6MALLISME9@GMAIL.COM</t>
+          <t>JOSE5535072149@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>09-02-2026 17:35:12</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>25-02-2026 07:44:10</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5567,17 +5571,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>09-02-2026 17:38:30</t>
+          <t>25-02-2026 07:47:45</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>09-02-2026 17:38:05</t>
+          <t>25-02-2026 07:46:50</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5587,7 +5591,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5597,7 +5601,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26160522203170001811</t>
+          <t>26160522646040002634</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -5609,7 +5613,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5621,12 +5625,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>342474</t>
+          <t>342336</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5636,17 +5640,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MELISSA</t>
+          <t>MARCO ALEJANDRO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5656,7 +5660,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6863242180</t>
+          <t>6861632588</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5666,22 +5670,22 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>25-07-1987</t>
+          <t>12-05-2006</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>YLEM51@GMAIL.COM</t>
+          <t>6MALLISME9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>09-02-2026 20:08:06</t>
+          <t>09-02-2026 17:35:12</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5702,7 +5706,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>09-02-2026 20:12:28</t>
+          <t>09-02-2026 17:38:30</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -5712,7 +5716,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>09-02-2026 20:10:07</t>
+          <t>09-02-2026 17:38:05</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5732,7 +5736,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26160522213110001840</t>
+          <t>26160522203170001811</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5756,12 +5760,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>342457</t>
+          <t>342474</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20274</t>
+          <t>20291</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5771,17 +5775,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE </t>
+          <t>MELISSA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FRANCISCO</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FIERRO</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5791,32 +5795,32 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6861575086</t>
+          <t>6863242180</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA02</t>
+          <t>INDEPENDENCIA01</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>15-09-1973</t>
+          <t>25-07-1987</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>FIERRO_PACO@HOTMAIL.COM</t>
+          <t>YLEM51@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>09-02-2026 19:49:15</t>
+          <t>09-02-2026 20:08:06</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5837,7 +5841,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>09-02-2026 19:51:47</t>
+          <t>09-02-2026 20:12:28</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5847,7 +5851,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>09-02-2026 19:50:53</t>
+          <t>09-02-2026 20:10:07</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5857,7 +5861,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5867,7 +5871,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26160522212280001839</t>
+          <t>26160522213110001840</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -5891,12 +5895,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>342583</t>
+          <t>342457</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20400</t>
+          <t>20274</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5906,17 +5910,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SHESLY DENNIS</t>
+          <t xml:space="preserve">JOSE </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>FRANCISCO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>FIERRO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5926,32 +5930,32 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6861234727</t>
+          <t>6861575086</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PRESA DE LA ANGOSURA 1491</t>
+          <t>INDEPENDENCIA02</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>30-07-1996</t>
+          <t>15-09-1973</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>SHES.MEZAGTZ@GMAIL.COM</t>
+          <t>FIERRO_PACO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>10-02-2026 11:28:40</t>
+          <t>09-02-2026 19:49:15</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5972,17 +5976,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>10-02-2026 11:31:11</t>
+          <t>09-02-2026 19:51:47</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>10-02-2026 11:30:36</t>
+          <t>09-02-2026 19:50:53</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6002,7 +6006,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26160522229140001874</t>
+          <t>26160522212280001839</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -6014,7 +6018,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Gerardo Arturo Alejo Oyarvide</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6026,12 +6030,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>346370</t>
+          <t>342583</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>88535</t>
+          <t>20400</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6041,17 +6045,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>JOSE ALBERTO</t>
+          <t>SHESLY DENNIS</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PAEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FRANCISCO</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6061,39 +6065,35 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>7123435473</t>
+          <t>6861234727</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>VILLAFONTANA</t>
+          <t>PRESA DE LA ANGOSURA 1491</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>26-06-2000</t>
+          <t>30-07-1996</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>JOSE5535072149@GMAIL.COM</t>
+          <t>SHES.MEZAGTZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>25-02-2026 07:44:10</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 11:28:40</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6111,17 +6111,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>25-02-2026 07:47:45</t>
+          <t>10-02-2026 11:31:11</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>25-02-2026 07:46:50</t>
+          <t>10-02-2026 11:30:36</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26160522646040002634</t>
+          <t>26160522229140001874</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Gerardo Arturo Alejo Oyarvide</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6427,12 +6427,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>342482</t>
+          <t>343384</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20299</t>
+          <t>21201</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6442,17 +6442,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>BRISA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>GASCA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CACERES</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6462,67 +6462,75 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6867220400</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>6863912198</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>25-08-1998</t>
+          <t>12-02-2006</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>JOSECACEREZ98@GMAIL.COM</t>
+          <t>GNAVARROGASCA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>09-02-2026 20:20:01</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 19:16:27</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>09-02-2026 20:21:16</t>
+          <t>12-02-2026 19:22:02</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>12-02-2026 19:21:22</t>
+        </is>
+      </c>
       <c r="U45" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6530,19 +6538,19 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26160522213460001843</t>
+          <t>26160522304540002036</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6554,12 +6562,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>343025</t>
+          <t>342482</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20842</t>
+          <t>20299</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6569,17 +6577,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DYLAN</t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t>CACERES</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6589,7 +6597,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6861698256</t>
+          <t>6867220400</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6600,17 +6608,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>06-08-2002</t>
+          <t>25-08-1998</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>DYLANMTZM.26@GMAIL.COM</t>
+          <t>JOSECACEREZ98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>11-02-2026 15:49:14</t>
+          <t>09-02-2026 20:20:01</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6625,22 +6633,22 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>11-02-2026 15:52:21</t>
+          <t>09-02-2026 20:21:16</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -6657,19 +6665,19 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26160522267270001952</t>
+          <t>26160522213460001843</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6681,12 +6689,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>342997</t>
+          <t>343025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20814</t>
+          <t>20842</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6696,17 +6704,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>JAZMIN</t>
+          <t>DYLAN</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6716,75 +6724,67 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8130964314</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>CERRO DEL POTOSI 1119</t>
-        </is>
-      </c>
+          <t>6861698256</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>18-03-1995</t>
+          <t>06-08-2002</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>YAAS.LOPEZ18@GMAIL.COM</t>
+          <t>DYLANMTZM.26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>11-02-2026 14:53:46</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>11-02-2026 15:49:14</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>12-02-2026 12:36:52</t>
+          <t>11-02-2026 15:52:21</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>12-02-2026 12:36:23</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6792,14 +6792,14 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26180522292630004399</t>
+          <t>26160522267270001952</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6816,12 +6816,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>343135</t>
+          <t>342997</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20952</t>
+          <t>20814</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6831,17 +6831,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>JAIME</t>
+          <t>JAZMIN</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6851,63 +6851,75 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6862316574</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>8130964314</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>CERRO DEL POTOSI 1119</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
+          <t>18-03-1995</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>YAAS.LOPEZ18@GMAIL.COM</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>11-02-2026 20:34:48</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>11-02-2026 14:53:46</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>13-02-2026 16:04:20</t>
+          <t>12-02-2026 12:36:52</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>12-02-2026 12:36:23</t>
+        </is>
+      </c>
       <c r="U48" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6915,44 +6927,36 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26160522323640002074</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26180522292630004399</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>343384</t>
+          <t>343135</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21201</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6962,12 +6966,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BRISA</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>GASCA</t>
+          <t>OLIVAS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -6982,75 +6986,63 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6863912198</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6862316574</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>12-02-2006</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>GNAVARROGASCA@GMAIL.COM</t>
-        </is>
-      </c>
+          <t>01-01-2000</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>12-02-2026 19:16:27</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>11-02-2026 20:34:48</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>12-02-2026 19:22:02</t>
+          <t>13-02-2026 16:04:20</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>12-02-2026 19:21:22</t>
-        </is>
-      </c>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7058,24 +7050,32 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26160522304540002036</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
+          <t>26160522323640002074</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>343139</t>
+          <t>344132</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20956</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NICZA ARELI</t>
+          <t xml:space="preserve">ANGELES </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>IZAGUIRRE</t>
+          <t>CARMONA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>SIQUEIROS</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7252,14 +7252,10 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6864650098</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TORRE LAS ARCAS </t>
-        </is>
-      </c>
+          <t>6863378715</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7267,60 +7263,56 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>03-11-1994</t>
+          <t>04-08-2006</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>IZAGUIRREARELI@GMAIL.COM</t>
+          <t>ANGELESWCARMONA763@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>11-02-2026 20:53:07</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>16-02-2026 15:44:25</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>13-02-2026 18:50:54</t>
+          <t>16-02-2026 15:45:32</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>13-02-2026 18:49:33</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7328,23 +7320,19 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26170522328830002369</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26160522393400002157</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -7356,12 +7344,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>344132</t>
+          <t>343139</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21949</t>
+          <t>20956</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7371,17 +7359,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGELES </t>
+          <t>NICZA ARELI</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CARMONA</t>
+          <t>IZAGUIRRE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SIQUEIROS</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7391,10 +7379,14 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6863378715</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>6864650098</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TORRE LAS ARCAS </t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7402,56 +7394,60 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>04-08-2006</t>
+          <t>03-11-1994</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>ANGELESWCARMONA763@GMAIL.COM</t>
+          <t>IZAGUIRREARELI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>16-02-2026 15:44:25</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>11-02-2026 20:53:07</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>16-02-2026 15:45:32</t>
+          <t>13-02-2026 18:50:54</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>13-02-2026 18:49:33</t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7459,19 +7455,23 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26160522393400002157</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr"/>
+          <t>26170522328830002369</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7868,12 +7868,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>344451</t>
+          <t>344515</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22268</t>
+          <t>22332</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7883,17 +7883,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>TIFFANY JAZMIN</t>
+          <t>ASTRID AITANA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>HOPKINS</t>
+          <t>HIDALGO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7903,37 +7903,37 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6866190407</t>
+          <t>5522151079</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>IND22222</t>
+          <t>RIO TULA 12</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>06-09-2006</t>
+          <t>19-10-2006</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>NOTIENEEE@SSS.COM</t>
+          <t>AITANAHIDALGO0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>17-02-2026 11:29:05</t>
+          <t>17-02-2026 15:10:23</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -7943,27 +7943,27 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>17-02-2026 11:32:47</t>
+          <t>23-02-2026 15:56:01</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>17-02-2026 11:32:10</t>
+          <t>23-02-2026 15:54:51</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7983,14 +7983,14 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26160522425100002242</t>
+          <t>26290522585740002451</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -8007,12 +8007,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>344464</t>
+          <t>344409</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22281</t>
+          <t>22226</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8022,17 +8022,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>MICHELLE JAZLIM</t>
+          <t>ISRAEL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t>VELAZQUEZ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>RICO</t>
+          <t>LIAÑO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8042,53 +8042,57 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6865111469</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>6863940285</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>EEEE12</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>09-02-1992</t>
+          <t>18-04-1977</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>MICHELLE.RLEYVA@GMAIL.COM</t>
+          <t>MASTERBOY1930@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>17-02-2026 12:06:32</t>
+          <t>17-02-2026 08:06:52</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>17-02-2026 12:07:57</t>
+          <t>17-02-2026 08:09:37</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -8096,13 +8100,21 @@
           <t>17-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr"/>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>17-02-2026 08:08:58</t>
+        </is>
+      </c>
       <c r="U57" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr"/>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W57" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8110,19 +8122,19 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26160522425750002244</t>
+          <t>26160522421530002234</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -8134,12 +8146,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>344409</t>
+          <t>344451</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22226</t>
+          <t>22268</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8149,17 +8161,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ISRAEL</t>
+          <t>TIFFANY JAZMIN</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>LIAÑO</t>
+          <t>HOPKINS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8169,12 +8181,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6863940285</t>
+          <t>6866190407</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>EEEE12</t>
+          <t>IND22222</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8184,17 +8196,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>18-04-1977</t>
+          <t>06-09-2006</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>MASTERBOY1930@GMAIL.COM</t>
+          <t>NOTIENEEE@SSS.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>17-02-2026 08:06:52</t>
+          <t>17-02-2026 11:29:05</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8219,7 +8231,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>17-02-2026 08:09:37</t>
+          <t>17-02-2026 11:32:47</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -8229,7 +8241,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>17-02-2026 08:08:58</t>
+          <t>17-02-2026 11:32:10</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -8249,7 +8261,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26160522421530002234</t>
+          <t>26160522425100002242</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
@@ -8273,12 +8285,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>344515</t>
+          <t>344464</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>22332</t>
+          <t>22281</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8288,17 +8300,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ASTRID AITANA</t>
+          <t>MICHELLE JAZLIM</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>LEYVA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t>RICO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8308,14 +8320,10 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>5522151079</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>RIO TULA 12</t>
-        </is>
-      </c>
+          <t>6865111469</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8323,17 +8331,17 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>19-10-2006</t>
+          <t>09-02-1992</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>AITANAHIDALGO0@GMAIL.COM</t>
+          <t>MICHELLE.RLEYVA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>17-02-2026 15:10:23</t>
+          <t>17-02-2026 12:06:32</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8343,12 +8351,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -8358,29 +8366,21 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>23-02-2026 15:56:01</t>
+          <t>17-02-2026 12:07:57</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>23-02-2026 15:54:51</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26290522585740002451</t>
+          <t>26160522425750002244</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -8412,12 +8412,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>344391</t>
+          <t>345376</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>87541</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8427,17 +8427,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t>SOPHIA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ARTEAGA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8447,67 +8447,79 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6311261612</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>6865307488</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>18-06-1985</t>
+          <t>26-06-1993</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>COLORGRAFICO@HOTMAIL.COM</t>
+          <t>SOPHIA.QUINDI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>17-02-2026 07:06:31</t>
+          <t>20-02-2026 17:55:33</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>17-02-2026 07:07:36</t>
+          <t>20-02-2026 18:01:22</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr"/>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:00:10</t>
+        </is>
+      </c>
       <c r="U60" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8515,19 +8527,19 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26160522420050002226</t>
+          <t>26160522533220002443</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -8539,12 +8551,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>344630</t>
+          <t>345386</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>87551</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8554,17 +8566,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>JESUS LEONEL</t>
+          <t xml:space="preserve">ALEJANDRO </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>GALAVIZ</t>
+          <t>LAURIAS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8574,10 +8586,14 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6865866356</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>6866441611</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -8585,56 +8601,64 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>28-10-1986</t>
+          <t>10-08-1994</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>JESUSLEONEL@GMAIL.COM</t>
+          <t>ALGSMQD26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>17-02-2026 17:54:18</t>
+          <t>20-02-2026 18:13:38</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>17-02-2026 17:56:16</t>
+          <t>20-02-2026 18:16:09</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr"/>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:15:32</t>
+        </is>
+      </c>
       <c r="U61" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8642,19 +8666,19 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26160522439290002266</t>
+          <t>26160522533690002445</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -8666,12 +8690,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>344948</t>
+          <t>345399</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22765</t>
+          <t>87564</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8681,17 +8705,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KENIA LORENA</t>
+          <t>NATALIA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CASAREZ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>BATISTA</t>
+          <t>VALLE</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8701,12 +8725,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6862417380</t>
+          <t>6861221578</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 1</t>
+          <t>INDEPENDENCIA1</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8716,17 +8740,17 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>10-06-1998</t>
+          <t>09-11-1995</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>KENIAMB98@GMAIL.COM</t>
+          <t>NATALIACASAREZVALLE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>18-02-2026 19:27:03</t>
+          <t>20-02-2026 18:53:23</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -8751,17 +8775,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>18-02-2026 19:31:59</t>
+          <t>20-02-2026 18:57:38</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>18-02-2026 19:30:17</t>
+          <t>20-02-2026 18:56:28</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -8771,7 +8795,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -8781,7 +8805,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26160522475220002354</t>
+          <t>26160522534930002446</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
@@ -8805,12 +8829,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>344197</t>
+          <t>344948</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22014</t>
+          <t>22765</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8820,17 +8844,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SILVIA</t>
+          <t>KENIA LORENA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>BATISTA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8840,12 +8864,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6863845214</t>
+          <t>6862417380</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA1</t>
+          <t>INDEPENDENCIA 1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8855,17 +8879,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
+          <t>10-06-1998</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>MARIA.932573@GMAIL.COM</t>
+          <t>KENIAMB98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>16-02-2026 17:11:26</t>
+          <t>18-02-2026 19:27:03</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8890,7 +8914,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>18-02-2026 17:47:52</t>
+          <t>18-02-2026 19:31:59</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -8900,7 +8924,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>18-02-2026 17:43:52</t>
+          <t>18-02-2026 19:30:17</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -8910,7 +8934,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -8920,19 +8944,11 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26160522470320002337</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26160522475220002354</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
           <t>649</t>
@@ -8940,7 +8956,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -8952,12 +8968,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>345376</t>
+          <t>344391</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>87541</t>
+          <t>22208</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8967,17 +8983,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SOPHIA</t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>ARTEAGA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8987,79 +9003,67 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6865307488</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6311261612</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>26-06-1993</t>
+          <t>18-06-1985</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>SOPHIA.QUINDI@GMAIL.COM</t>
+          <t>COLORGRAFICO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>20-02-2026 17:55:33</t>
+          <t>17-02-2026 07:06:31</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>20-02-2026 18:01:22</t>
+          <t>17-02-2026 07:07:36</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>20-02-2026 18:00:10</t>
-        </is>
-      </c>
+          <t>17-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9067,19 +9071,19 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26160522533220002443</t>
+          <t>26160522420050002226</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -9091,12 +9095,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>345386</t>
+          <t>344630</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>87551</t>
+          <t>22447</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9106,17 +9110,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEJANDRO </t>
+          <t>JESUS LEONEL</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>LAURIAS</t>
+          <t>GALAVIZ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9126,14 +9130,10 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6866441611</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6865866356</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -9141,64 +9141,56 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>10-08-1994</t>
+          <t>28-10-1986</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>ALGSMQD26@GMAIL.COM</t>
+          <t>JESUSLEONEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>20-02-2026 18:13:38</t>
+          <t>17-02-2026 17:54:18</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>20-02-2026 18:16:09</t>
+          <t>17-02-2026 17:56:16</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>20-02-2026 18:15:32</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9206,19 +9198,19 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26160522533690002445</t>
+          <t>26160522439290002266</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -9230,12 +9222,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>345399</t>
+          <t>344197</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>87564</t>
+          <t>22014</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9245,17 +9237,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NATALIA</t>
+          <t>SILVIA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CASAREZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>VALLE</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9265,7 +9257,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6861221578</t>
+          <t>6863845214</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -9280,17 +9272,17 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>09-11-1995</t>
+          <t>01-01-2000</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>NATALIACASAREZVALLE@GMAIL.COM</t>
+          <t>MARIA.932573@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>20-02-2026 18:53:23</t>
+          <t>16-02-2026 17:11:26</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -9315,17 +9307,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>20-02-2026 18:57:38</t>
+          <t>18-02-2026 17:47:52</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>20-02-2026 18:56:28</t>
+          <t>18-02-2026 17:43:52</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -9345,11 +9337,19 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26160522534930002446</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
+          <t>26160522470320002337</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>649</t>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -9508,12 +9508,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>345809</t>
+          <t>345976</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>87974</t>
+          <t>88141</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>JOAQUIN</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9543,14 +9543,10 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6863504737</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA1</t>
-        </is>
-      </c>
+          <t>6861822047</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -9558,42 +9554,42 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>08-04-2000</t>
+          <t>10-06-1982</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>ALETSMIRANDA7@GMAIL.COM</t>
+          <t>JOTAQN.RUIZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>23-02-2026 14:46:02</t>
+          <t>23-02-2026 18:22:36</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>23-02-2026 15:06:54</t>
+          <t>23-02-2026 18:24:38</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -9601,21 +9597,13 @@
           <t>23-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>23-02-2026 14:52:57</t>
-        </is>
-      </c>
+      <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9623,14 +9611,14 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26160522583760002502</t>
+          <t>26160522595470002522</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
@@ -9647,12 +9635,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>345976</t>
+          <t>345809</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>88141</t>
+          <t>87974</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9662,17 +9650,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>JOAQUIN</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>HARO</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9682,10 +9670,14 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6861822047</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>6863504737</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA1</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -9693,42 +9685,42 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>10-06-1982</t>
+          <t>08-04-2000</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>JOTAQN.RUIZ@HOTMAIL.COM</t>
+          <t>ALETSMIRANDA7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>23-02-2026 18:22:36</t>
+          <t>23-02-2026 14:46:02</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>23-02-2026 18:24:38</t>
+          <t>23-02-2026 15:06:54</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -9736,13 +9728,21 @@
           <t>23-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr"/>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>23-02-2026 14:52:57</t>
+        </is>
+      </c>
       <c r="U69" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr"/>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W69" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9750,14 +9750,14 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26160522595470002522</t>
+          <t>26160522583760002502</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
@@ -9774,12 +9774,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>345971</t>
+          <t>346272</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>88136</t>
+          <t>88437</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9789,17 +9789,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>JOAQUIN</t>
+          <t>ANGELA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>OJEDA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>IBAÑEZ</t>
+          <t>UREÑA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9809,33 +9809,33 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6862034774</t>
+          <t>6461508837</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>21-03-2009</t>
+          <t>21-04-1999</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>RUIZIBAÑEZJQN@OUTLOOK.COM</t>
+          <t>ANGELA.OJEDA0421@GMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>23-02-2026 18:17:27</t>
+          <t>24-02-2026 17:44:34</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -9845,22 +9845,22 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>23-02-2026 18:19:45</t>
+          <t>24-02-2026 17:45:53</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>24-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T70" t="inlineStr"/>
@@ -9877,36 +9877,36 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26160522595030002521</t>
+          <t>26160522628990002594</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>346272</t>
+          <t>345971</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>88437</t>
+          <t>88136</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9916,17 +9916,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ANGELA</t>
+          <t>JOAQUIN</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>OJEDA</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UREÑA</t>
+          <t>IBAÑEZ</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9936,33 +9936,33 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>6461508837</t>
+          <t>6862034774</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>21-04-1999</t>
+          <t>21-03-2009</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>ANGELA.OJEDA0421@GMAIL.COM</t>
+          <t>RUIZIBAÑEZJQN@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>24-02-2026 17:44:34</t>
+          <t>23-02-2026 18:17:27</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -9972,22 +9972,22 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>24-02-2026 17:45:53</t>
+          <t>23-02-2026 18:19:45</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>24-05-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T71" t="inlineStr"/>
@@ -10004,24 +10004,24 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26160522628990002594</t>
+          <t>26160522595030002521</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347382</t>
+          <t>347397</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89547</t>
+          <t>89562</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CHANTAL POLET</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARMONA </t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>USTOA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,28 +613,28 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6861915346</t>
+          <t>6863319761</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>12-07-2005</t>
+          <t>30-04-2009</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CHANTY.CARMONA.C@GMAIL.COM</t>
+          <t>SESAUS20@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>02-03-2026 05:09:55</t>
+          <t>02-03-2026 06:00:40</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 05:11:13</t>
+          <t>02-03-2026 06:02:19</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -670,7 +670,7 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -681,7 +681,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26160522772570002807</t>
+          <t>26160522774100002814</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -705,12 +705,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347430</t>
+          <t>347501</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89595</t>
+          <t>89666</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RACIEL ANTONIO</t>
+          <t>SILVIA LORENA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DELGADO</t>
+          <t xml:space="preserve">ENRIQUEZ </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,28 +740,28 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6461842318</t>
+          <t>6865892371</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>10-08-2000</t>
+          <t>08-10-1983</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>RACIEL1410V@GMAIL.COM</t>
+          <t>SI.ALVAREZ08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 07:54:12</t>
+          <t>02-03-2026 11:10:21</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 07:56:28</t>
+          <t>02-03-2026 12:43:37</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -797,7 +797,7 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -808,7 +808,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26160522783170002825</t>
+          <t>26160522791620002850</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -832,12 +832,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347397</t>
+          <t>347472</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89562</t>
+          <t>89637</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,17 +847,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t xml:space="preserve">FERNANDA CECILIA </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>USTOA</t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -867,43 +867,47 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6863319761</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6863944624</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>DEL AMATE 3138</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>30-04-2009</t>
+          <t>16-06-2002</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>SESAUS20@GMAIL.COM</t>
+          <t>A1176937@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 06:00:40</t>
+          <t>02-03-2026 09:49:48</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -913,7 +917,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 06:02:19</t>
+          <t>02-03-2026 09:57:22</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -921,13 +925,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>02-03-2026 09:56:34</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -935,7 +947,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26160522774100002814</t>
+          <t>26160522786810002837</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -959,12 +971,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347501</t>
+          <t>347382</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89666</t>
+          <t>89547</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -974,17 +986,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SILVIA LORENA</t>
+          <t>CHANTAL POLET</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t xml:space="preserve">CARMONA </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENRIQUEZ </t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -994,7 +1006,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6865892371</t>
+          <t>6861915346</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,22 +1017,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>08-10-1983</t>
+          <t>12-07-2005</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>SI.ALVAREZ08@GMAIL.COM</t>
+          <t>CHANTY.CARMONA.C@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 11:10:21</t>
+          <t>02-03-2026 05:09:55</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1030,17 +1042,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 12:43:37</t>
+          <t>02-03-2026 05:11:13</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1062,14 +1074,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26160522791620002850</t>
+          <t>26160522772570002807</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1086,12 +1098,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347472</t>
+          <t>347430</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89637</t>
+          <t>89595</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1101,17 +1113,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDA CECILIA </t>
+          <t>RACIEL ANTONIO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>VELAZQUEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t>DELGADO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1121,32 +1133,28 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6863944624</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>DEL AMATE 3138</t>
-        </is>
-      </c>
+          <t>6461842318</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>16-06-2002</t>
+          <t>10-08-2000</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>A1176937@UABC.EDU.MX</t>
+          <t>RACIEL1410V@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 09:49:48</t>
+          <t>02-03-2026 07:54:12</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1156,22 +1164,22 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 09:57:22</t>
+          <t>02-03-2026 07:56:28</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1179,21 +1187,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>02-03-2026 09:56:34</t>
-        </is>
-      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1201,14 +1201,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26160522786810002837</t>
+          <t>26160522783170002825</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1491,10 +1491,391 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>Sergio  Cordova Hernandez</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>348295</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>90460</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AYEAN</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MALDONADO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>GALAVIZ</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3333878465</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>13-06-2012</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NAOMI_MGALAVIZ@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>03-03-2026 21:23:20</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>03-03-2026 22:05:53</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>26160522862540003003</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>348072</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>90237</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>JOEL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FLORES</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>HERRERA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6863309454</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>01-04-1974</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>JOELF3086@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:59:50</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:01:24</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>26160522842820002952</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>348293</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>90458</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AMAYA NAOMI</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MALDONADO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>GALAVIZ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3318420233</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>04-01-2010</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NAOMI_MGALAVIZ@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>03-03-2026 21:18:34</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>03-03-2026 22:02:31</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>26160522862510003002</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347397</t>
+          <t>324401</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89562</t>
+          <t>21340</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>LUCERO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>USTOA</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,28 +613,28 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6863319761</t>
+          <t>6862415611</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>30-04-2009</t>
+          <t>07-12-1991</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>SESAUS20@GMAIL.COM</t>
+          <t>COSMEGESPINOZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>02-03-2026 06:00:40</t>
+          <t>19-11-2025 14:28:33</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -659,18 +659,18 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 06:02:19</t>
+          <t>04-03-2026 09:14:24</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -681,11 +681,19 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26160522774100002814</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+          <t>26160522877040003015</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>MARIO ALBERTO GARCIA CERON</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>549</t>
@@ -705,12 +713,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347501</t>
+          <t>347472</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89666</t>
+          <t>89637</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +728,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SILVIA LORENA</t>
+          <t xml:space="preserve">FERNANDA CECILIA </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENRIQUEZ </t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,10 +748,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6865892371</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>6863944624</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>DEL AMATE 3138</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -751,17 +763,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>08-10-1983</t>
+          <t>16-06-2002</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>SI.ALVAREZ08@GMAIL.COM</t>
+          <t>A1176937@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 11:10:21</t>
+          <t>02-03-2026 09:49:48</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -771,22 +783,22 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 12:43:37</t>
+          <t>02-03-2026 09:57:22</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -794,13 +806,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>02-03-2026 09:56:34</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -808,14 +828,14 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26160522791620002850</t>
+          <t>26160522786810002837</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -832,12 +852,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347472</t>
+          <t>347382</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89637</t>
+          <t>89547</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDA CECILIA </t>
+          <t>CHANTAL POLET</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t xml:space="preserve">CARMONA </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -867,14 +887,10 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6863944624</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>DEL AMATE 3138</t>
-        </is>
-      </c>
+          <t>6861915346</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -882,32 +898,32 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>16-06-2002</t>
+          <t>12-07-2005</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>A1176937@UABC.EDU.MX</t>
+          <t>CHANTY.CARMONA.C@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 09:49:48</t>
+          <t>02-03-2026 05:09:55</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -917,7 +933,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 09:57:22</t>
+          <t>02-03-2026 05:11:13</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -925,21 +941,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>02-03-2026 09:56:34</t>
-        </is>
-      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -947,7 +955,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26160522786810002837</t>
+          <t>26160522772570002807</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -971,12 +979,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347382</t>
+          <t>347430</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89547</t>
+          <t>89595</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -986,17 +994,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CHANTAL POLET</t>
+          <t>RACIEL ANTONIO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARMONA </t>
+          <t>VELAZQUEZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>DELGADO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1006,33 +1014,33 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6861915346</t>
+          <t>6461842318</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>12-07-2005</t>
+          <t>10-08-2000</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CHANTY.CARMONA.C@GMAIL.COM</t>
+          <t>RACIEL1410V@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 05:09:55</t>
+          <t>02-03-2026 07:54:12</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1042,17 +1050,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 05:11:13</t>
+          <t>02-03-2026 07:56:28</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1063,7 +1071,7 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1074,14 +1082,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26160522772570002807</t>
+          <t>26160522783170002825</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1098,12 +1106,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347430</t>
+          <t>347485</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89595</t>
+          <t>89650</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1113,17 +1121,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RACIEL ANTONIO</t>
+          <t>ADRIANA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>DELGADO</t>
+          <t>ACEVEDO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1133,67 +1141,79 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6461842318</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>6864222249</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>PABLO QUIROGA ESCAMILLA 2325</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>10-08-2000</t>
+          <t>16-03-2007</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>RACIEL1410V@GMAIL.COM</t>
+          <t>GONZALEZACEVEDOADRIANA808@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 07:54:12</t>
+          <t>02-03-2026 10:24:46</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 07:56:28</t>
+          <t>04-03-2026 08:58:08</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:57:30</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1201,14 +1221,22 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26160522783170002825</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>26160522876670003012</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>MARIO ALBERTO GARCIA CERON</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1225,12 +1253,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347502</t>
+          <t>347456</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89667</t>
+          <t>89621</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1240,17 +1268,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>NAIDELIN ISABELA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TAMAYO</t>
+          <t xml:space="preserve">CURIEL </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BURGOS</t>
+          <t xml:space="preserve">GUERRERO </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1260,47 +1288,43 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6862727241</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>ISLA DEL PACIFICO 2158</t>
-        </is>
-      </c>
+          <t>6865268187</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>04-07-1986</t>
+          <t>02-11-2008</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CHAPOGABO@GMAIL.COM</t>
+          <t>ISABELLANYN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 11:16:32</t>
+          <t>02-03-2026 08:50:02</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1310,29 +1334,21 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 11:20:43</t>
+          <t>04-03-2026 09:15:26</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>02-03-2026 11:19:51</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1340,11 +1356,19 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26160522788980002846</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>26160522877070003016</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>MARIO ALBERTO GARCIA CERON</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>549</t>
@@ -1364,12 +1388,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347865</t>
+          <t>347502</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90030</t>
+          <t>89667</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1379,17 +1403,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CACHO</t>
+          <t>TAMAYO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>BURGOS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1399,32 +1423,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6862677979</t>
+          <t>6862727241</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>INDEOENDENCIA 1</t>
+          <t>ISLA DEL PACIFICO 2158</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>27-06-2004</t>
+          <t>04-07-1986</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CACHOVALERIA09@GMAIL.COM</t>
+          <t>CHAPOGABO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 19:22:12</t>
+          <t>02-03-2026 11:16:32</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1449,7 +1473,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 19:26:57</t>
+          <t>02-03-2026 11:20:43</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1459,7 +1483,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>02-03-2026 19:25:56</t>
+          <t>02-03-2026 11:19:51</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1469,7 +1493,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1479,7 +1503,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26160522816630002904</t>
+          <t>26160522788980002846</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1491,12 +1515,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -1618,12 +1642,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1781,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348293</t>
+          <t>347865</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90458</t>
+          <t>90030</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1772,17 +1796,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AMAYA NAOMI</t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>CACHO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GALAVIZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1792,10 +1816,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3318420233</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>6862677979</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>INDEOENDENCIA 1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1803,32 +1831,32 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>04-01-2010</t>
+          <t>27-06-2004</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>NAOMI_MGALAVIZ@ICLOUD.COM</t>
+          <t>CACHOVALERIA09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 21:18:34</t>
+          <t>02-03-2026 19:22:12</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1838,21 +1866,29 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-03-2026 22:02:31</t>
+          <t>02-03-2026 19:26:57</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:25:56</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1860,7 +1896,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26160522862510003002</t>
+          <t>26160522816630002904</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1872,10 +1908,1169 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>Sergio  Cordova Hernandez</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>347765</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>89930</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EMILIANO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MURILLO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6862234584</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>27-04-2002</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>EMILIANOMURILLO0204@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:48:06</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:54:58</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>26160522892240003037</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Recepcion Independencia Mexicali</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Sergio  Cordova Hernandez</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>348571</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>90736</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>RAMON</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>VALDEZ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DAFOLLA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6862585270</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>31-08-2001</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>RAMON.DAFOLLA3108@GMAIL.OCM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:35:05</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:36:18</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>26160522894860003045</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Sergio  Cordova Hernandez</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>347397</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>89562</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>USTOA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6863319761</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>30-04-2009</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>SESAUS20@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>02-03-2026 06:00:40</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>02-03-2026 06:02:19</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>26160522774100002814</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>347501</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>89666</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SILVIA LORENA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENRIQUEZ </t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6865892371</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>08-10-1983</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>SI.ALVAREZ08@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>02-03-2026 11:10:21</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:43:37</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>26160522791620002850</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>348679</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>90844</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARICELA </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>BADILLA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6862555010</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>19-10-1969</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>MARIANELA691020@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>05-03-2026 12:13:29</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>anualidad LE 300</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>ANUALIDAD + MES REGALO $5,999</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>461.46</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>05-03-2026 12:15:24</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>05-04-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26160522914430003085</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>5999</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>347966</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>90131</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANDRES </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORTIZ </t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLORES </t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6531210593</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>30-11-1992</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>AMDRES_Z23@LIVE.COM.MX</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:29:59</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>05-03-2026 08:26:00</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26160522910710003079</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>MARIO ALBERTO GARCIA CERON</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>348293</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>90458</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AMAYA NAOMI</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>MALDONADO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>GALAVIZ</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3318420233</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>04-01-2010</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NAOMI_MGALAVIZ@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>03-03-2026 21:18:34</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>03-03-2026 22:02:31</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26160522862510003002</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>348815</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>90980</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>XIMENA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SOZA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6381095092</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>09-07-2003</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>XIMESOZA03@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>05-03-2026 20:33:06</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>05-03-2026 20:36:29</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26160522931570003119</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>348816</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>90981</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BLANCA PAOLA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ELIZONDO</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>LIZARRAGA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6383865795</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>17-09-2003</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>ELIZONDOPAOLA76@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>05-03-2026 20:37:57</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>05-03-2026 20:39:46</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26160522931690003120</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,7 +664,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -713,12 +713,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347472</t>
+          <t>347397</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89637</t>
+          <t>89562</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDA CECILIA </t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t>USTOA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -748,47 +748,43 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6863944624</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>DEL AMATE 3138</t>
-        </is>
-      </c>
+          <t>6863319761</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16-06-2002</t>
+          <t>30-04-2009</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>A1176937@UABC.EDU.MX</t>
+          <t>SESAUS20@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 09:49:48</t>
+          <t>02-03-2026 06:00:40</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -798,29 +794,21 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 09:57:22</t>
+          <t>02-03-2026 06:02:19</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>02-03-2026 09:56:34</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -828,7 +816,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26160522786810002837</t>
+          <t>26160522774100002814</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -852,12 +840,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347382</t>
+          <t>347456</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89547</t>
+          <t>89621</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +855,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CHANTAL POLET</t>
+          <t>NAIDELIN ISABELA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARMONA </t>
+          <t xml:space="preserve">CURIEL </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t xml:space="preserve">GUERRERO </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,7 +875,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6861915346</t>
+          <t>6865268187</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -898,17 +886,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>12-07-2005</t>
+          <t>02-11-2008</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CHANTY.CARMONA.C@GMAIL.COM</t>
+          <t>ISABELLANYN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 05:09:55</t>
+          <t>02-03-2026 08:50:02</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -933,12 +921,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 05:11:13</t>
+          <t>04-03-2026 09:15:26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -955,11 +943,19 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26160522772570002807</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26160522877070003016</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>MARIO ALBERTO GARCIA CERON</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>549</t>
@@ -979,12 +975,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347430</t>
+          <t>347382</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89595</t>
+          <t>89547</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -994,17 +990,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RACIEL ANTONIO</t>
+          <t>CHANTAL POLET</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t xml:space="preserve">CARMONA </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DELGADO</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1014,33 +1010,33 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6461842318</t>
+          <t>6861915346</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>10-08-2000</t>
+          <t>12-07-2005</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>RACIEL1410V@GMAIL.COM</t>
+          <t>CHANTY.CARMONA.C@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 07:54:12</t>
+          <t>02-03-2026 05:09:55</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1050,28 +1046,28 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 07:56:28</t>
+          <t>02-03-2026 05:11:13</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1082,14 +1078,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26160522783170002825</t>
+          <t>26160522772570002807</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1106,12 +1102,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347485</t>
+          <t>347430</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89650</t>
+          <t>89595</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1121,17 +1117,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ADRIANA</t>
+          <t>RACIEL ANTONIO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>VELAZQUEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ACEVEDO</t>
+          <t>DELGADO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1141,79 +1137,67 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6864222249</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>PABLO QUIROGA ESCAMILLA 2325</t>
-        </is>
-      </c>
+          <t>6461842318</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>16-03-2007</t>
+          <t>10-08-2000</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>GONZALEZACEVEDOADRIANA808@GMAIL.COM</t>
+          <t>RACIEL1410V@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 10:24:46</t>
+          <t>02-03-2026 07:54:12</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>04-03-2026 08:58:08</t>
+          <t>02-03-2026 07:56:28</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>04-03-2026 08:57:30</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1221,22 +1205,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26160522876670003012</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>MARIO ALBERTO GARCIA CERON</t>
-        </is>
-      </c>
+          <t>26160522783170002825</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1253,12 +1229,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347456</t>
+          <t>347485</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89621</t>
+          <t>89650</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1268,17 +1244,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NAIDELIN ISABELA</t>
+          <t>ADRIANA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CURIEL </t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUERRERO </t>
+          <t>ACEVEDO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1288,10 +1264,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6865268187</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>6864222249</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>PABLO QUIROGA ESCAMILLA 2325</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1299,32 +1279,32 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>02-11-2008</t>
+          <t>16-03-2007</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ISABELLANYN@GMAIL.COM</t>
+          <t>GONZALEZACEVEDOADRIANA808@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 08:50:02</t>
+          <t>02-03-2026 10:24:46</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1334,21 +1314,29 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>04-03-2026 09:15:26</t>
+          <t>04-03-2026 08:58:08</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:57:30</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1356,7 +1344,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26160522877070003016</t>
+          <t>26160522876670003012</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1388,12 +1376,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347502</t>
+          <t>347501</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89667</t>
+          <t>89666</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1403,17 +1391,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>SILVIA LORENA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TAMAYO</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BURGOS</t>
+          <t xml:space="preserve">ENRIQUEZ </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1423,79 +1411,67 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6862727241</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>ISLA DEL PACIFICO 2158</t>
-        </is>
-      </c>
+          <t>6865892371</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>04-07-1986</t>
+          <t>08-10-1983</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CHAPOGABO@GMAIL.COM</t>
+          <t>SI.ALVAREZ08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 11:16:32</t>
+          <t>02-03-2026 11:10:21</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 11:20:43</t>
+          <t>02-03-2026 12:43:37</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>02-03-2026 11:19:51</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1503,14 +1479,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26160522788980002846</t>
+          <t>26160522791620002850</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1527,12 +1503,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>348295</t>
+          <t>347765</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90460</t>
+          <t>89930</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1542,17 +1518,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AYEAN</t>
+          <t>EMILIANO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>MURILLO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GALAVIZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1562,7 +1538,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3333878465</t>
+          <t>6862234584</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1573,22 +1549,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>13-06-2012</t>
+          <t>27-04-2002</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>NAOMI_MGALAVIZ@HOTMAIL.COM</t>
+          <t>EMILIANOMURILLO0204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>03-03-2026 21:23:20</t>
+          <t>02-03-2026 17:48:06</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1598,17 +1574,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-03-2026 22:05:53</t>
+          <t>04-03-2026 17:54:58</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1630,19 +1606,27 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26160522862540003003</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>26160522892240003037</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Recepcion Independencia Mexicali</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1654,12 +1638,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>348072</t>
+          <t>347502</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90237</t>
+          <t>89667</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1669,17 +1653,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JOEL</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>TAMAYO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>BURGOS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1689,10 +1673,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6863309454</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>6862727241</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ISLA DEL PACIFICO 2158</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1700,32 +1688,32 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>01-04-1974</t>
+          <t>04-07-1986</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>JOELF3086@GMAIL.COM</t>
+          <t>CHAPOGABO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>03-03-2026 14:59:50</t>
+          <t>02-03-2026 11:16:32</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1735,21 +1723,29 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-03-2026 15:01:24</t>
+          <t>02-03-2026 11:20:43</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>02-03-2026 11:19:51</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1757,7 +1753,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26160522842820002952</t>
+          <t>26160522788980002846</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1769,12 +1765,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1867,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1920,12 +1916,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347765</t>
+          <t>348072</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89930</t>
+          <t>90237</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1935,17 +1931,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EMILIANO</t>
+          <t>JOEL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MURILLO</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1955,7 +1951,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6862234584</t>
+          <t>6863309454</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1966,22 +1962,22 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>27-04-2002</t>
+          <t>01-04-1974</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>EMILIANOMURILLO0204@GMAIL.COM</t>
+          <t>JOELF3086@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 17:48:06</t>
+          <t>03-03-2026 14:59:50</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1991,22 +1987,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>04-03-2026 17:54:58</t>
+          <t>03-03-2026 15:01:24</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2023,27 +2019,19 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26160522892240003037</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Recepcion Independencia Mexicali</t>
-        </is>
-      </c>
+          <t>26160522842820002952</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2055,12 +2043,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>348571</t>
+          <t>347472</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90736</t>
+          <t>89637</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2070,17 +2058,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>RAMON</t>
+          <t xml:space="preserve">FERNANDA CECILIA </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DAFOLLA</t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2090,28 +2078,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6862585270</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>6863944624</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>DEL AMATE 3138</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>31-08-2001</t>
+          <t>16-06-2002</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>RAMON.DAFOLLA3108@GMAIL.OCM</t>
+          <t>A1176937@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>04-03-2026 18:35:05</t>
+          <t>02-03-2026 09:49:48</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2121,36 +2113,44 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>04-03-2026 18:36:18</t>
+          <t>02-03-2026 09:57:22</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>02-03-2026 09:56:34</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2158,36 +2158,36 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26160522894860003045</t>
+          <t>26160522786810002837</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347397</t>
+          <t>348293</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89562</t>
+          <t>90458</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2197,17 +2197,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>AMAYA NAOMI</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USTOA</t>
+          <t>GALAVIZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2217,28 +2217,28 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6863319761</t>
+          <t>3318420233</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>30-04-2009</t>
+          <t>04-01-2010</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>SESAUS20@GMAIL.COM</t>
+          <t>NAOMI_MGALAVIZ@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 06:00:40</t>
+          <t>03-03-2026 21:18:34</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 06:02:19</t>
+          <t>03-03-2026 22:02:31</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26160522774100002814</t>
+          <t>26160522862510003002</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2297,24 +2297,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347501</t>
+          <t>348295</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89666</t>
+          <t>90460</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2324,17 +2324,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SILVIA LORENA</t>
+          <t>AYEAN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENRIQUEZ </t>
+          <t>GALAVIZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2344,33 +2344,33 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6865892371</t>
+          <t>3333878465</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>08-10-1983</t>
+          <t>13-06-2012</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>SI.ALVAREZ08@GMAIL.COM</t>
+          <t>NAOMI_MGALAVIZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 11:10:21</t>
+          <t>03-03-2026 21:23:20</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2380,17 +2380,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 12:43:37</t>
+          <t>03-03-2026 22:05:53</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2401,7 +2401,7 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2412,36 +2412,36 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26160522791620002850</t>
+          <t>26160522862540003003</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348679</t>
+          <t>347966</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90844</t>
+          <t>90131</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2451,17 +2451,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARICELA </t>
+          <t xml:space="preserve">ANDRES </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">ORTIZ </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>BADILLA</t>
+          <t xml:space="preserve">FLORES </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6862555010</t>
+          <t>6531210593</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2482,22 +2482,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19-10-1969</t>
+          <t>30-11-1992</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>MARIANELA691020@HOTMAIL.COM</t>
+          <t>AMDRES_Z23@LIVE.COM.MX</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>05-03-2026 12:13:29</t>
+          <t>03-03-2026 08:29:59</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>anualidad LE 300</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2507,22 +2507,22 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>ANUALIDAD + MES REGALO $5,999</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>461.46</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>05-03-2026 12:15:24</t>
+          <t>05-03-2026 08:26:00</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>05-04-2027 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2539,14 +2539,22 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26160522914430003085</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+          <t>26160522910710003079</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>MARIO ALBERTO GARCIA CERON</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2563,12 +2571,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347966</t>
+          <t>349163</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90131</t>
+          <t>91328</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2578,17 +2586,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDRES </t>
+          <t>ADREANA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORTIZ </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t>TAMAYO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2598,33 +2606,33 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6531210593</t>
+          <t>6861386979</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>30-11-1992</t>
+          <t>29-05-1969</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>AMDRES_Z23@LIVE.COM.MX</t>
+          <t>ANDREA_FT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>03-03-2026 08:29:59</t>
+          <t>07-03-2026 14:56:51</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2634,22 +2642,22 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>05-03-2026 08:26:00</t>
+          <t>07-03-2026 14:58:35</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>06-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2666,22 +2674,14 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26160522910710003079</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>MARIO ALBERTO GARCIA CERON</t>
-        </is>
-      </c>
+          <t>26160522976100003178</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2698,12 +2698,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>348293</t>
+          <t>348816</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90458</t>
+          <t>90981</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AMAYA NAOMI</t>
+          <t>BLANCA PAOLA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>ELIZONDO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GALAVIZ</t>
+          <t>LIZARRAGA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3318420233</t>
+          <t>6383865795</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2744,17 +2744,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>04-01-2010</t>
+          <t>17-09-2003</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>NAOMI_MGALAVIZ@ICLOUD.COM</t>
+          <t>ELIZONDOPAOLA76@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-03-2026 21:18:34</t>
+          <t>05-03-2026 20:37:57</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-03-2026 22:02:31</t>
+          <t>05-03-2026 20:39:46</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26160522862510003002</t>
+          <t>26160522931690003120</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2813,24 +2813,24 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>348815</t>
+          <t>348679</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90980</t>
+          <t>90844</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2840,17 +2840,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>XIMENA</t>
+          <t xml:space="preserve">MARICELA </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SOZA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>BADILLA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2860,33 +2860,33 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6381095092</t>
+          <t>6862555010</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>09-07-2003</t>
+          <t>19-10-1969</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>XIMESOZA03@OUTLOOK.COM</t>
+          <t>MARIANELA691020@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>05-03-2026 20:33:06</t>
+          <t>05-03-2026 12:13:29</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>anualidad LE 300</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2896,28 +2896,28 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>ANUALIDAD + MES REGALO $5,999</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>461.46</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>05-03-2026 20:36:29</t>
+          <t>05-03-2026 12:15:24</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>04-04-2027 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2928,14 +2928,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26160522931570003119</t>
+          <t>26160522914430003085</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2952,12 +2952,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>348816</t>
+          <t>348815</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90981</t>
+          <t>90980</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2967,17 +2967,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BLANCA PAOLA</t>
+          <t>XIMENA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ELIZONDO</t>
+          <t>SOZA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LIZARRAGA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6383865795</t>
+          <t>6381095092</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2998,17 +2998,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>17-09-2003</t>
+          <t>09-07-2003</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ELIZONDOPAOLA76@GMAIL.COM</t>
+          <t>XIMESOZA03@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>05-03-2026 20:37:57</t>
+          <t>05-03-2026 20:33:06</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>05-03-2026 20:39:46</t>
+          <t>05-03-2026 20:36:29</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26160522931690003120</t>
+          <t>26160522931570003119</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3067,12 +3067,139 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>348571</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>90736</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RAMON</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>VALDEZ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>DAFOLLA</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6862585270</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>31-08-2001</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>RAMON.DAFOLLA3108@GMAIL.OCM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:35:05</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:36:18</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26160522894860003045</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Sergio  Cordova Hernandez</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>324401</t>
+          <t>74710</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21340</t>
+          <t>72526</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LUCERO</t>
+          <t>SANDRA NAYELLY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t xml:space="preserve">SALAZAR </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,10 +613,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6862415611</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>6864404721</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>JALSICO CONTRERAS 244</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -624,32 +628,32 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>07-12-1991</t>
+          <t>25-08-1993</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>COSMEGESPINOZA@GMAIL.COM</t>
+          <t>NAYELLYSALAZARGARCIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>19-11-2025 14:28:33</t>
+          <t>22-02-2022 19:29:14</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -659,21 +663,29 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>04-03-2026 09:14:24</t>
+          <t>18-03-2026 14:55:13</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>18-03-2026 14:53:30</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -681,19 +693,11 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26160522877040003015</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>MARIO ALBERTO GARCIA CERON</t>
-        </is>
-      </c>
+          <t>26160523293730003751</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
           <t>549</t>
@@ -701,24 +705,24 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347397</t>
+          <t>328336</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89562</t>
+          <t>25273</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>SILVIA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>USTOA</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -748,67 +752,79 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6863319761</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>6861486520</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INDEPENDENCIA </t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>30-04-2009</t>
+          <t>27-06-1986</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>SESAUS20@GMAIL.COM</t>
+          <t>SILVIARODRIGUEZRO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 06:00:40</t>
+          <t>10-12-2025 11:40:41</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 06:02:19</t>
+          <t>17-03-2026 15:17:11</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>17-03-2026 15:16:33</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -816,36 +832,36 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26160522774100002814</t>
+          <t>26160523255720003663</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347456</t>
+          <t>315882</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89621</t>
+          <t>13381</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,17 +871,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NAIDELIN ISABELA</t>
+          <t>AYLIN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CURIEL </t>
+          <t>CANO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUERRERO </t>
+          <t>FAJARDO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -875,7 +891,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6865268187</t>
+          <t>6865104831</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -886,17 +902,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>02-11-2008</t>
+          <t>27-10-2002</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ISABELLANYN@GMAIL.COM</t>
+          <t>AYLIN_CANO27@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 08:50:02</t>
+          <t>25-09-2025 19:02:29</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -921,12 +937,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>04-03-2026 09:15:26</t>
+          <t>16-03-2026 15:57:00</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>16-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -943,7 +959,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26160522877070003016</t>
+          <t>26160523226070003609</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -953,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>MARIO ALBERTO GARCIA CERON</t>
+          <t>ANDREA PATRICIA ACUÑA PERALTA</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -963,24 +979,24 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347382</t>
+          <t>324401</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89547</t>
+          <t>21340</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,17 +1006,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CHANTAL POLET</t>
+          <t>LUCERO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARMONA </t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1010,7 +1026,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6861915346</t>
+          <t>6862415611</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,17 +1037,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>12-07-2005</t>
+          <t>07-12-1991</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CHANTY.CARMONA.C@GMAIL.COM</t>
+          <t>COSMEGESPINOZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 05:09:55</t>
+          <t>19-11-2025 14:28:33</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1056,12 +1072,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 05:11:13</t>
+          <t>04-03-2026 09:14:24</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1078,11 +1094,19 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26160522772570002807</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>26160522877040003015</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>MARIO ALBERTO GARCIA CERON</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>549</t>
@@ -1090,24 +1114,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347430</t>
+          <t>341072</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89595</t>
+          <t>18890</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1117,17 +1141,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RACIEL ANTONIO</t>
+          <t xml:space="preserve">DANIEL </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>DELGADO</t>
+          <t>INZUNZA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1137,7 +1161,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6461842318</t>
+          <t>6862111905</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,17 +1172,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>10-08-2000</t>
+          <t>08-04-2010</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>RACIEL1410V@GMAIL.COM</t>
+          <t>LENIADTERRI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 07:54:12</t>
+          <t>04-02-2026 16:22:31</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1173,28 +1197,28 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>SALVATIERRA $399</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 07:56:28</t>
+          <t>11-03-2026 14:38:26</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>10-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1205,36 +1229,44 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26160522783170002825</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>26160523090380003379</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347485</t>
+          <t>333708</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89650</t>
+          <t>17575</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1244,17 +1276,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ADRIANA</t>
+          <t xml:space="preserve">MARIA CRISTINA </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ACEVEDO</t>
+          <t>AVILEZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1264,14 +1296,10 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6864222249</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>PABLO QUIROGA ESCAMILLA 2325</t>
-        </is>
-      </c>
+          <t>6862835443</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1279,32 +1307,32 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>16-03-2007</t>
+          <t>09-10-1958</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>GONZALEZACEVEDOADRIANA808@GMAIL.COM</t>
+          <t>ASDFSAD@GSADFGD.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 10:24:46</t>
+          <t>12-01-2026 08:36:04</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1314,29 +1342,21 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>04-03-2026 08:58:08</t>
+          <t>17-03-2026 08:21:29</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>04-03-2026 08:57:30</t>
-        </is>
-      </c>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1344,19 +1364,11 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26160522876670003012</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>MARIO ALBERTO GARCIA CERON</t>
-        </is>
-      </c>
+          <t>26160523246610003650</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
           <t>549</t>
@@ -1376,12 +1388,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347501</t>
+          <t>345256</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89666</t>
+          <t>87421</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1391,17 +1403,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SILVIA LORENA</t>
+          <t>DANIELA SARAI</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENRIQUEZ </t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1411,7 +1423,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6865892371</t>
+          <t>6143686988</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,22 +1434,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>08-10-1983</t>
+          <t>13-09-1992</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>SI.ALVAREZ08@GMAIL.COM</t>
+          <t>CHDH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 11:10:21</t>
+          <t>20-02-2026 11:31:05</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1447,22 +1459,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 12:43:37</t>
+          <t>11-03-2026 07:15:33</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>10-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1479,14 +1491,22 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26160522791620002850</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+          <t>26200523082080003204</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1503,12 +1523,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347765</t>
+          <t>347456</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89930</t>
+          <t>89621</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1518,17 +1538,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EMILIANO</t>
+          <t>NAIDELIN ISABELA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MURILLO</t>
+          <t xml:space="preserve">CURIEL </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t xml:space="preserve">GUERRERO </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1538,33 +1558,33 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6862234584</t>
+          <t>6865268187</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>27-04-2002</t>
+          <t>02-11-2008</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>EMILIANOMURILLO0204@GMAIL.COM</t>
+          <t>ISABELLANYN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 17:48:06</t>
+          <t>02-03-2026 08:50:02</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1574,17 +1594,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>04-03-2026 17:54:58</t>
+          <t>04-03-2026 09:15:26</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1595,7 +1615,7 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1606,7 +1626,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26160522892240003037</t>
+          <t>26160522877070003016</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1616,17 +1636,17 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Recepcion Independencia Mexicali</t>
+          <t>MARIO ALBERTO GARCIA CERON</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1638,12 +1658,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347502</t>
+          <t>347397</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89667</t>
+          <t>89562</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1653,17 +1673,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TAMAYO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BURGOS</t>
+          <t>USTOA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1673,14 +1693,10 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6862727241</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>ISLA DEL PACIFICO 2158</t>
-        </is>
-      </c>
+          <t>6863319761</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1688,32 +1704,32 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>04-07-1986</t>
+          <t>30-04-2009</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CHAPOGABO@GMAIL.COM</t>
+          <t>SESAUS20@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 11:16:32</t>
+          <t>02-03-2026 06:00:40</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1723,7 +1739,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 11:20:43</t>
+          <t>02-03-2026 06:02:19</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1731,21 +1747,13 @@
           <t>01-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>02-03-2026 11:19:51</t>
-        </is>
-      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1753,7 +1761,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26160522788980002846</t>
+          <t>26160522774100002814</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1765,24 +1773,24 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347865</t>
+          <t>347382</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90030</t>
+          <t>89547</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1792,17 +1800,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t>CHANTAL POLET</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CACHO</t>
+          <t xml:space="preserve">CARMONA </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1812,14 +1820,10 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6862677979</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>INDEOENDENCIA 1</t>
-        </is>
-      </c>
+          <t>6861915346</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1827,32 +1831,32 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>27-06-2004</t>
+          <t>12-07-2005</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CACHOVALERIA09@GMAIL.COM</t>
+          <t>CHANTY.CARMONA.C@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 19:22:12</t>
+          <t>02-03-2026 05:09:55</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1862,7 +1866,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 19:26:57</t>
+          <t>02-03-2026 05:11:13</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1870,21 +1874,13 @@
           <t>01-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>02-03-2026 19:25:56</t>
-        </is>
-      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1892,7 +1888,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26160522816630002904</t>
+          <t>26160522772570002807</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1904,7 +1900,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1916,12 +1912,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>348072</t>
+          <t>347430</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90237</t>
+          <t>89595</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1931,17 +1927,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JOEL</t>
+          <t>RACIEL ANTONIO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>VELAZQUEZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>DELGADO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1951,7 +1947,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6863309454</t>
+          <t>6461842318</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1962,22 +1958,22 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>01-04-1974</t>
+          <t>10-08-2000</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>JOELF3086@GMAIL.COM</t>
+          <t>RACIEL1410V@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>03-03-2026 14:59:50</t>
+          <t>02-03-2026 07:54:12</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1987,22 +1983,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-03-2026 15:01:24</t>
+          <t>02-03-2026 07:56:28</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2019,19 +2015,19 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26160522842820002952</t>
+          <t>26160522783170002825</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2043,12 +2039,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347472</t>
+          <t>347485</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89637</t>
+          <t>89650</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2058,17 +2054,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDA CECILIA </t>
+          <t>ADRIANA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t>ACEVEDO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2078,12 +2074,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6863944624</t>
+          <t>6864222249</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>DEL AMATE 3138</t>
+          <t>PABLO QUIROGA ESCAMILLA 2325</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2093,22 +2089,22 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>16-06-2002</t>
+          <t>16-03-2007</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>A1176937@UABC.EDU.MX</t>
+          <t>GONZALEZACEVEDOADRIANA808@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 09:49:48</t>
+          <t>02-03-2026 10:24:46</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2118,7 +2114,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2128,17 +2124,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 09:57:22</t>
+          <t>04-03-2026 08:58:08</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>02-03-2026 09:56:34</t>
+          <t>04-03-2026 08:57:30</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2158,11 +2154,19 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26160522786810002837</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>26160522876670003012</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>MARIO ALBERTO GARCIA CERON</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>549</t>
@@ -2170,24 +2174,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>348293</t>
+          <t>347501</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90458</t>
+          <t>89666</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2197,17 +2201,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AMAYA NAOMI</t>
+          <t>SILVIA LORENA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GALAVIZ</t>
+          <t xml:space="preserve">ENRIQUEZ </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2217,7 +2221,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3318420233</t>
+          <t>6865892371</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2228,22 +2232,22 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>04-01-2010</t>
+          <t>08-10-1983</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>NAOMI_MGALAVIZ@ICLOUD.COM</t>
+          <t>SI.ALVAREZ08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-03-2026 21:18:34</t>
+          <t>02-03-2026 11:10:21</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2253,28 +2257,28 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-03-2026 22:02:31</t>
+          <t>02-03-2026 12:43:37</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -2285,19 +2289,19 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26160522862510003002</t>
+          <t>26160522791620002850</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2309,12 +2313,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>348295</t>
+          <t>347675</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90460</t>
+          <t>89840</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2324,17 +2328,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AYEAN</t>
+          <t>PAMELA ROCIO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>CUREÑO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GALAVIZ</t>
+          <t>VELAZQUEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2344,67 +2348,79 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3333878465</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>6862166891</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA 1</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>13-06-2012</t>
+          <t>21-09-1982</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>NAOMI_MGALAVIZ@HOTMAIL.COM</t>
+          <t>PAMELACURENO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-03-2026 21:23:20</t>
+          <t>02-03-2026 16:29:24</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-03-2026 22:05:53</t>
+          <t>09-03-2026 18:45:23</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:44:38</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2412,19 +2428,23 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26160522862540003003</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
+          <t>26160523023960003240</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2436,12 +2456,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347966</t>
+          <t>347678</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90131</t>
+          <t>89843</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2451,17 +2471,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDRES </t>
+          <t>ISABELLA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORTIZ </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t>CUREÑO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2471,28 +2491,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6531210593</t>
+          <t>6862373744</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>30-11-1992</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>AMDRES_Z23@LIVE.COM.MX</t>
-        </is>
-      </c>
+          <t>21-12-2010</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>03-03-2026 08:29:59</t>
+          <t>02-03-2026 16:31:22</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2517,12 +2529,12 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>05-03-2026 08:26:00</t>
+          <t>09-03-2026 18:39:03</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2539,19 +2551,15 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26160522910710003079</t>
+          <t>26160523023380003239</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>MARIO ALBERTO GARCIA CERON</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
           <t>549</t>
@@ -2571,12 +2579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>349163</t>
+          <t>347502</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>91328</t>
+          <t>89667</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2586,17 +2594,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ADREANA</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>TAMAYO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TAMAYO</t>
+          <t>BURGOS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2606,67 +2614,79 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6861386979</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>6862727241</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ISLA DEL PACIFICO 2158</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>29-05-1969</t>
+          <t>04-07-1986</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ANDREA_FT@GMAIL.COM</t>
+          <t>CHAPOGABO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>07-03-2026 14:56:51</t>
+          <t>02-03-2026 11:16:32</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>07-03-2026 14:58:35</t>
+          <t>02-03-2026 11:20:43</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>06-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>02-03-2026 11:19:51</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2674,36 +2694,36 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26160522976100003178</t>
+          <t>26160522788980002846</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>348816</t>
+          <t>347765</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90981</t>
+          <t>89930</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2713,17 +2733,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BLANCA PAOLA</t>
+          <t>EMILIANO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ELIZONDO</t>
+          <t>MURILLO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LIZARRAGA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2733,33 +2753,33 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6383865795</t>
+          <t>6862234584</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>17-09-2003</t>
+          <t>27-04-2002</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ELIZONDOPAOLA76@GMAIL.COM</t>
+          <t>EMILIANOMURILLO0204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>05-03-2026 20:37:57</t>
+          <t>02-03-2026 17:48:06</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2769,22 +2789,22 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>05-03-2026 20:39:46</t>
+          <t>04-03-2026 17:54:58</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2801,36 +2821,44 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26160522931690003120</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>26160522892240003037</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Recepcion Independencia Mexicali</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>348679</t>
+          <t>347865</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90844</t>
+          <t>90030</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2840,17 +2868,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARICELA </t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>CACHO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BADILLA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2860,67 +2888,79 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6862555010</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>6862677979</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>INDEOENDENCIA 1</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>19-10-1969</t>
+          <t>27-06-2004</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>MARIANELA691020@HOTMAIL.COM</t>
+          <t>CACHOVALERIA09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>05-03-2026 12:13:29</t>
+          <t>02-03-2026 19:22:12</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>anualidad LE 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>ANUALIDAD + MES REGALO $5,999</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>461.46</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>05-03-2026 12:15:24</t>
+          <t>02-03-2026 19:26:57</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>04-04-2027 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:25:56</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2928,36 +2968,36 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26160522914430003085</t>
+          <t>26160522816630002904</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>348815</t>
+          <t>347472</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90980</t>
+          <t>89637</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2967,17 +3007,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>XIMENA</t>
+          <t xml:space="preserve">FERNANDA CECILIA </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SOZA</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2987,10 +3027,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6381095092</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>6863944624</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>DEL AMATE 3138</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2998,32 +3042,32 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>09-07-2003</t>
+          <t>16-06-2002</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>XIMESOZA03@OUTLOOK.COM</t>
+          <t>A1176937@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>05-03-2026 20:33:06</t>
+          <t>02-03-2026 09:49:48</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -3033,21 +3077,29 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>05-03-2026 20:36:29</t>
+          <t>02-03-2026 09:57:22</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>02-03-2026 09:56:34</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3055,7 +3107,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26160522931570003119</t>
+          <t>26160522786810002837</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3067,7 +3119,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3079,12 +3131,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>348571</t>
+          <t>348072</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90736</t>
+          <t>90237</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3094,17 +3146,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>RAMON</t>
+          <t>JOEL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>DAFOLLA</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3114,7 +3166,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6862585270</t>
+          <t>6863309454</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3125,22 +3177,22 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>31-08-2001</t>
+          <t>01-04-1974</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>RAMON.DAFOLLA3108@GMAIL.OCM</t>
+          <t>JOELF3086@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>04-03-2026 18:35:05</t>
+          <t>03-03-2026 14:59:50</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -3150,28 +3202,28 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>04-03-2026 18:36:18</t>
+          <t>03-03-2026 15:01:24</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
@@ -3182,24 +3234,4534 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26160522894860003045</t>
+          <t>26160522842820002952</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>347932</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>90097</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LOURDES MAGADALENA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORDUÑO </t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GALVEZ </t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6869454842</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ALTALOMA 2514</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>22-07-1972</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>LOURDES.ORDUNO@NOTARIA10MEXICALI.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>03-03-2026 05:12:21</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>09-03-2026 05:11:29</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>09-03-2026 05:10:24</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26160522989500003180</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>auxiliar independencia mexicali</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Julio Alonso Lerma Sanchez</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>347966</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>90131</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANDRES </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORTIZ </t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLORES </t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6531210593</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>30-11-1992</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>AMDRES_Z23@LIVE.COM.MX</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:29:59</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>05-03-2026 08:26:00</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26160522910710003079</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>MARIO ALBERTO GARCIA CERON</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Ricardo Alexis Alvarez Camarena</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>348295</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>90460</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AYEAN</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MALDONADO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>GALAVIZ</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>3333878465</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>13-06-2012</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NAOMI_MGALAVIZ@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>03-03-2026 21:23:20</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>03-03-2026 22:05:53</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26160522862540003003</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>348293</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>90458</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AMAYA NAOMI</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MALDONADO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>GALAVIZ</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>3318420233</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>04-01-2010</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NAOMI_MGALAVIZ@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>03-03-2026 21:18:34</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>03-03-2026 22:02:31</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26160522862510003002</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>348679</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>90844</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARICELA </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>BADILLA</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6862555010</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>19-10-1969</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>MARIANELA691020@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>05-03-2026 12:13:29</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>anualidad LE 300</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>ANUALIDAD + MES REGALO $5,999</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>461.46</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>05-03-2026 12:15:24</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>04-04-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26160522914430003085</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>5999</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Ricardo Alexis Alvarez Camarena</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>348571</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>90736</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>RAMON</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>VALDEZ</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DAFOLLA</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6862585270</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>31-08-2001</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>RAMON.DAFOLLA3108@GMAIL.OCM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:35:05</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
           <t>899</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:36:18</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26160522894860003045</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
         <is>
           <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>348815</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>90980</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>XIMENA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SOZA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6381095092</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>09-07-2003</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>XIMESOZA03@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>05-03-2026 20:33:06</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>05-03-2026 20:36:29</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26160522931570003119</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>348848</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>91013</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>GUSTAVO ALBERTO</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>CRUZ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6866077308</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>15-12-1985</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>LIC_GUSTAVOTORRES@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>06-03-2026 08:06:57</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>12-03-2026 08:11:38</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26160523117280003449</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>ANDREA PATRICIA ACUÑA PERALTA</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Ricardo Alexis Alvarez Camarena</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>349163</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>91328</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ADREANA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>FLORES</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>TAMAYO</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6861386979</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>29-05-1969</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>ANDREA_FT@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>07-03-2026 14:56:51</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>07-03-2026 14:58:35</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>06-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26160522976100003178</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Ricardo Alexis Alvarez Camarena</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>349018</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>91183</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ELODIA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>COLLADO</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6864604705</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA 1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>03-07-1976</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>APAOLAVZLA20@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>06-03-2026 18:09:34</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:53:05</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:52:11</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26160523010040003207</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>349290</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>91455</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>GRISELDA ANGELICA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>MARISCAL</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6861220141</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>VILLA DEL PASEO</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>05-03-1988</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>GRYZKK@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>09-03-2026 06:04:45</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>09-03-2026 06:08:12</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>09-03-2026 06:07:33</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26160522990700003183</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Ricardo Alexis Alvarez Camarena</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>349465</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>91630</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>JUAN ROBERTO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SAMANO</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CHAVEZ</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>6863231447</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA 14</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>12-08-1995</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>SAMANO.JROBERTO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:57:52</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>09-03-2026 15:01:57</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>09-03-2026 15:01:09</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26160523010370003208</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>348816</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>90981</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BLANCA PAOLA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ELIZONDO</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>LIZARRAGA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>6383865795</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>17-09-2003</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>ELIZONDOPAOLA76@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>05-03-2026 20:37:57</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>05-03-2026 20:39:46</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26160522931690003120</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Ricardo Alexis Alvarez Camarena</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>349397</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>91562</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADRIAN ARTURO </t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BONILLA </t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESPINOZA </t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6862131889</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>22-06-1997</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>ADRIANBONILLAXOCHI@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>09-03-2026 12:27:28</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>09-03-2026 12:29:28</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26160523005930003199</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Ricardo Alexis Alvarez Camarena</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>349560</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>91725</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ARLIN VICTORIA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>IBARRA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>6862921253</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>06-05-1982</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>ARLINIBARRA52@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:42:48</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:44:34</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26160523018890003225</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>349863</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>92028</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>MIA PAULETT</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>COLOSIO</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>6861946974</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>25-09-2009</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>MIA.COLOSIO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:54:21</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:56:18</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26160523053950003298</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>349437</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>91602</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SANDA LUZ</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AYON</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>TOLOSA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6863530093</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>19-11-1993</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>SANDRALUZAYON@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:11:00</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:12:13</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26160523008520003205</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>Sergio  Cordova Hernandez</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>350561</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>92725</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOISES </t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MENDOZA </t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MASCAREÑO </t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6677480860</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>01-03-1985</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>FIMSAVENTAS01@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>13-03-2026 11:58:24</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>13-03-2026 12:00:40</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26160523151040003520</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>349722</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>91887</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>RUBI</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>CEJA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ROMAN</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>7831110926</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA 1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>25-01-1991</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>BYBIROOMAN25@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>09-03-2026 20:41:55</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>09-03-2026 20:50:36</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>09-03-2026 20:49:21</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26160523032570003266</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Sergio  Cordova Hernandez</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>349957</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>92122</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LUISELLA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>BARRAGAN</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6862134760</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>11-11-2011</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>LBARRAGANE@EDU.MX</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>10-03-2026 18:36:43</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:16:06</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26160523232600003629</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>349868</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>92033</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ERICK</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>GOMEZ</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>LIRA</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>7226145244</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>08-05-2007</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>GOMEZLIRAEK@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>10-03-2026 15:11:36</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SALVATIERRA $399</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>10-03-2026 15:13:21</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26160523054450003299</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>349985</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>92150</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>JOSE SALVADOR</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>ALMARAZ</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>6863079015</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>26-05-2012</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>JOSE26RAMIREZ05@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:18:34</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>14-03-2026 12:43:19</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>13-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26160523183450003559</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Ricardo Alexis Alvarez Camarena</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>349869</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>92034</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>RENATO</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>TAFOLLA</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6862146814</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>04-07-2008</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>RENATOGARCIATAFOLLA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>10-03-2026 15:14:54</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SALVATIERRA $399</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>10-03-2026 15:16:57</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26160523054590003300</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>350304</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>92468</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANDRA ELIZABETH </t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BARRIENTOS </t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>TELLEZ</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6862164334</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>HACIENDA CIENEGA 3347</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>24-09-1987</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>SANDRA.BARRIENTOS@UABC.EDU.MX</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>12-03-2026 12:18:00</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>12-03-2026 12:27:43</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>12-03-2026 12:23:49</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26160523121310003453</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Ricardo Alexis Alvarez Camarena</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>350562</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>92726</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>KEVIN ADAN</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MENDOZA </t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEREZ </t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6677858027</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>18-10-2006</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>FIMSAVENTAS02@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>13-03-2026 12:04:23</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>13-03-2026 12:06:47</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26160523151170003521</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Ricardo Alexis Alvarez Camarena</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>350794</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>92958</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LOBNY GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>MUÑOZ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>MORALES</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>6633222685</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>01-01-2000</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>ANDERSONMUNOSLOB@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>14-03-2026 12:02:28</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:00:33</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>17-03-2026 16:58:49</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26110523260150005714</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Viridiana Ramirez</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>350563</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>92727</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>MOISES</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MENDOZA </t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6671315555</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>24-08-2003</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>M0SES.2203@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>13-03-2026 12:08:48</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>13-03-2026 12:10:24</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26160523151250003522</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Ricardo Alexis Alvarez Camarena</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>351203</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>93367</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>WALTER</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>DURAZO</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>6861971149</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA 1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>14-01-1989</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>WALDURAZO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>16-03-2026 14:13:40</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>16-03-2026 14:18:29</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>16-03-2026 14:17:46</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26160523223290003600</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>351234</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>93398</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>CASTRO</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>ZUÑIGA</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>6861786900</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>MONTORGUEIL 498</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>03-09-1995</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>ALEJANDRACASTRO@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>16-03-2026 16:07:23</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>18-03-2026 17:27:32</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>18-03-2026 17:27:01</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26160523299170003761</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>350797</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>92961</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>JORGE ANTONIO</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>LORIA</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>9982448340</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CENTRO </t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>01-01-2000</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>JORGERONALDO2401@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>14-03-2026 12:06:17</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:04:33</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:03:42</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26110523260440005716</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Viridiana Ramirez</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>352146</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>94310</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DIEGO</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PEÑA</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>CAMACHO</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>6863477343</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>30-04-1996</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>DIEGO_CMACHO15@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>19-03-2026 17:10:16</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>19-03-2026 17:14:55</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26160523334270003831</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Sergio  Cordova Hernandez</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>351348</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>93512</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>JOSE ARMANDO</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>FUENTES</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ALCARAZ</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6863223039</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>20-03-2010</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>FUENTES.ARMANDO2010@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:39:13</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:41:02</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26160523233600003631</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>351448</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>93612</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>IVONE</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>VIRGEN</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>6862304998</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>15-04-1988</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>TIVONEGV@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>17-03-2026 10:02:45</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>19-03-2026 10:03:04</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>18-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>26160523324670003818</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>ANDREA PATRICIA ACUÑA PERALTA</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>352025</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>94189</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOEMI JAZMIN </t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORTIZ </t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>9092666191</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>PARALELO 28</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>14-01-2001</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>SANCHEZORTIZNOEMIJAZMIN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>19-03-2026 05:17:03</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>19-03-2026 05:32:36</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>19-03-2026 05:19:18</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>26160523313030003808</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__INDEPENDENCIA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>74710</t>
+          <t>247711</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>72526</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SANDRA NAYELLY</t>
+          <t xml:space="preserve">JEFTE </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALAZAR </t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">AGUIRRE </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,79 +613,63 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6864404721</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>JALSICO CONTRERAS 244</t>
-        </is>
-      </c>
+          <t>6865264288</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>25-08-1993</t>
+          <t>18-10-1988</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>NAYELLYSALAZARGARCIA@GMAIL.COM</t>
+          <t>JEFTE_GOMZALEZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>22-02-2022 19:29:14</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Inscripcion $150</t>
-        </is>
-      </c>
+          <t>22-07-2024 19:55:20</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18-03-2026 14:55:13</t>
+          <t>24-03-2026 11:04:08</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>18-03-2026 14:53:30</t>
-        </is>
-      </c>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -693,36 +677,36 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26160523293730003751</t>
+          <t>26160523463760004012</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>328336</t>
+          <t>74710</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25273</t>
+          <t>72526</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +716,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SILVIA</t>
+          <t>SANDRA NAYELLY</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">SALAZAR </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,12 +736,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6861486520</t>
+          <t>6864404721</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">INDEPENDENCIA </t>
+          <t>JALSICO CONTRERAS 244</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -767,52 +751,52 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>27-06-1986</t>
+          <t>25-08-1993</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>SILVIARODRIGUEZRO@HOTMAIL.COM</t>
+          <t>NAYELLYSALAZARGARCIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>10-12-2025 11:40:41</t>
+          <t>22-02-2022 19:29:14</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>17-03-2026 15:17:11</t>
+          <t>18-03-2026 14:55:13</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
+          <t>17-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>17-03-2026 15:16:33</t>
+          <t>18-03-2026 14:53:30</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -832,14 +816,14 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26160523255720003663</t>
+          <t>26160523293730003751</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -856,12 +840,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>315882</t>
+          <t>333708</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13381</t>
+          <t>17575</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,17 +855,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AYLIN</t>
+          <t xml:space="preserve">MARIA CRISTINA </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CANO</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FAJARDO</t>
+          <t>AVILEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -891,7 +875,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6865104831</t>
+          <t>6862835443</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -902,17 +886,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>27-10-2002</t>
+          <t>09-10-1958</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>AYLIN_CANO27@HOTMAIL.COM</t>
+          <t>ASDFSAD@GSADFGD.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>25-09-2025 19:02:29</t>
+          <t>12-01-2026 08:36:04</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -937,7 +921,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>16-03-2026 15:57:00</t>
+          <t>17-03-2026 08:21:29</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -959,19 +943,11 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26160523226070003609</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>ANDREA PATRICIA ACUÑA PERALTA</t>
-        </is>
-      </c>
+          <t>26160523246610003650</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>549</t>
@@ -979,7 +955,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -991,12 +967,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>324401</t>
+          <t>247715</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21340</t>
+          <t>45219</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1006,17 +982,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LUCERO</t>
+          <t xml:space="preserve">PALOMA ANGELINA </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t xml:space="preserve">CORRALES </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t xml:space="preserve">ZAZUETA </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1026,10 +1002,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6862415611</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>6861618766</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>JOSE JOAQUIN FERNANDEZ DE LIZARDI 1440</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1037,56 +1017,64 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>07-12-1991</t>
+          <t>17-12-1987</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>COSMEGESPINOZA@GMAIL.COM</t>
+          <t>PALOMA_CORRALES@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>19-11-2025 14:28:33</t>
+          <t>22-07-2024 19:57:18</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>04-03-2026 09:14:24</t>
+          <t>24-03-2026 11:04:08</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>24-03-2026 11:03:03</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1094,32 +1082,24 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26160522877040003015</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>MARIO ALBERTO GARCIA CERON</t>
-        </is>
-      </c>
+          <t>26160523463760004012</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1241,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>333708</t>
+          <t>315882</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17575</t>
+          <t>13381</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1276,17 +1256,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA CRISTINA </t>
+          <t>AYLIN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>CANO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AVILEZ</t>
+          <t>FAJARDO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1296,7 +1276,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6862835443</t>
+          <t>6865104831</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1307,17 +1287,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>09-10-1958</t>
+          <t>27-10-2002</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ASDFSAD@GSADFGD.COM</t>
+          <t>AYLIN_CANO27@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12-01-2026 08:36:04</t>
+          <t>25-09-2025 19:02:29</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1342,7 +1322,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>17-03-2026 08:21:29</t>
+          <t>16-03-2026 15:57:00</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1364,11 +1344,19 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26160523246610003650</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>26160523226070003609</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>ANDREA PATRICIA ACUÑA PERALTA</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>549</t>
@@ -1376,24 +1364,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>345256</t>
+          <t>324401</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>87421</t>
+          <t>21340</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1403,17 +1391,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DANIELA SARAI</t>
+          <t>LUCERO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1423,7 +1411,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6143686988</t>
+          <t>6862415611</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1434,17 +1422,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>13-09-1992</t>
+          <t>07-12-1991</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CHDH@GMAIL.COM</t>
+          <t>COSMEGESPINOZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>20-02-2026 11:31:05</t>
+          <t>19-11-2025 14:28:33</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1469,12 +1457,12 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>11-03-2026 07:15:33</t>
+          <t>04-03-2026 09:14:24</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>10-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1491,17 +1479,17 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26200523082080003204</t>
+          <t>26160522877040003015</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+          <t>MARIO ALBERTO GARCIA CERON</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1511,24 +1499,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347456</t>
+          <t>328336</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89621</t>
+          <t>25273</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1538,17 +1526,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NAIDELIN ISABELA</t>
+          <t>SILVIA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CURIEL </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUERRERO </t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1558,10 +1546,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6865268187</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>6861486520</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INDEPENDENCIA </t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1569,56 +1561,64 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>02-11-2008</t>
+          <t>27-06-1986</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ISABELLANYN@GMAIL.COM</t>
+          <t>SILVIARODRIGUEZRO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 08:50:02</t>
+          <t>10-12-2025 11:40:41</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>04-03-2026 09:15:26</t>
+          <t>17-03-2026 15:17:11</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>17-03-2026 15:16:33</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1626,27 +1626,19 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26160522877070003016</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>MARIO ALBERTO GARCIA CERON</t>
-        </is>
-      </c>
+          <t>26160523255720003663</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1658,12 +1650,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347397</t>
+          <t>347382</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89562</t>
+          <t>89547</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1673,17 +1665,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>CHANTAL POLET</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">CARMONA </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USTOA</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1693,28 +1685,28 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6863319761</t>
+          <t>6861915346</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>30-04-2009</t>
+          <t>12-07-2005</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>SESAUS20@GMAIL.COM</t>
+          <t>CHANTY.CARMONA.C@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 06:00:40</t>
+          <t>02-03-2026 05:09:55</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1739,7 +1731,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 06:02:19</t>
+          <t>02-03-2026 05:11:13</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1750,7 +1742,7 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1761,7 +1753,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26160522774100002814</t>
+          <t>26160522772570002807</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1785,12 +1777,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347382</t>
+          <t>347430</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89547</t>
+          <t>89595</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1800,17 +1792,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CHANTAL POLET</t>
+          <t>RACIEL ANTONIO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARMONA </t>
+          <t>VELAZQUEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>DELGADO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1820,33 +1812,33 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6861915346</t>
+          <t>6461842318</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>12-07-2005</t>
+          <t>10-08-2000</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CHANTY.CARMONA.C@GMAIL.COM</t>
+          <t>RACIEL1410V@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 05:09:55</t>
+          <t>02-03-2026 07:54:12</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1856,17 +1848,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 05:11:13</t>
+          <t>02-03-2026 07:56:28</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1877,7 +1869,7 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1888,14 +1880,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26160522772570002807</t>
+          <t>26160522783170002825</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1912,12 +1904,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347430</t>
+          <t>347485</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89595</t>
+          <t>89650</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1927,17 +1919,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>RACIEL ANTONIO</t>
+          <t>ADRIANA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DELGADO</t>
+          <t>ACEVEDO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1947,67 +1939,79 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6461842318</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>6864222249</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PABLO QUIROGA ESCAMILLA 2325</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>10-08-2000</t>
+          <t>16-03-2007</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>RACIEL1410V@GMAIL.COM</t>
+          <t>GONZALEZACEVEDOADRIANA808@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 07:54:12</t>
+          <t>02-03-2026 10:24:46</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 07:56:28</t>
+          <t>04-03-2026 08:58:08</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:57:30</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2015,14 +2019,22 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26160522783170002825</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+          <t>26160522876670003012</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>MARIO ALBERTO GARCIA CERON</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2039,12 +2051,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347485</t>
+          <t>347397</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89650</t>
+          <t>89562</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2054,17 +2066,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ADRIANA</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ACEVEDO</t>
+          <t>USTOA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2074,47 +2086,43 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6864222249</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>PABLO QUIROGA ESCAMILLA 2325</t>
-        </is>
-      </c>
+          <t>6863319761</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>16-03-2007</t>
+          <t>30-04-2009</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>GONZALEZACEVEDOADRIANA808@GMAIL.COM</t>
+          <t>SESAUS20@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 10:24:46</t>
+          <t>02-03-2026 06:00:40</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2124,29 +2132,21 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>04-03-2026 08:58:08</t>
+          <t>02-03-2026 06:02:19</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>04-03-2026 08:57:30</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2154,19 +2154,11 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26160522876670003012</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>MARIO ALBERTO GARCIA CERON</t>
-        </is>
-      </c>
+          <t>26160522774100002814</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
           <t>549</t>
@@ -2313,12 +2305,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347675</t>
+          <t>345256</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89840</t>
+          <t>87421</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2328,17 +2320,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PAMELA ROCIO</t>
+          <t>DANIELA SARAI</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CUREÑO</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>VELAZQUEZ</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2348,14 +2340,10 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6862166891</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA 1</t>
-        </is>
-      </c>
+          <t>6143686988</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2363,64 +2351,56 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>21-09-1982</t>
+          <t>13-09-1992</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>PAMELACURENO@HOTMAIL.COM</t>
+          <t>CHDH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 16:29:24</t>
+          <t>20-02-2026 11:31:05</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>09-03-2026 18:45:23</t>
+          <t>11-03-2026 07:15:33</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>09-03-2026 18:44:38</t>
-        </is>
-      </c>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2428,7 +2408,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26160523023960003240</t>
+          <t>26200523082080003204</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2436,32 +2416,36 @@
           <t>PASE 2 DÍAS GRATIS WEB</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347678</t>
+          <t>347472</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>89843</t>
+          <t>89637</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2471,17 +2455,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ISABELLA</t>
+          <t xml:space="preserve">FERNANDA CECILIA </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CUREÑO</t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2491,35 +2475,47 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6862373744</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>6863944624</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>DEL AMATE 3138</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>21-12-2010</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>16-06-2002</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>A1176937@UABC.EDU.MX</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 16:31:22</t>
+          <t>02-03-2026 09:49:48</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2529,21 +2525,29 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>09-03-2026 18:39:03</t>
+          <t>02-03-2026 09:57:22</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>02-03-2026 09:56:34</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2551,14 +2555,10 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26160523023380003239</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26160522786810002837</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2567,24 +2567,24 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347502</t>
+          <t>347675</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89667</t>
+          <t>89840</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2594,17 +2594,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>PAMELA ROCIO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TAMAYO</t>
+          <t>CUREÑO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>BURGOS</t>
+          <t>VELAZQUEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2614,67 +2614,67 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6862727241</t>
+          <t>6862166891</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ISLA DEL PACIFICO 2158</t>
+          <t>INDEPENDENCIA 1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>04-07-1986</t>
+          <t>21-09-1982</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CHAPOGABO@GMAIL.COM</t>
+          <t>PAMELACURENO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-03-2026 11:16:32</t>
+          <t>02-03-2026 16:29:24</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-03-2026 11:20:43</t>
+          <t>09-03-2026 18:45:23</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>02-03-2026 11:19:51</t>
+          <t>09-03-2026 18:44:38</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2694,19 +2694,23 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26160522788980002846</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
+          <t>26160523023960003240</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2718,12 +2722,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347765</t>
+          <t>347865</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>89930</t>
+          <t>90030</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2733,17 +2737,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EMILIANO</t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MURILLO</t>
+          <t>CACHO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2753,67 +2757,79 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6862234584</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>6862677979</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>INDEOENDENCIA 1</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>27-04-2002</t>
+          <t>27-06-2004</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>EMILIANOMURILLO0204@GMAIL.COM</t>
+          <t>CACHOVALERIA09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 17:48:06</t>
+          <t>02-03-2026 19:22:12</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>04-03-2026 17:54:58</t>
+          <t>02-03-2026 19:26:57</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:25:56</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2821,22 +2837,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26160522892240003037</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Recepcion Independencia Mexicali</t>
-        </is>
-      </c>
+          <t>26160522816630002904</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2853,12 +2861,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347865</t>
+          <t>347932</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90030</t>
+          <t>90097</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2868,17 +2876,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t>LOURDES MAGADALENA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CACHO</t>
+          <t xml:space="preserve">ORDUÑO </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">GALVEZ </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2888,12 +2896,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6862677979</t>
+          <t>6869454842</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>INDEOENDENCIA 1</t>
+          <t>ALTALOMA 2514</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2903,17 +2911,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>27-06-2004</t>
+          <t>22-07-1972</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CACHOVALERIA09@GMAIL.COM</t>
+          <t>LOURDES.ORDUNO@NOTARIA10MEXICALI.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-03-2026 19:22:12</t>
+          <t>03-03-2026 05:12:21</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2938,17 +2946,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-03-2026 19:26:57</t>
+          <t>09-03-2026 05:11:29</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>02-03-2026 19:25:56</t>
+          <t>09-03-2026 05:10:24</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2968,11 +2976,19 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26160522816630002904</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>26160522989500003180</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>auxiliar independencia mexicali</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>549</t>
@@ -2980,7 +2996,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2992,12 +3008,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347472</t>
+          <t>347966</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>89637</t>
+          <t>90131</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3007,17 +3023,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDA CECILIA </t>
+          <t xml:space="preserve">ANDRES </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t xml:space="preserve">ORTIZ </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t xml:space="preserve">FLORES </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3027,47 +3043,43 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6863944624</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>DEL AMATE 3138</t>
-        </is>
-      </c>
+          <t>6531210593</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>16-06-2002</t>
+          <t>30-11-1992</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>A1176937@UABC.EDU.MX</t>
+          <t>AMDRES_Z23@LIVE.COM.MX</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 09:49:48</t>
+          <t>03-03-2026 08:29:59</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -3077,29 +3089,21 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-03-2026 09:57:22</t>
+          <t>05-03-2026 08:26:00</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>02-03-2026 09:56:34</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3107,11 +3111,19 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26160522786810002837</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+          <t>26160522910710003079</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>MARIO ALBERTO GARCIA CERON</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>549</t>
@@ -3119,7 +3131,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3131,12 +3143,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>348072</t>
+          <t>347502</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90237</t>
+          <t>89667</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3146,17 +3158,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>JOEL</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>TAMAYO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>BURGOS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3166,10 +3178,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6863309454</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>6862727241</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ISLA DEL PACIFICO 2158</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3177,32 +3193,32 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>01-04-1974</t>
+          <t>04-07-1986</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>JOELF3086@GMAIL.COM</t>
+          <t>CHAPOGABO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>03-03-2026 14:59:50</t>
+          <t>02-03-2026 11:16:32</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3212,21 +3228,29 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>03-03-2026 15:01:24</t>
+          <t>02-03-2026 11:20:43</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>02-03-2026 11:19:51</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3234,7 +3258,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26160522842820002952</t>
+          <t>26160522788980002846</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3246,7 +3270,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3258,12 +3282,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>347932</t>
+          <t>347765</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90097</t>
+          <t>89930</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3273,17 +3297,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LOURDES MAGADALENA</t>
+          <t>EMILIANO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORDUÑO </t>
+          <t>MURILLO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALVEZ </t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3293,79 +3317,67 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6869454842</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>ALTALOMA 2514</t>
-        </is>
-      </c>
+          <t>6862234584</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>22-07-1972</t>
+          <t>27-04-2002</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>LOURDES.ORDUNO@NOTARIA10MEXICALI.COM</t>
+          <t>EMILIANOMURILLO0204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>03-03-2026 05:12:21</t>
+          <t>02-03-2026 17:48:06</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>09-03-2026 05:11:29</t>
+          <t>04-03-2026 17:54:58</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>09-03-2026 05:10:24</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3373,7 +3385,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26160522989500003180</t>
+          <t>26160522892240003037</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3383,17 +3395,17 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>auxiliar independencia mexicali</t>
+          <t>Recepcion Independencia Mexicali</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Julio Alonso Lerma Sanchez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3405,12 +3417,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>347966</t>
+          <t>348295</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90131</t>
+          <t>90460</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3420,17 +3432,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDRES </t>
+          <t>AYEAN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORTIZ </t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t>GALAVIZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3440,7 +3452,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6531210593</t>
+          <t>3333878465</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3451,17 +3463,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>30-11-1992</t>
+          <t>13-06-2012</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>AMDRES_Z23@LIVE.COM.MX</t>
+          <t>NAOMI_MGALAVIZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>03-03-2026 08:29:59</t>
+          <t>03-03-2026 21:23:20</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3486,18 +3498,18 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>05-03-2026 08:26:00</t>
+          <t>03-03-2026 22:05:53</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V23" t="inlineStr"/>
@@ -3508,19 +3520,11 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26160522910710003079</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>MARIO ALBERTO GARCIA CERON</t>
-        </is>
-      </c>
+          <t>26160522862540003003</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
           <t>549</t>
@@ -3528,7 +3532,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3540,12 +3544,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>348295</t>
+          <t>348571</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90460</t>
+          <t>90736</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3555,17 +3559,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AYEAN</t>
+          <t>RAMON</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GALAVIZ</t>
+          <t>DAFOLLA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3575,7 +3579,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3333878465</t>
+          <t>6862585270</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3586,22 +3590,22 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>13-06-2012</t>
+          <t>31-08-2001</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>NAOMI_MGALAVIZ@HOTMAIL.COM</t>
+          <t>RAMON.DAFOLLA3108@GMAIL.OCM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>03-03-2026 21:23:20</t>
+          <t>04-03-2026 18:35:05</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -3611,28 +3615,28 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>03-03-2026 22:05:53</t>
+          <t>04-03-2026 18:36:18</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V24" t="inlineStr"/>
@@ -3643,19 +3647,19 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26160522862540003003</t>
+          <t>26160522894860003045</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3667,12 +3671,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>348293</t>
+          <t>347456</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90458</t>
+          <t>89621</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3682,17 +3686,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AMAYA NAOMI</t>
+          <t>NAIDELIN ISABELA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t xml:space="preserve">CURIEL </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>GALAVIZ</t>
+          <t xml:space="preserve">GUERRERO </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3702,7 +3706,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3318420233</t>
+          <t>6865268187</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3713,17 +3717,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>04-01-2010</t>
+          <t>02-11-2008</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>NAOMI_MGALAVIZ@ICLOUD.COM</t>
+          <t>ISABELLANYN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>03-03-2026 21:18:34</t>
+          <t>02-03-2026 08:50:02</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3748,18 +3752,18 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>03-03-2026 22:02:31</t>
+          <t>04-03-2026 09:15:26</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V25" t="inlineStr"/>
@@ -3770,11 +3774,19 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26160522862510003002</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+          <t>26160522877070003016</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>MARIO ALBERTO GARCIA CERON</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>549</t>
@@ -3782,7 +3794,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Julio Alonso Lerma Sanchez</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3794,12 +3806,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>348679</t>
+          <t>347678</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90844</t>
+          <t>89843</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3809,17 +3821,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARICELA </t>
+          <t>ISABELLA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BADILLA</t>
+          <t>CUREÑO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3829,33 +3841,25 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6862555010</t>
+          <t>6862373744</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>19-10-1969</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>MARIANELA691020@HOTMAIL.COM</t>
-        </is>
-      </c>
+          <t>21-12-2010</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>05-03-2026 12:13:29</t>
+          <t>02-03-2026 16:31:22</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>anualidad LE 300</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3865,22 +3869,22 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>ANUALIDAD + MES REGALO $5,999</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>461.46</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>05-03-2026 12:15:24</t>
+          <t>09-03-2026 18:39:03</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>04-04-2027 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3897,36 +3901,40 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26160522914430003085</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
+          <t>26160523023380003239</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>348571</t>
+          <t>349018</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>90736</t>
+          <t>91183</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3936,17 +3944,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>RAMON</t>
+          <t>ELODIA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DAFOLLA</t>
+          <t>COLLADO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3956,28 +3964,32 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6862585270</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>6864604705</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA 1</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>31-08-2001</t>
+          <t>03-07-1976</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>RAMON.DAFOLLA3108@GMAIL.OCM</t>
+          <t>APAOLAVZLA20@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>04-03-2026 18:35:05</t>
+          <t>06-03-2026 18:09:34</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3987,36 +3999,44 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>04-03-2026 18:36:18</t>
+          <t>09-03-2026 14:53:05</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:52:11</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4024,19 +4044,23 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26160522894860003045</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
+          <t>26160523010040003207</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4048,12 +4072,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>348815</t>
+          <t>349290</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>90980</t>
+          <t>91455</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4063,12 +4087,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>XIMENA</t>
+          <t>GRISELDA ANGELICA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SOZA</t>
+          <t>MARISCAL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4083,10 +4107,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6381095092</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>6861220141</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>VILLA DEL PASEO</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4094,32 +4122,32 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>09-07-2003</t>
+          <t>05-03-1988</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>XIMESOZA03@OUTLOOK.COM</t>
+          <t>GRYZKK@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>05-03-2026 20:33:06</t>
+          <t>09-03-2026 06:04:45</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -4129,21 +4157,29 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>05-03-2026 20:36:29</t>
+          <t>09-03-2026 06:08:12</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>09-03-2026 06:07:33</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4151,7 +4187,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26160522931570003119</t>
+          <t>26160522990700003183</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
@@ -4163,7 +4199,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4175,12 +4211,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>348848</t>
+          <t>348293</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>91013</t>
+          <t>90458</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4190,17 +4226,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GUSTAVO ALBERTO</t>
+          <t>AMAYA NAOMI</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>GALAVIZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4210,28 +4246,28 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6866077308</t>
+          <t>3318420233</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>15-12-1985</t>
+          <t>04-01-2010</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>LIC_GUSTAVOTORRES@HOTMAIL.COM</t>
+          <t>NAOMI_MGALAVIZ@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>06-03-2026 08:06:57</t>
+          <t>03-03-2026 21:18:34</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4256,12 +4292,12 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>12-03-2026 08:11:38</t>
+          <t>03-03-2026 22:02:31</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -4278,19 +4314,11 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26160523117280003449</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>ANDREA PATRICIA ACUÑA PERALTA</t>
-        </is>
-      </c>
+          <t>26160522862510003002</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
           <t>549</t>
@@ -4298,7 +4326,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4437,12 +4465,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>349018</t>
+          <t>348815</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>91183</t>
+          <t>90980</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4452,19 +4480,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ELODIA</t>
+          <t>XIMENA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>SOZA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>GARCIA</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>COLLADO</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>52</t>
@@ -4472,14 +4500,10 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6864604705</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA 1</t>
-        </is>
-      </c>
+          <t>6381095092</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4487,64 +4511,56 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>03-07-1976</t>
+          <t>09-07-2003</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>APAOLAVZLA20@GMAIL.COM</t>
+          <t>XIMESOZA03@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>06-03-2026 18:09:34</t>
+          <t>05-03-2026 20:33:06</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>09-03-2026 14:53:05</t>
+          <t>05-03-2026 20:36:29</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>09-03-2026 14:52:11</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4552,18 +4568,14 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26160523010040003207</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26160522931570003119</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4580,12 +4592,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>349290</t>
+          <t>348816</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>91455</t>
+          <t>90981</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4595,17 +4607,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GRISELDA ANGELICA</t>
+          <t>BLANCA PAOLA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MARISCAL</t>
+          <t>ELIZONDO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>LIZARRAGA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4615,14 +4627,10 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6861220141</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>VILLA DEL PASEO</t>
-        </is>
-      </c>
+          <t>6383865795</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4630,32 +4638,32 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>05-03-1988</t>
+          <t>17-09-2003</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>GRYZKK@GMAIL.COM</t>
+          <t>ELIZONDOPAOLA76@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>09-03-2026 06:04:45</t>
+          <t>05-03-2026 20:37:57</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -4665,29 +4673,21 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>09-03-2026 06:08:12</t>
+          <t>05-03-2026 20:39:46</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>09-03-2026 06:07:33</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26160522990700003183</t>
+          <t>26160522931690003120</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -4719,12 +4719,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>349465</t>
+          <t>349868</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>91630</t>
+          <t>92033</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4734,17 +4734,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>JUAN ROBERTO</t>
+          <t>ERICK</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SAMANO</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>LIRA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4754,14 +4754,10 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6863231447</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA 14</t>
-        </is>
-      </c>
+          <t>7226145244</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4769,17 +4765,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>12-08-1995</t>
+          <t>08-05-2007</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>SAMANO.JROBERTO@GMAIL.COM</t>
+          <t>GOMEZLIRAEK@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>09-03-2026 14:57:52</t>
+          <t>10-03-2026 15:11:36</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4789,44 +4785,36 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>SALVATIERRA $399</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>09-03-2026 15:01:57</t>
+          <t>10-03-2026 15:13:21</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>09-03-2026 15:01:09</t>
-        </is>
-      </c>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4834,14 +4822,14 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26160523010370003208</t>
+          <t>26160523054450003299</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4858,12 +4846,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>348816</t>
+          <t>349985</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>90981</t>
+          <t>92150</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4873,17 +4861,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BLANCA PAOLA</t>
+          <t>JOSE SALVADOR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ELIZONDO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>LIZARRAGA</t>
+          <t>ALMARAZ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4893,28 +4881,28 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6383865795</t>
+          <t>6863079015</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>17-09-2003</t>
+          <t>26-05-2012</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ELIZONDOPAOLA76@GMAIL.COM</t>
+          <t>JOSE26RAMIREZ05@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>05-03-2026 20:37:57</t>
+          <t>10-03-2026 19:18:34</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4939,18 +4927,18 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>05-03-2026 20:39:46</t>
+          <t>14-03-2026 12:43:19</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>13-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V34" t="inlineStr"/>
@@ -4961,11 +4949,19 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26160522931690003120</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
+          <t>26160523183450003559</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>549</t>
@@ -4985,12 +4981,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>349397</t>
+          <t>349560</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>91562</t>
+          <t>91725</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5000,17 +4996,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADRIAN ARTURO </t>
+          <t>ARLIN VICTORIA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">BONILLA </t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESPINOZA </t>
+          <t>X</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5020,28 +5016,28 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6862131889</t>
+          <t>6862921253</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>22-06-1997</t>
+          <t>06-05-1982</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>ADRIANBONILLAXOCHI@GMAIL.COM</t>
+          <t>ARLINIBARRA52@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>09-03-2026 12:27:28</t>
+          <t>09-03-2026 17:42:48</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5066,7 +5062,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>09-03-2026 12:29:28</t>
+          <t>09-03-2026 17:44:34</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -5077,7 +5073,7 @@
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V35" t="inlineStr"/>
@@ -5088,7 +5084,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26160523005930003199</t>
+          <t>26160523018890003225</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5100,7 +5096,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5112,12 +5108,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>349560</t>
+          <t>350563</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>91725</t>
+          <t>92727</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5127,17 +5123,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ARLIN VICTORIA</t>
+          <t>MOISES</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t xml:space="preserve">MENDOZA </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5147,33 +5143,33 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6862921253</t>
+          <t>6671315555</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>06-05-1982</t>
+          <t>24-08-2003</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ARLINIBARRA52@GMAIL.COM</t>
+          <t>M0SES.2203@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>09-03-2026 17:42:48</t>
+          <t>13-03-2026 12:08:48</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -5183,28 +5179,28 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>09-03-2026 17:44:34</t>
+          <t>13-03-2026 12:10:24</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>12-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V36" t="inlineStr"/>
@@ -5215,19 +5211,19 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26160523018890003225</t>
+          <t>26160523151250003522</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5239,12 +5235,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>349863</t>
+          <t>348848</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>92028</t>
+          <t>91013</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5254,17 +5250,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MIA PAULETT</t>
+          <t>GUSTAVO ALBERTO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>COLOSIO</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5274,28 +5270,28 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6861946974</t>
+          <t>6866077308</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>25-09-2009</t>
+          <t>15-12-1985</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>MIA.COLOSIO@GMAIL.COM</t>
+          <t>LIC_GUSTAVOTORRES@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>10-03-2026 14:54:21</t>
+          <t>06-03-2026 08:06:57</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5320,12 +5316,12 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>10-03-2026 14:56:18</t>
+          <t>12-03-2026 08:11:38</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>11-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -5342,11 +5338,19 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26160523053950003298</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
+          <t>26160523117280003449</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>ANDREA PATRICIA ACUÑA PERALTA</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>549</t>
@@ -5354,7 +5358,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5366,12 +5370,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>349437</t>
+          <t>350561</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>91602</t>
+          <t>92725</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5381,17 +5385,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SANDA LUZ</t>
+          <t xml:space="preserve">MOISES </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AYON</t>
+          <t xml:space="preserve">MENDOZA </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TOLOSA</t>
+          <t xml:space="preserve">MASCAREÑO </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5401,28 +5405,28 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6863530093</t>
+          <t>6677480860</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>19-11-1993</t>
+          <t>01-03-1985</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>SANDRALUZAYON@OUTLOOK.COM</t>
+          <t>FIMSAVENTAS01@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>09-03-2026 14:11:00</t>
+          <t>13-03-2026 11:58:24</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5447,18 +5451,18 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>09-03-2026 14:12:13</t>
+          <t>13-03-2026 12:00:40</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>12-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V38" t="inlineStr"/>
@@ -5469,7 +5473,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26160523008520003205</t>
+          <t>26160523151040003520</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -5481,7 +5485,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5493,12 +5497,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>350561</t>
+          <t>349722</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>92725</t>
+          <t>91887</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5508,17 +5512,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOISES </t>
+          <t>RUBI</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">MENDOZA </t>
+          <t>CEJA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">MASCAREÑO </t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5528,67 +5532,79 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6677480860</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>7831110926</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA 1</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>01-03-1985</t>
+          <t>25-01-1991</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>FIMSAVENTAS01@GMAIL.COM</t>
+          <t>BYBIROOMAN25@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>13-03-2026 11:58:24</t>
+          <t>09-03-2026 20:41:55</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>13-03-2026 12:00:40</t>
+          <t>09-03-2026 20:50:36</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>12-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>09-03-2026 20:49:21</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5596,19 +5612,19 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26160523151040003520</t>
+          <t>26160523032570003266</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5620,12 +5636,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>349722</t>
+          <t>349957</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>91887</t>
+          <t>92122</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5635,17 +5651,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>RUBI</t>
+          <t>LUISELLA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CEJA</t>
+          <t>BARRAGAN</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5655,14 +5671,10 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>7831110926</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>INDEPENDENCIA 1</t>
-        </is>
-      </c>
+          <t>6862134760</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5670,64 +5682,56 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>25-01-1991</t>
+          <t>11-11-2011</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>BYBIROOMAN25@GMAIL.COM</t>
+          <t>LBARRAGANE@EDU.MX</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>09-03-2026 20:41:55</t>
+          <t>10-03-2026 18:36:43</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>09-03-2026 20:50:36</t>
+          <t>16-03-2026 19:16:06</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>09-03-2026 20:49:21</t>
-        </is>
-      </c>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5735,19 +5739,27 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26160523032570003266</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
+          <t>26160523232600003629</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5759,12 +5771,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>349957</t>
+          <t>348072</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>92122</t>
+          <t>90237</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5774,17 +5786,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LUISELLA</t>
+          <t>JOEL</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>BARRAGAN</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5794,28 +5806,28 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6862134760</t>
+          <t>6863309454</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>11-11-2011</t>
+          <t>01-04-1974</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>LBARRAGANE@EDU.MX</t>
+          <t>JOELF3086@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>10-03-2026 18:36:43</t>
+          <t>03-03-2026 14:59:50</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5840,12 +5852,12 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>16-03-2026 19:16:06</t>
+          <t>03-03-2026 15:01:24</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -5862,19 +5874,11 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26160523232600003629</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26160522842820002952</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
           <t>549</t>
@@ -5894,12 +5898,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>349868</t>
+          <t>349437</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>92033</t>
+          <t>91602</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5909,17 +5913,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ERICK</t>
+          <t>SANDA LUZ</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>AYON</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>LIRA</t>
+          <t>TOLOSA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5929,33 +5933,33 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>7226145244</t>
+          <t>6863530093</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>08-05-2007</t>
+          <t>19-11-1993</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>GOMEZLIRAEK@GMAIL.COM</t>
+          <t>SANDRALUZAYON@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>10-03-2026 15:11:36</t>
+          <t>09-03-2026 14:11:00</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -5965,28 +5969,28 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>SALVATIERRA $399</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>10-03-2026 15:13:21</t>
+          <t>09-03-2026 14:12:13</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V42" t="inlineStr"/>
@@ -5997,19 +6001,19 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26160523054450003299</t>
+          <t>26160523008520003205</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6021,12 +6025,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>349985</t>
+          <t>351203</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>92150</t>
+          <t>93367</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6036,17 +6040,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>JOSE SALVADOR</t>
+          <t>WALTER</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>DURAZO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ALMARAZ</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6056,10 +6060,14 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6863079015</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>6861971149</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA 1</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6067,32 +6075,32 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>26-05-2012</t>
+          <t>14-01-1989</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>JOSE26RAMIREZ05@GMAIL.COM</t>
+          <t>WALDURAZO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>10-03-2026 19:18:34</t>
+          <t>16-03-2026 14:13:40</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -6102,21 +6110,29 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>14-03-2026 12:43:19</t>
+          <t>16-03-2026 14:18:29</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>13-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr"/>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>16-03-2026 14:17:46</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6124,19 +6140,11 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26160523183450003559</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>26160523223290003600</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
           <t>549</t>
@@ -6144,7 +6152,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6156,12 +6164,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>349869</t>
+          <t>350304</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>92034</t>
+          <t>92468</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6171,17 +6179,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>RENATO</t>
+          <t xml:space="preserve">SANDRA ELIZABETH </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">BARRIENTOS </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TAFOLLA</t>
+          <t>TELLEZ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6191,67 +6199,79 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6862146814</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>6862164334</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>HACIENDA CIENEGA 3347</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>04-07-2008</t>
+          <t>24-09-1987</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>RENATOGARCIATAFOLLA@GMAIL.COM</t>
+          <t>SANDRA.BARRIENTOS@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>10-03-2026 15:14:54</t>
+          <t>12-03-2026 12:18:00</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>SALVATIERRA $399</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>10-03-2026 15:16:57</t>
+          <t>12-03-2026 12:27:43</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr"/>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>12-03-2026 12:23:49</t>
+        </is>
+      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6259,19 +6279,19 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26160523054590003300</t>
+          <t>26160523121310003453</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6283,12 +6303,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>350304</t>
+          <t>349869</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>92468</t>
+          <t>92034</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6298,17 +6318,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANDRA ELIZABETH </t>
+          <t>RENATO</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARRIENTOS </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TELLEZ</t>
+          <t>TAFOLLA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6318,79 +6338,67 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6862164334</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>HACIENDA CIENEGA 3347</t>
-        </is>
-      </c>
+          <t>6862146814</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>24-09-1987</t>
+          <t>04-07-2008</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>SANDRA.BARRIENTOS@UABC.EDU.MX</t>
+          <t>RENATOGARCIATAFOLLA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>12-03-2026 12:18:00</t>
+          <t>10-03-2026 15:14:54</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>SALVATIERRA $399</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>12-03-2026 12:27:43</t>
+          <t>10-03-2026 15:16:57</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>12-03-2026 12:23:49</t>
-        </is>
-      </c>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6398,19 +6406,19 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26160523121310003453</t>
+          <t>26160523054590003300</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Ricardo Alexis Alvarez Camarena</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6422,12 +6430,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>350562</t>
+          <t>349397</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>92726</t>
+          <t>91562</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6437,17 +6445,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KEVIN ADAN</t>
+          <t xml:space="preserve">ADRIAN ARTURO </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">MENDOZA </t>
+          <t xml:space="preserve">BONILLA </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t xml:space="preserve">ESPINOZA </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6457,7 +6465,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6677858027</t>
+          <t>6862131889</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6468,22 +6476,22 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>18-10-2006</t>
+          <t>22-06-1997</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>FIMSAVENTAS02@GMAIL.COM</t>
+          <t>ADRIANBONILLAXOCHI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>13-03-2026 12:04:23</t>
+          <t>09-03-2026 12:27:28</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -6493,22 +6501,22 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>13-03-2026 12:06:47</t>
+          <t>09-03-2026 12:29:28</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>12-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -6525,14 +6533,14 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26160523151170003521</t>
+          <t>26160523005930003199</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -6549,12 +6557,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>350794</t>
+          <t>351348</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>92958</t>
+          <t>93512</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6564,17 +6572,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LOBNY GUADALUPE</t>
+          <t>JOSE ARMANDO</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>FUENTES</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>ALCARAZ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6584,14 +6592,10 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6633222685</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>CENTRO</t>
-        </is>
-      </c>
+          <t>6863223039</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6599,32 +6603,32 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
+          <t>20-03-2010</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>ANDERSONMUNOSLOB@GMAIL.COM</t>
+          <t>FUENTES.ARMANDO2010@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>14-03-2026 12:02:28</t>
+          <t>16-03-2026 19:39:13</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -6634,29 +6638,21 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>17-03-2026 17:00:33</t>
+          <t>16-03-2026 19:41:02</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>17-03-2026 16:58:49</t>
-        </is>
-      </c>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6664,7 +6660,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26110523260150005714</t>
+          <t>26160523233600003631</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -6676,7 +6672,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -6688,12 +6684,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>350563</t>
+          <t>350562</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>92727</t>
+          <t>92726</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6703,7 +6699,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>MOISES</t>
+          <t>KEVIN ADAN</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6713,7 +6709,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6723,7 +6719,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6671315555</t>
+          <t>6677858027</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6734,17 +6730,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>24-08-2003</t>
+          <t>18-10-2006</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>M0SES.2203@OUTLOOK.COM</t>
+          <t>FIMSAVENTAS02@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>13-03-2026 12:08:48</t>
+          <t>13-03-2026 12:04:23</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6769,7 +6765,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>13-03-2026 12:10:24</t>
+          <t>13-03-2026 12:06:47</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -6791,7 +6787,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26160523151250003522</t>
+          <t>26160523151170003521</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
@@ -6815,12 +6811,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>351203</t>
+          <t>350794</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>93367</t>
+          <t>92958</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6830,17 +6826,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>WALTER</t>
+          <t>LOBNY GUADALUPE</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>DURAZO</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6850,12 +6846,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6861971149</t>
+          <t>6633222685</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA 1</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6865,17 +6861,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>14-01-1989</t>
+          <t>01-01-2000</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>WALDURAZO@GMAIL.COM</t>
+          <t>ANDERSONMUNOSLOB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>16-03-2026 14:13:40</t>
+          <t>14-03-2026 12:02:28</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -6900,17 +6896,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>16-03-2026 14:18:29</t>
+          <t>17-03-2026 17:00:33</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
+          <t>16-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>16-03-2026 14:17:46</t>
+          <t>17-03-2026 16:58:49</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -6930,7 +6926,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26160523223290003600</t>
+          <t>26110523260150005714</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
@@ -6942,7 +6938,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>Viridiana Ramirez</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -6954,12 +6950,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>351234</t>
+          <t>352167</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>93398</t>
+          <t>94331</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6969,17 +6965,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ALEJANDRA</t>
+          <t>JOSE MANUEL</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t xml:space="preserve">ORTEGA </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ZUÑIGA</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -6989,32 +6985,32 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6861786900</t>
+          <t>6864055189</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>MONTORGUEIL 498</t>
+          <t>INDEPENDENCIA 1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>03-09-1995</t>
+          <t>05-03-1992</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>ALEJANDRACASTRO@HOTMAIL.COM</t>
+          <t>JOSE.ORTEGA92@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>16-03-2026 16:07:23</t>
+          <t>19-03-2026 18:05:34</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7039,17 +7035,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>18-03-2026 17:27:32</t>
+          <t>23-03-2026 17:30:01</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
+          <t>22-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>18-03-2026 17:27:01</t>
+          <t>23-03-2026 17:29:22</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7069,19 +7065,15 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26160523299170003761</t>
+          <t>26160523435620003947</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
           <t>649</t>
@@ -7089,24 +7081,24 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>350797</t>
+          <t>348679</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>92961</t>
+          <t>90844</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7116,17 +7108,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>JORGE ANTONIO</t>
+          <t xml:space="preserve">MARICELA </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>LORIA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>BADILLA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7136,14 +7128,10 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>9982448340</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CENTRO </t>
-        </is>
-      </c>
+          <t>6862555010</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7151,64 +7139,56 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
+          <t>19-10-1969</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>JORGERONALDO2401@GMAIL.COM</t>
+          <t>MARIANELA691020@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>14-03-2026 12:06:17</t>
+          <t>05-03-2026 12:13:29</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>anualidad LE 300</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>ANUALIDAD + MES REGALO $5,999</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>461.46</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>17-03-2026 17:04:33</t>
+          <t>05-03-2026 12:15:24</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>17-03-2026 17:03:42</t>
-        </is>
-      </c>
+          <t>04-04-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7216,19 +7196,19 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26110523260440005716</t>
+          <t>26160522914430003085</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Viridiana Ramirez</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -7240,12 +7220,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>352146</t>
+          <t>352680</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>94310</t>
+          <t>94844</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7255,17 +7235,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t xml:space="preserve">BIANCA </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PEÑA</t>
+          <t xml:space="preserve">ROJAS </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t xml:space="preserve">AMEZQUITA </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7275,35 +7255,31 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6863477343</t>
+          <t>6861059335</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>30-04-1996</t>
+          <t>19-06-2010</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>DIEGO_CMACHO15@HOTMAIL.COM</t>
+          <t>BIANCAROJAS1983@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>19-03-2026 17:10:16</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>23-03-2026 09:15:57</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -7311,28 +7287,28 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>19-03-2026 17:14:55</t>
+          <t>23-03-2026 10:05:57</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>18-04-2026 23:59:59</t>
+          <t>23-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V52" t="inlineStr"/>
@@ -7343,36 +7319,44 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26160523334270003831</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
+          <t>26160523421300003933</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>ANDREA PATRICIA ACUÑA PERALTA</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Sergio  Cordova Hernandez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>351348</t>
+          <t>351993</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>93512</t>
+          <t>94157</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7382,17 +7366,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>JOSE ARMANDO</t>
+          <t>MARIO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FUENTES</t>
+          <t>MALACON</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ALCARAZ</t>
+          <t>PSIHAS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7402,7 +7386,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6863223039</t>
+          <t>6861194035</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7413,22 +7397,22 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>20-03-2010</t>
+          <t>18-12-1994</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>FUENTES.ARMANDO2010@GMAIL.COM</t>
+          <t>RECICLADORA.PMP@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>16-03-2026 19:39:13</t>
+          <t>18-03-2026 20:10:23</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -7438,22 +7422,22 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>16-03-2026 19:41:02</t>
+          <t>23-03-2026 08:35:41</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
+          <t>22-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -7470,36 +7454,36 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26160523233600003631</t>
+          <t>26160523418730003922</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Kevin Daniel Gonzalez Vasquez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>351448</t>
+          <t>352146</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>93612</t>
+          <t>94310</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7509,17 +7493,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>IVONE</t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>VIRGEN</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7529,28 +7513,28 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6862304998</t>
+          <t>6863477343</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>15-04-1988</t>
+          <t>30-04-1996</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>TIVONEGV@GMAIL.COM</t>
+          <t>DIEGO_CMACHO15@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>17-03-2026 10:02:45</t>
+          <t>19-03-2026 17:10:16</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7565,28 +7549,28 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>19-03-2026 10:03:04</t>
+          <t>19-03-2026 17:14:55</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>18-06-2026 23:59:59</t>
+          <t>18-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V54" t="inlineStr"/>
@@ -7597,169 +7581,2575 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26160523324670003818</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>ANDREA PATRICIA ACUÑA PERALTA</t>
-        </is>
-      </c>
+          <t>26160523334270003831</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Sergio  Cordova Hernandez</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>352682</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>94846</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUGEY ALEJANDRA </t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>BELTRAN</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROJAS </t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>6863669806</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>PUENTE LATONE 857</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>17-11-1998</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>ALEJANDRABELTRA04@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>23-03-2026 09:19:00</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>23-03-2026 10:05:57</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>23-03-2026 10:05:17</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>26160523421300003933</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>ANDREA PATRICIA ACUÑA PERALTA</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>353257</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>95421</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>FRANCISCO JOSE</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>CORONADO</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>LUGO</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>6861944527</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA 12</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>07-10-1987</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>FRANCISCO.CORONADO1987@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>24-03-2026 21:45:04</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>24-03-2026 21:50:06</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>24-03-2026 21:48:43</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>26160523487290004065</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>Sergio  Cordova Hernandez</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>352998</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>95162</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CARLOS RENE</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>LIZARTE</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>6862451620</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>14-12-1994</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>SANCHEZ.CARLOS28@EDU.UABC.MX</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>23-03-2026 20:58:42</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>23-03-2026 21:04:13</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>26160523449780003995</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>353243</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>95407</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>KARLA</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRILLO </t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASTRO </t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>6863866882</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>28-05-2010</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>KARLACARRILLOCASTRO0@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>24-03-2026 20:17:31</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>24-03-2026 20:20:13</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>26160523485020004056</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>350797</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>92961</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>JORGE ANTONIO</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>LORIA</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>9982448340</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CENTRO </t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>01-01-2000</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>JORGERONALDO2401@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>14-03-2026 12:06:17</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:04:33</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:03:42</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>26110523260440005716</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Viridiana Ramirez</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>353620</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>95784</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ANA ROSA</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RINCON</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>CARRILLO</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>6861254031</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>04-01-1996</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>ANNA.RC12@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>26-03-2026 18:24:41</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>26-03-2026 18:26:56</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>26160523543020004141</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>353788</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>95952</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>JOSE MANUEL</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>FERREIRA</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>6865734238</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>24-01-2004</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>JOSE.24.FERREIRA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>27-03-2026 17:24:57</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>27-03-2026 17:26:44</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>26-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>26160523569830004179</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>349465</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>91630</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>JUAN ROBERTO</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>SAMANO</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>CHAVEZ</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>6863231447</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA 14</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>12-08-1995</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>SAMANO.JROBERTO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:57:52</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>09-03-2026 15:01:57</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>09-03-2026 15:01:09</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>26160523010370003208</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>354366</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>96530</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DIEGO ALFONSO</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>6864222480</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>14-08-2010</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>DIEGOALFONSOMT@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>30-03-2026 18:24:33</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>30-03-2026 18:26:01</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>26160523642310004265</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>354126</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>96290</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SANDRA PATRICIA</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ACOSTA</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>6144441486</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>RIO CONCHOS 241</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>09-12-1993</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>SPPA.009@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>30-03-2026 10:08:47</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>30-03-2026 18:07:03</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>30-03-2026 18:06:31</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>26200523640770004136</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>349863</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>92028</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>MIA PAULETT</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>COLOSIO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>6861946974</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>25-09-2009</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>MIA.COLOSIO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:54:21</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:56:18</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>26160523053950003298</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>351448</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>93612</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>IVONE</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>VIRGEN</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>6862304998</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>15-04-1988</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>TIVONEGV@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>17-03-2026 10:02:45</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>19-03-2026 10:03:04</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>18-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>26160523324670003818</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>ANDREA PATRICIA ACUÑA PERALTA</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>351234</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>93398</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>CASTRO</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ZUÑIGA</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>6861786900</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>MONTORGUEIL 498</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>03-09-1995</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>ALEJANDRACASTRO@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>16-03-2026 16:07:23</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>18-03-2026 17:27:32</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>18-03-2026 17:27:01</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>26160523299170003761</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>352025</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>94189</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>INDEPENDENCIA</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t xml:space="preserve">NOEMI JAZMIN </t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>SANCHEZ</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t xml:space="preserve">ORTIZ </t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>9092666191</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>PARALELO 28</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>14-01-2001</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>SANCHEZORTIZNOEMIJAZMIN@GMAIL.COM</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>19-03-2026 05:17:03</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>Inscripcion $150</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>Forzoso</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>549</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>19-03-2026 05:32:36</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>18-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>19-03-2026 05:19:18</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="V68" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>26160523313030003808</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr">
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr">
         <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>351577</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>93741</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>IVETTE</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>CAMPOS</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>ARMENTA</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>6863843514</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>12-02-2000</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>ARMENTAIVETTE@OCLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>17-03-2026 16:42:19</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>23-03-2026 17:36:12</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>26160523436080003948</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>GUILLERMO  PALMA Y MEZA OTERO</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>352799</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>94963</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SANTIAGO</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>AVEYTA</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>6863060011</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>12-10-2009</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>LOPEZAVEYTASANTIAGO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>23-03-2026 15:28:10</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>23-03-2026 15:29:51</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>26160523429840003940</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>Kevin Daniel Gonzalez Vasquez</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>354180</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>96344</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ILIANA RAFAELA</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>NUÑEZ</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>ANDUAGA</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>6532093060</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>CJN JALISCO 590</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>05-01-1968</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>ILIANARAFAELA6@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>30-03-2026 12:29:04</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>30-03-2026 17:41:28</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>30-03-2026 17:39:58</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>26150523638570003334</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>354116</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>96280</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ALFREDO LUCA</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRAMONTINI </t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAPIA </t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>6861500741</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>23-03-1998</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>LUCA.TRAMONTINI98@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>30-03-2026 09:37:07</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2 MESES X $ 1250</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>30-03-2026 09:38:35</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>29-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>26160523621830004224</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>354128</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>96292</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>KARLA</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>ACOSTA</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>6142534411</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>CHARLES MORNGAS 14306</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>18-08-1987</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>KARLAELISAPEREZACOSTA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>30-03-2026 10:13:39</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>30-03-2026 17:53:54</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>30-03-2026 17:52:21</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>26200523639750004135</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>
